--- a/precios.xlsx
+++ b/precios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linoS\Documents\precios entel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336BED87-F4CE-43A5-9A27-6E559317C0BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A24621-AE2B-4983-9B2E-B3BD0192DCBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1114,7 +1114,8 @@
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
     <col min="2" max="2" width="22.140625" customWidth="1"/>
-    <col min="3" max="3" width="26" style="5" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1124,11 +1125,11 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1138,11 +1139,11 @@
       <c r="B2" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="4">
+        <v>80000</v>
+      </c>
+      <c r="D2" s="6">
         <v>990</v>
-      </c>
-      <c r="D2" s="4">
-        <v>80000</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1152,11 +1153,11 @@
       <c r="B3" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="4">
+        <v>80000</v>
+      </c>
+      <c r="D3" s="6">
         <v>990</v>
-      </c>
-      <c r="D3" s="4">
-        <v>80000</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1166,11 +1167,11 @@
       <c r="B4" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="4">
+        <v>80000</v>
+      </c>
+      <c r="D4" s="6">
         <v>990</v>
-      </c>
-      <c r="D4" s="4">
-        <v>80000</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1180,11 +1181,11 @@
       <c r="B5" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="4">
+        <v>120000</v>
+      </c>
+      <c r="D5" s="6">
         <v>990</v>
-      </c>
-      <c r="D5" s="4">
-        <v>120000</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1194,11 +1195,11 @@
       <c r="B6" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="4">
+        <v>120000</v>
+      </c>
+      <c r="D6" s="6">
         <v>990</v>
-      </c>
-      <c r="D6" s="4">
-        <v>120000</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1208,11 +1209,11 @@
       <c r="B7" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="4">
+        <v>120000</v>
+      </c>
+      <c r="D7" s="6">
         <v>990</v>
-      </c>
-      <c r="D7" s="4">
-        <v>120000</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1222,11 +1223,11 @@
       <c r="B8" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D8" s="6">
         <v>19990</v>
-      </c>
-      <c r="D8" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1236,11 +1237,11 @@
       <c r="B9" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D9" s="6">
         <v>89990</v>
-      </c>
-      <c r="D9" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1250,11 +1251,11 @@
       <c r="B10" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D10" s="6">
         <v>89990</v>
-      </c>
-      <c r="D10" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1264,11 +1265,11 @@
       <c r="B11" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D11" s="6">
         <v>89990</v>
-      </c>
-      <c r="D11" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1278,11 +1279,11 @@
       <c r="B12" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="4">
+        <v>110000</v>
+      </c>
+      <c r="D12" s="6">
         <v>39990</v>
-      </c>
-      <c r="D12" s="4">
-        <v>110000</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1292,11 +1293,11 @@
       <c r="B13" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="4">
+        <v>110000</v>
+      </c>
+      <c r="D13" s="6">
         <v>39990</v>
-      </c>
-      <c r="D13" s="4">
-        <v>110000</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1306,11 +1307,11 @@
       <c r="B14" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D14" s="6">
         <v>39990</v>
-      </c>
-      <c r="D14" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1320,11 +1321,11 @@
       <c r="B15" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D15" s="6">
         <v>39990</v>
-      </c>
-      <c r="D15" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1334,11 +1335,11 @@
       <c r="B16" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D16" s="6">
         <v>39990</v>
-      </c>
-      <c r="D16" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1348,11 +1349,11 @@
       <c r="B17" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="4">
+        <v>100000</v>
+      </c>
+      <c r="D17" s="6">
         <v>79990</v>
-      </c>
-      <c r="D17" s="4">
-        <v>100000</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1362,11 +1363,11 @@
       <c r="B18" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="4">
+        <v>100000</v>
+      </c>
+      <c r="D18" s="6">
         <v>109990</v>
-      </c>
-      <c r="D18" s="4">
-        <v>100000</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1376,11 +1377,11 @@
       <c r="B19" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="4">
+        <v>100000</v>
+      </c>
+      <c r="D19" s="6">
         <v>109990</v>
-      </c>
-      <c r="D19" s="4">
-        <v>100000</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1390,11 +1391,11 @@
       <c r="B20" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="4">
+        <v>100000</v>
+      </c>
+      <c r="D20" s="6">
         <v>109990</v>
-      </c>
-      <c r="D20" s="4">
-        <v>100000</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1404,11 +1405,11 @@
       <c r="B21" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="4">
+        <v>130000</v>
+      </c>
+      <c r="D21" s="6">
         <v>119990</v>
-      </c>
-      <c r="D21" s="4">
-        <v>130000</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1418,11 +1419,11 @@
       <c r="B22" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="4">
+        <v>130000</v>
+      </c>
+      <c r="D22" s="6">
         <v>119990</v>
-      </c>
-      <c r="D22" s="4">
-        <v>130000</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1432,11 +1433,11 @@
       <c r="B23" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="4">
+        <v>130000</v>
+      </c>
+      <c r="D23" s="6">
         <v>119990</v>
-      </c>
-      <c r="D23" s="4">
-        <v>130000</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1446,11 +1447,11 @@
       <c r="B24" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="4">
+        <v>130000</v>
+      </c>
+      <c r="D24" s="6">
         <v>119990</v>
-      </c>
-      <c r="D24" s="4">
-        <v>130000</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1460,11 +1461,11 @@
       <c r="B25" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="4">
+        <v>120000</v>
+      </c>
+      <c r="D25" s="6">
         <v>209990</v>
-      </c>
-      <c r="D25" s="4">
-        <v>120000</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1474,11 +1475,11 @@
       <c r="B26" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="4">
+        <v>120000</v>
+      </c>
+      <c r="D26" s="6">
         <v>209990</v>
-      </c>
-      <c r="D26" s="4">
-        <v>120000</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1488,11 +1489,11 @@
       <c r="B27" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="4">
+        <v>130000</v>
+      </c>
+      <c r="D27" s="6">
         <v>199990</v>
-      </c>
-      <c r="D27" s="4">
-        <v>130000</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1502,11 +1503,11 @@
       <c r="B28" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="4">
+        <v>130000</v>
+      </c>
+      <c r="D28" s="6">
         <v>259990</v>
-      </c>
-      <c r="D28" s="4">
-        <v>130000</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1516,11 +1517,11 @@
       <c r="B29" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D29" s="6">
         <v>579990</v>
-      </c>
-      <c r="D29" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1530,11 +1531,11 @@
       <c r="B30" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D30" s="6">
         <v>579990</v>
-      </c>
-      <c r="D30" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1544,11 +1545,11 @@
       <c r="B31" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D31" s="6">
         <v>579990</v>
-      </c>
-      <c r="D31" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1558,11 +1559,11 @@
       <c r="B32" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D32" s="6">
         <v>379990</v>
-      </c>
-      <c r="D32" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1572,11 +1573,11 @@
       <c r="B33" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D33" s="6">
         <v>479990</v>
-      </c>
-      <c r="D33" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1586,11 +1587,11 @@
       <c r="B34" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D34" s="6">
         <v>529990</v>
-      </c>
-      <c r="D34" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1600,11 +1601,11 @@
       <c r="B35" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D35" s="6">
         <v>529990</v>
-      </c>
-      <c r="D35" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1614,11 +1615,11 @@
       <c r="B36" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D36" s="6">
         <v>529990</v>
-      </c>
-      <c r="D36" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1628,11 +1629,11 @@
       <c r="B37" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D37" s="6">
         <v>559990</v>
-      </c>
-      <c r="D37" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1642,11 +1643,11 @@
       <c r="B38" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D38" s="6">
         <v>559990</v>
-      </c>
-      <c r="D38" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1656,11 +1657,11 @@
       <c r="B39" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D39" s="6">
         <v>559990</v>
-      </c>
-      <c r="D39" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1670,11 +1671,11 @@
       <c r="B40" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D40" s="6">
         <v>729990</v>
-      </c>
-      <c r="D40" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1684,11 +1685,11 @@
       <c r="B41" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D41" s="6">
         <v>1109990</v>
-      </c>
-      <c r="D41" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1698,11 +1699,11 @@
       <c r="B42" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C42" s="6">
+      <c r="C42" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D42" s="6">
         <v>1109990</v>
-      </c>
-      <c r="D42" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1712,11 +1713,11 @@
       <c r="B43" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C43" s="6">
+      <c r="C43" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D43" s="6">
         <v>1109990</v>
-      </c>
-      <c r="D43" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1726,11 +1727,11 @@
       <c r="B44" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C44" s="6">
+      <c r="C44" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D44" s="6">
         <v>19990</v>
-      </c>
-      <c r="D44" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1740,11 +1741,11 @@
       <c r="B45" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C45" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D45" s="6">
         <v>19990</v>
-      </c>
-      <c r="D45" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1754,11 +1755,11 @@
       <c r="B46" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C46" s="6">
+      <c r="C46" s="4">
+        <v>80000</v>
+      </c>
+      <c r="D46" s="6">
         <v>29990</v>
-      </c>
-      <c r="D46" s="4">
-        <v>80000</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1768,11 +1769,11 @@
       <c r="B47" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C47" s="6">
+      <c r="C47" s="4">
+        <v>80000</v>
+      </c>
+      <c r="D47" s="6">
         <v>29990</v>
-      </c>
-      <c r="D47" s="4">
-        <v>80000</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1782,11 +1783,11 @@
       <c r="B48" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C48" s="6">
+      <c r="C48" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D48" s="6">
         <v>990</v>
-      </c>
-      <c r="D48" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1796,11 +1797,11 @@
       <c r="B49" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C49" s="6">
+      <c r="C49" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D49" s="6">
         <v>990</v>
-      </c>
-      <c r="D49" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1810,11 +1811,11 @@
       <c r="B50" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C50" s="6">
+      <c r="C50" s="4">
+        <v>100000</v>
+      </c>
+      <c r="D50" s="6">
         <v>29990</v>
-      </c>
-      <c r="D50" s="4">
-        <v>100000</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1824,11 +1825,11 @@
       <c r="B51" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C51" s="6">
+      <c r="C51" s="4">
+        <v>100000</v>
+      </c>
+      <c r="D51" s="6">
         <v>29990</v>
-      </c>
-      <c r="D51" s="4">
-        <v>100000</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1838,11 +1839,11 @@
       <c r="B52" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C52" s="6">
+      <c r="C52" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D52" s="6">
         <v>19990</v>
-      </c>
-      <c r="D52" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1852,11 +1853,11 @@
       <c r="B53" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C53" s="6">
+      <c r="C53" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D53" s="6">
         <v>19990</v>
-      </c>
-      <c r="D53" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1866,11 +1867,11 @@
       <c r="B54" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C54" s="6">
+      <c r="C54" s="4">
+        <v>100000</v>
+      </c>
+      <c r="D54" s="6">
         <v>49990</v>
-      </c>
-      <c r="D54" s="4">
-        <v>100000</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1880,11 +1881,11 @@
       <c r="B55" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C55" s="6">
+      <c r="C55" s="4">
+        <v>100000</v>
+      </c>
+      <c r="D55" s="6">
         <v>49990</v>
-      </c>
-      <c r="D55" s="4">
-        <v>100000</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1894,11 +1895,11 @@
       <c r="B56" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C56" s="6">
+      <c r="C56" s="4">
+        <v>80000</v>
+      </c>
+      <c r="D56" s="6">
         <v>59990</v>
-      </c>
-      <c r="D56" s="4">
-        <v>80000</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1908,11 +1909,11 @@
       <c r="B57" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C57" s="6">
+      <c r="C57" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D57" s="6">
         <v>89990</v>
-      </c>
-      <c r="D57" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1922,11 +1923,11 @@
       <c r="B58" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C58" s="6">
+      <c r="C58" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D58" s="6">
         <v>89990</v>
-      </c>
-      <c r="D58" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1936,11 +1937,11 @@
       <c r="B59" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C59" s="6">
+      <c r="C59" s="4">
+        <v>80000</v>
+      </c>
+      <c r="D59" s="6">
         <v>149990</v>
-      </c>
-      <c r="D59" s="4">
-        <v>80000</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1950,11 +1951,11 @@
       <c r="B60" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C60" s="6">
+      <c r="C60" s="4">
+        <v>80000</v>
+      </c>
+      <c r="D60" s="6">
         <v>149990</v>
-      </c>
-      <c r="D60" s="4">
-        <v>80000</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1964,11 +1965,11 @@
       <c r="B61" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C61" s="6">
+      <c r="C61" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D61" s="6">
         <v>119990</v>
-      </c>
-      <c r="D61" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1978,11 +1979,11 @@
       <c r="B62" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C62" s="6">
+      <c r="C62" s="4">
+        <v>90000</v>
+      </c>
+      <c r="D62" s="6">
         <v>199990</v>
-      </c>
-      <c r="D62" s="4">
-        <v>90000</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -1992,11 +1993,11 @@
       <c r="B63" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C63" s="6">
+      <c r="C63" s="4">
+        <v>90000</v>
+      </c>
+      <c r="D63" s="6">
         <v>179990</v>
-      </c>
-      <c r="D63" s="4">
-        <v>90000</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2006,11 +2007,11 @@
       <c r="B64" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C64" s="6">
+      <c r="C64" s="4">
+        <v>90000</v>
+      </c>
+      <c r="D64" s="6">
         <v>259990</v>
-      </c>
-      <c r="D64" s="4">
-        <v>90000</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2020,11 +2021,11 @@
       <c r="B65" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C65" s="6">
+      <c r="C65" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D65" s="6">
         <v>239990</v>
-      </c>
-      <c r="D65" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2034,11 +2035,11 @@
       <c r="B66" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C66" s="6">
+      <c r="C66" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D66" s="6">
         <v>409990</v>
-      </c>
-      <c r="D66" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2048,11 +2049,11 @@
       <c r="B67" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C67" s="6">
+      <c r="C67" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D67" s="6">
         <v>329990</v>
-      </c>
-      <c r="D67" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2062,11 +2063,11 @@
       <c r="B68" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C68" s="6">
+      <c r="C68" s="4">
+        <v>90000</v>
+      </c>
+      <c r="D68" s="6">
         <v>409990</v>
-      </c>
-      <c r="D68" s="4">
-        <v>90000</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2076,11 +2077,11 @@
       <c r="B69" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C69" s="6">
+      <c r="C69" s="4">
+        <v>90000</v>
+      </c>
+      <c r="D69" s="6">
         <v>409990</v>
-      </c>
-      <c r="D69" s="4">
-        <v>90000</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2090,11 +2091,11 @@
       <c r="B70" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C70" s="6">
+      <c r="C70" s="4">
+        <v>90000</v>
+      </c>
+      <c r="D70" s="6">
         <v>409990</v>
-      </c>
-      <c r="D70" s="4">
-        <v>90000</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2104,11 +2105,11 @@
       <c r="B71" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C71" s="6">
+      <c r="C71" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D71" s="6">
         <v>589990</v>
-      </c>
-      <c r="D71" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2118,11 +2119,11 @@
       <c r="B72" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C72" s="6">
+      <c r="C72" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D72" s="6">
         <v>589990</v>
-      </c>
-      <c r="D72" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2132,11 +2133,11 @@
       <c r="B73" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C73" s="6">
+      <c r="C73" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D73" s="6">
         <v>589990</v>
-      </c>
-      <c r="D73" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2146,11 +2147,11 @@
       <c r="B74" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C74" s="6">
+      <c r="C74" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D74" s="6">
         <v>529990</v>
-      </c>
-      <c r="D74" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2160,11 +2161,11 @@
       <c r="B75" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C75" s="6">
+      <c r="C75" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D75" s="6">
         <v>529990</v>
-      </c>
-      <c r="D75" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2174,11 +2175,11 @@
       <c r="B76" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C76" s="6">
+      <c r="C76" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D76" s="6">
         <v>929990</v>
-      </c>
-      <c r="D76" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2188,11 +2189,11 @@
       <c r="B77" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C77" s="6">
+      <c r="C77" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D77" s="6">
         <v>929990</v>
-      </c>
-      <c r="D77" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2202,11 +2203,11 @@
       <c r="B78" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C78" s="6">
+      <c r="C78" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D78" s="6">
         <v>509990</v>
-      </c>
-      <c r="D78" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2216,11 +2217,11 @@
       <c r="B79" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C79" s="6">
+      <c r="C79" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D79" s="6">
         <v>509990</v>
-      </c>
-      <c r="D79" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2230,11 +2231,11 @@
       <c r="B80" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C80" s="6">
+      <c r="C80" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D80" s="6">
         <v>629990</v>
-      </c>
-      <c r="D80" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2244,11 +2245,11 @@
       <c r="B81" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C81" s="6">
+      <c r="C81" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D81" s="6">
         <v>659990</v>
-      </c>
-      <c r="D81" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2258,11 +2259,11 @@
       <c r="B82" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C82" s="6">
+      <c r="C82" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D82" s="6">
         <v>489990</v>
-      </c>
-      <c r="D82" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2272,11 +2273,11 @@
       <c r="B83" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C83" s="6">
+      <c r="C83" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D83" s="6">
         <v>489990</v>
-      </c>
-      <c r="D83" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2286,11 +2287,11 @@
       <c r="B84" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C84" s="6">
+      <c r="C84" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D84" s="6">
         <v>729990</v>
-      </c>
-      <c r="D84" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2300,11 +2301,11 @@
       <c r="B85" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C85" s="6">
+      <c r="C85" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D85" s="6">
         <v>819990</v>
-      </c>
-      <c r="D85" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2314,11 +2315,11 @@
       <c r="B86" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C86" s="6">
+      <c r="C86" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D86" s="6">
         <v>819990</v>
-      </c>
-      <c r="D86" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2328,11 +2329,11 @@
       <c r="B87" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C87" s="6">
+      <c r="C87" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D87" s="6">
         <v>969990</v>
-      </c>
-      <c r="D87" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -2342,11 +2343,11 @@
       <c r="B88" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C88" s="6">
+      <c r="C88" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D88" s="6">
         <v>1079990</v>
-      </c>
-      <c r="D88" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -2356,11 +2357,11 @@
       <c r="B89" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C89" s="6">
+      <c r="C89" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D89" s="6">
         <v>1079990</v>
-      </c>
-      <c r="D89" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -2370,11 +2371,11 @@
       <c r="B90" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C90" s="6">
+      <c r="C90" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D90" s="6">
         <v>1229990</v>
-      </c>
-      <c r="D90" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -2384,11 +2385,11 @@
       <c r="B91" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C91" s="6">
+      <c r="C91" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D91" s="6">
         <v>1279990</v>
-      </c>
-      <c r="D91" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2398,11 +2399,11 @@
       <c r="B92" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C92" s="6">
+      <c r="C92" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D92" s="6">
         <v>1279990</v>
-      </c>
-      <c r="D92" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -2412,11 +2413,11 @@
       <c r="B93" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C93" s="6">
+      <c r="C93" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D93" s="6">
         <v>1179990</v>
-      </c>
-      <c r="D93" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -2426,11 +2427,11 @@
       <c r="B94" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C94" s="6">
+      <c r="C94" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D94" s="6">
         <v>1179990</v>
-      </c>
-      <c r="D94" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -2440,11 +2441,11 @@
       <c r="B95" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C95" s="6">
+      <c r="C95" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D95" s="6">
         <v>1179990</v>
-      </c>
-      <c r="D95" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -2454,11 +2455,11 @@
       <c r="B96" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C96" s="6">
+      <c r="C96" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D96" s="6">
         <v>1179990</v>
-      </c>
-      <c r="D96" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -2468,11 +2469,11 @@
       <c r="B97" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C97" s="6">
+      <c r="C97" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D97" s="6">
         <v>1429990</v>
-      </c>
-      <c r="D97" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -2482,11 +2483,11 @@
       <c r="B98" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C98" s="6">
+      <c r="C98" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D98" s="6">
         <v>1429990</v>
-      </c>
-      <c r="D98" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -2496,11 +2497,11 @@
       <c r="B99" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C99" s="6">
+      <c r="C99" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D99" s="6">
         <v>1429990</v>
-      </c>
-      <c r="D99" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2510,11 +2511,11 @@
       <c r="B100" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C100" s="6">
+      <c r="C100" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D100" s="6">
         <v>1329990</v>
-      </c>
-      <c r="D100" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -2524,11 +2525,11 @@
       <c r="B101" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C101" s="6">
+      <c r="C101" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D101" s="6">
         <v>1329990</v>
-      </c>
-      <c r="D101" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -2538,11 +2539,11 @@
       <c r="B102" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C102" s="6">
+      <c r="C102" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D102" s="6">
         <v>1329990</v>
-      </c>
-      <c r="D102" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2552,11 +2553,11 @@
       <c r="B103" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C103" s="6">
+      <c r="C103" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D103" s="6">
         <v>899990</v>
-      </c>
-      <c r="D103" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2566,11 +2567,11 @@
       <c r="B104" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C104" s="6">
+      <c r="C104" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D104" s="6">
         <v>899990</v>
-      </c>
-      <c r="D104" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2580,11 +2581,11 @@
       <c r="B105" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C105" s="6">
+      <c r="C105" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D105" s="6">
         <v>899990</v>
-      </c>
-      <c r="D105" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2594,11 +2595,11 @@
       <c r="B106" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C106" s="6">
+      <c r="C106" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D106" s="6">
         <v>899990</v>
-      </c>
-      <c r="D106" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2608,11 +2609,11 @@
       <c r="B107" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C107" s="6">
+      <c r="C107" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D107" s="6">
         <v>899990</v>
-      </c>
-      <c r="D107" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2622,11 +2623,11 @@
       <c r="B108" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C108" s="6">
+      <c r="C108" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D108" s="6">
         <v>9990</v>
-      </c>
-      <c r="D108" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2636,11 +2637,11 @@
       <c r="B109" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C109" s="6">
+      <c r="C109" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D109" s="6">
         <v>9990</v>
-      </c>
-      <c r="D109" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2650,11 +2651,11 @@
       <c r="B110" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C110" s="6">
+      <c r="C110" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D110" s="6">
         <v>29990</v>
-      </c>
-      <c r="D110" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2664,11 +2665,11 @@
       <c r="B111" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C111" s="6">
+      <c r="C111" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D111" s="6">
         <v>29990</v>
-      </c>
-      <c r="D111" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2678,11 +2679,11 @@
       <c r="B112" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C112" s="6">
+      <c r="C112" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D112" s="6">
         <v>19990</v>
-      </c>
-      <c r="D112" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2692,11 +2693,11 @@
       <c r="B113" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C113" s="6">
+      <c r="C113" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D113" s="6">
         <v>19990</v>
-      </c>
-      <c r="D113" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2706,11 +2707,11 @@
       <c r="B114" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C114" s="6">
+      <c r="C114" s="4">
+        <v>80000</v>
+      </c>
+      <c r="D114" s="6">
         <v>24990</v>
-      </c>
-      <c r="D114" s="4">
-        <v>80000</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2720,11 +2721,11 @@
       <c r="B115" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C115" s="6">
+      <c r="C115" s="4">
+        <v>80000</v>
+      </c>
+      <c r="D115" s="6">
         <v>24990</v>
-      </c>
-      <c r="D115" s="4">
-        <v>80000</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2734,11 +2735,11 @@
       <c r="B116" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C116" s="6">
+      <c r="C116" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D116" s="6">
         <v>34990</v>
-      </c>
-      <c r="D116" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2748,11 +2749,11 @@
       <c r="B117" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C117" s="6">
+      <c r="C117" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D117" s="6">
         <v>34990</v>
-      </c>
-      <c r="D117" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2762,11 +2763,11 @@
       <c r="B118" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C118" s="6">
+      <c r="C118" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D118" s="6">
         <v>39990</v>
-      </c>
-      <c r="D118" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2776,11 +2777,11 @@
       <c r="B119" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C119" s="6">
+      <c r="C119" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D119" s="6">
         <v>39990</v>
-      </c>
-      <c r="D119" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2790,11 +2791,11 @@
       <c r="B120" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C120" s="6">
+      <c r="C120" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D120" s="6">
         <v>44990</v>
-      </c>
-      <c r="D120" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2804,11 +2805,11 @@
       <c r="B121" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C121" s="6">
+      <c r="C121" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D121" s="6">
         <v>44990</v>
-      </c>
-      <c r="D121" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2818,11 +2819,11 @@
       <c r="B122" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C122" s="6">
+      <c r="C122" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D122" s="6">
         <v>44990</v>
-      </c>
-      <c r="D122" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2832,11 +2833,11 @@
       <c r="B123" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C123" s="6">
+      <c r="C123" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D123" s="6">
         <v>49990</v>
-      </c>
-      <c r="D123" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2846,11 +2847,11 @@
       <c r="B124" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C124" s="6">
+      <c r="C124" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D124" s="6">
         <v>49990</v>
-      </c>
-      <c r="D124" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2860,11 +2861,11 @@
       <c r="B125" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C125" s="6">
+      <c r="C125" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D125" s="6">
         <v>119990</v>
-      </c>
-      <c r="D125" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2874,11 +2875,11 @@
       <c r="B126" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C126" s="6">
+      <c r="C126" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D126" s="6">
         <v>119990</v>
-      </c>
-      <c r="D126" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2888,11 +2889,11 @@
       <c r="B127" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C127" s="6">
+      <c r="C127" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D127" s="6">
         <v>79990</v>
-      </c>
-      <c r="D127" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2902,11 +2903,11 @@
       <c r="B128" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C128" s="6">
+      <c r="C128" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D128" s="6">
         <v>79990</v>
-      </c>
-      <c r="D128" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2916,11 +2917,11 @@
       <c r="B129" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C129" s="6">
+      <c r="C129" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D129" s="6">
         <v>149990</v>
-      </c>
-      <c r="D129" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2930,11 +2931,11 @@
       <c r="B130" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C130" s="6">
+      <c r="C130" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D130" s="6">
         <v>149990</v>
-      </c>
-      <c r="D130" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2944,11 +2945,11 @@
       <c r="B131" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C131" s="6">
+      <c r="C131" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D131" s="6">
         <v>139990</v>
-      </c>
-      <c r="D131" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2958,11 +2959,11 @@
       <c r="B132" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C132" s="6">
+      <c r="C132" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D132" s="6">
         <v>169990</v>
-      </c>
-      <c r="D132" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2972,11 +2973,11 @@
       <c r="B133" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C133" s="6">
+      <c r="C133" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D133" s="6">
         <v>169990</v>
-      </c>
-      <c r="D133" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2986,11 +2987,11 @@
       <c r="B134" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C134" s="6">
+      <c r="C134" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D134" s="6">
         <v>169990</v>
-      </c>
-      <c r="D134" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -3000,11 +3001,11 @@
       <c r="B135" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C135" s="6">
+      <c r="C135" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D135" s="6">
         <v>239990</v>
-      </c>
-      <c r="D135" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3014,11 +3015,11 @@
       <c r="B136" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C136" s="6">
+      <c r="C136" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D136" s="6">
         <v>239990</v>
-      </c>
-      <c r="D136" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3028,11 +3029,11 @@
       <c r="B137" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C137" s="6">
+      <c r="C137" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D137" s="6">
         <v>209990</v>
-      </c>
-      <c r="D137" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3042,11 +3043,11 @@
       <c r="B138" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C138" s="6">
+      <c r="C138" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D138" s="6">
         <v>209990</v>
-      </c>
-      <c r="D138" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3056,11 +3057,11 @@
       <c r="B139" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C139" s="6">
+      <c r="C139" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D139" s="6">
         <v>279990</v>
-      </c>
-      <c r="D139" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3070,11 +3071,11 @@
       <c r="B140" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C140" s="6">
+      <c r="C140" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D140" s="6">
         <v>279990</v>
-      </c>
-      <c r="D140" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3084,11 +3085,11 @@
       <c r="B141" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C141" s="6">
+      <c r="C141" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D141" s="6">
         <v>299990</v>
-      </c>
-      <c r="D141" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3098,11 +3099,11 @@
       <c r="B142" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C142" s="6">
+      <c r="C142" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D142" s="6">
         <v>299990</v>
-      </c>
-      <c r="D142" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -3112,11 +3113,11 @@
       <c r="B143" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C143" s="6">
+      <c r="C143" s="4">
+        <v>80000</v>
+      </c>
+      <c r="D143" s="6">
         <v>9990</v>
-      </c>
-      <c r="D143" s="4">
-        <v>80000</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -3126,11 +3127,11 @@
       <c r="B144" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C144" s="6">
+      <c r="C144" s="4">
+        <v>100000</v>
+      </c>
+      <c r="D144" s="6">
         <v>9990</v>
-      </c>
-      <c r="D144" s="4">
-        <v>100000</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3140,11 +3141,11 @@
       <c r="B145" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C145" s="6">
+      <c r="C145" s="4">
+        <v>80000</v>
+      </c>
+      <c r="D145" s="6">
         <v>39990</v>
-      </c>
-      <c r="D145" s="4">
-        <v>80000</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3154,11 +3155,11 @@
       <c r="B146" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C146" s="6">
+      <c r="C146" s="4">
+        <v>90000</v>
+      </c>
+      <c r="D146" s="6">
         <v>49990</v>
-      </c>
-      <c r="D146" s="4">
-        <v>90000</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3168,11 +3169,11 @@
       <c r="B147" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C147" s="6">
+      <c r="C147" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D147" s="6">
         <v>69990</v>
-      </c>
-      <c r="D147" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3182,11 +3183,11 @@
       <c r="B148" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C148" s="6">
+      <c r="C148" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D148" s="6">
         <v>69990</v>
-      </c>
-      <c r="D148" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -3196,11 +3197,11 @@
       <c r="B149" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C149" s="6">
+      <c r="C149" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D149" s="6">
         <v>79990</v>
-      </c>
-      <c r="D149" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -3210,11 +3211,11 @@
       <c r="B150" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C150" s="6">
+      <c r="C150" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D150" s="6">
         <v>79990</v>
-      </c>
-      <c r="D150" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -3224,11 +3225,11 @@
       <c r="B151" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C151" s="6">
+      <c r="C151" s="4">
+        <v>80000</v>
+      </c>
+      <c r="D151" s="6">
         <v>119990</v>
-      </c>
-      <c r="D151" s="4">
-        <v>80000</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -3238,11 +3239,11 @@
       <c r="B152" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C152" s="6">
+      <c r="C152" s="4">
+        <v>80000</v>
+      </c>
+      <c r="D152" s="6">
         <v>119990</v>
-      </c>
-      <c r="D152" s="4">
-        <v>80000</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -3252,11 +3253,11 @@
       <c r="B153" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C153" s="6">
+      <c r="C153" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D153" s="6">
         <v>109990</v>
-      </c>
-      <c r="D153" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -3266,11 +3267,11 @@
       <c r="B154" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C154" s="6">
+      <c r="C154" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D154" s="6">
         <v>109990</v>
-      </c>
-      <c r="D154" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -3280,11 +3281,11 @@
       <c r="B155" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C155" s="6">
+      <c r="C155" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D155" s="6">
         <v>149990</v>
-      </c>
-      <c r="D155" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -3294,11 +3295,11 @@
       <c r="B156" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C156" s="6">
+      <c r="C156" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D156" s="6">
         <v>149990</v>
-      </c>
-      <c r="D156" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -3308,11 +3309,11 @@
       <c r="B157" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C157" s="6">
+      <c r="C157" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D157" s="6">
         <v>149990</v>
-      </c>
-      <c r="D157" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -3322,11 +3323,11 @@
       <c r="B158" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C158" s="6">
+      <c r="C158" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D158" s="6">
         <v>149990</v>
-      </c>
-      <c r="D158" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3336,11 +3337,11 @@
       <c r="B159" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C159" s="6">
+      <c r="C159" s="4">
+        <v>90000</v>
+      </c>
+      <c r="D159" s="6">
         <v>199990</v>
-      </c>
-      <c r="D159" s="4">
-        <v>90000</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3350,11 +3351,11 @@
       <c r="B160" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C160" s="6">
+      <c r="C160" s="4">
+        <v>90000</v>
+      </c>
+      <c r="D160" s="6">
         <v>199990</v>
-      </c>
-      <c r="D160" s="4">
-        <v>90000</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3364,11 +3365,11 @@
       <c r="B161" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C161" s="6">
+      <c r="C161" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D161" s="6">
         <v>199990</v>
-      </c>
-      <c r="D161" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3378,11 +3379,11 @@
       <c r="B162" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C162" s="6">
+      <c r="C162" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D162" s="6">
         <v>199990</v>
-      </c>
-      <c r="D162" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -3392,11 +3393,11 @@
       <c r="B163" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C163" s="6">
+      <c r="C163" s="4">
+        <v>120000</v>
+      </c>
+      <c r="D163" s="6">
         <v>269990</v>
-      </c>
-      <c r="D163" s="4">
-        <v>120000</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -3406,11 +3407,11 @@
       <c r="B164" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C164" s="6">
+      <c r="C164" s="4">
+        <v>120000</v>
+      </c>
+      <c r="D164" s="6">
         <v>269990</v>
-      </c>
-      <c r="D164" s="4">
-        <v>120000</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3420,11 +3421,11 @@
       <c r="B165" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C165" s="6">
+      <c r="C165" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D165" s="6">
         <v>309990</v>
-      </c>
-      <c r="D165" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3434,11 +3435,11 @@
       <c r="B166" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C166" s="6">
+      <c r="C166" s="4">
+        <v>120000</v>
+      </c>
+      <c r="D166" s="6">
         <v>339990</v>
-      </c>
-      <c r="D166" s="4">
-        <v>120000</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3448,11 +3449,11 @@
       <c r="B167" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C167" s="6">
+      <c r="C167" s="4">
+        <v>120000</v>
+      </c>
+      <c r="D167" s="6">
         <v>339990</v>
-      </c>
-      <c r="D167" s="4">
-        <v>120000</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3462,11 +3463,11 @@
       <c r="B168" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C168" s="6">
+      <c r="C168" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D168" s="6">
         <v>559990</v>
-      </c>
-      <c r="D168" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3476,11 +3477,11 @@
       <c r="B169" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C169" s="6">
+      <c r="C169" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D169" s="6">
         <v>829990</v>
-      </c>
-      <c r="D169" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3490,11 +3491,11 @@
       <c r="B170" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C170" s="6">
+      <c r="C170" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D170" s="6">
         <v>429990</v>
-      </c>
-      <c r="D170" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3504,11 +3505,11 @@
       <c r="B171" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C171" s="6">
+      <c r="C171" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D171" s="6">
         <v>429990</v>
-      </c>
-      <c r="D171" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3518,11 +3519,11 @@
       <c r="B172" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C172" s="6">
+      <c r="C172" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D172" s="6">
         <v>529990</v>
-      </c>
-      <c r="D172" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3532,11 +3533,11 @@
       <c r="B173" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C173" s="6">
+      <c r="C173" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D173" s="6">
         <v>929990</v>
-      </c>
-      <c r="D173" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3546,11 +3547,11 @@
       <c r="B174" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C174" s="6">
+      <c r="C174" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D174" s="6">
         <v>929990</v>
-      </c>
-      <c r="D174" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -3560,11 +3561,11 @@
       <c r="B175" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C175" s="6">
+      <c r="C175" s="4">
+        <v>100000</v>
+      </c>
+      <c r="D175" s="6">
         <v>29990</v>
-      </c>
-      <c r="D175" s="4">
-        <v>100000</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -3574,11 +3575,11 @@
       <c r="B176" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C176" s="6">
+      <c r="C176" s="4">
+        <v>100000</v>
+      </c>
+      <c r="D176" s="6">
         <v>29990</v>
-      </c>
-      <c r="D176" s="4">
-        <v>100000</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -3588,11 +3589,11 @@
       <c r="B177" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C177" s="6">
+      <c r="C177" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D177" s="6">
         <v>89990</v>
-      </c>
-      <c r="D177" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -3602,11 +3603,11 @@
       <c r="B178" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C178" s="6">
+      <c r="C178" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D178" s="6">
         <v>89990</v>
-      </c>
-      <c r="D178" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3616,11 +3617,11 @@
       <c r="B179" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C179" s="6">
+      <c r="C179" s="4">
+        <v>80000</v>
+      </c>
+      <c r="D179" s="6">
         <v>139990</v>
-      </c>
-      <c r="D179" s="4">
-        <v>80000</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -3630,11 +3631,11 @@
       <c r="B180" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C180" s="6">
+      <c r="C180" s="4">
+        <v>80000</v>
+      </c>
+      <c r="D180" s="6">
         <v>139990</v>
-      </c>
-      <c r="D180" s="4">
-        <v>80000</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -3644,11 +3645,11 @@
       <c r="B181" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C181" s="6">
+      <c r="C181" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D181" s="6">
         <v>169990</v>
-      </c>
-      <c r="D181" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3658,11 +3659,11 @@
       <c r="B182" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C182" s="6">
+      <c r="C182" s="4">
+        <v>100000</v>
+      </c>
+      <c r="D182" s="6">
         <v>209990</v>
-      </c>
-      <c r="D182" s="4">
-        <v>100000</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3672,11 +3673,11 @@
       <c r="B183" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C183" s="6">
+      <c r="C183" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D183" s="6">
         <v>199990</v>
-      </c>
-      <c r="D183" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3686,11 +3687,11 @@
       <c r="B184" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C184" s="6">
+      <c r="C184" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D184" s="6">
         <v>199990</v>
-      </c>
-      <c r="D184" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3700,11 +3701,11 @@
       <c r="B185" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C185" s="6">
+      <c r="C185" s="4">
+        <v>100000</v>
+      </c>
+      <c r="D185" s="6">
         <v>259990</v>
-      </c>
-      <c r="D185" s="4">
-        <v>100000</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3714,11 +3715,11 @@
       <c r="B186" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C186" s="6">
+      <c r="C186" s="4">
+        <v>100000</v>
+      </c>
+      <c r="D186" s="6">
         <v>259990</v>
-      </c>
-      <c r="D186" s="4">
-        <v>100000</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3728,11 +3729,11 @@
       <c r="B187" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C187" s="6">
+      <c r="C187" s="4">
+        <v>100000</v>
+      </c>
+      <c r="D187" s="6">
         <v>259990</v>
-      </c>
-      <c r="D187" s="4">
-        <v>100000</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3742,11 +3743,11 @@
       <c r="B188" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C188" s="6">
+      <c r="C188" s="4">
+        <v>100000</v>
+      </c>
+      <c r="D188" s="6">
         <v>259990</v>
-      </c>
-      <c r="D188" s="4">
-        <v>100000</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -3756,11 +3757,11 @@
       <c r="B189" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C189" s="6">
+      <c r="C189" s="4">
+        <v>150000</v>
+      </c>
+      <c r="D189" s="6">
         <v>399990</v>
-      </c>
-      <c r="D189" s="4">
-        <v>150000</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -3770,11 +3771,11 @@
       <c r="B190" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C190" s="6">
+      <c r="C190" s="4">
+        <v>150000</v>
+      </c>
+      <c r="D190" s="6">
         <v>399990</v>
-      </c>
-      <c r="D190" s="4">
-        <v>150000</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3784,11 +3785,11 @@
       <c r="B191" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C191" s="6">
+      <c r="C191" s="4">
+        <v>100000</v>
+      </c>
+      <c r="D191" s="6">
         <v>649990</v>
-      </c>
-      <c r="D191" s="4">
-        <v>100000</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -3798,11 +3799,11 @@
       <c r="B192" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C192" s="6">
+      <c r="C192" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D192" s="6">
         <v>79990</v>
-      </c>
-      <c r="D192" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -3812,11 +3813,11 @@
       <c r="B193" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C193" s="6">
+      <c r="C193" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D193" s="6">
         <v>79990</v>
-      </c>
-      <c r="D193" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3826,11 +3827,11 @@
       <c r="B194" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C194" s="6">
+      <c r="C194" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D194" s="6">
         <v>169990</v>
-      </c>
-      <c r="D194" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3840,11 +3841,11 @@
       <c r="B195" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C195" s="6">
+      <c r="C195" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D195" s="6">
         <v>169990</v>
-      </c>
-      <c r="D195" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3854,11 +3855,11 @@
       <c r="B196" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C196" s="6">
+      <c r="C196" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D196" s="6">
         <v>189990</v>
-      </c>
-      <c r="D196" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3868,11 +3869,11 @@
       <c r="B197" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C197" s="6">
+      <c r="C197" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D197" s="6">
         <v>189990</v>
-      </c>
-      <c r="D197" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3882,11 +3883,11 @@
       <c r="B198" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C198" s="6">
+      <c r="C198" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D198" s="6">
         <v>229990</v>
-      </c>
-      <c r="D198" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3896,11 +3897,11 @@
       <c r="B199" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C199" s="6">
+      <c r="C199" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D199" s="6">
         <v>279990</v>
-      </c>
-      <c r="D199" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3910,11 +3911,11 @@
       <c r="B200" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C200" s="6">
+      <c r="C200" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D200" s="6">
         <v>279990</v>
-      </c>
-      <c r="D200" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -3924,11 +3925,11 @@
       <c r="B201" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="C201" s="6">
+      <c r="C201" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D201" s="6">
         <v>990</v>
-      </c>
-      <c r="D201" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -3938,11 +3939,11 @@
       <c r="B202" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="C202" s="6">
+      <c r="C202" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D202" s="6">
         <v>9990</v>
-      </c>
-      <c r="D202" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3952,11 +3953,11 @@
       <c r="B203" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="C203" s="6">
+      <c r="C203" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D203" s="6">
         <v>19990</v>
-      </c>
-      <c r="D203" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3966,11 +3967,11 @@
       <c r="B204" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="C204" s="6">
+      <c r="C204" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D204" s="6">
         <v>129990</v>
-      </c>
-      <c r="D204" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -3980,11 +3981,11 @@
       <c r="B205" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C205" s="6">
+      <c r="C205" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D205" s="6">
         <v>19990</v>
-      </c>
-      <c r="D205" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -3994,11 +3995,11 @@
       <c r="B206" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C206" s="6">
+      <c r="C206" s="4">
+        <v>70000</v>
+      </c>
+      <c r="D206" s="6">
         <v>29990</v>
-      </c>
-      <c r="D206" s="4">
-        <v>70000</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -4008,11 +4009,11 @@
       <c r="B207" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C207" s="6">
+      <c r="C207" s="4">
+        <v>44000</v>
+      </c>
+      <c r="D207" s="6">
         <v>4990</v>
-      </c>
-      <c r="D207" s="4">
-        <v>44000</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -4022,11 +4023,11 @@
       <c r="B208" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C208" s="6">
+      <c r="C208" s="4">
+        <v>39000</v>
+      </c>
+      <c r="D208" s="6">
         <v>990</v>
-      </c>
-      <c r="D208" s="4">
-        <v>39000</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -4036,11 +4037,11 @@
       <c r="B209" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C209" s="6">
+      <c r="C209" s="4">
+        <v>69000</v>
+      </c>
+      <c r="D209" s="6">
         <v>990</v>
-      </c>
-      <c r="D209" s="4">
-        <v>69000</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -4050,11 +4051,11 @@
       <c r="B210" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C210" s="6">
+      <c r="C210" s="4">
+        <v>75000</v>
+      </c>
+      <c r="D210" s="6">
         <v>24990</v>
-      </c>
-      <c r="D210" s="4">
-        <v>75000</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -4064,11 +4065,11 @@
       <c r="B211" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C211" s="6">
+      <c r="C211" s="4">
+        <v>75000</v>
+      </c>
+      <c r="D211" s="6">
         <v>24990</v>
-      </c>
-      <c r="D211" s="4">
-        <v>75000</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -4078,11 +4079,11 @@
       <c r="B212" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C212" s="6">
+      <c r="C212" s="4">
+        <v>95000</v>
+      </c>
+      <c r="D212" s="6">
         <v>54990</v>
-      </c>
-      <c r="D212" s="4">
-        <v>95000</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -4092,11 +4093,11 @@
       <c r="B213" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C213" s="6">
+      <c r="C213" s="4">
+        <v>95000</v>
+      </c>
+      <c r="D213" s="6">
         <v>54990</v>
-      </c>
-      <c r="D213" s="4">
-        <v>95000</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -4106,11 +4107,11 @@
       <c r="B214" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C214" s="6">
+      <c r="C214" s="4">
+        <v>100000</v>
+      </c>
+      <c r="D214" s="6">
         <v>119990</v>
-      </c>
-      <c r="D214" s="4">
-        <v>100000</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -4120,11 +4121,11 @@
       <c r="B215" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C215" s="6">
+      <c r="C215" s="4">
+        <v>100000</v>
+      </c>
+      <c r="D215" s="6">
         <v>119990</v>
-      </c>
-      <c r="D215" s="4">
-        <v>100000</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -4134,11 +4135,11 @@
       <c r="B216" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C216" s="6">
+      <c r="C216" s="4">
+        <v>100000</v>
+      </c>
+      <c r="D216" s="6">
         <v>199990</v>
-      </c>
-      <c r="D216" s="4">
-        <v>100000</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -4148,2850 +4149,2850 @@
       <c r="B217" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C217" s="6">
+      <c r="C217" s="4">
+        <v>100000</v>
+      </c>
+      <c r="D217" s="6">
         <v>349990</v>
-      </c>
-      <c r="D217" s="4">
-        <v>100000</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
-      <c r="C218" s="7"/>
-      <c r="D218" s="2"/>
+      <c r="C218" s="2"/>
+      <c r="D218" s="7"/>
     </row>
     <row r="219" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
-      <c r="C219" s="7"/>
-      <c r="D219" s="2"/>
+      <c r="C219" s="2"/>
+      <c r="D219" s="7"/>
     </row>
     <row r="220" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
-      <c r="C220" s="7"/>
-      <c r="D220" s="2"/>
+      <c r="C220" s="2"/>
+      <c r="D220" s="7"/>
     </row>
     <row r="221" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
-      <c r="C221" s="7"/>
-      <c r="D221" s="2"/>
+      <c r="C221" s="2"/>
+      <c r="D221" s="7"/>
     </row>
     <row r="222" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
-      <c r="C222" s="7"/>
-      <c r="D222" s="2"/>
+      <c r="C222" s="2"/>
+      <c r="D222" s="7"/>
     </row>
     <row r="223" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
-      <c r="C223" s="7"/>
-      <c r="D223" s="2"/>
+      <c r="C223" s="2"/>
+      <c r="D223" s="7"/>
     </row>
     <row r="224" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
-      <c r="C224" s="7"/>
-      <c r="D224" s="2"/>
+      <c r="C224" s="2"/>
+      <c r="D224" s="7"/>
     </row>
     <row r="225" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
-      <c r="C225" s="7"/>
-      <c r="D225" s="2"/>
+      <c r="C225" s="2"/>
+      <c r="D225" s="7"/>
     </row>
     <row r="226" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
-      <c r="C226" s="7"/>
-      <c r="D226" s="2"/>
+      <c r="C226" s="2"/>
+      <c r="D226" s="7"/>
     </row>
     <row r="227" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
-      <c r="C227" s="7"/>
-      <c r="D227" s="2"/>
+      <c r="C227" s="2"/>
+      <c r="D227" s="7"/>
     </row>
     <row r="228" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
-      <c r="C228" s="7"/>
-      <c r="D228" s="2"/>
+      <c r="C228" s="2"/>
+      <c r="D228" s="7"/>
     </row>
     <row r="229" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
-      <c r="C229" s="7"/>
-      <c r="D229" s="2"/>
+      <c r="C229" s="2"/>
+      <c r="D229" s="7"/>
     </row>
     <row r="230" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
-      <c r="C230" s="7"/>
-      <c r="D230" s="2"/>
+      <c r="C230" s="2"/>
+      <c r="D230" s="7"/>
     </row>
     <row r="231" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
-      <c r="C231" s="7"/>
-      <c r="D231" s="2"/>
+      <c r="C231" s="2"/>
+      <c r="D231" s="7"/>
     </row>
     <row r="232" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
-      <c r="C232" s="7"/>
-      <c r="D232" s="2"/>
+      <c r="C232" s="2"/>
+      <c r="D232" s="7"/>
     </row>
     <row r="233" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
-      <c r="C233" s="7"/>
-      <c r="D233" s="2"/>
+      <c r="C233" s="2"/>
+      <c r="D233" s="7"/>
     </row>
     <row r="234" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
-      <c r="C234" s="7"/>
-      <c r="D234" s="2"/>
+      <c r="C234" s="2"/>
+      <c r="D234" s="7"/>
     </row>
     <row r="235" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
-      <c r="C235" s="7"/>
-      <c r="D235" s="2"/>
+      <c r="C235" s="2"/>
+      <c r="D235" s="7"/>
     </row>
     <row r="236" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
-      <c r="C236" s="7"/>
-      <c r="D236" s="2"/>
+      <c r="C236" s="2"/>
+      <c r="D236" s="7"/>
     </row>
     <row r="237" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
-      <c r="C237" s="7"/>
-      <c r="D237" s="2"/>
+      <c r="C237" s="2"/>
+      <c r="D237" s="7"/>
     </row>
     <row r="238" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
-      <c r="C238" s="7"/>
-      <c r="D238" s="2"/>
+      <c r="C238" s="2"/>
+      <c r="D238" s="7"/>
     </row>
     <row r="239" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
-      <c r="C239" s="7"/>
-      <c r="D239" s="2"/>
+      <c r="C239" s="2"/>
+      <c r="D239" s="7"/>
     </row>
     <row r="240" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
-      <c r="C240" s="7"/>
-      <c r="D240" s="2"/>
+      <c r="C240" s="2"/>
+      <c r="D240" s="7"/>
     </row>
     <row r="241" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
-      <c r="C241" s="7"/>
-      <c r="D241" s="2"/>
+      <c r="C241" s="2"/>
+      <c r="D241" s="7"/>
     </row>
     <row r="242" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
-      <c r="C242" s="7"/>
-      <c r="D242" s="2"/>
+      <c r="C242" s="2"/>
+      <c r="D242" s="7"/>
     </row>
     <row r="243" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
-      <c r="C243" s="7"/>
-      <c r="D243" s="2"/>
+      <c r="C243" s="2"/>
+      <c r="D243" s="7"/>
     </row>
     <row r="244" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
-      <c r="C244" s="7"/>
-      <c r="D244" s="2"/>
+      <c r="C244" s="2"/>
+      <c r="D244" s="7"/>
     </row>
     <row r="245" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
-      <c r="C245" s="7"/>
-      <c r="D245" s="2"/>
+      <c r="C245" s="2"/>
+      <c r="D245" s="7"/>
     </row>
     <row r="246" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
-      <c r="C246" s="7"/>
-      <c r="D246" s="2"/>
+      <c r="C246" s="2"/>
+      <c r="D246" s="7"/>
     </row>
     <row r="247" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
-      <c r="C247" s="7"/>
-      <c r="D247" s="2"/>
+      <c r="C247" s="2"/>
+      <c r="D247" s="7"/>
     </row>
     <row r="248" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
-      <c r="C248" s="7"/>
-      <c r="D248" s="2"/>
+      <c r="C248" s="2"/>
+      <c r="D248" s="7"/>
     </row>
     <row r="249" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
-      <c r="C249" s="7"/>
-      <c r="D249" s="2"/>
+      <c r="C249" s="2"/>
+      <c r="D249" s="7"/>
     </row>
     <row r="250" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
-      <c r="C250" s="7"/>
-      <c r="D250" s="2"/>
+      <c r="C250" s="2"/>
+      <c r="D250" s="7"/>
     </row>
     <row r="251" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
-      <c r="C251" s="7"/>
-      <c r="D251" s="2"/>
+      <c r="C251" s="2"/>
+      <c r="D251" s="7"/>
     </row>
     <row r="252" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
-      <c r="C252" s="7"/>
-      <c r="D252" s="2"/>
+      <c r="C252" s="2"/>
+      <c r="D252" s="7"/>
     </row>
     <row r="253" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
-      <c r="C253" s="7"/>
-      <c r="D253" s="2"/>
+      <c r="C253" s="2"/>
+      <c r="D253" s="7"/>
     </row>
     <row r="254" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
-      <c r="C254" s="7"/>
-      <c r="D254" s="2"/>
+      <c r="C254" s="2"/>
+      <c r="D254" s="7"/>
     </row>
     <row r="255" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
-      <c r="C255" s="7"/>
-      <c r="D255" s="2"/>
+      <c r="C255" s="2"/>
+      <c r="D255" s="7"/>
     </row>
     <row r="256" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
-      <c r="C256" s="7"/>
-      <c r="D256" s="2"/>
+      <c r="C256" s="2"/>
+      <c r="D256" s="7"/>
     </row>
     <row r="257" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
-      <c r="C257" s="7"/>
-      <c r="D257" s="2"/>
+      <c r="C257" s="2"/>
+      <c r="D257" s="7"/>
     </row>
     <row r="258" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
-      <c r="C258" s="7"/>
-      <c r="D258" s="2"/>
+      <c r="C258" s="2"/>
+      <c r="D258" s="7"/>
     </row>
     <row r="259" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
-      <c r="C259" s="7"/>
-      <c r="D259" s="2"/>
+      <c r="C259" s="2"/>
+      <c r="D259" s="7"/>
     </row>
     <row r="260" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
-      <c r="C260" s="7"/>
-      <c r="D260" s="2"/>
+      <c r="C260" s="2"/>
+      <c r="D260" s="7"/>
     </row>
     <row r="261" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
-      <c r="C261" s="7"/>
-      <c r="D261" s="2"/>
+      <c r="C261" s="2"/>
+      <c r="D261" s="7"/>
     </row>
     <row r="262" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
-      <c r="C262" s="7"/>
-      <c r="D262" s="2"/>
+      <c r="C262" s="2"/>
+      <c r="D262" s="7"/>
     </row>
     <row r="263" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
-      <c r="C263" s="7"/>
-      <c r="D263" s="2"/>
+      <c r="C263" s="2"/>
+      <c r="D263" s="7"/>
     </row>
     <row r="264" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
-      <c r="C264" s="7"/>
-      <c r="D264" s="2"/>
+      <c r="C264" s="2"/>
+      <c r="D264" s="7"/>
     </row>
     <row r="265" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
-      <c r="C265" s="7"/>
-      <c r="D265" s="2"/>
+      <c r="C265" s="2"/>
+      <c r="D265" s="7"/>
     </row>
     <row r="266" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
-      <c r="C266" s="7"/>
-      <c r="D266" s="2"/>
+      <c r="C266" s="2"/>
+      <c r="D266" s="7"/>
     </row>
     <row r="267" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
-      <c r="C267" s="7"/>
-      <c r="D267" s="2"/>
+      <c r="C267" s="2"/>
+      <c r="D267" s="7"/>
     </row>
     <row r="268" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
-      <c r="C268" s="7"/>
-      <c r="D268" s="2"/>
+      <c r="C268" s="2"/>
+      <c r="D268" s="7"/>
     </row>
     <row r="269" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
-      <c r="C269" s="7"/>
-      <c r="D269" s="2"/>
+      <c r="C269" s="2"/>
+      <c r="D269" s="7"/>
     </row>
     <row r="270" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
-      <c r="C270" s="7"/>
-      <c r="D270" s="2"/>
+      <c r="C270" s="2"/>
+      <c r="D270" s="7"/>
     </row>
     <row r="271" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
-      <c r="C271" s="7"/>
-      <c r="D271" s="2"/>
+      <c r="C271" s="2"/>
+      <c r="D271" s="7"/>
     </row>
     <row r="272" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
-      <c r="C272" s="7"/>
-      <c r="D272" s="2"/>
+      <c r="C272" s="2"/>
+      <c r="D272" s="7"/>
     </row>
     <row r="273" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
-      <c r="C273" s="7"/>
-      <c r="D273" s="2"/>
+      <c r="C273" s="2"/>
+      <c r="D273" s="7"/>
     </row>
     <row r="274" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
-      <c r="C274" s="7"/>
-      <c r="D274" s="2"/>
+      <c r="C274" s="2"/>
+      <c r="D274" s="7"/>
     </row>
     <row r="275" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
-      <c r="C275" s="7"/>
-      <c r="D275" s="2"/>
+      <c r="C275" s="2"/>
+      <c r="D275" s="7"/>
     </row>
     <row r="276" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
-      <c r="C276" s="7"/>
-      <c r="D276" s="2"/>
+      <c r="C276" s="2"/>
+      <c r="D276" s="7"/>
     </row>
     <row r="277" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
-      <c r="C277" s="7"/>
-      <c r="D277" s="2"/>
+      <c r="C277" s="2"/>
+      <c r="D277" s="7"/>
     </row>
     <row r="278" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
-      <c r="C278" s="7"/>
-      <c r="D278" s="2"/>
+      <c r="C278" s="2"/>
+      <c r="D278" s="7"/>
     </row>
     <row r="279" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
-      <c r="C279" s="7"/>
-      <c r="D279" s="2"/>
+      <c r="C279" s="2"/>
+      <c r="D279" s="7"/>
     </row>
     <row r="280" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
-      <c r="C280" s="7"/>
-      <c r="D280" s="2"/>
+      <c r="C280" s="2"/>
+      <c r="D280" s="7"/>
     </row>
     <row r="281" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
-      <c r="C281" s="7"/>
-      <c r="D281" s="2"/>
+      <c r="C281" s="2"/>
+      <c r="D281" s="7"/>
     </row>
     <row r="282" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
-      <c r="C282" s="7"/>
-      <c r="D282" s="2"/>
+      <c r="C282" s="2"/>
+      <c r="D282" s="7"/>
     </row>
     <row r="283" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" s="2"/>
       <c r="B283" s="2"/>
-      <c r="C283" s="7"/>
-      <c r="D283" s="2"/>
+      <c r="C283" s="2"/>
+      <c r="D283" s="7"/>
     </row>
     <row r="284" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
-      <c r="C284" s="7"/>
-      <c r="D284" s="2"/>
+      <c r="C284" s="2"/>
+      <c r="D284" s="7"/>
     </row>
     <row r="285" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
-      <c r="C285" s="7"/>
-      <c r="D285" s="2"/>
+      <c r="C285" s="2"/>
+      <c r="D285" s="7"/>
     </row>
     <row r="286" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
-      <c r="C286" s="7"/>
-      <c r="D286" s="2"/>
+      <c r="C286" s="2"/>
+      <c r="D286" s="7"/>
     </row>
     <row r="287" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
-      <c r="C287" s="7"/>
-      <c r="D287" s="2"/>
+      <c r="C287" s="2"/>
+      <c r="D287" s="7"/>
     </row>
     <row r="288" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
-      <c r="C288" s="7"/>
-      <c r="D288" s="2"/>
+      <c r="C288" s="2"/>
+      <c r="D288" s="7"/>
     </row>
     <row r="289" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
-      <c r="C289" s="7"/>
-      <c r="D289" s="2"/>
+      <c r="C289" s="2"/>
+      <c r="D289" s="7"/>
     </row>
     <row r="290" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
-      <c r="C290" s="7"/>
-      <c r="D290" s="2"/>
+      <c r="C290" s="2"/>
+      <c r="D290" s="7"/>
     </row>
     <row r="291" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
-      <c r="C291" s="7"/>
-      <c r="D291" s="2"/>
+      <c r="C291" s="2"/>
+      <c r="D291" s="7"/>
     </row>
     <row r="292" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
-      <c r="C292" s="7"/>
-      <c r="D292" s="2"/>
+      <c r="C292" s="2"/>
+      <c r="D292" s="7"/>
     </row>
     <row r="293" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" s="2"/>
       <c r="B293" s="2"/>
-      <c r="C293" s="7"/>
-      <c r="D293" s="2"/>
+      <c r="C293" s="2"/>
+      <c r="D293" s="7"/>
     </row>
     <row r="294" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294" s="2"/>
       <c r="B294" s="2"/>
-      <c r="C294" s="7"/>
-      <c r="D294" s="2"/>
+      <c r="C294" s="2"/>
+      <c r="D294" s="7"/>
     </row>
     <row r="295" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" s="2"/>
       <c r="B295" s="2"/>
-      <c r="C295" s="7"/>
-      <c r="D295" s="2"/>
+      <c r="C295" s="2"/>
+      <c r="D295" s="7"/>
     </row>
     <row r="296" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" s="2"/>
       <c r="B296" s="2"/>
-      <c r="C296" s="7"/>
-      <c r="D296" s="2"/>
+      <c r="C296" s="2"/>
+      <c r="D296" s="7"/>
     </row>
     <row r="297" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A297" s="2"/>
       <c r="B297" s="2"/>
-      <c r="C297" s="7"/>
-      <c r="D297" s="2"/>
+      <c r="C297" s="2"/>
+      <c r="D297" s="7"/>
     </row>
     <row r="298" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" s="2"/>
       <c r="B298" s="2"/>
-      <c r="C298" s="7"/>
-      <c r="D298" s="2"/>
+      <c r="C298" s="2"/>
+      <c r="D298" s="7"/>
     </row>
     <row r="299" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" s="2"/>
       <c r="B299" s="2"/>
-      <c r="C299" s="7"/>
-      <c r="D299" s="2"/>
+      <c r="C299" s="2"/>
+      <c r="D299" s="7"/>
     </row>
     <row r="300" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" s="2"/>
       <c r="B300" s="2"/>
-      <c r="C300" s="7"/>
-      <c r="D300" s="2"/>
+      <c r="C300" s="2"/>
+      <c r="D300" s="7"/>
     </row>
     <row r="301" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
-      <c r="C301" s="7"/>
-      <c r="D301" s="2"/>
+      <c r="C301" s="2"/>
+      <c r="D301" s="7"/>
     </row>
     <row r="302" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" s="2"/>
       <c r="B302" s="2"/>
-      <c r="C302" s="7"/>
-      <c r="D302" s="2"/>
+      <c r="C302" s="2"/>
+      <c r="D302" s="7"/>
     </row>
     <row r="303" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" s="2"/>
       <c r="B303" s="2"/>
-      <c r="C303" s="7"/>
-      <c r="D303" s="2"/>
+      <c r="C303" s="2"/>
+      <c r="D303" s="7"/>
     </row>
     <row r="304" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" s="2"/>
       <c r="B304" s="2"/>
-      <c r="C304" s="7"/>
-      <c r="D304" s="2"/>
+      <c r="C304" s="2"/>
+      <c r="D304" s="7"/>
     </row>
     <row r="305" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" s="2"/>
       <c r="B305" s="2"/>
-      <c r="C305" s="7"/>
-      <c r="D305" s="2"/>
+      <c r="C305" s="2"/>
+      <c r="D305" s="7"/>
     </row>
     <row r="306" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A306" s="2"/>
       <c r="B306" s="2"/>
-      <c r="C306" s="7"/>
-      <c r="D306" s="2"/>
+      <c r="C306" s="2"/>
+      <c r="D306" s="7"/>
     </row>
     <row r="307" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" s="2"/>
       <c r="B307" s="2"/>
-      <c r="C307" s="7"/>
-      <c r="D307" s="2"/>
+      <c r="C307" s="2"/>
+      <c r="D307" s="7"/>
     </row>
     <row r="308" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" s="2"/>
       <c r="B308" s="2"/>
-      <c r="C308" s="7"/>
-      <c r="D308" s="2"/>
+      <c r="C308" s="2"/>
+      <c r="D308" s="7"/>
     </row>
     <row r="309" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A309" s="2"/>
       <c r="B309" s="2"/>
-      <c r="C309" s="7"/>
-      <c r="D309" s="2"/>
+      <c r="C309" s="2"/>
+      <c r="D309" s="7"/>
     </row>
     <row r="310" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" s="2"/>
       <c r="B310" s="2"/>
-      <c r="C310" s="7"/>
-      <c r="D310" s="2"/>
+      <c r="C310" s="2"/>
+      <c r="D310" s="7"/>
     </row>
     <row r="311" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" s="2"/>
       <c r="B311" s="2"/>
-      <c r="C311" s="7"/>
-      <c r="D311" s="2"/>
+      <c r="C311" s="2"/>
+      <c r="D311" s="7"/>
     </row>
     <row r="312" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" s="2"/>
       <c r="B312" s="2"/>
-      <c r="C312" s="7"/>
-      <c r="D312" s="2"/>
+      <c r="C312" s="2"/>
+      <c r="D312" s="7"/>
     </row>
     <row r="313" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" s="2"/>
       <c r="B313" s="2"/>
-      <c r="C313" s="7"/>
-      <c r="D313" s="2"/>
+      <c r="C313" s="2"/>
+      <c r="D313" s="7"/>
     </row>
     <row r="314" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" s="2"/>
       <c r="B314" s="2"/>
-      <c r="C314" s="7"/>
-      <c r="D314" s="2"/>
+      <c r="C314" s="2"/>
+      <c r="D314" s="7"/>
     </row>
     <row r="315" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" s="2"/>
       <c r="B315" s="2"/>
-      <c r="C315" s="7"/>
-      <c r="D315" s="2"/>
+      <c r="C315" s="2"/>
+      <c r="D315" s="7"/>
     </row>
     <row r="316" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" s="2"/>
       <c r="B316" s="2"/>
-      <c r="C316" s="7"/>
-      <c r="D316" s="2"/>
+      <c r="C316" s="2"/>
+      <c r="D316" s="7"/>
     </row>
     <row r="317" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" s="2"/>
       <c r="B317" s="2"/>
-      <c r="C317" s="7"/>
-      <c r="D317" s="2"/>
+      <c r="C317" s="2"/>
+      <c r="D317" s="7"/>
     </row>
     <row r="318" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" s="2"/>
       <c r="B318" s="2"/>
-      <c r="C318" s="7"/>
-      <c r="D318" s="2"/>
+      <c r="C318" s="2"/>
+      <c r="D318" s="7"/>
     </row>
     <row r="319" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" s="2"/>
       <c r="B319" s="2"/>
-      <c r="C319" s="7"/>
-      <c r="D319" s="2"/>
+      <c r="C319" s="2"/>
+      <c r="D319" s="7"/>
     </row>
     <row r="320" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" s="2"/>
       <c r="B320" s="2"/>
-      <c r="C320" s="7"/>
-      <c r="D320" s="2"/>
+      <c r="C320" s="2"/>
+      <c r="D320" s="7"/>
     </row>
     <row r="321" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" s="2"/>
       <c r="B321" s="2"/>
-      <c r="C321" s="7"/>
-      <c r="D321" s="2"/>
+      <c r="C321" s="2"/>
+      <c r="D321" s="7"/>
     </row>
     <row r="322" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" s="2"/>
       <c r="B322" s="2"/>
-      <c r="C322" s="7"/>
-      <c r="D322" s="2"/>
+      <c r="C322" s="2"/>
+      <c r="D322" s="7"/>
     </row>
     <row r="323" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" s="2"/>
       <c r="B323" s="2"/>
-      <c r="C323" s="7"/>
-      <c r="D323" s="2"/>
+      <c r="C323" s="2"/>
+      <c r="D323" s="7"/>
     </row>
     <row r="324" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" s="2"/>
       <c r="B324" s="2"/>
-      <c r="C324" s="7"/>
-      <c r="D324" s="2"/>
+      <c r="C324" s="2"/>
+      <c r="D324" s="7"/>
     </row>
     <row r="325" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" s="2"/>
       <c r="B325" s="2"/>
-      <c r="C325" s="7"/>
-      <c r="D325" s="2"/>
+      <c r="C325" s="2"/>
+      <c r="D325" s="7"/>
     </row>
     <row r="326" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" s="2"/>
       <c r="B326" s="2"/>
-      <c r="C326" s="7"/>
-      <c r="D326" s="2"/>
+      <c r="C326" s="2"/>
+      <c r="D326" s="7"/>
     </row>
     <row r="327" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" s="2"/>
       <c r="B327" s="2"/>
-      <c r="C327" s="7"/>
-      <c r="D327" s="2"/>
+      <c r="C327" s="2"/>
+      <c r="D327" s="7"/>
     </row>
     <row r="328" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" s="2"/>
       <c r="B328" s="2"/>
-      <c r="C328" s="7"/>
-      <c r="D328" s="2"/>
+      <c r="C328" s="2"/>
+      <c r="D328" s="7"/>
     </row>
     <row r="329" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" s="2"/>
       <c r="B329" s="2"/>
-      <c r="C329" s="7"/>
-      <c r="D329" s="2"/>
+      <c r="C329" s="2"/>
+      <c r="D329" s="7"/>
     </row>
     <row r="330" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" s="2"/>
       <c r="B330" s="2"/>
-      <c r="C330" s="7"/>
-      <c r="D330" s="2"/>
+      <c r="C330" s="2"/>
+      <c r="D330" s="7"/>
     </row>
     <row r="331" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" s="2"/>
       <c r="B331" s="2"/>
-      <c r="C331" s="7"/>
-      <c r="D331" s="2"/>
+      <c r="C331" s="2"/>
+      <c r="D331" s="7"/>
     </row>
     <row r="332" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" s="2"/>
       <c r="B332" s="2"/>
-      <c r="C332" s="7"/>
-      <c r="D332" s="2"/>
+      <c r="C332" s="2"/>
+      <c r="D332" s="7"/>
     </row>
     <row r="333" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" s="2"/>
       <c r="B333" s="2"/>
-      <c r="C333" s="7"/>
-      <c r="D333" s="2"/>
+      <c r="C333" s="2"/>
+      <c r="D333" s="7"/>
     </row>
     <row r="334" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" s="2"/>
       <c r="B334" s="2"/>
-      <c r="C334" s="7"/>
-      <c r="D334" s="2"/>
+      <c r="C334" s="2"/>
+      <c r="D334" s="7"/>
     </row>
     <row r="335" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" s="2"/>
       <c r="B335" s="2"/>
-      <c r="C335" s="7"/>
-      <c r="D335" s="2"/>
+      <c r="C335" s="2"/>
+      <c r="D335" s="7"/>
     </row>
     <row r="336" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" s="2"/>
       <c r="B336" s="2"/>
-      <c r="C336" s="7"/>
-      <c r="D336" s="2"/>
+      <c r="C336" s="2"/>
+      <c r="D336" s="7"/>
     </row>
     <row r="337" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" s="2"/>
       <c r="B337" s="2"/>
-      <c r="C337" s="7"/>
-      <c r="D337" s="2"/>
+      <c r="C337" s="2"/>
+      <c r="D337" s="7"/>
     </row>
     <row r="338" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" s="2"/>
       <c r="B338" s="2"/>
-      <c r="C338" s="7"/>
-      <c r="D338" s="2"/>
+      <c r="C338" s="2"/>
+      <c r="D338" s="7"/>
     </row>
     <row r="339" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" s="2"/>
       <c r="B339" s="2"/>
-      <c r="C339" s="7"/>
-      <c r="D339" s="2"/>
+      <c r="C339" s="2"/>
+      <c r="D339" s="7"/>
     </row>
     <row r="340" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" s="2"/>
       <c r="B340" s="2"/>
-      <c r="C340" s="7"/>
-      <c r="D340" s="2"/>
+      <c r="C340" s="2"/>
+      <c r="D340" s="7"/>
     </row>
     <row r="341" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" s="2"/>
       <c r="B341" s="2"/>
-      <c r="C341" s="7"/>
-      <c r="D341" s="2"/>
+      <c r="C341" s="2"/>
+      <c r="D341" s="7"/>
     </row>
     <row r="342" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" s="2"/>
       <c r="B342" s="2"/>
-      <c r="C342" s="7"/>
-      <c r="D342" s="2"/>
+      <c r="C342" s="2"/>
+      <c r="D342" s="7"/>
     </row>
     <row r="343" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" s="2"/>
       <c r="B343" s="2"/>
-      <c r="C343" s="7"/>
-      <c r="D343" s="2"/>
+      <c r="C343" s="2"/>
+      <c r="D343" s="7"/>
     </row>
     <row r="344" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" s="2"/>
       <c r="B344" s="2"/>
-      <c r="C344" s="7"/>
-      <c r="D344" s="2"/>
+      <c r="C344" s="2"/>
+      <c r="D344" s="7"/>
     </row>
     <row r="345" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" s="2"/>
       <c r="B345" s="2"/>
-      <c r="C345" s="7"/>
-      <c r="D345" s="2"/>
+      <c r="C345" s="2"/>
+      <c r="D345" s="7"/>
     </row>
     <row r="346" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" s="2"/>
       <c r="B346" s="2"/>
-      <c r="C346" s="7"/>
-      <c r="D346" s="2"/>
+      <c r="C346" s="2"/>
+      <c r="D346" s="7"/>
     </row>
     <row r="347" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" s="2"/>
       <c r="B347" s="2"/>
-      <c r="C347" s="7"/>
-      <c r="D347" s="2"/>
+      <c r="C347" s="2"/>
+      <c r="D347" s="7"/>
     </row>
     <row r="348" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" s="2"/>
       <c r="B348" s="2"/>
-      <c r="C348" s="7"/>
-      <c r="D348" s="2"/>
+      <c r="C348" s="2"/>
+      <c r="D348" s="7"/>
     </row>
     <row r="349" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" s="2"/>
       <c r="B349" s="2"/>
-      <c r="C349" s="7"/>
-      <c r="D349" s="2"/>
+      <c r="C349" s="2"/>
+      <c r="D349" s="7"/>
     </row>
     <row r="350" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" s="2"/>
       <c r="B350" s="2"/>
-      <c r="C350" s="7"/>
-      <c r="D350" s="2"/>
+      <c r="C350" s="2"/>
+      <c r="D350" s="7"/>
     </row>
     <row r="351" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" s="2"/>
       <c r="B351" s="2"/>
-      <c r="C351" s="7"/>
-      <c r="D351" s="2"/>
+      <c r="C351" s="2"/>
+      <c r="D351" s="7"/>
     </row>
     <row r="352" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" s="2"/>
       <c r="B352" s="2"/>
-      <c r="C352" s="7"/>
-      <c r="D352" s="2"/>
+      <c r="C352" s="2"/>
+      <c r="D352" s="7"/>
     </row>
     <row r="353" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" s="2"/>
       <c r="B353" s="2"/>
-      <c r="C353" s="7"/>
-      <c r="D353" s="2"/>
+      <c r="C353" s="2"/>
+      <c r="D353" s="7"/>
     </row>
     <row r="354" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" s="2"/>
       <c r="B354" s="2"/>
-      <c r="C354" s="7"/>
-      <c r="D354" s="2"/>
+      <c r="C354" s="2"/>
+      <c r="D354" s="7"/>
     </row>
     <row r="355" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" s="2"/>
       <c r="B355" s="2"/>
-      <c r="C355" s="7"/>
-      <c r="D355" s="2"/>
+      <c r="C355" s="2"/>
+      <c r="D355" s="7"/>
     </row>
     <row r="356" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" s="2"/>
       <c r="B356" s="2"/>
-      <c r="C356" s="7"/>
-      <c r="D356" s="2"/>
+      <c r="C356" s="2"/>
+      <c r="D356" s="7"/>
     </row>
     <row r="357" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" s="2"/>
       <c r="B357" s="2"/>
-      <c r="C357" s="7"/>
-      <c r="D357" s="2"/>
+      <c r="C357" s="2"/>
+      <c r="D357" s="7"/>
     </row>
     <row r="358" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" s="2"/>
       <c r="B358" s="2"/>
-      <c r="C358" s="7"/>
-      <c r="D358" s="2"/>
+      <c r="C358" s="2"/>
+      <c r="D358" s="7"/>
     </row>
     <row r="359" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" s="2"/>
       <c r="B359" s="2"/>
-      <c r="C359" s="7"/>
-      <c r="D359" s="2"/>
+      <c r="C359" s="2"/>
+      <c r="D359" s="7"/>
     </row>
     <row r="360" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" s="2"/>
       <c r="B360" s="2"/>
-      <c r="C360" s="7"/>
-      <c r="D360" s="2"/>
+      <c r="C360" s="2"/>
+      <c r="D360" s="7"/>
     </row>
     <row r="361" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" s="2"/>
       <c r="B361" s="2"/>
-      <c r="C361" s="7"/>
-      <c r="D361" s="2"/>
+      <c r="C361" s="2"/>
+      <c r="D361" s="7"/>
     </row>
     <row r="362" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" s="2"/>
       <c r="B362" s="2"/>
-      <c r="C362" s="7"/>
-      <c r="D362" s="2"/>
+      <c r="C362" s="2"/>
+      <c r="D362" s="7"/>
     </row>
     <row r="363" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" s="2"/>
       <c r="B363" s="2"/>
-      <c r="C363" s="7"/>
-      <c r="D363" s="2"/>
+      <c r="C363" s="2"/>
+      <c r="D363" s="7"/>
     </row>
     <row r="364" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" s="2"/>
       <c r="B364" s="2"/>
-      <c r="C364" s="7"/>
-      <c r="D364" s="2"/>
+      <c r="C364" s="2"/>
+      <c r="D364" s="7"/>
     </row>
     <row r="365" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" s="2"/>
       <c r="B365" s="2"/>
-      <c r="C365" s="7"/>
-      <c r="D365" s="2"/>
+      <c r="C365" s="2"/>
+      <c r="D365" s="7"/>
     </row>
     <row r="366" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" s="2"/>
       <c r="B366" s="2"/>
-      <c r="C366" s="7"/>
-      <c r="D366" s="2"/>
+      <c r="C366" s="2"/>
+      <c r="D366" s="7"/>
     </row>
     <row r="367" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" s="2"/>
       <c r="B367" s="2"/>
-      <c r="C367" s="7"/>
-      <c r="D367" s="2"/>
+      <c r="C367" s="2"/>
+      <c r="D367" s="7"/>
     </row>
     <row r="368" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" s="2"/>
       <c r="B368" s="2"/>
-      <c r="C368" s="7"/>
-      <c r="D368" s="2"/>
+      <c r="C368" s="2"/>
+      <c r="D368" s="7"/>
     </row>
     <row r="369" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" s="2"/>
       <c r="B369" s="2"/>
-      <c r="C369" s="7"/>
-      <c r="D369" s="2"/>
+      <c r="C369" s="2"/>
+      <c r="D369" s="7"/>
     </row>
     <row r="370" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" s="2"/>
       <c r="B370" s="2"/>
-      <c r="C370" s="7"/>
-      <c r="D370" s="2"/>
+      <c r="C370" s="2"/>
+      <c r="D370" s="7"/>
     </row>
     <row r="371" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" s="2"/>
       <c r="B371" s="2"/>
-      <c r="C371" s="7"/>
-      <c r="D371" s="2"/>
+      <c r="C371" s="2"/>
+      <c r="D371" s="7"/>
     </row>
     <row r="372" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" s="2"/>
       <c r="B372" s="2"/>
-      <c r="C372" s="7"/>
-      <c r="D372" s="2"/>
+      <c r="C372" s="2"/>
+      <c r="D372" s="7"/>
     </row>
     <row r="373" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" s="2"/>
       <c r="B373" s="2"/>
-      <c r="C373" s="7"/>
-      <c r="D373" s="2"/>
+      <c r="C373" s="2"/>
+      <c r="D373" s="7"/>
     </row>
     <row r="374" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" s="2"/>
       <c r="B374" s="2"/>
-      <c r="C374" s="7"/>
-      <c r="D374" s="2"/>
+      <c r="C374" s="2"/>
+      <c r="D374" s="7"/>
     </row>
     <row r="375" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" s="2"/>
       <c r="B375" s="2"/>
-      <c r="C375" s="7"/>
-      <c r="D375" s="2"/>
+      <c r="C375" s="2"/>
+      <c r="D375" s="7"/>
     </row>
     <row r="376" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A376" s="2"/>
       <c r="B376" s="2"/>
-      <c r="C376" s="7"/>
-      <c r="D376" s="2"/>
+      <c r="C376" s="2"/>
+      <c r="D376" s="7"/>
     </row>
     <row r="377" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" s="2"/>
       <c r="B377" s="2"/>
-      <c r="C377" s="7"/>
-      <c r="D377" s="2"/>
+      <c r="C377" s="2"/>
+      <c r="D377" s="7"/>
     </row>
     <row r="378" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" s="2"/>
       <c r="B378" s="2"/>
-      <c r="C378" s="7"/>
-      <c r="D378" s="2"/>
+      <c r="C378" s="2"/>
+      <c r="D378" s="7"/>
     </row>
     <row r="379" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
-      <c r="C379" s="7"/>
-      <c r="D379" s="2"/>
+      <c r="C379" s="2"/>
+      <c r="D379" s="7"/>
     </row>
     <row r="380" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
-      <c r="C380" s="7"/>
-      <c r="D380" s="2"/>
+      <c r="C380" s="2"/>
+      <c r="D380" s="7"/>
     </row>
     <row r="381" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" s="2"/>
       <c r="B381" s="2"/>
-      <c r="C381" s="7"/>
-      <c r="D381" s="2"/>
+      <c r="C381" s="2"/>
+      <c r="D381" s="7"/>
     </row>
     <row r="382" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" s="2"/>
       <c r="B382" s="2"/>
-      <c r="C382" s="7"/>
-      <c r="D382" s="2"/>
+      <c r="C382" s="2"/>
+      <c r="D382" s="7"/>
     </row>
     <row r="383" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" s="2"/>
       <c r="B383" s="2"/>
-      <c r="C383" s="7"/>
-      <c r="D383" s="2"/>
+      <c r="C383" s="2"/>
+      <c r="D383" s="7"/>
     </row>
     <row r="384" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" s="2"/>
       <c r="B384" s="2"/>
-      <c r="C384" s="7"/>
-      <c r="D384" s="2"/>
+      <c r="C384" s="2"/>
+      <c r="D384" s="7"/>
     </row>
     <row r="385" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" s="2"/>
       <c r="B385" s="2"/>
-      <c r="C385" s="7"/>
-      <c r="D385" s="2"/>
+      <c r="C385" s="2"/>
+      <c r="D385" s="7"/>
     </row>
     <row r="386" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" s="2"/>
       <c r="B386" s="2"/>
-      <c r="C386" s="7"/>
-      <c r="D386" s="2"/>
+      <c r="C386" s="2"/>
+      <c r="D386" s="7"/>
     </row>
     <row r="387" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" s="2"/>
       <c r="B387" s="2"/>
-      <c r="C387" s="7"/>
-      <c r="D387" s="2"/>
+      <c r="C387" s="2"/>
+      <c r="D387" s="7"/>
     </row>
     <row r="388" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" s="2"/>
       <c r="B388" s="2"/>
-      <c r="C388" s="7"/>
-      <c r="D388" s="2"/>
+      <c r="C388" s="2"/>
+      <c r="D388" s="7"/>
     </row>
     <row r="389" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" s="2"/>
       <c r="B389" s="2"/>
-      <c r="C389" s="7"/>
-      <c r="D389" s="2"/>
+      <c r="C389" s="2"/>
+      <c r="D389" s="7"/>
     </row>
     <row r="390" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" s="2"/>
       <c r="B390" s="2"/>
-      <c r="C390" s="7"/>
-      <c r="D390" s="2"/>
+      <c r="C390" s="2"/>
+      <c r="D390" s="7"/>
     </row>
     <row r="391" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" s="2"/>
       <c r="B391" s="2"/>
-      <c r="C391" s="7"/>
-      <c r="D391" s="2"/>
+      <c r="C391" s="2"/>
+      <c r="D391" s="7"/>
     </row>
     <row r="392" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" s="2"/>
       <c r="B392" s="2"/>
-      <c r="C392" s="7"/>
-      <c r="D392" s="2"/>
+      <c r="C392" s="2"/>
+      <c r="D392" s="7"/>
     </row>
     <row r="393" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" s="2"/>
       <c r="B393" s="2"/>
-      <c r="C393" s="7"/>
-      <c r="D393" s="2"/>
+      <c r="C393" s="2"/>
+      <c r="D393" s="7"/>
     </row>
     <row r="394" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" s="2"/>
       <c r="B394" s="2"/>
-      <c r="C394" s="7"/>
-      <c r="D394" s="2"/>
+      <c r="C394" s="2"/>
+      <c r="D394" s="7"/>
     </row>
     <row r="395" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" s="2"/>
       <c r="B395" s="2"/>
-      <c r="C395" s="7"/>
-      <c r="D395" s="2"/>
+      <c r="C395" s="2"/>
+      <c r="D395" s="7"/>
     </row>
     <row r="396" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" s="2"/>
       <c r="B396" s="2"/>
-      <c r="C396" s="7"/>
-      <c r="D396" s="2"/>
+      <c r="C396" s="2"/>
+      <c r="D396" s="7"/>
     </row>
     <row r="397" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" s="2"/>
       <c r="B397" s="2"/>
-      <c r="C397" s="7"/>
-      <c r="D397" s="2"/>
+      <c r="C397" s="2"/>
+      <c r="D397" s="7"/>
     </row>
     <row r="398" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" s="2"/>
       <c r="B398" s="2"/>
-      <c r="C398" s="7"/>
-      <c r="D398" s="2"/>
+      <c r="C398" s="2"/>
+      <c r="D398" s="7"/>
     </row>
     <row r="399" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" s="2"/>
       <c r="B399" s="2"/>
-      <c r="C399" s="7"/>
-      <c r="D399" s="2"/>
+      <c r="C399" s="2"/>
+      <c r="D399" s="7"/>
     </row>
     <row r="400" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" s="2"/>
       <c r="B400" s="2"/>
-      <c r="C400" s="7"/>
-      <c r="D400" s="2"/>
+      <c r="C400" s="2"/>
+      <c r="D400" s="7"/>
     </row>
     <row r="401" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" s="2"/>
       <c r="B401" s="2"/>
-      <c r="C401" s="7"/>
-      <c r="D401" s="2"/>
+      <c r="C401" s="2"/>
+      <c r="D401" s="7"/>
     </row>
     <row r="402" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" s="2"/>
       <c r="B402" s="2"/>
-      <c r="C402" s="7"/>
-      <c r="D402" s="2"/>
+      <c r="C402" s="2"/>
+      <c r="D402" s="7"/>
     </row>
     <row r="403" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" s="2"/>
       <c r="B403" s="2"/>
-      <c r="C403" s="7"/>
-      <c r="D403" s="2"/>
+      <c r="C403" s="2"/>
+      <c r="D403" s="7"/>
     </row>
     <row r="404" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" s="2"/>
       <c r="B404" s="2"/>
-      <c r="C404" s="7"/>
-      <c r="D404" s="2"/>
+      <c r="C404" s="2"/>
+      <c r="D404" s="7"/>
     </row>
     <row r="405" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" s="2"/>
       <c r="B405" s="2"/>
-      <c r="C405" s="7"/>
-      <c r="D405" s="2"/>
+      <c r="C405" s="2"/>
+      <c r="D405" s="7"/>
     </row>
     <row r="406" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" s="2"/>
       <c r="B406" s="2"/>
-      <c r="C406" s="7"/>
-      <c r="D406" s="2"/>
+      <c r="C406" s="2"/>
+      <c r="D406" s="7"/>
     </row>
     <row r="407" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" s="2"/>
       <c r="B407" s="2"/>
-      <c r="C407" s="7"/>
-      <c r="D407" s="2"/>
+      <c r="C407" s="2"/>
+      <c r="D407" s="7"/>
     </row>
     <row r="408" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" s="2"/>
       <c r="B408" s="2"/>
-      <c r="C408" s="7"/>
-      <c r="D408" s="2"/>
+      <c r="C408" s="2"/>
+      <c r="D408" s="7"/>
     </row>
     <row r="409" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" s="2"/>
       <c r="B409" s="2"/>
-      <c r="C409" s="7"/>
-      <c r="D409" s="2"/>
+      <c r="C409" s="2"/>
+      <c r="D409" s="7"/>
     </row>
     <row r="410" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" s="2"/>
       <c r="B410" s="2"/>
-      <c r="C410" s="7"/>
-      <c r="D410" s="2"/>
+      <c r="C410" s="2"/>
+      <c r="D410" s="7"/>
     </row>
     <row r="411" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" s="2"/>
       <c r="B411" s="2"/>
-      <c r="C411" s="7"/>
-      <c r="D411" s="2"/>
+      <c r="C411" s="2"/>
+      <c r="D411" s="7"/>
     </row>
     <row r="412" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" s="2"/>
       <c r="B412" s="2"/>
-      <c r="C412" s="7"/>
-      <c r="D412" s="2"/>
+      <c r="C412" s="2"/>
+      <c r="D412" s="7"/>
     </row>
     <row r="413" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" s="2"/>
       <c r="B413" s="2"/>
-      <c r="C413" s="7"/>
-      <c r="D413" s="2"/>
+      <c r="C413" s="2"/>
+      <c r="D413" s="7"/>
     </row>
     <row r="414" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" s="2"/>
       <c r="B414" s="2"/>
-      <c r="C414" s="7"/>
-      <c r="D414" s="2"/>
+      <c r="C414" s="2"/>
+      <c r="D414" s="7"/>
     </row>
     <row r="415" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" s="2"/>
       <c r="B415" s="2"/>
-      <c r="C415" s="7"/>
-      <c r="D415" s="2"/>
+      <c r="C415" s="2"/>
+      <c r="D415" s="7"/>
     </row>
     <row r="416" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" s="2"/>
       <c r="B416" s="2"/>
-      <c r="C416" s="7"/>
-      <c r="D416" s="2"/>
+      <c r="C416" s="2"/>
+      <c r="D416" s="7"/>
     </row>
     <row r="417" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" s="2"/>
       <c r="B417" s="2"/>
-      <c r="C417" s="7"/>
-      <c r="D417" s="2"/>
+      <c r="C417" s="2"/>
+      <c r="D417" s="7"/>
     </row>
     <row r="418" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" s="2"/>
       <c r="B418" s="2"/>
-      <c r="C418" s="7"/>
-      <c r="D418" s="2"/>
+      <c r="C418" s="2"/>
+      <c r="D418" s="7"/>
     </row>
     <row r="419" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" s="2"/>
       <c r="B419" s="2"/>
-      <c r="C419" s="7"/>
-      <c r="D419" s="2"/>
+      <c r="C419" s="2"/>
+      <c r="D419" s="7"/>
     </row>
     <row r="420" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" s="2"/>
       <c r="B420" s="2"/>
-      <c r="C420" s="7"/>
-      <c r="D420" s="2"/>
+      <c r="C420" s="2"/>
+      <c r="D420" s="7"/>
     </row>
     <row r="421" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" s="2"/>
       <c r="B421" s="2"/>
-      <c r="C421" s="7"/>
-      <c r="D421" s="2"/>
+      <c r="C421" s="2"/>
+      <c r="D421" s="7"/>
     </row>
     <row r="422" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" s="2"/>
       <c r="B422" s="2"/>
-      <c r="C422" s="7"/>
-      <c r="D422" s="2"/>
+      <c r="C422" s="2"/>
+      <c r="D422" s="7"/>
     </row>
     <row r="423" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" s="2"/>
       <c r="B423" s="2"/>
-      <c r="C423" s="7"/>
-      <c r="D423" s="2"/>
+      <c r="C423" s="2"/>
+      <c r="D423" s="7"/>
     </row>
     <row r="424" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" s="2"/>
       <c r="B424" s="2"/>
-      <c r="C424" s="7"/>
-      <c r="D424" s="2"/>
+      <c r="C424" s="2"/>
+      <c r="D424" s="7"/>
     </row>
     <row r="425" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" s="2"/>
       <c r="B425" s="2"/>
-      <c r="C425" s="7"/>
-      <c r="D425" s="2"/>
+      <c r="C425" s="2"/>
+      <c r="D425" s="7"/>
     </row>
     <row r="426" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" s="2"/>
       <c r="B426" s="2"/>
-      <c r="C426" s="7"/>
-      <c r="D426" s="2"/>
+      <c r="C426" s="2"/>
+      <c r="D426" s="7"/>
     </row>
     <row r="427" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" s="2"/>
       <c r="B427" s="2"/>
-      <c r="C427" s="7"/>
-      <c r="D427" s="2"/>
+      <c r="C427" s="2"/>
+      <c r="D427" s="7"/>
     </row>
     <row r="428" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" s="2"/>
       <c r="B428" s="2"/>
-      <c r="C428" s="7"/>
-      <c r="D428" s="2"/>
+      <c r="C428" s="2"/>
+      <c r="D428" s="7"/>
     </row>
     <row r="429" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" s="2"/>
       <c r="B429" s="2"/>
-      <c r="C429" s="7"/>
-      <c r="D429" s="2"/>
+      <c r="C429" s="2"/>
+      <c r="D429" s="7"/>
     </row>
     <row r="430" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" s="2"/>
       <c r="B430" s="2"/>
-      <c r="C430" s="7"/>
-      <c r="D430" s="2"/>
+      <c r="C430" s="2"/>
+      <c r="D430" s="7"/>
     </row>
     <row r="431" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" s="2"/>
       <c r="B431" s="2"/>
-      <c r="C431" s="7"/>
-      <c r="D431" s="2"/>
+      <c r="C431" s="2"/>
+      <c r="D431" s="7"/>
     </row>
     <row r="432" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" s="2"/>
       <c r="B432" s="2"/>
-      <c r="C432" s="7"/>
-      <c r="D432" s="2"/>
+      <c r="C432" s="2"/>
+      <c r="D432" s="7"/>
     </row>
     <row r="433" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" s="2"/>
       <c r="B433" s="2"/>
-      <c r="C433" s="7"/>
-      <c r="D433" s="2"/>
+      <c r="C433" s="2"/>
+      <c r="D433" s="7"/>
     </row>
     <row r="434" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" s="2"/>
       <c r="B434" s="2"/>
-      <c r="C434" s="7"/>
-      <c r="D434" s="2"/>
+      <c r="C434" s="2"/>
+      <c r="D434" s="7"/>
     </row>
     <row r="435" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" s="2"/>
       <c r="B435" s="2"/>
-      <c r="C435" s="7"/>
-      <c r="D435" s="2"/>
+      <c r="C435" s="2"/>
+      <c r="D435" s="7"/>
     </row>
     <row r="436" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" s="2"/>
       <c r="B436" s="2"/>
-      <c r="C436" s="7"/>
-      <c r="D436" s="2"/>
+      <c r="C436" s="2"/>
+      <c r="D436" s="7"/>
     </row>
     <row r="437" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" s="2"/>
       <c r="B437" s="2"/>
-      <c r="C437" s="7"/>
-      <c r="D437" s="2"/>
+      <c r="C437" s="2"/>
+      <c r="D437" s="7"/>
     </row>
     <row r="438" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" s="2"/>
       <c r="B438" s="2"/>
-      <c r="C438" s="7"/>
-      <c r="D438" s="2"/>
+      <c r="C438" s="2"/>
+      <c r="D438" s="7"/>
     </row>
     <row r="439" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" s="2"/>
       <c r="B439" s="2"/>
-      <c r="C439" s="7"/>
-      <c r="D439" s="2"/>
+      <c r="C439" s="2"/>
+      <c r="D439" s="7"/>
     </row>
     <row r="440" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" s="2"/>
       <c r="B440" s="2"/>
-      <c r="C440" s="7"/>
-      <c r="D440" s="2"/>
+      <c r="C440" s="2"/>
+      <c r="D440" s="7"/>
     </row>
     <row r="441" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" s="2"/>
       <c r="B441" s="2"/>
-      <c r="C441" s="7"/>
-      <c r="D441" s="2"/>
+      <c r="C441" s="2"/>
+      <c r="D441" s="7"/>
     </row>
     <row r="442" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" s="2"/>
       <c r="B442" s="2"/>
-      <c r="C442" s="7"/>
-      <c r="D442" s="2"/>
+      <c r="C442" s="2"/>
+      <c r="D442" s="7"/>
     </row>
     <row r="443" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" s="2"/>
       <c r="B443" s="2"/>
-      <c r="C443" s="7"/>
-      <c r="D443" s="2"/>
+      <c r="C443" s="2"/>
+      <c r="D443" s="7"/>
     </row>
     <row r="444" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" s="2"/>
       <c r="B444" s="2"/>
-      <c r="C444" s="7"/>
-      <c r="D444" s="2"/>
+      <c r="C444" s="2"/>
+      <c r="D444" s="7"/>
     </row>
     <row r="445" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" s="2"/>
       <c r="B445" s="2"/>
-      <c r="C445" s="7"/>
-      <c r="D445" s="2"/>
+      <c r="C445" s="2"/>
+      <c r="D445" s="7"/>
     </row>
     <row r="446" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" s="2"/>
       <c r="B446" s="2"/>
-      <c r="C446" s="7"/>
-      <c r="D446" s="2"/>
+      <c r="C446" s="2"/>
+      <c r="D446" s="7"/>
     </row>
     <row r="447" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" s="2"/>
       <c r="B447" s="2"/>
-      <c r="C447" s="7"/>
-      <c r="D447" s="2"/>
+      <c r="C447" s="2"/>
+      <c r="D447" s="7"/>
     </row>
     <row r="448" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" s="2"/>
       <c r="B448" s="2"/>
-      <c r="C448" s="7"/>
-      <c r="D448" s="2"/>
+      <c r="C448" s="2"/>
+      <c r="D448" s="7"/>
     </row>
     <row r="449" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" s="2"/>
       <c r="B449" s="2"/>
-      <c r="C449" s="7"/>
-      <c r="D449" s="2"/>
+      <c r="C449" s="2"/>
+      <c r="D449" s="7"/>
     </row>
     <row r="450" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" s="2"/>
       <c r="B450" s="2"/>
-      <c r="C450" s="7"/>
-      <c r="D450" s="2"/>
+      <c r="C450" s="2"/>
+      <c r="D450" s="7"/>
     </row>
     <row r="451" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" s="2"/>
       <c r="B451" s="2"/>
-      <c r="C451" s="7"/>
-      <c r="D451" s="2"/>
+      <c r="C451" s="2"/>
+      <c r="D451" s="7"/>
     </row>
     <row r="452" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" s="2"/>
       <c r="B452" s="2"/>
-      <c r="C452" s="7"/>
-      <c r="D452" s="2"/>
+      <c r="C452" s="2"/>
+      <c r="D452" s="7"/>
     </row>
     <row r="453" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" s="2"/>
       <c r="B453" s="2"/>
-      <c r="C453" s="7"/>
-      <c r="D453" s="2"/>
+      <c r="C453" s="2"/>
+      <c r="D453" s="7"/>
     </row>
     <row r="454" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" s="2"/>
       <c r="B454" s="2"/>
-      <c r="C454" s="7"/>
-      <c r="D454" s="2"/>
+      <c r="C454" s="2"/>
+      <c r="D454" s="7"/>
     </row>
     <row r="455" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" s="2"/>
       <c r="B455" s="2"/>
-      <c r="C455" s="7"/>
-      <c r="D455" s="2"/>
+      <c r="C455" s="2"/>
+      <c r="D455" s="7"/>
     </row>
     <row r="456" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" s="2"/>
       <c r="B456" s="2"/>
-      <c r="C456" s="7"/>
-      <c r="D456" s="2"/>
+      <c r="C456" s="2"/>
+      <c r="D456" s="7"/>
     </row>
     <row r="457" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" s="2"/>
       <c r="B457" s="2"/>
-      <c r="C457" s="7"/>
-      <c r="D457" s="2"/>
+      <c r="C457" s="2"/>
+      <c r="D457" s="7"/>
     </row>
     <row r="458" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" s="2"/>
       <c r="B458" s="2"/>
-      <c r="C458" s="7"/>
-      <c r="D458" s="2"/>
+      <c r="C458" s="2"/>
+      <c r="D458" s="7"/>
     </row>
     <row r="459" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" s="2"/>
       <c r="B459" s="2"/>
-      <c r="C459" s="7"/>
-      <c r="D459" s="2"/>
+      <c r="C459" s="2"/>
+      <c r="D459" s="7"/>
     </row>
     <row r="460" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" s="2"/>
       <c r="B460" s="2"/>
-      <c r="C460" s="7"/>
-      <c r="D460" s="2"/>
+      <c r="C460" s="2"/>
+      <c r="D460" s="7"/>
     </row>
     <row r="461" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" s="2"/>
       <c r="B461" s="2"/>
-      <c r="C461" s="7"/>
-      <c r="D461" s="2"/>
+      <c r="C461" s="2"/>
+      <c r="D461" s="7"/>
     </row>
     <row r="462" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" s="2"/>
       <c r="B462" s="2"/>
-      <c r="C462" s="7"/>
-      <c r="D462" s="2"/>
+      <c r="C462" s="2"/>
+      <c r="D462" s="7"/>
     </row>
     <row r="463" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" s="2"/>
       <c r="B463" s="2"/>
-      <c r="C463" s="7"/>
-      <c r="D463" s="2"/>
+      <c r="C463" s="2"/>
+      <c r="D463" s="7"/>
     </row>
     <row r="464" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" s="2"/>
       <c r="B464" s="2"/>
-      <c r="C464" s="7"/>
-      <c r="D464" s="2"/>
+      <c r="C464" s="2"/>
+      <c r="D464" s="7"/>
     </row>
     <row r="465" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" s="2"/>
       <c r="B465" s="2"/>
-      <c r="C465" s="7"/>
-      <c r="D465" s="2"/>
+      <c r="C465" s="2"/>
+      <c r="D465" s="7"/>
     </row>
     <row r="466" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" s="2"/>
       <c r="B466" s="2"/>
-      <c r="C466" s="7"/>
-      <c r="D466" s="2"/>
+      <c r="C466" s="2"/>
+      <c r="D466" s="7"/>
     </row>
     <row r="467" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" s="2"/>
       <c r="B467" s="2"/>
-      <c r="C467" s="7"/>
-      <c r="D467" s="2"/>
+      <c r="C467" s="2"/>
+      <c r="D467" s="7"/>
     </row>
     <row r="468" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" s="2"/>
       <c r="B468" s="2"/>
-      <c r="C468" s="7"/>
-      <c r="D468" s="2"/>
+      <c r="C468" s="2"/>
+      <c r="D468" s="7"/>
     </row>
     <row r="469" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" s="2"/>
       <c r="B469" s="2"/>
-      <c r="C469" s="7"/>
-      <c r="D469" s="2"/>
+      <c r="C469" s="2"/>
+      <c r="D469" s="7"/>
     </row>
     <row r="470" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" s="2"/>
       <c r="B470" s="2"/>
-      <c r="C470" s="7"/>
-      <c r="D470" s="2"/>
+      <c r="C470" s="2"/>
+      <c r="D470" s="7"/>
     </row>
     <row r="471" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" s="2"/>
       <c r="B471" s="2"/>
-      <c r="C471" s="7"/>
-      <c r="D471" s="2"/>
+      <c r="C471" s="2"/>
+      <c r="D471" s="7"/>
     </row>
     <row r="472" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" s="2"/>
       <c r="B472" s="2"/>
-      <c r="C472" s="7"/>
-      <c r="D472" s="2"/>
+      <c r="C472" s="2"/>
+      <c r="D472" s="7"/>
     </row>
     <row r="473" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" s="2"/>
       <c r="B473" s="2"/>
-      <c r="C473" s="7"/>
-      <c r="D473" s="2"/>
+      <c r="C473" s="2"/>
+      <c r="D473" s="7"/>
     </row>
     <row r="474" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" s="2"/>
       <c r="B474" s="2"/>
-      <c r="C474" s="7"/>
-      <c r="D474" s="2"/>
+      <c r="C474" s="2"/>
+      <c r="D474" s="7"/>
     </row>
     <row r="475" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" s="2"/>
       <c r="B475" s="2"/>
-      <c r="C475" s="7"/>
-      <c r="D475" s="2"/>
+      <c r="C475" s="2"/>
+      <c r="D475" s="7"/>
     </row>
     <row r="476" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" s="2"/>
       <c r="B476" s="2"/>
-      <c r="C476" s="7"/>
-      <c r="D476" s="2"/>
+      <c r="C476" s="2"/>
+      <c r="D476" s="7"/>
     </row>
     <row r="477" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" s="2"/>
       <c r="B477" s="2"/>
-      <c r="C477" s="7"/>
-      <c r="D477" s="2"/>
+      <c r="C477" s="2"/>
+      <c r="D477" s="7"/>
     </row>
     <row r="478" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A478" s="2"/>
       <c r="B478" s="2"/>
-      <c r="C478" s="7"/>
-      <c r="D478" s="2"/>
+      <c r="C478" s="2"/>
+      <c r="D478" s="7"/>
     </row>
     <row r="479" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A479" s="2"/>
       <c r="B479" s="2"/>
-      <c r="C479" s="7"/>
-      <c r="D479" s="2"/>
+      <c r="C479" s="2"/>
+      <c r="D479" s="7"/>
     </row>
     <row r="480" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A480" s="2"/>
       <c r="B480" s="2"/>
-      <c r="C480" s="7"/>
-      <c r="D480" s="2"/>
+      <c r="C480" s="2"/>
+      <c r="D480" s="7"/>
     </row>
     <row r="481" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" s="2"/>
       <c r="B481" s="2"/>
-      <c r="C481" s="7"/>
-      <c r="D481" s="2"/>
+      <c r="C481" s="2"/>
+      <c r="D481" s="7"/>
     </row>
     <row r="482" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" s="2"/>
       <c r="B482" s="2"/>
-      <c r="C482" s="7"/>
-      <c r="D482" s="2"/>
+      <c r="C482" s="2"/>
+      <c r="D482" s="7"/>
     </row>
     <row r="483" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A483" s="2"/>
       <c r="B483" s="2"/>
-      <c r="C483" s="7"/>
-      <c r="D483" s="2"/>
+      <c r="C483" s="2"/>
+      <c r="D483" s="7"/>
     </row>
     <row r="484" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A484" s="2"/>
       <c r="B484" s="2"/>
-      <c r="C484" s="7"/>
-      <c r="D484" s="2"/>
+      <c r="C484" s="2"/>
+      <c r="D484" s="7"/>
     </row>
     <row r="485" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" s="2"/>
       <c r="B485" s="2"/>
-      <c r="C485" s="7"/>
-      <c r="D485" s="2"/>
+      <c r="C485" s="2"/>
+      <c r="D485" s="7"/>
     </row>
     <row r="486" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" s="2"/>
       <c r="B486" s="2"/>
-      <c r="C486" s="7"/>
-      <c r="D486" s="2"/>
+      <c r="C486" s="2"/>
+      <c r="D486" s="7"/>
     </row>
     <row r="487" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" s="2"/>
       <c r="B487" s="2"/>
-      <c r="C487" s="7"/>
-      <c r="D487" s="2"/>
+      <c r="C487" s="2"/>
+      <c r="D487" s="7"/>
     </row>
     <row r="488" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" s="2"/>
       <c r="B488" s="2"/>
-      <c r="C488" s="7"/>
-      <c r="D488" s="2"/>
+      <c r="C488" s="2"/>
+      <c r="D488" s="7"/>
     </row>
     <row r="489" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" s="2"/>
       <c r="B489" s="2"/>
-      <c r="C489" s="7"/>
-      <c r="D489" s="2"/>
+      <c r="C489" s="2"/>
+      <c r="D489" s="7"/>
     </row>
     <row r="490" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" s="2"/>
       <c r="B490" s="2"/>
-      <c r="C490" s="7"/>
-      <c r="D490" s="2"/>
+      <c r="C490" s="2"/>
+      <c r="D490" s="7"/>
     </row>
     <row r="491" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" s="2"/>
       <c r="B491" s="2"/>
-      <c r="C491" s="7"/>
-      <c r="D491" s="2"/>
+      <c r="C491" s="2"/>
+      <c r="D491" s="7"/>
     </row>
     <row r="492" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" s="2"/>
       <c r="B492" s="2"/>
-      <c r="C492" s="7"/>
-      <c r="D492" s="2"/>
+      <c r="C492" s="2"/>
+      <c r="D492" s="7"/>
     </row>
     <row r="493" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" s="2"/>
       <c r="B493" s="2"/>
-      <c r="C493" s="7"/>
-      <c r="D493" s="2"/>
+      <c r="C493" s="2"/>
+      <c r="D493" s="7"/>
     </row>
     <row r="494" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" s="2"/>
       <c r="B494" s="2"/>
-      <c r="C494" s="7"/>
-      <c r="D494" s="2"/>
+      <c r="C494" s="2"/>
+      <c r="D494" s="7"/>
     </row>
     <row r="495" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" s="2"/>
       <c r="B495" s="2"/>
-      <c r="C495" s="7"/>
-      <c r="D495" s="2"/>
+      <c r="C495" s="2"/>
+      <c r="D495" s="7"/>
     </row>
     <row r="496" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A496" s="2"/>
       <c r="B496" s="2"/>
-      <c r="C496" s="7"/>
-      <c r="D496" s="2"/>
+      <c r="C496" s="2"/>
+      <c r="D496" s="7"/>
     </row>
     <row r="497" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A497" s="2"/>
       <c r="B497" s="2"/>
-      <c r="C497" s="7"/>
-      <c r="D497" s="2"/>
+      <c r="C497" s="2"/>
+      <c r="D497" s="7"/>
     </row>
     <row r="498" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A498" s="2"/>
       <c r="B498" s="2"/>
-      <c r="C498" s="7"/>
-      <c r="D498" s="2"/>
+      <c r="C498" s="2"/>
+      <c r="D498" s="7"/>
     </row>
     <row r="499" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" s="2"/>
       <c r="B499" s="2"/>
-      <c r="C499" s="7"/>
-      <c r="D499" s="2"/>
+      <c r="C499" s="2"/>
+      <c r="D499" s="7"/>
     </row>
     <row r="500" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A500" s="2"/>
       <c r="B500" s="2"/>
-      <c r="C500" s="7"/>
-      <c r="D500" s="2"/>
+      <c r="C500" s="2"/>
+      <c r="D500" s="7"/>
     </row>
     <row r="501" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" s="2"/>
       <c r="B501" s="2"/>
-      <c r="C501" s="7"/>
-      <c r="D501" s="2"/>
+      <c r="C501" s="2"/>
+      <c r="D501" s="7"/>
     </row>
     <row r="502" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A502" s="2"/>
       <c r="B502" s="2"/>
-      <c r="C502" s="7"/>
-      <c r="D502" s="2"/>
+      <c r="C502" s="2"/>
+      <c r="D502" s="7"/>
     </row>
     <row r="503" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A503" s="2"/>
       <c r="B503" s="2"/>
-      <c r="C503" s="7"/>
-      <c r="D503" s="2"/>
+      <c r="C503" s="2"/>
+      <c r="D503" s="7"/>
     </row>
     <row r="504" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A504" s="2"/>
       <c r="B504" s="2"/>
-      <c r="C504" s="7"/>
-      <c r="D504" s="2"/>
+      <c r="C504" s="2"/>
+      <c r="D504" s="7"/>
     </row>
     <row r="505" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A505" s="2"/>
       <c r="B505" s="2"/>
-      <c r="C505" s="7"/>
-      <c r="D505" s="2"/>
+      <c r="C505" s="2"/>
+      <c r="D505" s="7"/>
     </row>
     <row r="506" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A506" s="2"/>
       <c r="B506" s="2"/>
-      <c r="C506" s="7"/>
-      <c r="D506" s="2"/>
+      <c r="C506" s="2"/>
+      <c r="D506" s="7"/>
     </row>
     <row r="507" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A507" s="2"/>
       <c r="B507" s="2"/>
-      <c r="C507" s="7"/>
-      <c r="D507" s="2"/>
+      <c r="C507" s="2"/>
+      <c r="D507" s="7"/>
     </row>
     <row r="508" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A508" s="2"/>
       <c r="B508" s="2"/>
-      <c r="C508" s="7"/>
-      <c r="D508" s="2"/>
+      <c r="C508" s="2"/>
+      <c r="D508" s="7"/>
     </row>
     <row r="509" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A509" s="2"/>
       <c r="B509" s="2"/>
-      <c r="C509" s="7"/>
-      <c r="D509" s="2"/>
+      <c r="C509" s="2"/>
+      <c r="D509" s="7"/>
     </row>
     <row r="510" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A510" s="2"/>
       <c r="B510" s="2"/>
-      <c r="C510" s="7"/>
-      <c r="D510" s="2"/>
+      <c r="C510" s="2"/>
+      <c r="D510" s="7"/>
     </row>
     <row r="511" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A511" s="2"/>
       <c r="B511" s="2"/>
-      <c r="C511" s="7"/>
-      <c r="D511" s="2"/>
+      <c r="C511" s="2"/>
+      <c r="D511" s="7"/>
     </row>
     <row r="512" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A512" s="2"/>
       <c r="B512" s="2"/>
-      <c r="C512" s="7"/>
-      <c r="D512" s="2"/>
+      <c r="C512" s="2"/>
+      <c r="D512" s="7"/>
     </row>
     <row r="513" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A513" s="2"/>
       <c r="B513" s="2"/>
-      <c r="C513" s="7"/>
-      <c r="D513" s="2"/>
+      <c r="C513" s="2"/>
+      <c r="D513" s="7"/>
     </row>
     <row r="514" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A514" s="2"/>
       <c r="B514" s="2"/>
-      <c r="C514" s="7"/>
-      <c r="D514" s="2"/>
+      <c r="C514" s="2"/>
+      <c r="D514" s="7"/>
     </row>
     <row r="515" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A515" s="2"/>
       <c r="B515" s="2"/>
-      <c r="C515" s="7"/>
-      <c r="D515" s="2"/>
+      <c r="C515" s="2"/>
+      <c r="D515" s="7"/>
     </row>
     <row r="516" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A516" s="2"/>
       <c r="B516" s="2"/>
-      <c r="C516" s="7"/>
-      <c r="D516" s="2"/>
+      <c r="C516" s="2"/>
+      <c r="D516" s="7"/>
     </row>
     <row r="517" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A517" s="2"/>
       <c r="B517" s="2"/>
-      <c r="C517" s="7"/>
-      <c r="D517" s="2"/>
+      <c r="C517" s="2"/>
+      <c r="D517" s="7"/>
     </row>
     <row r="518" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A518" s="2"/>
       <c r="B518" s="2"/>
-      <c r="C518" s="7"/>
-      <c r="D518" s="2"/>
+      <c r="C518" s="2"/>
+      <c r="D518" s="7"/>
     </row>
     <row r="519" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A519" s="2"/>
       <c r="B519" s="2"/>
-      <c r="C519" s="7"/>
-      <c r="D519" s="2"/>
+      <c r="C519" s="2"/>
+      <c r="D519" s="7"/>
     </row>
     <row r="520" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A520" s="2"/>
       <c r="B520" s="2"/>
-      <c r="C520" s="7"/>
-      <c r="D520" s="2"/>
+      <c r="C520" s="2"/>
+      <c r="D520" s="7"/>
     </row>
     <row r="521" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A521" s="2"/>
       <c r="B521" s="2"/>
-      <c r="C521" s="7"/>
-      <c r="D521" s="2"/>
+      <c r="C521" s="2"/>
+      <c r="D521" s="7"/>
     </row>
     <row r="522" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A522" s="2"/>
       <c r="B522" s="2"/>
-      <c r="C522" s="7"/>
-      <c r="D522" s="2"/>
+      <c r="C522" s="2"/>
+      <c r="D522" s="7"/>
     </row>
     <row r="523" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A523" s="2"/>
       <c r="B523" s="2"/>
-      <c r="C523" s="7"/>
-      <c r="D523" s="2"/>
+      <c r="C523" s="2"/>
+      <c r="D523" s="7"/>
     </row>
     <row r="524" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A524" s="2"/>
       <c r="B524" s="2"/>
-      <c r="C524" s="7"/>
-      <c r="D524" s="2"/>
+      <c r="C524" s="2"/>
+      <c r="D524" s="7"/>
     </row>
     <row r="525" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A525" s="2"/>
       <c r="B525" s="2"/>
-      <c r="C525" s="7"/>
-      <c r="D525" s="2"/>
+      <c r="C525" s="2"/>
+      <c r="D525" s="7"/>
     </row>
     <row r="526" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A526" s="2"/>
       <c r="B526" s="2"/>
-      <c r="C526" s="7"/>
-      <c r="D526" s="2"/>
+      <c r="C526" s="2"/>
+      <c r="D526" s="7"/>
     </row>
     <row r="527" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A527" s="2"/>
       <c r="B527" s="2"/>
-      <c r="C527" s="7"/>
-      <c r="D527" s="2"/>
+      <c r="C527" s="2"/>
+      <c r="D527" s="7"/>
     </row>
     <row r="528" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A528" s="2"/>
       <c r="B528" s="2"/>
-      <c r="C528" s="7"/>
-      <c r="D528" s="2"/>
+      <c r="C528" s="2"/>
+      <c r="D528" s="7"/>
     </row>
     <row r="529" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A529" s="2"/>
       <c r="B529" s="2"/>
-      <c r="C529" s="7"/>
-      <c r="D529" s="2"/>
+      <c r="C529" s="2"/>
+      <c r="D529" s="7"/>
     </row>
     <row r="530" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A530" s="2"/>
       <c r="B530" s="2"/>
-      <c r="C530" s="7"/>
-      <c r="D530" s="2"/>
+      <c r="C530" s="2"/>
+      <c r="D530" s="7"/>
     </row>
     <row r="531" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A531" s="2"/>
       <c r="B531" s="2"/>
-      <c r="C531" s="7"/>
-      <c r="D531" s="2"/>
+      <c r="C531" s="2"/>
+      <c r="D531" s="7"/>
     </row>
     <row r="532" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A532" s="2"/>
       <c r="B532" s="2"/>
-      <c r="C532" s="7"/>
-      <c r="D532" s="2"/>
+      <c r="C532" s="2"/>
+      <c r="D532" s="7"/>
     </row>
     <row r="533" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A533" s="2"/>
       <c r="B533" s="2"/>
-      <c r="C533" s="7"/>
-      <c r="D533" s="2"/>
+      <c r="C533" s="2"/>
+      <c r="D533" s="7"/>
     </row>
     <row r="534" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A534" s="2"/>
       <c r="B534" s="2"/>
-      <c r="C534" s="7"/>
-      <c r="D534" s="2"/>
+      <c r="C534" s="2"/>
+      <c r="D534" s="7"/>
     </row>
     <row r="535" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A535" s="2"/>
       <c r="B535" s="2"/>
-      <c r="C535" s="7"/>
-      <c r="D535" s="2"/>
+      <c r="C535" s="2"/>
+      <c r="D535" s="7"/>
     </row>
     <row r="536" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A536" s="2"/>
       <c r="B536" s="2"/>
-      <c r="C536" s="7"/>
-      <c r="D536" s="2"/>
+      <c r="C536" s="2"/>
+      <c r="D536" s="7"/>
     </row>
     <row r="537" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A537" s="2"/>
       <c r="B537" s="2"/>
-      <c r="C537" s="7"/>
-      <c r="D537" s="2"/>
+      <c r="C537" s="2"/>
+      <c r="D537" s="7"/>
     </row>
     <row r="538" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A538" s="2"/>
       <c r="B538" s="2"/>
-      <c r="C538" s="7"/>
-      <c r="D538" s="2"/>
+      <c r="C538" s="2"/>
+      <c r="D538" s="7"/>
     </row>
     <row r="539" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A539" s="2"/>
       <c r="B539" s="2"/>
-      <c r="C539" s="7"/>
-      <c r="D539" s="2"/>
+      <c r="C539" s="2"/>
+      <c r="D539" s="7"/>
     </row>
     <row r="540" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A540" s="2"/>
       <c r="B540" s="2"/>
-      <c r="C540" s="7"/>
-      <c r="D540" s="2"/>
+      <c r="C540" s="2"/>
+      <c r="D540" s="7"/>
     </row>
     <row r="541" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A541" s="2"/>
       <c r="B541" s="2"/>
-      <c r="C541" s="7"/>
-      <c r="D541" s="2"/>
+      <c r="C541" s="2"/>
+      <c r="D541" s="7"/>
     </row>
     <row r="542" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A542" s="2"/>
       <c r="B542" s="2"/>
-      <c r="C542" s="7"/>
-      <c r="D542" s="2"/>
+      <c r="C542" s="2"/>
+      <c r="D542" s="7"/>
     </row>
     <row r="543" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A543" s="2"/>
       <c r="B543" s="2"/>
-      <c r="C543" s="7"/>
-      <c r="D543" s="2"/>
+      <c r="C543" s="2"/>
+      <c r="D543" s="7"/>
     </row>
     <row r="544" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A544" s="2"/>
       <c r="B544" s="2"/>
-      <c r="C544" s="7"/>
-      <c r="D544" s="2"/>
+      <c r="C544" s="2"/>
+      <c r="D544" s="7"/>
     </row>
     <row r="545" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A545" s="2"/>
       <c r="B545" s="2"/>
-      <c r="C545" s="7"/>
-      <c r="D545" s="2"/>
+      <c r="C545" s="2"/>
+      <c r="D545" s="7"/>
     </row>
     <row r="546" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A546" s="2"/>
       <c r="B546" s="2"/>
-      <c r="C546" s="7"/>
-      <c r="D546" s="2"/>
+      <c r="C546" s="2"/>
+      <c r="D546" s="7"/>
     </row>
     <row r="547" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A547" s="2"/>
       <c r="B547" s="2"/>
-      <c r="C547" s="7"/>
-      <c r="D547" s="2"/>
+      <c r="C547" s="2"/>
+      <c r="D547" s="7"/>
     </row>
     <row r="548" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A548" s="2"/>
       <c r="B548" s="2"/>
-      <c r="C548" s="7"/>
-      <c r="D548" s="2"/>
+      <c r="C548" s="2"/>
+      <c r="D548" s="7"/>
     </row>
     <row r="549" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A549" s="2"/>
       <c r="B549" s="2"/>
-      <c r="C549" s="7"/>
-      <c r="D549" s="2"/>
+      <c r="C549" s="2"/>
+      <c r="D549" s="7"/>
     </row>
     <row r="550" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A550" s="2"/>
       <c r="B550" s="2"/>
-      <c r="C550" s="7"/>
-      <c r="D550" s="2"/>
+      <c r="C550" s="2"/>
+      <c r="D550" s="7"/>
     </row>
     <row r="551" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A551" s="2"/>
       <c r="B551" s="2"/>
-      <c r="C551" s="7"/>
-      <c r="D551" s="2"/>
+      <c r="C551" s="2"/>
+      <c r="D551" s="7"/>
     </row>
     <row r="552" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A552" s="2"/>
       <c r="B552" s="2"/>
-      <c r="C552" s="7"/>
-      <c r="D552" s="2"/>
+      <c r="C552" s="2"/>
+      <c r="D552" s="7"/>
     </row>
     <row r="553" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A553" s="2"/>
       <c r="B553" s="2"/>
-      <c r="C553" s="7"/>
-      <c r="D553" s="2"/>
+      <c r="C553" s="2"/>
+      <c r="D553" s="7"/>
     </row>
     <row r="554" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A554" s="2"/>
       <c r="B554" s="2"/>
-      <c r="C554" s="7"/>
-      <c r="D554" s="2"/>
+      <c r="C554" s="2"/>
+      <c r="D554" s="7"/>
     </row>
     <row r="555" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A555" s="2"/>
       <c r="B555" s="2"/>
-      <c r="C555" s="7"/>
-      <c r="D555" s="2"/>
+      <c r="C555" s="2"/>
+      <c r="D555" s="7"/>
     </row>
     <row r="556" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A556" s="2"/>
       <c r="B556" s="2"/>
-      <c r="C556" s="7"/>
-      <c r="D556" s="2"/>
+      <c r="C556" s="2"/>
+      <c r="D556" s="7"/>
     </row>
     <row r="557" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A557" s="2"/>
       <c r="B557" s="2"/>
-      <c r="C557" s="7"/>
-      <c r="D557" s="2"/>
+      <c r="C557" s="2"/>
+      <c r="D557" s="7"/>
     </row>
     <row r="558" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A558" s="2"/>
       <c r="B558" s="2"/>
-      <c r="C558" s="7"/>
-      <c r="D558" s="2"/>
+      <c r="C558" s="2"/>
+      <c r="D558" s="7"/>
     </row>
     <row r="559" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A559" s="2"/>
       <c r="B559" s="2"/>
-      <c r="C559" s="7"/>
-      <c r="D559" s="2"/>
+      <c r="C559" s="2"/>
+      <c r="D559" s="7"/>
     </row>
     <row r="560" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A560" s="2"/>
       <c r="B560" s="2"/>
-      <c r="C560" s="7"/>
-      <c r="D560" s="2"/>
+      <c r="C560" s="2"/>
+      <c r="D560" s="7"/>
     </row>
     <row r="561" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A561" s="2"/>
       <c r="B561" s="2"/>
-      <c r="C561" s="7"/>
-      <c r="D561" s="2"/>
+      <c r="C561" s="2"/>
+      <c r="D561" s="7"/>
     </row>
     <row r="562" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A562" s="2"/>
       <c r="B562" s="2"/>
-      <c r="C562" s="7"/>
-      <c r="D562" s="2"/>
+      <c r="C562" s="2"/>
+      <c r="D562" s="7"/>
     </row>
     <row r="563" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A563" s="2"/>
       <c r="B563" s="2"/>
-      <c r="C563" s="7"/>
-      <c r="D563" s="2"/>
+      <c r="C563" s="2"/>
+      <c r="D563" s="7"/>
     </row>
     <row r="564" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A564" s="2"/>
       <c r="B564" s="2"/>
-      <c r="C564" s="7"/>
-      <c r="D564" s="2"/>
+      <c r="C564" s="2"/>
+      <c r="D564" s="7"/>
     </row>
     <row r="565" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A565" s="2"/>
       <c r="B565" s="2"/>
-      <c r="C565" s="7"/>
-      <c r="D565" s="2"/>
+      <c r="C565" s="2"/>
+      <c r="D565" s="7"/>
     </row>
     <row r="566" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A566" s="2"/>
       <c r="B566" s="2"/>
-      <c r="C566" s="7"/>
-      <c r="D566" s="2"/>
+      <c r="C566" s="2"/>
+      <c r="D566" s="7"/>
     </row>
     <row r="567" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A567" s="2"/>
       <c r="B567" s="2"/>
-      <c r="C567" s="7"/>
-      <c r="D567" s="2"/>
+      <c r="C567" s="2"/>
+      <c r="D567" s="7"/>
     </row>
     <row r="568" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A568" s="2"/>
       <c r="B568" s="2"/>
-      <c r="C568" s="7"/>
-      <c r="D568" s="2"/>
+      <c r="C568" s="2"/>
+      <c r="D568" s="7"/>
     </row>
     <row r="569" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A569" s="2"/>
       <c r="B569" s="2"/>
-      <c r="C569" s="7"/>
-      <c r="D569" s="2"/>
+      <c r="C569" s="2"/>
+      <c r="D569" s="7"/>
     </row>
     <row r="570" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A570" s="2"/>
       <c r="B570" s="2"/>
-      <c r="C570" s="7"/>
-      <c r="D570" s="2"/>
+      <c r="C570" s="2"/>
+      <c r="D570" s="7"/>
     </row>
     <row r="571" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A571" s="2"/>
       <c r="B571" s="2"/>
-      <c r="C571" s="7"/>
-      <c r="D571" s="2"/>
+      <c r="C571" s="2"/>
+      <c r="D571" s="7"/>
     </row>
     <row r="572" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A572" s="2"/>
       <c r="B572" s="2"/>
-      <c r="C572" s="7"/>
-      <c r="D572" s="2"/>
+      <c r="C572" s="2"/>
+      <c r="D572" s="7"/>
     </row>
     <row r="573" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A573" s="2"/>
       <c r="B573" s="2"/>
-      <c r="C573" s="7"/>
-      <c r="D573" s="2"/>
+      <c r="C573" s="2"/>
+      <c r="D573" s="7"/>
     </row>
     <row r="574" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A574" s="2"/>
       <c r="B574" s="2"/>
-      <c r="C574" s="7"/>
-      <c r="D574" s="2"/>
+      <c r="C574" s="2"/>
+      <c r="D574" s="7"/>
     </row>
     <row r="575" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A575" s="2"/>
       <c r="B575" s="2"/>
-      <c r="C575" s="7"/>
-      <c r="D575" s="2"/>
+      <c r="C575" s="2"/>
+      <c r="D575" s="7"/>
     </row>
     <row r="576" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A576" s="2"/>
       <c r="B576" s="2"/>
-      <c r="C576" s="7"/>
-      <c r="D576" s="2"/>
+      <c r="C576" s="2"/>
+      <c r="D576" s="7"/>
     </row>
     <row r="577" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A577" s="2"/>
       <c r="B577" s="2"/>
-      <c r="C577" s="7"/>
-      <c r="D577" s="2"/>
+      <c r="C577" s="2"/>
+      <c r="D577" s="7"/>
     </row>
     <row r="578" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A578" s="2"/>
       <c r="B578" s="2"/>
-      <c r="C578" s="7"/>
-      <c r="D578" s="2"/>
+      <c r="C578" s="2"/>
+      <c r="D578" s="7"/>
     </row>
     <row r="579" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A579" s="2"/>
       <c r="B579" s="2"/>
-      <c r="C579" s="7"/>
-      <c r="D579" s="2"/>
+      <c r="C579" s="2"/>
+      <c r="D579" s="7"/>
     </row>
     <row r="580" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A580" s="2"/>
       <c r="B580" s="2"/>
-      <c r="C580" s="7"/>
-      <c r="D580" s="2"/>
+      <c r="C580" s="2"/>
+      <c r="D580" s="7"/>
     </row>
     <row r="581" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A581" s="2"/>
       <c r="B581" s="2"/>
-      <c r="C581" s="7"/>
-      <c r="D581" s="2"/>
+      <c r="C581" s="2"/>
+      <c r="D581" s="7"/>
     </row>
     <row r="582" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A582" s="2"/>
       <c r="B582" s="2"/>
-      <c r="C582" s="7"/>
-      <c r="D582" s="2"/>
+      <c r="C582" s="2"/>
+      <c r="D582" s="7"/>
     </row>
     <row r="583" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A583" s="2"/>
       <c r="B583" s="2"/>
-      <c r="C583" s="7"/>
-      <c r="D583" s="2"/>
+      <c r="C583" s="2"/>
+      <c r="D583" s="7"/>
     </row>
     <row r="584" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A584" s="2"/>
       <c r="B584" s="2"/>
-      <c r="C584" s="7"/>
-      <c r="D584" s="2"/>
+      <c r="C584" s="2"/>
+      <c r="D584" s="7"/>
     </row>
     <row r="585" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A585" s="2"/>
       <c r="B585" s="2"/>
-      <c r="C585" s="7"/>
-      <c r="D585" s="2"/>
+      <c r="C585" s="2"/>
+      <c r="D585" s="7"/>
     </row>
     <row r="586" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A586" s="2"/>
       <c r="B586" s="2"/>
-      <c r="C586" s="7"/>
-      <c r="D586" s="2"/>
+      <c r="C586" s="2"/>
+      <c r="D586" s="7"/>
     </row>
     <row r="587" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A587" s="2"/>
       <c r="B587" s="2"/>
-      <c r="C587" s="7"/>
-      <c r="D587" s="2"/>
+      <c r="C587" s="2"/>
+      <c r="D587" s="7"/>
     </row>
     <row r="588" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A588" s="2"/>
       <c r="B588" s="2"/>
-      <c r="C588" s="7"/>
-      <c r="D588" s="2"/>
+      <c r="C588" s="2"/>
+      <c r="D588" s="7"/>
     </row>
     <row r="589" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A589" s="2"/>
       <c r="B589" s="2"/>
-      <c r="C589" s="7"/>
-      <c r="D589" s="2"/>
+      <c r="C589" s="2"/>
+      <c r="D589" s="7"/>
     </row>
     <row r="590" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A590" s="2"/>
       <c r="B590" s="2"/>
-      <c r="C590" s="7"/>
-      <c r="D590" s="2"/>
+      <c r="C590" s="2"/>
+      <c r="D590" s="7"/>
     </row>
     <row r="591" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A591" s="2"/>
       <c r="B591" s="2"/>
-      <c r="C591" s="7"/>
-      <c r="D591" s="2"/>
+      <c r="C591" s="2"/>
+      <c r="D591" s="7"/>
     </row>
     <row r="592" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A592" s="2"/>
       <c r="B592" s="2"/>
-      <c r="C592" s="7"/>
-      <c r="D592" s="2"/>
+      <c r="C592" s="2"/>
+      <c r="D592" s="7"/>
     </row>
     <row r="593" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A593" s="2"/>
       <c r="B593" s="2"/>
-      <c r="C593" s="7"/>
-      <c r="D593" s="2"/>
+      <c r="C593" s="2"/>
+      <c r="D593" s="7"/>
     </row>
     <row r="594" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A594" s="2"/>
       <c r="B594" s="2"/>
-      <c r="C594" s="7"/>
-      <c r="D594" s="2"/>
+      <c r="C594" s="2"/>
+      <c r="D594" s="7"/>
     </row>
     <row r="595" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A595" s="2"/>
       <c r="B595" s="2"/>
-      <c r="C595" s="7"/>
-      <c r="D595" s="2"/>
+      <c r="C595" s="2"/>
+      <c r="D595" s="7"/>
     </row>
     <row r="596" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A596" s="2"/>
       <c r="B596" s="2"/>
-      <c r="C596" s="7"/>
-      <c r="D596" s="2"/>
+      <c r="C596" s="2"/>
+      <c r="D596" s="7"/>
     </row>
     <row r="597" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A597" s="2"/>
       <c r="B597" s="2"/>
-      <c r="C597" s="7"/>
-      <c r="D597" s="2"/>
+      <c r="C597" s="2"/>
+      <c r="D597" s="7"/>
     </row>
     <row r="598" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A598" s="2"/>
       <c r="B598" s="2"/>
-      <c r="C598" s="7"/>
-      <c r="D598" s="2"/>
+      <c r="C598" s="2"/>
+      <c r="D598" s="7"/>
     </row>
     <row r="599" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A599" s="2"/>
       <c r="B599" s="2"/>
-      <c r="C599" s="7"/>
-      <c r="D599" s="2"/>
+      <c r="C599" s="2"/>
+      <c r="D599" s="7"/>
     </row>
     <row r="600" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A600" s="2"/>
       <c r="B600" s="2"/>
-      <c r="C600" s="7"/>
-      <c r="D600" s="2"/>
+      <c r="C600" s="2"/>
+      <c r="D600" s="7"/>
     </row>
     <row r="601" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A601" s="2"/>
       <c r="B601" s="2"/>
-      <c r="C601" s="7"/>
-      <c r="D601" s="2"/>
+      <c r="C601" s="2"/>
+      <c r="D601" s="7"/>
     </row>
     <row r="602" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A602" s="2"/>
       <c r="B602" s="2"/>
-      <c r="C602" s="7"/>
-      <c r="D602" s="2"/>
+      <c r="C602" s="2"/>
+      <c r="D602" s="7"/>
     </row>
     <row r="603" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A603" s="2"/>
       <c r="B603" s="2"/>
-      <c r="C603" s="7"/>
-      <c r="D603" s="2"/>
+      <c r="C603" s="2"/>
+      <c r="D603" s="7"/>
     </row>
     <row r="604" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A604" s="2"/>
       <c r="B604" s="2"/>
-      <c r="C604" s="7"/>
-      <c r="D604" s="2"/>
+      <c r="C604" s="2"/>
+      <c r="D604" s="7"/>
     </row>
     <row r="605" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A605" s="2"/>
       <c r="B605" s="2"/>
-      <c r="C605" s="7"/>
-      <c r="D605" s="2"/>
+      <c r="C605" s="2"/>
+      <c r="D605" s="7"/>
     </row>
     <row r="606" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A606" s="2"/>
       <c r="B606" s="2"/>
-      <c r="C606" s="7"/>
-      <c r="D606" s="2"/>
+      <c r="C606" s="2"/>
+      <c r="D606" s="7"/>
     </row>
     <row r="607" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A607" s="2"/>
       <c r="B607" s="2"/>
-      <c r="C607" s="7"/>
-      <c r="D607" s="2"/>
+      <c r="C607" s="2"/>
+      <c r="D607" s="7"/>
     </row>
     <row r="608" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A608" s="2"/>
       <c r="B608" s="2"/>
-      <c r="C608" s="7"/>
-      <c r="D608" s="2"/>
+      <c r="C608" s="2"/>
+      <c r="D608" s="7"/>
     </row>
     <row r="609" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A609" s="2"/>
       <c r="B609" s="2"/>
-      <c r="C609" s="7"/>
-      <c r="D609" s="2"/>
+      <c r="C609" s="2"/>
+      <c r="D609" s="7"/>
     </row>
     <row r="610" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A610" s="2"/>
       <c r="B610" s="2"/>
-      <c r="C610" s="7"/>
-      <c r="D610" s="2"/>
+      <c r="C610" s="2"/>
+      <c r="D610" s="7"/>
     </row>
     <row r="611" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A611" s="2"/>
       <c r="B611" s="2"/>
-      <c r="C611" s="7"/>
-      <c r="D611" s="2"/>
+      <c r="C611" s="2"/>
+      <c r="D611" s="7"/>
     </row>
     <row r="612" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A612" s="2"/>
       <c r="B612" s="2"/>
-      <c r="C612" s="7"/>
-      <c r="D612" s="2"/>
+      <c r="C612" s="2"/>
+      <c r="D612" s="7"/>
     </row>
     <row r="613" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A613" s="2"/>
       <c r="B613" s="2"/>
-      <c r="C613" s="7"/>
-      <c r="D613" s="2"/>
+      <c r="C613" s="2"/>
+      <c r="D613" s="7"/>
     </row>
     <row r="614" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A614" s="2"/>
       <c r="B614" s="2"/>
-      <c r="C614" s="7"/>
-      <c r="D614" s="2"/>
+      <c r="C614" s="2"/>
+      <c r="D614" s="7"/>
     </row>
     <row r="615" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A615" s="2"/>
       <c r="B615" s="2"/>
-      <c r="C615" s="7"/>
-      <c r="D615" s="2"/>
+      <c r="C615" s="2"/>
+      <c r="D615" s="7"/>
     </row>
     <row r="616" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A616" s="2"/>
       <c r="B616" s="2"/>
-      <c r="C616" s="7"/>
-      <c r="D616" s="2"/>
+      <c r="C616" s="2"/>
+      <c r="D616" s="7"/>
     </row>
     <row r="617" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A617" s="2"/>
       <c r="B617" s="2"/>
-      <c r="C617" s="7"/>
-      <c r="D617" s="2"/>
+      <c r="C617" s="2"/>
+      <c r="D617" s="7"/>
     </row>
     <row r="618" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A618" s="2"/>
       <c r="B618" s="2"/>
-      <c r="C618" s="7"/>
-      <c r="D618" s="2"/>
+      <c r="C618" s="2"/>
+      <c r="D618" s="7"/>
     </row>
     <row r="619" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A619" s="2"/>
       <c r="B619" s="2"/>
-      <c r="C619" s="7"/>
-      <c r="D619" s="2"/>
+      <c r="C619" s="2"/>
+      <c r="D619" s="7"/>
     </row>
     <row r="620" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A620" s="2"/>
       <c r="B620" s="2"/>
-      <c r="C620" s="7"/>
-      <c r="D620" s="2"/>
+      <c r="C620" s="2"/>
+      <c r="D620" s="7"/>
     </row>
     <row r="621" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A621" s="2"/>
       <c r="B621" s="2"/>
-      <c r="C621" s="7"/>
-      <c r="D621" s="2"/>
+      <c r="C621" s="2"/>
+      <c r="D621" s="7"/>
     </row>
     <row r="622" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A622" s="2"/>
       <c r="B622" s="2"/>
-      <c r="C622" s="7"/>
-      <c r="D622" s="2"/>
+      <c r="C622" s="2"/>
+      <c r="D622" s="7"/>
     </row>
     <row r="623" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A623" s="2"/>
       <c r="B623" s="2"/>
-      <c r="C623" s="7"/>
-      <c r="D623" s="2"/>
+      <c r="C623" s="2"/>
+      <c r="D623" s="7"/>
     </row>
     <row r="624" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A624" s="2"/>
       <c r="B624" s="2"/>
-      <c r="C624" s="7"/>
-      <c r="D624" s="2"/>
+      <c r="C624" s="2"/>
+      <c r="D624" s="7"/>
     </row>
     <row r="625" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A625" s="2"/>
       <c r="B625" s="2"/>
-      <c r="C625" s="7"/>
-      <c r="D625" s="2"/>
+      <c r="C625" s="2"/>
+      <c r="D625" s="7"/>
     </row>
     <row r="626" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A626" s="2"/>
       <c r="B626" s="2"/>
-      <c r="C626" s="7"/>
-      <c r="D626" s="2"/>
+      <c r="C626" s="2"/>
+      <c r="D626" s="7"/>
     </row>
     <row r="627" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A627" s="2"/>
       <c r="B627" s="2"/>
-      <c r="C627" s="7"/>
-      <c r="D627" s="2"/>
+      <c r="C627" s="2"/>
+      <c r="D627" s="7"/>
     </row>
     <row r="628" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A628" s="2"/>
       <c r="B628" s="2"/>
-      <c r="C628" s="7"/>
-      <c r="D628" s="2"/>
+      <c r="C628" s="2"/>
+      <c r="D628" s="7"/>
     </row>
     <row r="629" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A629" s="2"/>
       <c r="B629" s="2"/>
-      <c r="C629" s="7"/>
-      <c r="D629" s="2"/>
+      <c r="C629" s="2"/>
+      <c r="D629" s="7"/>
     </row>
     <row r="630" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A630" s="2"/>
       <c r="B630" s="2"/>
-      <c r="C630" s="7"/>
-      <c r="D630" s="2"/>
+      <c r="C630" s="2"/>
+      <c r="D630" s="7"/>
     </row>
     <row r="631" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A631" s="2"/>
       <c r="B631" s="2"/>
-      <c r="C631" s="7"/>
-      <c r="D631" s="2"/>
+      <c r="C631" s="2"/>
+      <c r="D631" s="7"/>
     </row>
     <row r="632" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A632" s="2"/>
       <c r="B632" s="2"/>
-      <c r="C632" s="7"/>
-      <c r="D632" s="2"/>
+      <c r="C632" s="2"/>
+      <c r="D632" s="7"/>
     </row>
     <row r="633" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A633" s="2"/>
       <c r="B633" s="2"/>
-      <c r="C633" s="7"/>
-      <c r="D633" s="2"/>
+      <c r="C633" s="2"/>
+      <c r="D633" s="7"/>
     </row>
     <row r="634" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A634" s="2"/>
       <c r="B634" s="2"/>
-      <c r="C634" s="7"/>
-      <c r="D634" s="2"/>
+      <c r="C634" s="2"/>
+      <c r="D634" s="7"/>
     </row>
     <row r="635" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A635" s="2"/>
       <c r="B635" s="2"/>
-      <c r="C635" s="7"/>
-      <c r="D635" s="2"/>
+      <c r="C635" s="2"/>
+      <c r="D635" s="7"/>
     </row>
     <row r="636" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A636" s="2"/>
       <c r="B636" s="2"/>
-      <c r="C636" s="7"/>
-      <c r="D636" s="2"/>
+      <c r="C636" s="2"/>
+      <c r="D636" s="7"/>
     </row>
     <row r="637" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A637" s="2"/>
       <c r="B637" s="2"/>
-      <c r="C637" s="7"/>
-      <c r="D637" s="2"/>
+      <c r="C637" s="2"/>
+      <c r="D637" s="7"/>
     </row>
     <row r="638" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A638" s="2"/>
       <c r="B638" s="2"/>
-      <c r="C638" s="7"/>
-      <c r="D638" s="2"/>
+      <c r="C638" s="2"/>
+      <c r="D638" s="7"/>
     </row>
     <row r="639" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A639" s="2"/>
       <c r="B639" s="2"/>
-      <c r="C639" s="7"/>
-      <c r="D639" s="2"/>
+      <c r="C639" s="2"/>
+      <c r="D639" s="7"/>
     </row>
     <row r="640" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A640" s="2"/>
       <c r="B640" s="2"/>
-      <c r="C640" s="7"/>
-      <c r="D640" s="2"/>
+      <c r="C640" s="2"/>
+      <c r="D640" s="7"/>
     </row>
     <row r="641" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A641" s="2"/>
       <c r="B641" s="2"/>
-      <c r="C641" s="7"/>
-      <c r="D641" s="2"/>
+      <c r="C641" s="2"/>
+      <c r="D641" s="7"/>
     </row>
     <row r="642" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A642" s="2"/>
       <c r="B642" s="2"/>
-      <c r="C642" s="7"/>
-      <c r="D642" s="2"/>
+      <c r="C642" s="2"/>
+      <c r="D642" s="7"/>
     </row>
     <row r="643" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A643" s="2"/>
       <c r="B643" s="2"/>
-      <c r="C643" s="7"/>
-      <c r="D643" s="2"/>
+      <c r="C643" s="2"/>
+      <c r="D643" s="7"/>
     </row>
     <row r="644" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A644" s="2"/>
       <c r="B644" s="2"/>
-      <c r="C644" s="7"/>
-      <c r="D644" s="2"/>
+      <c r="C644" s="2"/>
+      <c r="D644" s="7"/>
     </row>
     <row r="645" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A645" s="2"/>
       <c r="B645" s="2"/>
-      <c r="C645" s="7"/>
-      <c r="D645" s="2"/>
+      <c r="C645" s="2"/>
+      <c r="D645" s="7"/>
     </row>
     <row r="646" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A646" s="2"/>
       <c r="B646" s="2"/>
-      <c r="C646" s="7"/>
-      <c r="D646" s="2"/>
+      <c r="C646" s="2"/>
+      <c r="D646" s="7"/>
     </row>
     <row r="647" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A647" s="2"/>
       <c r="B647" s="2"/>
-      <c r="C647" s="7"/>
-      <c r="D647" s="2"/>
+      <c r="C647" s="2"/>
+      <c r="D647" s="7"/>
     </row>
     <row r="648" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A648" s="2"/>
       <c r="B648" s="2"/>
-      <c r="C648" s="7"/>
-      <c r="D648" s="2"/>
+      <c r="C648" s="2"/>
+      <c r="D648" s="7"/>
     </row>
     <row r="649" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A649" s="2"/>
       <c r="B649" s="2"/>
-      <c r="C649" s="7"/>
-      <c r="D649" s="2"/>
+      <c r="C649" s="2"/>
+      <c r="D649" s="7"/>
     </row>
     <row r="650" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A650" s="2"/>
       <c r="B650" s="2"/>
-      <c r="C650" s="7"/>
-      <c r="D650" s="2"/>
+      <c r="C650" s="2"/>
+      <c r="D650" s="7"/>
     </row>
     <row r="651" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A651" s="2"/>
       <c r="B651" s="2"/>
-      <c r="C651" s="7"/>
-      <c r="D651" s="2"/>
+      <c r="C651" s="2"/>
+      <c r="D651" s="7"/>
     </row>
     <row r="652" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A652" s="2"/>
       <c r="B652" s="2"/>
-      <c r="C652" s="7"/>
-      <c r="D652" s="2"/>
+      <c r="C652" s="2"/>
+      <c r="D652" s="7"/>
     </row>
     <row r="653" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A653" s="2"/>
       <c r="B653" s="2"/>
-      <c r="C653" s="7"/>
-      <c r="D653" s="2"/>
+      <c r="C653" s="2"/>
+      <c r="D653" s="7"/>
     </row>
     <row r="654" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A654" s="2"/>
       <c r="B654" s="2"/>
-      <c r="C654" s="7"/>
-      <c r="D654" s="2"/>
+      <c r="C654" s="2"/>
+      <c r="D654" s="7"/>
     </row>
     <row r="655" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A655" s="2"/>
       <c r="B655" s="2"/>
-      <c r="C655" s="7"/>
-      <c r="D655" s="2"/>
+      <c r="C655" s="2"/>
+      <c r="D655" s="7"/>
     </row>
     <row r="656" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A656" s="2"/>
       <c r="B656" s="2"/>
-      <c r="C656" s="7"/>
-      <c r="D656" s="2"/>
+      <c r="C656" s="2"/>
+      <c r="D656" s="7"/>
     </row>
     <row r="657" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A657" s="2"/>
       <c r="B657" s="2"/>
-      <c r="C657" s="7"/>
-      <c r="D657" s="2"/>
+      <c r="C657" s="2"/>
+      <c r="D657" s="7"/>
     </row>
     <row r="658" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A658" s="2"/>
       <c r="B658" s="2"/>
-      <c r="C658" s="7"/>
-      <c r="D658" s="2"/>
+      <c r="C658" s="2"/>
+      <c r="D658" s="7"/>
     </row>
     <row r="659" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A659" s="2"/>
       <c r="B659" s="2"/>
-      <c r="C659" s="7"/>
-      <c r="D659" s="2"/>
+      <c r="C659" s="2"/>
+      <c r="D659" s="7"/>
     </row>
     <row r="660" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A660" s="2"/>
       <c r="B660" s="2"/>
-      <c r="C660" s="7"/>
-      <c r="D660" s="2"/>
+      <c r="C660" s="2"/>
+      <c r="D660" s="7"/>
     </row>
     <row r="661" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A661" s="2"/>
       <c r="B661" s="2"/>
-      <c r="C661" s="7"/>
-      <c r="D661" s="2"/>
+      <c r="C661" s="2"/>
+      <c r="D661" s="7"/>
     </row>
     <row r="662" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A662" s="2"/>
       <c r="B662" s="2"/>
-      <c r="C662" s="7"/>
-      <c r="D662" s="2"/>
+      <c r="C662" s="2"/>
+      <c r="D662" s="7"/>
     </row>
     <row r="663" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A663" s="2"/>
       <c r="B663" s="2"/>
-      <c r="C663" s="7"/>
-      <c r="D663" s="2"/>
+      <c r="C663" s="2"/>
+      <c r="D663" s="7"/>
     </row>
     <row r="664" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A664" s="2"/>
       <c r="B664" s="2"/>
-      <c r="C664" s="7"/>
-      <c r="D664" s="2"/>
+      <c r="C664" s="2"/>
+      <c r="D664" s="7"/>
     </row>
     <row r="665" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A665" s="2"/>
       <c r="B665" s="2"/>
-      <c r="C665" s="7"/>
-      <c r="D665" s="2"/>
+      <c r="C665" s="2"/>
+      <c r="D665" s="7"/>
     </row>
     <row r="666" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A666" s="2"/>
       <c r="B666" s="2"/>
-      <c r="C666" s="7"/>
-      <c r="D666" s="2"/>
+      <c r="C666" s="2"/>
+      <c r="D666" s="7"/>
     </row>
     <row r="667" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A667" s="2"/>
       <c r="B667" s="2"/>
-      <c r="C667" s="7"/>
-      <c r="D667" s="2"/>
+      <c r="C667" s="2"/>
+      <c r="D667" s="7"/>
     </row>
     <row r="668" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A668" s="2"/>
       <c r="B668" s="2"/>
-      <c r="C668" s="7"/>
-      <c r="D668" s="2"/>
+      <c r="C668" s="2"/>
+      <c r="D668" s="7"/>
     </row>
     <row r="669" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A669" s="2"/>
       <c r="B669" s="2"/>
-      <c r="C669" s="7"/>
-      <c r="D669" s="2"/>
+      <c r="C669" s="2"/>
+      <c r="D669" s="7"/>
     </row>
     <row r="670" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A670" s="2"/>
       <c r="B670" s="2"/>
-      <c r="C670" s="7"/>
-      <c r="D670" s="2"/>
+      <c r="C670" s="2"/>
+      <c r="D670" s="7"/>
     </row>
     <row r="671" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A671" s="2"/>
       <c r="B671" s="2"/>
-      <c r="C671" s="7"/>
-      <c r="D671" s="2"/>
+      <c r="C671" s="2"/>
+      <c r="D671" s="7"/>
     </row>
     <row r="672" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A672" s="2"/>
       <c r="B672" s="2"/>
-      <c r="C672" s="7"/>
-      <c r="D672" s="2"/>
+      <c r="C672" s="2"/>
+      <c r="D672" s="7"/>
     </row>
     <row r="673" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A673" s="2"/>
       <c r="B673" s="2"/>
-      <c r="C673" s="7"/>
-      <c r="D673" s="2"/>
+      <c r="C673" s="2"/>
+      <c r="D673" s="7"/>
     </row>
     <row r="674" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A674" s="2"/>
       <c r="B674" s="2"/>
-      <c r="C674" s="7"/>
-      <c r="D674" s="2"/>
+      <c r="C674" s="2"/>
+      <c r="D674" s="7"/>
     </row>
     <row r="675" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A675" s="2"/>
       <c r="B675" s="2"/>
-      <c r="C675" s="7"/>
-      <c r="D675" s="2"/>
+      <c r="C675" s="2"/>
+      <c r="D675" s="7"/>
     </row>
     <row r="676" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A676" s="2"/>
       <c r="B676" s="2"/>
-      <c r="C676" s="7"/>
-      <c r="D676" s="2"/>
+      <c r="C676" s="2"/>
+      <c r="D676" s="7"/>
     </row>
     <row r="677" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A677" s="2"/>
       <c r="B677" s="2"/>
-      <c r="C677" s="7"/>
-      <c r="D677" s="2"/>
+      <c r="C677" s="2"/>
+      <c r="D677" s="7"/>
     </row>
     <row r="678" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A678" s="2"/>
       <c r="B678" s="2"/>
-      <c r="C678" s="7"/>
-      <c r="D678" s="2"/>
+      <c r="C678" s="2"/>
+      <c r="D678" s="7"/>
     </row>
     <row r="679" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A679" s="2"/>
       <c r="B679" s="2"/>
-      <c r="C679" s="7"/>
-      <c r="D679" s="2"/>
+      <c r="C679" s="2"/>
+      <c r="D679" s="7"/>
     </row>
     <row r="680" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A680" s="2"/>
       <c r="B680" s="2"/>
-      <c r="C680" s="7"/>
-      <c r="D680" s="2"/>
+      <c r="C680" s="2"/>
+      <c r="D680" s="7"/>
     </row>
     <row r="681" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A681" s="2"/>
       <c r="B681" s="2"/>
-      <c r="C681" s="7"/>
-      <c r="D681" s="2"/>
+      <c r="C681" s="2"/>
+      <c r="D681" s="7"/>
     </row>
     <row r="682" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A682" s="2"/>
       <c r="B682" s="2"/>
-      <c r="C682" s="7"/>
-      <c r="D682" s="2"/>
+      <c r="C682" s="2"/>
+      <c r="D682" s="7"/>
     </row>
     <row r="683" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A683" s="2"/>
       <c r="B683" s="2"/>
-      <c r="C683" s="7"/>
-      <c r="D683" s="2"/>
+      <c r="C683" s="2"/>
+      <c r="D683" s="7"/>
     </row>
     <row r="684" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A684" s="2"/>
       <c r="B684" s="2"/>
-      <c r="C684" s="7"/>
-      <c r="D684" s="2"/>
+      <c r="C684" s="2"/>
+      <c r="D684" s="7"/>
     </row>
     <row r="685" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A685" s="2"/>
       <c r="B685" s="2"/>
-      <c r="C685" s="7"/>
-      <c r="D685" s="2"/>
+      <c r="C685" s="2"/>
+      <c r="D685" s="7"/>
     </row>
     <row r="686" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A686" s="2"/>
       <c r="B686" s="2"/>
-      <c r="C686" s="7"/>
-      <c r="D686" s="2"/>
+      <c r="C686" s="2"/>
+      <c r="D686" s="7"/>
     </row>
     <row r="687" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A687" s="2"/>
       <c r="B687" s="2"/>
-      <c r="C687" s="7"/>
-      <c r="D687" s="2"/>
+      <c r="C687" s="2"/>
+      <c r="D687" s="7"/>
     </row>
     <row r="688" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A688" s="2"/>
       <c r="B688" s="2"/>
-      <c r="C688" s="7"/>
-      <c r="D688" s="2"/>
+      <c r="C688" s="2"/>
+      <c r="D688" s="7"/>
     </row>
     <row r="689" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A689" s="2"/>
       <c r="B689" s="2"/>
-      <c r="C689" s="7"/>
-      <c r="D689" s="2"/>
+      <c r="C689" s="2"/>
+      <c r="D689" s="7"/>
     </row>
     <row r="690" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A690" s="2"/>
       <c r="B690" s="2"/>
-      <c r="C690" s="7"/>
-      <c r="D690" s="2"/>
+      <c r="C690" s="2"/>
+      <c r="D690" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/precios.xlsx
+++ b/precios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linoS\Documents\precios entel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A24621-AE2B-4983-9B2E-B3BD0192DCBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE9E544-DC80-4DC6-8AC2-08F66CBAD56E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,9 +33,6 @@
     <t>sku</t>
   </si>
   <si>
-    <t>precio</t>
-  </si>
-  <si>
     <t>descuento</t>
   </si>
   <si>
@@ -712,6 +709,9 @@
   </si>
   <si>
     <t>INFINIX</t>
+  </si>
+  <si>
+    <t>precio plan</t>
   </si>
 </sst>
 </file>
@@ -1126,18 +1126,18 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>2</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C2" s="4">
         <v>80000</v>
@@ -1148,10 +1148,10 @@
     </row>
     <row r="3" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C3" s="4">
         <v>80000</v>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C4" s="4">
         <v>80000</v>
@@ -1176,10 +1176,10 @@
     </row>
     <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C5" s="4">
         <v>120000</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C6" s="4">
         <v>120000</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C7" s="4">
         <v>120000</v>
@@ -1218,10 +1218,10 @@
     </row>
     <row r="8" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C8" s="4">
         <v>70000</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C9" s="4">
         <v>70000</v>
@@ -1246,10 +1246,10 @@
     </row>
     <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C10" s="4">
         <v>70000</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C11" s="4">
         <v>70000</v>
@@ -1274,10 +1274,10 @@
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C12" s="4">
         <v>110000</v>
@@ -1288,10 +1288,10 @@
     </row>
     <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C13" s="4">
         <v>110000</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="14" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C14" s="4">
         <v>70000</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="15" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C15" s="4">
         <v>70000</v>
@@ -1330,10 +1330,10 @@
     </row>
     <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C16" s="4">
         <v>70000</v>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="17" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C17" s="4">
         <v>100000</v>
@@ -1358,10 +1358,10 @@
     </row>
     <row r="18" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C18" s="4">
         <v>100000</v>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="19" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C19" s="4">
         <v>100000</v>
@@ -1386,10 +1386,10 @@
     </row>
     <row r="20" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C20" s="4">
         <v>100000</v>
@@ -1400,10 +1400,10 @@
     </row>
     <row r="21" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C21" s="4">
         <v>130000</v>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C22" s="4">
         <v>130000</v>
@@ -1428,10 +1428,10 @@
     </row>
     <row r="23" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C23" s="4">
         <v>130000</v>
@@ -1442,10 +1442,10 @@
     </row>
     <row r="24" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C24" s="4">
         <v>130000</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="25" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C25" s="4">
         <v>120000</v>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C26" s="4">
         <v>120000</v>
@@ -1484,10 +1484,10 @@
     </row>
     <row r="27" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C27" s="4">
         <v>130000</v>
@@ -1498,10 +1498,10 @@
     </row>
     <row r="28" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C28" s="4">
         <v>130000</v>
@@ -1512,10 +1512,10 @@
     </row>
     <row r="29" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C29" s="4">
         <v>70000</v>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="30" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C30" s="4">
         <v>70000</v>
@@ -1540,10 +1540,10 @@
     </row>
     <row r="31" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C31" s="4">
         <v>70000</v>
@@ -1554,10 +1554,10 @@
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C32" s="4">
         <v>70000</v>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="33" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C33" s="4">
         <v>70000</v>
@@ -1582,10 +1582,10 @@
     </row>
     <row r="34" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C34" s="4">
         <v>70000</v>
@@ -1596,10 +1596,10 @@
     </row>
     <row r="35" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C35" s="4">
         <v>70000</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="36" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C36" s="4">
         <v>70000</v>
@@ -1624,10 +1624,10 @@
     </row>
     <row r="37" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C37" s="4">
         <v>70000</v>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C38" s="4">
         <v>70000</v>
@@ -1652,10 +1652,10 @@
     </row>
     <row r="39" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C39" s="4">
         <v>70000</v>
@@ -1666,10 +1666,10 @@
     </row>
     <row r="40" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C40" s="4">
         <v>70000</v>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="41" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C41" s="4">
         <v>70000</v>
@@ -1694,10 +1694,10 @@
     </row>
     <row r="42" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C42" s="4">
         <v>70000</v>
@@ -1708,10 +1708,10 @@
     </row>
     <row r="43" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C43" s="4">
         <v>70000</v>
@@ -1722,10 +1722,10 @@
     </row>
     <row r="44" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C44" s="4">
         <v>70000</v>
@@ -1736,10 +1736,10 @@
     </row>
     <row r="45" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C45" s="4">
         <v>70000</v>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="46" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C46" s="4">
         <v>80000</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C47" s="4">
         <v>80000</v>
@@ -1778,10 +1778,10 @@
     </row>
     <row r="48" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C48" s="4">
         <v>70000</v>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="49" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C49" s="4">
         <v>70000</v>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="50" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C50" s="4">
         <v>100000</v>
@@ -1820,10 +1820,10 @@
     </row>
     <row r="51" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C51" s="4">
         <v>100000</v>
@@ -1834,10 +1834,10 @@
     </row>
     <row r="52" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C52" s="4">
         <v>70000</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="53" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C53" s="4">
         <v>70000</v>
@@ -1862,10 +1862,10 @@
     </row>
     <row r="54" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C54" s="4">
         <v>100000</v>
@@ -1876,10 +1876,10 @@
     </row>
     <row r="55" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C55" s="4">
         <v>100000</v>
@@ -1890,10 +1890,10 @@
     </row>
     <row r="56" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C56" s="4">
         <v>80000</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="57" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C57" s="4">
         <v>70000</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="58" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C58" s="4">
         <v>70000</v>
@@ -1932,10 +1932,10 @@
     </row>
     <row r="59" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C59" s="4">
         <v>80000</v>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="60" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C60" s="4">
         <v>80000</v>
@@ -1960,10 +1960,10 @@
     </row>
     <row r="61" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C61" s="4">
         <v>70000</v>
@@ -1974,10 +1974,10 @@
     </row>
     <row r="62" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C62" s="4">
         <v>90000</v>
@@ -1988,10 +1988,10 @@
     </row>
     <row r="63" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C63" s="4">
         <v>90000</v>
@@ -2002,10 +2002,10 @@
     </row>
     <row r="64" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C64" s="4">
         <v>90000</v>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="65" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C65" s="4">
         <v>70000</v>
@@ -2030,10 +2030,10 @@
     </row>
     <row r="66" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C66" s="4">
         <v>70000</v>
@@ -2044,10 +2044,10 @@
     </row>
     <row r="67" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C67" s="4">
         <v>70000</v>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="68" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C68" s="4">
         <v>90000</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="69" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C69" s="4">
         <v>90000</v>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="70" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C70" s="4">
         <v>90000</v>
@@ -2100,10 +2100,10 @@
     </row>
     <row r="71" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C71" s="4">
         <v>70000</v>
@@ -2114,10 +2114,10 @@
     </row>
     <row r="72" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C72" s="4">
         <v>70000</v>
@@ -2128,10 +2128,10 @@
     </row>
     <row r="73" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C73" s="4">
         <v>70000</v>
@@ -2142,10 +2142,10 @@
     </row>
     <row r="74" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C74" s="4">
         <v>70000</v>
@@ -2156,10 +2156,10 @@
     </row>
     <row r="75" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C75" s="4">
         <v>70000</v>
@@ -2170,10 +2170,10 @@
     </row>
     <row r="76" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C76" s="4">
         <v>70000</v>
@@ -2184,10 +2184,10 @@
     </row>
     <row r="77" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C77" s="4">
         <v>70000</v>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="78" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C78" s="4">
         <v>70000</v>
@@ -2212,10 +2212,10 @@
     </row>
     <row r="79" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C79" s="4">
         <v>70000</v>
@@ -2226,10 +2226,10 @@
     </row>
     <row r="80" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C80" s="4">
         <v>70000</v>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="81" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C81" s="4">
         <v>70000</v>
@@ -2254,10 +2254,10 @@
     </row>
     <row r="82" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C82" s="4">
         <v>70000</v>
@@ -2268,10 +2268,10 @@
     </row>
     <row r="83" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C83" s="4">
         <v>70000</v>
@@ -2282,10 +2282,10 @@
     </row>
     <row r="84" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C84" s="4">
         <v>70000</v>
@@ -2296,10 +2296,10 @@
     </row>
     <row r="85" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C85" s="4">
         <v>70000</v>
@@ -2310,10 +2310,10 @@
     </row>
     <row r="86" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C86" s="4">
         <v>70000</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="87" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C87" s="4">
         <v>70000</v>
@@ -2338,10 +2338,10 @@
     </row>
     <row r="88" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C88" s="4">
         <v>70000</v>
@@ -2352,10 +2352,10 @@
     </row>
     <row r="89" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C89" s="4">
         <v>70000</v>
@@ -2366,10 +2366,10 @@
     </row>
     <row r="90" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C90" s="4">
         <v>70000</v>
@@ -2380,10 +2380,10 @@
     </row>
     <row r="91" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C91" s="4">
         <v>70000</v>
@@ -2394,10 +2394,10 @@
     </row>
     <row r="92" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C92" s="4">
         <v>70000</v>
@@ -2408,10 +2408,10 @@
     </row>
     <row r="93" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C93" s="4">
         <v>70000</v>
@@ -2422,10 +2422,10 @@
     </row>
     <row r="94" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C94" s="4">
         <v>70000</v>
@@ -2436,10 +2436,10 @@
     </row>
     <row r="95" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C95" s="4">
         <v>70000</v>
@@ -2450,10 +2450,10 @@
     </row>
     <row r="96" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C96" s="4">
         <v>70000</v>
@@ -2464,10 +2464,10 @@
     </row>
     <row r="97" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C97" s="4">
         <v>70000</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="98" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C98" s="4">
         <v>70000</v>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="99" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C99" s="4">
         <v>70000</v>
@@ -2506,10 +2506,10 @@
     </row>
     <row r="100" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C100" s="4">
         <v>70000</v>
@@ -2520,10 +2520,10 @@
     </row>
     <row r="101" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C101" s="4">
         <v>70000</v>
@@ -2534,10 +2534,10 @@
     </row>
     <row r="102" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C102" s="4">
         <v>70000</v>
@@ -2548,10 +2548,10 @@
     </row>
     <row r="103" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C103" s="4">
         <v>70000</v>
@@ -2562,10 +2562,10 @@
     </row>
     <row r="104" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C104" s="4">
         <v>70000</v>
@@ -2576,10 +2576,10 @@
     </row>
     <row r="105" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C105" s="4">
         <v>70000</v>
@@ -2590,10 +2590,10 @@
     </row>
     <row r="106" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C106" s="4">
         <v>70000</v>
@@ -2604,10 +2604,10 @@
     </row>
     <row r="107" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C107" s="4">
         <v>70000</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="108" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C108" s="4">
         <v>70000</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="109" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C109" s="4">
         <v>70000</v>
@@ -2646,10 +2646,10 @@
     </row>
     <row r="110" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C110" s="4">
         <v>70000</v>
@@ -2660,10 +2660,10 @@
     </row>
     <row r="111" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C111" s="4">
         <v>70000</v>
@@ -2674,10 +2674,10 @@
     </row>
     <row r="112" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C112" s="4">
         <v>70000</v>
@@ -2688,10 +2688,10 @@
     </row>
     <row r="113" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C113" s="4">
         <v>70000</v>
@@ -2702,10 +2702,10 @@
     </row>
     <row r="114" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C114" s="4">
         <v>80000</v>
@@ -2716,10 +2716,10 @@
     </row>
     <row r="115" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C115" s="4">
         <v>80000</v>
@@ -2730,10 +2730,10 @@
     </row>
     <row r="116" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C116" s="4">
         <v>70000</v>
@@ -2744,10 +2744,10 @@
     </row>
     <row r="117" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C117" s="4">
         <v>70000</v>
@@ -2758,10 +2758,10 @@
     </row>
     <row r="118" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C118" s="4">
         <v>70000</v>
@@ -2772,10 +2772,10 @@
     </row>
     <row r="119" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C119" s="4">
         <v>70000</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="120" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C120" s="4">
         <v>70000</v>
@@ -2800,10 +2800,10 @@
     </row>
     <row r="121" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C121" s="4">
         <v>70000</v>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="122" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C122" s="4">
         <v>70000</v>
@@ -2828,10 +2828,10 @@
     </row>
     <row r="123" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C123" s="4">
         <v>70000</v>
@@ -2842,10 +2842,10 @@
     </row>
     <row r="124" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C124" s="4">
         <v>70000</v>
@@ -2856,10 +2856,10 @@
     </row>
     <row r="125" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C125" s="4">
         <v>70000</v>
@@ -2870,10 +2870,10 @@
     </row>
     <row r="126" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C126" s="4">
         <v>70000</v>
@@ -2884,10 +2884,10 @@
     </row>
     <row r="127" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C127" s="4">
         <v>70000</v>
@@ -2898,10 +2898,10 @@
     </row>
     <row r="128" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C128" s="4">
         <v>70000</v>
@@ -2912,10 +2912,10 @@
     </row>
     <row r="129" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C129" s="4">
         <v>70000</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="130" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C130" s="4">
         <v>70000</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="131" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C131" s="4">
         <v>70000</v>
@@ -2954,10 +2954,10 @@
     </row>
     <row r="132" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C132" s="4">
         <v>70000</v>
@@ -2968,10 +2968,10 @@
     </row>
     <row r="133" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C133" s="4">
         <v>70000</v>
@@ -2982,10 +2982,10 @@
     </row>
     <row r="134" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C134" s="4">
         <v>70000</v>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="135" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C135" s="4">
         <v>70000</v>
@@ -3010,10 +3010,10 @@
     </row>
     <row r="136" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C136" s="4">
         <v>70000</v>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="137" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C137" s="4">
         <v>70000</v>
@@ -3038,10 +3038,10 @@
     </row>
     <row r="138" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C138" s="4">
         <v>70000</v>
@@ -3052,10 +3052,10 @@
     </row>
     <row r="139" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C139" s="4">
         <v>70000</v>
@@ -3066,10 +3066,10 @@
     </row>
     <row r="140" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C140" s="4">
         <v>70000</v>
@@ -3080,10 +3080,10 @@
     </row>
     <row r="141" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C141" s="4">
         <v>70000</v>
@@ -3094,10 +3094,10 @@
     </row>
     <row r="142" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C142" s="4">
         <v>70000</v>
@@ -3108,10 +3108,10 @@
     </row>
     <row r="143" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C143" s="4">
         <v>80000</v>
@@ -3122,10 +3122,10 @@
     </row>
     <row r="144" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C144" s="4">
         <v>100000</v>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="145" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C145" s="4">
         <v>80000</v>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="146" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C146" s="4">
         <v>90000</v>
@@ -3164,10 +3164,10 @@
     </row>
     <row r="147" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C147" s="4">
         <v>70000</v>
@@ -3178,10 +3178,10 @@
     </row>
     <row r="148" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C148" s="4">
         <v>70000</v>
@@ -3192,10 +3192,10 @@
     </row>
     <row r="149" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C149" s="4">
         <v>70000</v>
@@ -3206,10 +3206,10 @@
     </row>
     <row r="150" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C150" s="4">
         <v>70000</v>
@@ -3220,10 +3220,10 @@
     </row>
     <row r="151" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C151" s="4">
         <v>80000</v>
@@ -3234,10 +3234,10 @@
     </row>
     <row r="152" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C152" s="4">
         <v>80000</v>
@@ -3248,10 +3248,10 @@
     </row>
     <row r="153" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C153" s="4">
         <v>70000</v>
@@ -3262,10 +3262,10 @@
     </row>
     <row r="154" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C154" s="4">
         <v>70000</v>
@@ -3276,10 +3276,10 @@
     </row>
     <row r="155" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C155" s="4">
         <v>70000</v>
@@ -3290,10 +3290,10 @@
     </row>
     <row r="156" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C156" s="4">
         <v>70000</v>
@@ -3304,10 +3304,10 @@
     </row>
     <row r="157" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C157" s="4">
         <v>70000</v>
@@ -3318,10 +3318,10 @@
     </row>
     <row r="158" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C158" s="4">
         <v>70000</v>
@@ -3332,10 +3332,10 @@
     </row>
     <row r="159" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C159" s="4">
         <v>90000</v>
@@ -3346,10 +3346,10 @@
     </row>
     <row r="160" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C160" s="4">
         <v>90000</v>
@@ -3360,10 +3360,10 @@
     </row>
     <row r="161" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C161" s="4">
         <v>70000</v>
@@ -3374,10 +3374,10 @@
     </row>
     <row r="162" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C162" s="4">
         <v>70000</v>
@@ -3388,10 +3388,10 @@
     </row>
     <row r="163" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C163" s="4">
         <v>120000</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="164" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C164" s="4">
         <v>120000</v>
@@ -3416,10 +3416,10 @@
     </row>
     <row r="165" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C165" s="4">
         <v>70000</v>
@@ -3430,10 +3430,10 @@
     </row>
     <row r="166" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C166" s="4">
         <v>120000</v>
@@ -3444,10 +3444,10 @@
     </row>
     <row r="167" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C167" s="4">
         <v>120000</v>
@@ -3458,10 +3458,10 @@
     </row>
     <row r="168" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C168" s="4">
         <v>70000</v>
@@ -3472,10 +3472,10 @@
     </row>
     <row r="169" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C169" s="4">
         <v>70000</v>
@@ -3486,10 +3486,10 @@
     </row>
     <row r="170" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C170" s="4">
         <v>70000</v>
@@ -3500,10 +3500,10 @@
     </row>
     <row r="171" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C171" s="4">
         <v>70000</v>
@@ -3514,10 +3514,10 @@
     </row>
     <row r="172" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C172" s="4">
         <v>70000</v>
@@ -3528,10 +3528,10 @@
     </row>
     <row r="173" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C173" s="4">
         <v>70000</v>
@@ -3542,10 +3542,10 @@
     </row>
     <row r="174" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C174" s="4">
         <v>70000</v>
@@ -3556,10 +3556,10 @@
     </row>
     <row r="175" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C175" s="4">
         <v>100000</v>
@@ -3570,10 +3570,10 @@
     </row>
     <row r="176" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C176" s="4">
         <v>100000</v>
@@ -3584,10 +3584,10 @@
     </row>
     <row r="177" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C177" s="4">
         <v>70000</v>
@@ -3598,10 +3598,10 @@
     </row>
     <row r="178" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C178" s="4">
         <v>70000</v>
@@ -3612,10 +3612,10 @@
     </row>
     <row r="179" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C179" s="4">
         <v>80000</v>
@@ -3626,10 +3626,10 @@
     </row>
     <row r="180" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C180" s="4">
         <v>80000</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="181" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C181" s="4">
         <v>70000</v>
@@ -3654,10 +3654,10 @@
     </row>
     <row r="182" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C182" s="4">
         <v>100000</v>
@@ -3668,10 +3668,10 @@
     </row>
     <row r="183" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C183" s="4">
         <v>70000</v>
@@ -3682,10 +3682,10 @@
     </row>
     <row r="184" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C184" s="4">
         <v>70000</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="185" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C185" s="4">
         <v>100000</v>
@@ -3710,10 +3710,10 @@
     </row>
     <row r="186" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C186" s="4">
         <v>100000</v>
@@ -3724,10 +3724,10 @@
     </row>
     <row r="187" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C187" s="4">
         <v>100000</v>
@@ -3738,10 +3738,10 @@
     </row>
     <row r="188" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C188" s="4">
         <v>100000</v>
@@ -3752,10 +3752,10 @@
     </row>
     <row r="189" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C189" s="4">
         <v>150000</v>
@@ -3766,10 +3766,10 @@
     </row>
     <row r="190" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C190" s="4">
         <v>150000</v>
@@ -3780,10 +3780,10 @@
     </row>
     <row r="191" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C191" s="4">
         <v>100000</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="192" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C192" s="4">
         <v>70000</v>
@@ -3808,10 +3808,10 @@
     </row>
     <row r="193" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C193" s="4">
         <v>70000</v>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="194" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C194" s="4">
         <v>70000</v>
@@ -3836,10 +3836,10 @@
     </row>
     <row r="195" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C195" s="4">
         <v>70000</v>
@@ -3850,10 +3850,10 @@
     </row>
     <row r="196" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C196" s="4">
         <v>70000</v>
@@ -3864,10 +3864,10 @@
     </row>
     <row r="197" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C197" s="4">
         <v>70000</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="198" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C198" s="4">
         <v>70000</v>
@@ -3892,10 +3892,10 @@
     </row>
     <row r="199" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C199" s="4">
         <v>70000</v>
@@ -3906,10 +3906,10 @@
     </row>
     <row r="200" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C200" s="4">
         <v>70000</v>
@@ -3920,10 +3920,10 @@
     </row>
     <row r="201" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C201" s="4">
         <v>70000</v>
@@ -3934,10 +3934,10 @@
     </row>
     <row r="202" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C202" s="4">
         <v>70000</v>
@@ -3948,10 +3948,10 @@
     </row>
     <row r="203" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C203" s="4">
         <v>70000</v>
@@ -3962,10 +3962,10 @@
     </row>
     <row r="204" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C204" s="4">
         <v>70000</v>
@@ -3976,10 +3976,10 @@
     </row>
     <row r="205" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C205" s="4">
         <v>70000</v>
@@ -3990,10 +3990,10 @@
     </row>
     <row r="206" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C206" s="4">
         <v>70000</v>
@@ -4004,10 +4004,10 @@
     </row>
     <row r="207" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C207" s="4">
         <v>44000</v>
@@ -4018,10 +4018,10 @@
     </row>
     <row r="208" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C208" s="4">
         <v>39000</v>
@@ -4032,10 +4032,10 @@
     </row>
     <row r="209" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C209" s="4">
         <v>69000</v>
@@ -4046,10 +4046,10 @@
     </row>
     <row r="210" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C210" s="4">
         <v>75000</v>
@@ -4060,10 +4060,10 @@
     </row>
     <row r="211" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C211" s="4">
         <v>75000</v>
@@ -4074,10 +4074,10 @@
     </row>
     <row r="212" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C212" s="4">
         <v>95000</v>
@@ -4088,10 +4088,10 @@
     </row>
     <row r="213" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C213" s="4">
         <v>95000</v>
@@ -4102,10 +4102,10 @@
     </row>
     <row r="214" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C214" s="4">
         <v>100000</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="215" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C215" s="4">
         <v>100000</v>
@@ -4130,10 +4130,10 @@
     </row>
     <row r="216" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C216" s="4">
         <v>100000</v>
@@ -4144,10 +4144,10 @@
     </row>
     <row r="217" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A217" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C217" s="4">
         <v>100000</v>

--- a/precios.xlsx
+++ b/precios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linoS\Documents\precios entel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE9E544-DC80-4DC6-8AC2-08F66CBAD56E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1DF2408-1C1F-4A61-BD4B-838BBFC70A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -711,7 +711,7 @@
     <t>INFINIX</t>
   </si>
   <si>
-    <t>precio plan</t>
+    <t>precio_plan</t>
   </si>
 </sst>
 </file>

--- a/precios.xlsx
+++ b/precios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linoS\Documents\precios entel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC71D7C2-C425-4F4E-BBAE-E2EF6D2208A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBFC30F5-7AAC-4AC0-852D-8389832FCB5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -711,7 +711,7 @@
     <t>DCTO</t>
   </si>
   <si>
-    <t>queda con</t>
+    <t>queda_con</t>
   </si>
 </sst>
 </file>
@@ -800,7 +800,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -818,7 +818,6 @@
     <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda [0]" xfId="2" builtinId="7"/>
@@ -1111,7 +1110,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" t="s">
         <v>226</v>
       </c>
       <c r="B1" t="s">

--- a/precios.xlsx
+++ b/precios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linoS\Documents\precios entel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBFC30F5-7AAC-4AC0-852D-8389832FCB5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9152CCE9-76B8-4467-BF6F-F6BB528A904E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="229">
   <si>
-    <t>sku</t>
-  </si>
-  <si>
     <t>A06 128GB BLACK</t>
   </si>
   <si>
@@ -711,7 +708,10 @@
     <t>DCTO</t>
   </si>
   <si>
-    <t>queda_con</t>
+    <t>COD_BARRA</t>
+  </si>
+  <si>
+    <t>QUEDA CON MANDATO LIGTH</t>
   </si>
 </sst>
 </file>
@@ -1111,13 +1111,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C1" t="s">
         <v>226</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>227</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>228</v>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C2" s="3">
         <v>80000</v>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="3" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C3" s="3">
         <v>80000</v>
@@ -1153,10 +1153,10 @@
     </row>
     <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C4" s="3">
         <v>80000</v>
@@ -1167,10 +1167,10 @@
     </row>
     <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C5" s="3">
         <v>120000</v>
@@ -1181,10 +1181,10 @@
     </row>
     <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C6" s="3">
         <v>120000</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C7" s="3">
         <v>120000</v>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="8" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C8" s="3">
         <v>70000</v>
@@ -1223,10 +1223,10 @@
     </row>
     <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C9" s="3">
         <v>70000</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C10" s="3">
         <v>70000</v>
@@ -1251,10 +1251,10 @@
     </row>
     <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C11" s="3">
         <v>70000</v>
@@ -1265,10 +1265,10 @@
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C12" s="3">
         <v>110000</v>
@@ -1279,10 +1279,10 @@
     </row>
     <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C13" s="3">
         <v>110000</v>
@@ -1293,10 +1293,10 @@
     </row>
     <row r="14" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C14" s="3">
         <v>70000</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="15" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C15" s="3">
         <v>70000</v>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C16" s="3">
         <v>70000</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="17" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C17" s="3">
         <v>100000</v>
@@ -1349,10 +1349,10 @@
     </row>
     <row r="18" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C18" s="3">
         <v>100000</v>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="19" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C19" s="3">
         <v>100000</v>
@@ -1377,10 +1377,10 @@
     </row>
     <row r="20" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C20" s="3">
         <v>100000</v>
@@ -1391,10 +1391,10 @@
     </row>
     <row r="21" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C21" s="3">
         <v>130000</v>
@@ -1405,10 +1405,10 @@
     </row>
     <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C22" s="3">
         <v>130000</v>
@@ -1419,10 +1419,10 @@
     </row>
     <row r="23" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C23" s="3">
         <v>130000</v>
@@ -1433,10 +1433,10 @@
     </row>
     <row r="24" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C24" s="3">
         <v>130000</v>
@@ -1447,10 +1447,10 @@
     </row>
     <row r="25" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C25" s="3">
         <v>120000</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C26" s="3">
         <v>120000</v>
@@ -1475,10 +1475,10 @@
     </row>
     <row r="27" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C27" s="3">
         <v>130000</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="28" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C28" s="3">
         <v>130000</v>
@@ -1503,10 +1503,10 @@
     </row>
     <row r="29" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C29" s="3">
         <v>70000</v>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="30" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C30" s="3">
         <v>70000</v>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="31" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C31" s="3">
         <v>70000</v>
@@ -1545,10 +1545,10 @@
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C32" s="3">
         <v>70000</v>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="33" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C33" s="3">
         <v>70000</v>
@@ -1573,10 +1573,10 @@
     </row>
     <row r="34" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C34" s="3">
         <v>70000</v>
@@ -1587,10 +1587,10 @@
     </row>
     <row r="35" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C35" s="3">
         <v>70000</v>
@@ -1601,10 +1601,10 @@
     </row>
     <row r="36" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C36" s="3">
         <v>70000</v>
@@ -1615,10 +1615,10 @@
     </row>
     <row r="37" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C37" s="3">
         <v>70000</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C38" s="3">
         <v>70000</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="39" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C39" s="3">
         <v>70000</v>
@@ -1657,10 +1657,10 @@
     </row>
     <row r="40" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C40" s="3">
         <v>70000</v>
@@ -1671,10 +1671,10 @@
     </row>
     <row r="41" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C41" s="3">
         <v>70000</v>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="42" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C42" s="3">
         <v>70000</v>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="43" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C43" s="3">
         <v>70000</v>
@@ -1713,10 +1713,10 @@
     </row>
     <row r="44" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C44" s="3">
         <v>70000</v>
@@ -1727,10 +1727,10 @@
     </row>
     <row r="45" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C45" s="3">
         <v>70000</v>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="46" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C46" s="3">
         <v>80000</v>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="47" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C47" s="3">
         <v>80000</v>
@@ -1769,10 +1769,10 @@
     </row>
     <row r="48" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C48" s="3">
         <v>70000</v>
@@ -1783,10 +1783,10 @@
     </row>
     <row r="49" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C49" s="3">
         <v>70000</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C50" s="3">
         <v>100000</v>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="51" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C51" s="3">
         <v>100000</v>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="52" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C52" s="3">
         <v>70000</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="53" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C53" s="3">
         <v>70000</v>
@@ -1853,10 +1853,10 @@
     </row>
     <row r="54" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C54" s="3">
         <v>100000</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="55" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C55" s="3">
         <v>100000</v>
@@ -1881,10 +1881,10 @@
     </row>
     <row r="56" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C56" s="3">
         <v>80000</v>
@@ -1895,10 +1895,10 @@
     </row>
     <row r="57" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C57" s="3">
         <v>70000</v>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="58" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C58" s="3">
         <v>70000</v>
@@ -1923,10 +1923,10 @@
     </row>
     <row r="59" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C59" s="3">
         <v>80000</v>
@@ -1937,10 +1937,10 @@
     </row>
     <row r="60" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C60" s="3">
         <v>80000</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="61" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C61" s="3">
         <v>70000</v>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="62" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C62" s="3">
         <v>90000</v>
@@ -1979,10 +1979,10 @@
     </row>
     <row r="63" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C63" s="3">
         <v>90000</v>
@@ -1993,10 +1993,10 @@
     </row>
     <row r="64" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C64" s="3">
         <v>90000</v>
@@ -2007,10 +2007,10 @@
     </row>
     <row r="65" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C65" s="3">
         <v>70000</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="66" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C66" s="3">
         <v>70000</v>
@@ -2035,10 +2035,10 @@
     </row>
     <row r="67" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C67" s="3">
         <v>70000</v>
@@ -2049,10 +2049,10 @@
     </row>
     <row r="68" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C68" s="3">
         <v>90000</v>
@@ -2063,10 +2063,10 @@
     </row>
     <row r="69" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C69" s="3">
         <v>90000</v>
@@ -2077,10 +2077,10 @@
     </row>
     <row r="70" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C70" s="3">
         <v>90000</v>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="71" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C71" s="3">
         <v>70000</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="72" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C72" s="3">
         <v>70000</v>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="73" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C73" s="3">
         <v>70000</v>
@@ -2133,10 +2133,10 @@
     </row>
     <row r="74" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C74" s="3">
         <v>70000</v>
@@ -2147,10 +2147,10 @@
     </row>
     <row r="75" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C75" s="3">
         <v>70000</v>
@@ -2161,10 +2161,10 @@
     </row>
     <row r="76" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C76" s="3">
         <v>70000</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="77" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C77" s="3">
         <v>70000</v>
@@ -2189,10 +2189,10 @@
     </row>
     <row r="78" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C78" s="3">
         <v>70000</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="79" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C79" s="3">
         <v>70000</v>
@@ -2217,10 +2217,10 @@
     </row>
     <row r="80" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C80" s="3">
         <v>70000</v>
@@ -2231,10 +2231,10 @@
     </row>
     <row r="81" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C81" s="3">
         <v>70000</v>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="82" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C82" s="3">
         <v>70000</v>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="83" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C83" s="3">
         <v>70000</v>
@@ -2273,10 +2273,10 @@
     </row>
     <row r="84" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C84" s="3">
         <v>70000</v>
@@ -2287,10 +2287,10 @@
     </row>
     <row r="85" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C85" s="3">
         <v>70000</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="86" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C86" s="3">
         <v>70000</v>
@@ -2315,10 +2315,10 @@
     </row>
     <row r="87" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C87" s="3">
         <v>70000</v>
@@ -2329,10 +2329,10 @@
     </row>
     <row r="88" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C88" s="3">
         <v>70000</v>
@@ -2343,10 +2343,10 @@
     </row>
     <row r="89" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C89" s="3">
         <v>70000</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="90" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C90" s="3">
         <v>70000</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="91" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C91" s="3">
         <v>70000</v>
@@ -2385,10 +2385,10 @@
     </row>
     <row r="92" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C92" s="3">
         <v>70000</v>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="93" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C93" s="3">
         <v>70000</v>
@@ -2413,10 +2413,10 @@
     </row>
     <row r="94" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C94" s="3">
         <v>70000</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="95" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C95" s="3">
         <v>70000</v>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="96" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C96" s="3">
         <v>70000</v>
@@ -2455,10 +2455,10 @@
     </row>
     <row r="97" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C97" s="3">
         <v>70000</v>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="98" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C98" s="3">
         <v>70000</v>
@@ -2483,10 +2483,10 @@
     </row>
     <row r="99" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C99" s="3">
         <v>70000</v>
@@ -2497,10 +2497,10 @@
     </row>
     <row r="100" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C100" s="3">
         <v>70000</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="101" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C101" s="3">
         <v>70000</v>
@@ -2525,10 +2525,10 @@
     </row>
     <row r="102" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C102" s="3">
         <v>70000</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="103" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C103" s="3">
         <v>70000</v>
@@ -2553,10 +2553,10 @@
     </row>
     <row r="104" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C104" s="3">
         <v>70000</v>
@@ -2567,10 +2567,10 @@
     </row>
     <row r="105" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C105" s="3">
         <v>70000</v>
@@ -2581,10 +2581,10 @@
     </row>
     <row r="106" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C106" s="3">
         <v>70000</v>
@@ -2595,10 +2595,10 @@
     </row>
     <row r="107" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C107" s="3">
         <v>70000</v>
@@ -2609,10 +2609,10 @@
     </row>
     <row r="108" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C108" s="3">
         <v>70000</v>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="109" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C109" s="3">
         <v>70000</v>
@@ -2637,10 +2637,10 @@
     </row>
     <row r="110" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C110" s="3">
         <v>70000</v>
@@ -2651,10 +2651,10 @@
     </row>
     <row r="111" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C111" s="3">
         <v>70000</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="112" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C112" s="3">
         <v>70000</v>
@@ -2679,10 +2679,10 @@
     </row>
     <row r="113" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C113" s="3">
         <v>70000</v>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="114" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C114" s="3">
         <v>80000</v>
@@ -2707,10 +2707,10 @@
     </row>
     <row r="115" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C115" s="3">
         <v>80000</v>
@@ -2721,10 +2721,10 @@
     </row>
     <row r="116" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C116" s="3">
         <v>70000</v>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="117" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C117" s="3">
         <v>70000</v>
@@ -2749,10 +2749,10 @@
     </row>
     <row r="118" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C118" s="3">
         <v>70000</v>
@@ -2763,10 +2763,10 @@
     </row>
     <row r="119" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C119" s="3">
         <v>70000</v>
@@ -2777,10 +2777,10 @@
     </row>
     <row r="120" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C120" s="3">
         <v>70000</v>
@@ -2791,10 +2791,10 @@
     </row>
     <row r="121" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C121" s="3">
         <v>70000</v>
@@ -2805,10 +2805,10 @@
     </row>
     <row r="122" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C122" s="3">
         <v>70000</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="123" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C123" s="3">
         <v>70000</v>
@@ -2833,10 +2833,10 @@
     </row>
     <row r="124" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C124" s="3">
         <v>70000</v>
@@ -2847,10 +2847,10 @@
     </row>
     <row r="125" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C125" s="3">
         <v>70000</v>
@@ -2861,10 +2861,10 @@
     </row>
     <row r="126" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C126" s="3">
         <v>70000</v>
@@ -2875,10 +2875,10 @@
     </row>
     <row r="127" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C127" s="3">
         <v>70000</v>
@@ -2889,10 +2889,10 @@
     </row>
     <row r="128" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C128" s="3">
         <v>70000</v>
@@ -2903,10 +2903,10 @@
     </row>
     <row r="129" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C129" s="3">
         <v>70000</v>
@@ -2917,10 +2917,10 @@
     </row>
     <row r="130" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C130" s="3">
         <v>70000</v>
@@ -2931,10 +2931,10 @@
     </row>
     <row r="131" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C131" s="3">
         <v>70000</v>
@@ -2945,10 +2945,10 @@
     </row>
     <row r="132" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C132" s="3">
         <v>70000</v>
@@ -2959,10 +2959,10 @@
     </row>
     <row r="133" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C133" s="3">
         <v>70000</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="134" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C134" s="3">
         <v>70000</v>
@@ -2987,10 +2987,10 @@
     </row>
     <row r="135" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C135" s="3">
         <v>70000</v>
@@ -3001,10 +3001,10 @@
     </row>
     <row r="136" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C136" s="3">
         <v>70000</v>
@@ -3015,10 +3015,10 @@
     </row>
     <row r="137" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C137" s="3">
         <v>70000</v>
@@ -3029,10 +3029,10 @@
     </row>
     <row r="138" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C138" s="3">
         <v>70000</v>
@@ -3043,10 +3043,10 @@
     </row>
     <row r="139" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C139" s="3">
         <v>70000</v>
@@ -3057,10 +3057,10 @@
     </row>
     <row r="140" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C140" s="3">
         <v>70000</v>
@@ -3071,10 +3071,10 @@
     </row>
     <row r="141" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C141" s="3">
         <v>70000</v>
@@ -3085,10 +3085,10 @@
     </row>
     <row r="142" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C142" s="3">
         <v>70000</v>
@@ -3099,10 +3099,10 @@
     </row>
     <row r="143" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C143" s="3">
         <v>80000</v>
@@ -3113,10 +3113,10 @@
     </row>
     <row r="144" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C144" s="3">
         <v>100000</v>
@@ -3127,10 +3127,10 @@
     </row>
     <row r="145" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C145" s="3">
         <v>80000</v>
@@ -3141,10 +3141,10 @@
     </row>
     <row r="146" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C146" s="3">
         <v>90000</v>
@@ -3155,10 +3155,10 @@
     </row>
     <row r="147" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C147" s="3">
         <v>70000</v>
@@ -3169,10 +3169,10 @@
     </row>
     <row r="148" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C148" s="3">
         <v>70000</v>
@@ -3183,10 +3183,10 @@
     </row>
     <row r="149" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C149" s="3">
         <v>70000</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="150" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C150" s="3">
         <v>70000</v>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="151" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C151" s="3">
         <v>80000</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="152" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C152" s="3">
         <v>80000</v>
@@ -3239,10 +3239,10 @@
     </row>
     <row r="153" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C153" s="3">
         <v>70000</v>
@@ -3253,10 +3253,10 @@
     </row>
     <row r="154" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C154" s="3">
         <v>70000</v>
@@ -3267,10 +3267,10 @@
     </row>
     <row r="155" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C155" s="3">
         <v>70000</v>
@@ -3281,10 +3281,10 @@
     </row>
     <row r="156" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C156" s="3">
         <v>70000</v>
@@ -3295,10 +3295,10 @@
     </row>
     <row r="157" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C157" s="3">
         <v>70000</v>
@@ -3309,10 +3309,10 @@
     </row>
     <row r="158" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C158" s="3">
         <v>70000</v>
@@ -3323,10 +3323,10 @@
     </row>
     <row r="159" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C159" s="3">
         <v>90000</v>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="160" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C160" s="3">
         <v>90000</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="161" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C161" s="3">
         <v>70000</v>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="162" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C162" s="3">
         <v>70000</v>
@@ -3379,10 +3379,10 @@
     </row>
     <row r="163" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C163" s="3">
         <v>120000</v>
@@ -3393,10 +3393,10 @@
     </row>
     <row r="164" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C164" s="3">
         <v>120000</v>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="165" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C165" s="3">
         <v>70000</v>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="166" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C166" s="3">
         <v>120000</v>
@@ -3435,10 +3435,10 @@
     </row>
     <row r="167" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C167" s="3">
         <v>120000</v>
@@ -3449,10 +3449,10 @@
     </row>
     <row r="168" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C168" s="3">
         <v>70000</v>
@@ -3463,10 +3463,10 @@
     </row>
     <row r="169" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C169" s="3">
         <v>70000</v>
@@ -3477,10 +3477,10 @@
     </row>
     <row r="170" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C170" s="3">
         <v>70000</v>
@@ -3491,10 +3491,10 @@
     </row>
     <row r="171" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C171" s="3">
         <v>70000</v>
@@ -3505,10 +3505,10 @@
     </row>
     <row r="172" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C172" s="3">
         <v>70000</v>
@@ -3519,10 +3519,10 @@
     </row>
     <row r="173" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C173" s="3">
         <v>70000</v>
@@ -3533,10 +3533,10 @@
     </row>
     <row r="174" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C174" s="3">
         <v>70000</v>
@@ -3547,10 +3547,10 @@
     </row>
     <row r="175" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C175" s="3">
         <v>100000</v>
@@ -3561,10 +3561,10 @@
     </row>
     <row r="176" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C176" s="3">
         <v>100000</v>
@@ -3575,10 +3575,10 @@
     </row>
     <row r="177" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C177" s="3">
         <v>70000</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="178" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C178" s="3">
         <v>70000</v>
@@ -3603,10 +3603,10 @@
     </row>
     <row r="179" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C179" s="3">
         <v>80000</v>
@@ -3617,10 +3617,10 @@
     </row>
     <row r="180" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C180" s="3">
         <v>80000</v>
@@ -3631,10 +3631,10 @@
     </row>
     <row r="181" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C181" s="3">
         <v>70000</v>
@@ -3645,10 +3645,10 @@
     </row>
     <row r="182" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C182" s="3">
         <v>100000</v>
@@ -3659,10 +3659,10 @@
     </row>
     <row r="183" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C183" s="3">
         <v>70000</v>
@@ -3673,10 +3673,10 @@
     </row>
     <row r="184" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C184" s="3">
         <v>70000</v>
@@ -3687,10 +3687,10 @@
     </row>
     <row r="185" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C185" s="3">
         <v>100000</v>
@@ -3701,10 +3701,10 @@
     </row>
     <row r="186" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C186" s="3">
         <v>100000</v>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="187" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C187" s="3">
         <v>100000</v>
@@ -3729,10 +3729,10 @@
     </row>
     <row r="188" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C188" s="3">
         <v>100000</v>
@@ -3743,10 +3743,10 @@
     </row>
     <row r="189" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C189" s="3">
         <v>150000</v>
@@ -3757,10 +3757,10 @@
     </row>
     <row r="190" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C190" s="3">
         <v>150000</v>
@@ -3771,10 +3771,10 @@
     </row>
     <row r="191" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C191" s="3">
         <v>100000</v>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="192" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C192" s="3">
         <v>70000</v>
@@ -3799,10 +3799,10 @@
     </row>
     <row r="193" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C193" s="3">
         <v>70000</v>
@@ -3813,10 +3813,10 @@
     </row>
     <row r="194" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C194" s="3">
         <v>70000</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="195" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C195" s="3">
         <v>70000</v>
@@ -3841,10 +3841,10 @@
     </row>
     <row r="196" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C196" s="3">
         <v>70000</v>
@@ -3855,10 +3855,10 @@
     </row>
     <row r="197" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C197" s="3">
         <v>70000</v>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="198" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C198" s="3">
         <v>70000</v>
@@ -3883,10 +3883,10 @@
     </row>
     <row r="199" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C199" s="3">
         <v>70000</v>
@@ -3897,10 +3897,10 @@
     </row>
     <row r="200" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C200" s="3">
         <v>70000</v>
@@ -3911,10 +3911,10 @@
     </row>
     <row r="201" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C201" s="3">
         <v>70000</v>
@@ -3925,10 +3925,10 @@
     </row>
     <row r="202" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C202" s="3">
         <v>70000</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="203" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C203" s="3">
         <v>70000</v>
@@ -3953,10 +3953,10 @@
     </row>
     <row r="204" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C204" s="3">
         <v>70000</v>
@@ -3967,10 +3967,10 @@
     </row>
     <row r="205" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C205" s="3">
         <v>70000</v>
@@ -3981,10 +3981,10 @@
     </row>
     <row r="206" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C206" s="3">
         <v>70000</v>
@@ -3995,10 +3995,10 @@
     </row>
     <row r="207" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C207" s="3">
         <v>44000</v>
@@ -4009,10 +4009,10 @@
     </row>
     <row r="208" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C208" s="3">
         <v>39000</v>
@@ -4023,10 +4023,10 @@
     </row>
     <row r="209" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C209" s="3">
         <v>69000</v>
@@ -4037,10 +4037,10 @@
     </row>
     <row r="210" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C210" s="3">
         <v>75000</v>
@@ -4051,10 +4051,10 @@
     </row>
     <row r="211" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C211" s="3">
         <v>75000</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="212" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C212" s="3">
         <v>95000</v>
@@ -4079,10 +4079,10 @@
     </row>
     <row r="213" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C213" s="3">
         <v>95000</v>
@@ -4093,10 +4093,10 @@
     </row>
     <row r="214" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C214" s="3">
         <v>100000</v>
@@ -4107,10 +4107,10 @@
     </row>
     <row r="215" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C215" s="3">
         <v>100000</v>
@@ -4121,10 +4121,10 @@
     </row>
     <row r="216" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C216" s="3">
         <v>100000</v>
@@ -4135,10 +4135,10 @@
     </row>
     <row r="217" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C217" s="3">
         <v>100000</v>

--- a/precios.xlsx
+++ b/precios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linoS\Documents\precios entel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9152CCE9-76B8-4467-BF6F-F6BB528A904E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF69A9F-7C86-44CC-83D1-319C4BBB5BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="218">
   <si>
     <t>A06 128GB BLACK</t>
   </si>
@@ -667,39 +667,6 @@
   </si>
   <si>
     <t>CEL_LIBRE INFINIX DARK GT_30_PRO 5G 512GB</t>
-  </si>
-  <si>
-    <t>SAMSUNG</t>
-  </si>
-  <si>
-    <t>XIAOMI</t>
-  </si>
-  <si>
-    <t>APPLE</t>
-  </si>
-  <si>
-    <t>MOTOROLA</t>
-  </si>
-  <si>
-    <t>HONOR</t>
-  </si>
-  <si>
-    <t>HUAWEI</t>
-  </si>
-  <si>
-    <t>VIVO</t>
-  </si>
-  <si>
-    <t>OPPO</t>
-  </si>
-  <si>
-    <t>ZTE</t>
-  </si>
-  <si>
-    <t>BMOBILE</t>
-  </si>
-  <si>
-    <t>INFINIX</t>
   </si>
   <si>
     <t>Descripción</t>
@@ -800,7 +767,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -817,6 +784,9 @@
     </xf>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1111,24 +1081,24 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="B1" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="C1" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>214</v>
+      <c r="B2" s="7">
+        <v>26975042</v>
       </c>
       <c r="C2" s="3">
         <v>80000</v>
@@ -1141,8 +1111,8 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>214</v>
+      <c r="B3" s="7">
+        <v>26975042</v>
       </c>
       <c r="C3" s="3">
         <v>80000</v>
@@ -1155,8 +1125,8 @@
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>214</v>
+      <c r="B4" s="7">
+        <v>26975042</v>
       </c>
       <c r="C4" s="3">
         <v>80000</v>
@@ -1169,8 +1139,8 @@
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>214</v>
+      <c r="B5" s="7">
+        <v>26975042</v>
       </c>
       <c r="C5" s="3">
         <v>120000</v>
@@ -1183,8 +1153,8 @@
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>214</v>
+      <c r="B6" s="7">
+        <v>26975042</v>
       </c>
       <c r="C6" s="3">
         <v>120000</v>
@@ -1197,8 +1167,8 @@
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>214</v>
+      <c r="B7" s="7">
+        <v>26975042</v>
       </c>
       <c r="C7" s="3">
         <v>120000</v>
@@ -1211,8 +1181,8 @@
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>214</v>
+      <c r="B8" s="7">
+        <v>26951291</v>
       </c>
       <c r="C8" s="3">
         <v>70000</v>
@@ -1225,8 +1195,8 @@
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>214</v>
+      <c r="B9" s="7">
+        <v>27512259</v>
       </c>
       <c r="C9" s="3">
         <v>70000</v>
@@ -1239,8 +1209,8 @@
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>214</v>
+      <c r="B10" s="7">
+        <v>27512259</v>
       </c>
       <c r="C10" s="3">
         <v>70000</v>
@@ -1253,8 +1223,8 @@
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>214</v>
+      <c r="B11" s="7">
+        <v>27512259</v>
       </c>
       <c r="C11" s="3">
         <v>70000</v>
@@ -1267,8 +1237,8 @@
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>214</v>
+      <c r="B12" s="7">
+        <v>27401732</v>
       </c>
       <c r="C12" s="3">
         <v>110000</v>
@@ -1281,8 +1251,8 @@
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>214</v>
+      <c r="B13" s="7">
+        <v>27401732</v>
       </c>
       <c r="C13" s="3">
         <v>110000</v>
@@ -1295,8 +1265,8 @@
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>214</v>
+      <c r="B14" s="7">
+        <v>27512259</v>
       </c>
       <c r="C14" s="3">
         <v>70000</v>
@@ -1309,8 +1279,8 @@
       <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>214</v>
+      <c r="B15" s="7">
+        <v>27512259</v>
       </c>
       <c r="C15" s="3">
         <v>70000</v>
@@ -1323,8 +1293,8 @@
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>214</v>
+      <c r="B16" s="7">
+        <v>27512259</v>
       </c>
       <c r="C16" s="3">
         <v>70000</v>
@@ -1337,8 +1307,8 @@
       <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>214</v>
+      <c r="B17" s="7">
+        <v>27512267</v>
       </c>
       <c r="C17" s="3">
         <v>100000</v>
@@ -1351,8 +1321,8 @@
       <c r="A18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>214</v>
+      <c r="B18" s="7">
+        <v>27512267</v>
       </c>
       <c r="C18" s="3">
         <v>100000</v>
@@ -1365,8 +1335,8 @@
       <c r="A19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>214</v>
+      <c r="B19" s="7">
+        <v>27512267</v>
       </c>
       <c r="C19" s="3">
         <v>100000</v>
@@ -1379,8 +1349,8 @@
       <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>214</v>
+      <c r="B20" s="7">
+        <v>27512267</v>
       </c>
       <c r="C20" s="3">
         <v>100000</v>
@@ -1393,8 +1363,8 @@
       <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>214</v>
+      <c r="B21" s="7">
+        <v>27070680</v>
       </c>
       <c r="C21" s="3">
         <v>130000</v>
@@ -1407,8 +1377,8 @@
       <c r="A22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>214</v>
+      <c r="B22" s="7">
+        <v>27070680</v>
       </c>
       <c r="C22" s="3">
         <v>130000</v>
@@ -1421,8 +1391,8 @@
       <c r="A23" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>214</v>
+      <c r="B23" s="7">
+        <v>27070680</v>
       </c>
       <c r="C23" s="3">
         <v>130000</v>
@@ -1435,8 +1405,8 @@
       <c r="A24" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>214</v>
+      <c r="B24" s="7">
+        <v>27070680</v>
       </c>
       <c r="C24" s="3">
         <v>130000</v>
@@ -1449,8 +1419,8 @@
       <c r="A25" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>214</v>
+      <c r="B25" s="7">
+        <v>27491731</v>
       </c>
       <c r="C25" s="3">
         <v>120000</v>
@@ -1463,8 +1433,8 @@
       <c r="A26" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>214</v>
+      <c r="B26" s="7">
+        <v>27491731</v>
       </c>
       <c r="C26" s="3">
         <v>120000</v>
@@ -1477,8 +1447,8 @@
       <c r="A27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>214</v>
+      <c r="B27" s="7">
+        <v>27070680</v>
       </c>
       <c r="C27" s="3">
         <v>130000</v>
@@ -1491,8 +1461,8 @@
       <c r="A28" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>214</v>
+      <c r="B28" s="7">
+        <v>27070680</v>
       </c>
       <c r="C28" s="3">
         <v>130000</v>
@@ -1505,8 +1475,8 @@
       <c r="A29" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>214</v>
+      <c r="B29" s="7">
+        <v>27512259</v>
       </c>
       <c r="C29" s="3">
         <v>70000</v>
@@ -1519,8 +1489,8 @@
       <c r="A30" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>214</v>
+      <c r="B30" s="7">
+        <v>27512259</v>
       </c>
       <c r="C30" s="3">
         <v>70000</v>
@@ -1533,8 +1503,8 @@
       <c r="A31" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>214</v>
+      <c r="B31" s="7">
+        <v>27512259</v>
       </c>
       <c r="C31" s="3">
         <v>70000</v>
@@ -1547,8 +1517,8 @@
       <c r="A32" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>214</v>
+      <c r="B32" s="7">
+        <v>27512259</v>
       </c>
       <c r="C32" s="3">
         <v>70000</v>
@@ -1561,8 +1531,8 @@
       <c r="A33" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>214</v>
+      <c r="B33" s="7">
+        <v>27512259</v>
       </c>
       <c r="C33" s="3">
         <v>70000</v>
@@ -1575,8 +1545,8 @@
       <c r="A34" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>214</v>
+      <c r="B34" s="7">
+        <v>27512259</v>
       </c>
       <c r="C34" s="3">
         <v>70000</v>
@@ -1589,8 +1559,8 @@
       <c r="A35" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>214</v>
+      <c r="B35" s="7">
+        <v>27512259</v>
       </c>
       <c r="C35" s="3">
         <v>70000</v>
@@ -1603,8 +1573,8 @@
       <c r="A36" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>214</v>
+      <c r="B36" s="7">
+        <v>27512259</v>
       </c>
       <c r="C36" s="3">
         <v>70000</v>
@@ -1617,8 +1587,8 @@
       <c r="A37" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>214</v>
+      <c r="B37" s="7">
+        <v>27512259</v>
       </c>
       <c r="C37" s="3">
         <v>70000</v>
@@ -1631,8 +1601,8 @@
       <c r="A38" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>214</v>
+      <c r="B38" s="7">
+        <v>27512259</v>
       </c>
       <c r="C38" s="3">
         <v>70000</v>
@@ -1645,8 +1615,8 @@
       <c r="A39" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>214</v>
+      <c r="B39" s="7">
+        <v>27512259</v>
       </c>
       <c r="C39" s="3">
         <v>70000</v>
@@ -1659,8 +1629,8 @@
       <c r="A40" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>214</v>
+      <c r="B40" s="7">
+        <v>27512259</v>
       </c>
       <c r="C40" s="3">
         <v>70000</v>
@@ -1673,8 +1643,8 @@
       <c r="A41" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>214</v>
+      <c r="B41" s="7">
+        <v>27512259</v>
       </c>
       <c r="C41" s="3">
         <v>70000</v>
@@ -1687,8 +1657,8 @@
       <c r="A42" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>214</v>
+      <c r="B42" s="7">
+        <v>27512259</v>
       </c>
       <c r="C42" s="3">
         <v>70000</v>
@@ -1701,8 +1671,8 @@
       <c r="A43" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>214</v>
+      <c r="B43" s="7">
+        <v>27512259</v>
       </c>
       <c r="C43" s="3">
         <v>70000</v>
@@ -1715,8 +1685,8 @@
       <c r="A44" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>215</v>
+      <c r="B44" s="7">
+        <v>26951291</v>
       </c>
       <c r="C44" s="3">
         <v>70000</v>
@@ -1729,8 +1699,8 @@
       <c r="A45" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>215</v>
+      <c r="B45" s="7">
+        <v>26951291</v>
       </c>
       <c r="C45" s="3">
         <v>70000</v>
@@ -1743,8 +1713,8 @@
       <c r="A46" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>215</v>
+      <c r="B46" s="7">
+        <v>27497756</v>
       </c>
       <c r="C46" s="3">
         <v>80000</v>
@@ -1757,8 +1727,8 @@
       <c r="A47" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>215</v>
+      <c r="B47" s="7">
+        <v>27497756</v>
       </c>
       <c r="C47" s="3">
         <v>80000</v>
@@ -1771,8 +1741,8 @@
       <c r="A48" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>215</v>
+      <c r="B48" s="7">
+        <v>26975042</v>
       </c>
       <c r="C48" s="3">
         <v>70000</v>
@@ -1785,8 +1755,8 @@
       <c r="A49" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>215</v>
+      <c r="B49" s="7">
+        <v>26975042</v>
       </c>
       <c r="C49" s="3">
         <v>70000</v>
@@ -1799,8 +1769,8 @@
       <c r="A50" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>215</v>
+      <c r="B50" s="7">
+        <v>27497756</v>
       </c>
       <c r="C50" s="3">
         <v>100000</v>
@@ -1813,8 +1783,8 @@
       <c r="A51" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>215</v>
+      <c r="B51" s="7">
+        <v>27497756</v>
       </c>
       <c r="C51" s="3">
         <v>100000</v>
@@ -1827,8 +1797,8 @@
       <c r="A52" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>215</v>
+      <c r="B52" s="7">
+        <v>26951291</v>
       </c>
       <c r="C52" s="3">
         <v>70000</v>
@@ -1841,8 +1811,8 @@
       <c r="A53" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>215</v>
+      <c r="B53" s="7">
+        <v>26951291</v>
       </c>
       <c r="C53" s="3">
         <v>70000</v>
@@ -1855,8 +1825,8 @@
       <c r="A54" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>215</v>
+      <c r="B54" s="7">
+        <v>27512267</v>
       </c>
       <c r="C54" s="3">
         <v>100000</v>
@@ -1869,8 +1839,8 @@
       <c r="A55" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>215</v>
+      <c r="B55" s="7">
+        <v>27512267</v>
       </c>
       <c r="C55" s="3">
         <v>100000</v>
@@ -1883,8 +1853,8 @@
       <c r="A56" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>215</v>
+      <c r="B56" s="7">
+        <v>27401724</v>
       </c>
       <c r="C56" s="3">
         <v>80000</v>
@@ -1897,8 +1867,8 @@
       <c r="A57" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>215</v>
+      <c r="B57" s="7">
+        <v>27512259</v>
       </c>
       <c r="C57" s="3">
         <v>70000</v>
@@ -1911,8 +1881,8 @@
       <c r="A58" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>215</v>
+      <c r="B58" s="7">
+        <v>27512259</v>
       </c>
       <c r="C58" s="3">
         <v>70000</v>
@@ -1925,8 +1895,8 @@
       <c r="A59" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>215</v>
+      <c r="B59" s="7">
+        <v>27401724</v>
       </c>
       <c r="C59" s="3">
         <v>80000</v>
@@ -1939,8 +1909,8 @@
       <c r="A60" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>215</v>
+      <c r="B60" s="7">
+        <v>27401724</v>
       </c>
       <c r="C60" s="3">
         <v>80000</v>
@@ -1953,8 +1923,8 @@
       <c r="A61" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>215</v>
+      <c r="B61" s="7">
+        <v>27512259</v>
       </c>
       <c r="C61" s="3">
         <v>70000</v>
@@ -1967,8 +1937,8 @@
       <c r="A62" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>215</v>
+      <c r="B62" s="7">
+        <v>27491766</v>
       </c>
       <c r="C62" s="3">
         <v>90000</v>
@@ -1981,8 +1951,8 @@
       <c r="A63" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>215</v>
+      <c r="B63" s="7">
+        <v>27491766</v>
       </c>
       <c r="C63" s="3">
         <v>90000</v>
@@ -1995,8 +1965,8 @@
       <c r="A64" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>215</v>
+      <c r="B64" s="7">
+        <v>27491766</v>
       </c>
       <c r="C64" s="3">
         <v>90000</v>
@@ -2009,8 +1979,8 @@
       <c r="A65" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>215</v>
+      <c r="B65" s="7">
+        <v>27512259</v>
       </c>
       <c r="C65" s="3">
         <v>70000</v>
@@ -2023,8 +1993,8 @@
       <c r="A66" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>215</v>
+      <c r="B66" s="7">
+        <v>27512259</v>
       </c>
       <c r="C66" s="3">
         <v>70000</v>
@@ -2037,8 +2007,8 @@
       <c r="A67" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>215</v>
+      <c r="B67" s="7">
+        <v>27512259</v>
       </c>
       <c r="C67" s="3">
         <v>70000</v>
@@ -2051,8 +2021,8 @@
       <c r="A68" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>215</v>
+      <c r="B68" s="7">
+        <v>27491766</v>
       </c>
       <c r="C68" s="3">
         <v>90000</v>
@@ -2065,8 +2035,8 @@
       <c r="A69" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>215</v>
+      <c r="B69" s="7">
+        <v>27491766</v>
       </c>
       <c r="C69" s="3">
         <v>90000</v>
@@ -2079,8 +2049,8 @@
       <c r="A70" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>215</v>
+      <c r="B70" s="7">
+        <v>27491766</v>
       </c>
       <c r="C70" s="3">
         <v>90000</v>
@@ -2093,8 +2063,8 @@
       <c r="A71" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>215</v>
+      <c r="B71" s="7">
+        <v>27512259</v>
       </c>
       <c r="C71" s="3">
         <v>70000</v>
@@ -2107,8 +2077,8 @@
       <c r="A72" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>215</v>
+      <c r="B72" s="7">
+        <v>27512259</v>
       </c>
       <c r="C72" s="3">
         <v>70000</v>
@@ -2121,8 +2091,8 @@
       <c r="A73" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>215</v>
+      <c r="B73" s="7">
+        <v>27512259</v>
       </c>
       <c r="C73" s="3">
         <v>70000</v>
@@ -2135,8 +2105,8 @@
       <c r="A74" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>215</v>
+      <c r="B74" s="7">
+        <v>27512259</v>
       </c>
       <c r="C74" s="3">
         <v>70000</v>
@@ -2149,8 +2119,8 @@
       <c r="A75" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>215</v>
+      <c r="B75" s="7">
+        <v>27512259</v>
       </c>
       <c r="C75" s="3">
         <v>70000</v>
@@ -2163,8 +2133,8 @@
       <c r="A76" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>215</v>
+      <c r="B76" s="7">
+        <v>27512259</v>
       </c>
       <c r="C76" s="3">
         <v>70000</v>
@@ -2177,8 +2147,8 @@
       <c r="A77" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>215</v>
+      <c r="B77" s="7">
+        <v>27512259</v>
       </c>
       <c r="C77" s="3">
         <v>70000</v>
@@ -2191,8 +2161,8 @@
       <c r="A78" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>216</v>
+      <c r="B78" s="7">
+        <v>27512259</v>
       </c>
       <c r="C78" s="3">
         <v>70000</v>
@@ -2205,8 +2175,8 @@
       <c r="A79" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>216</v>
+      <c r="B79" s="7">
+        <v>27512259</v>
       </c>
       <c r="C79" s="3">
         <v>70000</v>
@@ -2219,8 +2189,8 @@
       <c r="A80" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>216</v>
+      <c r="B80" s="7">
+        <v>27512259</v>
       </c>
       <c r="C80" s="3">
         <v>70000</v>
@@ -2233,8 +2203,8 @@
       <c r="A81" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>216</v>
+      <c r="B81" s="7">
+        <v>27512259</v>
       </c>
       <c r="C81" s="3">
         <v>70000</v>
@@ -2247,8 +2217,8 @@
       <c r="A82" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>216</v>
+      <c r="B82" s="7">
+        <v>27512259</v>
       </c>
       <c r="C82" s="3">
         <v>70000</v>
@@ -2261,8 +2231,8 @@
       <c r="A83" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>216</v>
+      <c r="B83" s="7">
+        <v>27512259</v>
       </c>
       <c r="C83" s="3">
         <v>70000</v>
@@ -2275,8 +2245,8 @@
       <c r="A84" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>216</v>
+      <c r="B84" s="7">
+        <v>27512259</v>
       </c>
       <c r="C84" s="3">
         <v>70000</v>
@@ -2289,8 +2259,8 @@
       <c r="A85" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>216</v>
+      <c r="B85" s="7">
+        <v>27512259</v>
       </c>
       <c r="C85" s="3">
         <v>70000</v>
@@ -2303,8 +2273,8 @@
       <c r="A86" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>216</v>
+      <c r="B86" s="7">
+        <v>27512259</v>
       </c>
       <c r="C86" s="3">
         <v>70000</v>
@@ -2317,8 +2287,8 @@
       <c r="A87" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>216</v>
+      <c r="B87" s="7">
+        <v>27512259</v>
       </c>
       <c r="C87" s="3">
         <v>70000</v>
@@ -2331,8 +2301,8 @@
       <c r="A88" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>216</v>
+      <c r="B88" s="7">
+        <v>27512259</v>
       </c>
       <c r="C88" s="3">
         <v>70000</v>
@@ -2345,8 +2315,8 @@
       <c r="A89" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>216</v>
+      <c r="B89" s="7">
+        <v>27512259</v>
       </c>
       <c r="C89" s="3">
         <v>70000</v>
@@ -2359,8 +2329,8 @@
       <c r="A90" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>216</v>
+      <c r="B90" s="7">
+        <v>27512259</v>
       </c>
       <c r="C90" s="3">
         <v>70000</v>
@@ -2373,8 +2343,8 @@
       <c r="A91" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>216</v>
+      <c r="B91" s="7">
+        <v>27512259</v>
       </c>
       <c r="C91" s="3">
         <v>70000</v>
@@ -2387,8 +2357,8 @@
       <c r="A92" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>216</v>
+      <c r="B92" s="7">
+        <v>27512259</v>
       </c>
       <c r="C92" s="3">
         <v>70000</v>
@@ -2401,8 +2371,8 @@
       <c r="A93" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>216</v>
+      <c r="B93" s="7">
+        <v>27512259</v>
       </c>
       <c r="C93" s="3">
         <v>70000</v>
@@ -2415,8 +2385,8 @@
       <c r="A94" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>216</v>
+      <c r="B94" s="7">
+        <v>27512259</v>
       </c>
       <c r="C94" s="3">
         <v>70000</v>
@@ -2429,8 +2399,8 @@
       <c r="A95" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>216</v>
+      <c r="B95" s="7">
+        <v>27512259</v>
       </c>
       <c r="C95" s="3">
         <v>70000</v>
@@ -2443,8 +2413,8 @@
       <c r="A96" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>216</v>
+      <c r="B96" s="7">
+        <v>27512259</v>
       </c>
       <c r="C96" s="3">
         <v>70000</v>
@@ -2457,8 +2427,8 @@
       <c r="A97" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>216</v>
+      <c r="B97" s="7">
+        <v>27512259</v>
       </c>
       <c r="C97" s="3">
         <v>70000</v>
@@ -2471,8 +2441,8 @@
       <c r="A98" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>216</v>
+      <c r="B98" s="7">
+        <v>27512259</v>
       </c>
       <c r="C98" s="3">
         <v>70000</v>
@@ -2485,8 +2455,8 @@
       <c r="A99" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>216</v>
+      <c r="B99" s="7">
+        <v>27512259</v>
       </c>
       <c r="C99" s="3">
         <v>70000</v>
@@ -2499,8 +2469,8 @@
       <c r="A100" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B100" s="2" t="s">
-        <v>216</v>
+      <c r="B100" s="7">
+        <v>27512259</v>
       </c>
       <c r="C100" s="3">
         <v>70000</v>
@@ -2513,8 +2483,8 @@
       <c r="A101" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>216</v>
+      <c r="B101" s="7">
+        <v>27512259</v>
       </c>
       <c r="C101" s="3">
         <v>70000</v>
@@ -2527,8 +2497,8 @@
       <c r="A102" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>216</v>
+      <c r="B102" s="7">
+        <v>27512259</v>
       </c>
       <c r="C102" s="3">
         <v>70000</v>
@@ -2541,8 +2511,8 @@
       <c r="A103" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B103" s="2" t="s">
-        <v>216</v>
+      <c r="B103" s="7">
+        <v>27512259</v>
       </c>
       <c r="C103" s="3">
         <v>70000</v>
@@ -2555,8 +2525,8 @@
       <c r="A104" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>216</v>
+      <c r="B104" s="7">
+        <v>27512259</v>
       </c>
       <c r="C104" s="3">
         <v>70000</v>
@@ -2569,8 +2539,8 @@
       <c r="A105" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>216</v>
+      <c r="B105" s="7">
+        <v>27512259</v>
       </c>
       <c r="C105" s="3">
         <v>70000</v>
@@ -2583,8 +2553,8 @@
       <c r="A106" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B106" s="2" t="s">
-        <v>216</v>
+      <c r="B106" s="7">
+        <v>27512259</v>
       </c>
       <c r="C106" s="3">
         <v>70000</v>
@@ -2597,8 +2567,8 @@
       <c r="A107" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B107" s="2" t="s">
-        <v>216</v>
+      <c r="B107" s="7">
+        <v>27512259</v>
       </c>
       <c r="C107" s="3">
         <v>70000</v>
@@ -2611,8 +2581,8 @@
       <c r="A108" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B108" s="2" t="s">
-        <v>217</v>
+      <c r="B108" s="7">
+        <v>27491723</v>
       </c>
       <c r="C108" s="3">
         <v>70000</v>
@@ -2625,8 +2595,8 @@
       <c r="A109" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B109" s="2" t="s">
-        <v>217</v>
+      <c r="B109" s="7">
+        <v>27491723</v>
       </c>
       <c r="C109" s="3">
         <v>70000</v>
@@ -2639,8 +2609,8 @@
       <c r="A110" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B110" s="2" t="s">
-        <v>217</v>
+      <c r="B110" s="7">
+        <v>27497756</v>
       </c>
       <c r="C110" s="3">
         <v>70000</v>
@@ -2653,8 +2623,8 @@
       <c r="A111" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B111" s="2" t="s">
-        <v>217</v>
+      <c r="B111" s="7">
+        <v>27497756</v>
       </c>
       <c r="C111" s="3">
         <v>70000</v>
@@ -2667,8 +2637,8 @@
       <c r="A112" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B112" s="2" t="s">
-        <v>217</v>
+      <c r="B112" s="7">
+        <v>26951291</v>
       </c>
       <c r="C112" s="3">
         <v>70000</v>
@@ -2681,8 +2651,8 @@
       <c r="A113" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B113" s="2" t="s">
-        <v>217</v>
+      <c r="B113" s="7">
+        <v>26951291</v>
       </c>
       <c r="C113" s="3">
         <v>70000</v>
@@ -2695,8 +2665,8 @@
       <c r="A114" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B114" s="2" t="s">
-        <v>217</v>
+      <c r="B114" s="7">
+        <v>25160720</v>
       </c>
       <c r="C114" s="3">
         <v>80000</v>
@@ -2709,8 +2679,8 @@
       <c r="A115" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B115" s="2" t="s">
-        <v>217</v>
+      <c r="B115" s="7">
+        <v>25160720</v>
       </c>
       <c r="C115" s="3">
         <v>80000</v>
@@ -2723,8 +2693,8 @@
       <c r="A116" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B116" s="2" t="s">
-        <v>217</v>
+      <c r="B116" s="7">
+        <v>27512259</v>
       </c>
       <c r="C116" s="3">
         <v>70000</v>
@@ -2737,8 +2707,8 @@
       <c r="A117" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B117" s="2" t="s">
-        <v>217</v>
+      <c r="B117" s="7">
+        <v>27512259</v>
       </c>
       <c r="C117" s="3">
         <v>70000</v>
@@ -2751,8 +2721,8 @@
       <c r="A118" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B118" s="2" t="s">
-        <v>217</v>
+      <c r="B118" s="7">
+        <v>27512259</v>
       </c>
       <c r="C118" s="3">
         <v>70000</v>
@@ -2765,8 +2735,8 @@
       <c r="A119" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B119" s="2" t="s">
-        <v>217</v>
+      <c r="B119" s="7">
+        <v>27512259</v>
       </c>
       <c r="C119" s="3">
         <v>70000</v>
@@ -2779,8 +2749,8 @@
       <c r="A120" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B120" s="2" t="s">
-        <v>217</v>
+      <c r="B120" s="7">
+        <v>27512259</v>
       </c>
       <c r="C120" s="3">
         <v>70000</v>
@@ -2793,8 +2763,8 @@
       <c r="A121" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B121" s="2" t="s">
-        <v>217</v>
+      <c r="B121" s="7">
+        <v>27512259</v>
       </c>
       <c r="C121" s="3">
         <v>70000</v>
@@ -2807,8 +2777,8 @@
       <c r="A122" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>217</v>
+      <c r="B122" s="7">
+        <v>27512259</v>
       </c>
       <c r="C122" s="3">
         <v>70000</v>
@@ -2821,8 +2791,8 @@
       <c r="A123" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B123" s="2" t="s">
-        <v>217</v>
+      <c r="B123" s="7">
+        <v>27512259</v>
       </c>
       <c r="C123" s="3">
         <v>70000</v>
@@ -2835,8 +2805,8 @@
       <c r="A124" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>217</v>
+      <c r="B124" s="7">
+        <v>27512259</v>
       </c>
       <c r="C124" s="3">
         <v>70000</v>
@@ -2849,8 +2819,8 @@
       <c r="A125" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B125" s="2" t="s">
-        <v>217</v>
+      <c r="B125" s="7">
+        <v>27512259</v>
       </c>
       <c r="C125" s="3">
         <v>70000</v>
@@ -2863,8 +2833,8 @@
       <c r="A126" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>217</v>
+      <c r="B126" s="7">
+        <v>27512259</v>
       </c>
       <c r="C126" s="3">
         <v>70000</v>
@@ -2877,8 +2847,8 @@
       <c r="A127" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B127" s="2" t="s">
-        <v>217</v>
+      <c r="B127" s="7">
+        <v>27512259</v>
       </c>
       <c r="C127" s="3">
         <v>70000</v>
@@ -2891,8 +2861,8 @@
       <c r="A128" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>217</v>
+      <c r="B128" s="7">
+        <v>27512259</v>
       </c>
       <c r="C128" s="3">
         <v>70000</v>
@@ -2905,8 +2875,8 @@
       <c r="A129" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B129" s="2" t="s">
-        <v>217</v>
+      <c r="B129" s="7">
+        <v>27512259</v>
       </c>
       <c r="C129" s="3">
         <v>70000</v>
@@ -2919,8 +2889,8 @@
       <c r="A130" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B130" s="2" t="s">
-        <v>217</v>
+      <c r="B130" s="7">
+        <v>27512259</v>
       </c>
       <c r="C130" s="3">
         <v>70000</v>
@@ -2933,8 +2903,8 @@
       <c r="A131" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B131" s="2" t="s">
-        <v>217</v>
+      <c r="B131" s="7">
+        <v>27512259</v>
       </c>
       <c r="C131" s="3">
         <v>70000</v>
@@ -2947,8 +2917,8 @@
       <c r="A132" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B132" s="2" t="s">
-        <v>217</v>
+      <c r="B132" s="7">
+        <v>27512259</v>
       </c>
       <c r="C132" s="3">
         <v>70000</v>
@@ -2961,8 +2931,8 @@
       <c r="A133" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B133" s="2" t="s">
-        <v>217</v>
+      <c r="B133" s="7">
+        <v>27512259</v>
       </c>
       <c r="C133" s="3">
         <v>70000</v>
@@ -2975,8 +2945,8 @@
       <c r="A134" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B134" s="2" t="s">
-        <v>217</v>
+      <c r="B134" s="7">
+        <v>27512259</v>
       </c>
       <c r="C134" s="3">
         <v>70000</v>
@@ -2989,8 +2959,8 @@
       <c r="A135" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B135" s="2" t="s">
-        <v>217</v>
+      <c r="B135" s="7">
+        <v>27512259</v>
       </c>
       <c r="C135" s="3">
         <v>70000</v>
@@ -3003,8 +2973,8 @@
       <c r="A136" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B136" s="2" t="s">
-        <v>217</v>
+      <c r="B136" s="7">
+        <v>27512259</v>
       </c>
       <c r="C136" s="3">
         <v>70000</v>
@@ -3017,8 +2987,8 @@
       <c r="A137" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B137" s="2" t="s">
-        <v>217</v>
+      <c r="B137" s="7">
+        <v>27512259</v>
       </c>
       <c r="C137" s="3">
         <v>70000</v>
@@ -3031,8 +3001,8 @@
       <c r="A138" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B138" s="2" t="s">
-        <v>217</v>
+      <c r="B138" s="7">
+        <v>27512259</v>
       </c>
       <c r="C138" s="3">
         <v>70000</v>
@@ -3045,8 +3015,8 @@
       <c r="A139" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B139" s="2" t="s">
-        <v>217</v>
+      <c r="B139" s="7">
+        <v>27512259</v>
       </c>
       <c r="C139" s="3">
         <v>70000</v>
@@ -3059,8 +3029,8 @@
       <c r="A140" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B140" s="2" t="s">
-        <v>217</v>
+      <c r="B140" s="7">
+        <v>27512259</v>
       </c>
       <c r="C140" s="3">
         <v>70000</v>
@@ -3073,8 +3043,8 @@
       <c r="A141" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B141" s="2" t="s">
-        <v>217</v>
+      <c r="B141" s="7">
+        <v>27512259</v>
       </c>
       <c r="C141" s="3">
         <v>70000</v>
@@ -3087,8 +3057,8 @@
       <c r="A142" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B142" s="2" t="s">
-        <v>217</v>
+      <c r="B142" s="7">
+        <v>27512259</v>
       </c>
       <c r="C142" s="3">
         <v>70000</v>
@@ -3101,8 +3071,8 @@
       <c r="A143" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B143" s="2" t="s">
-        <v>218</v>
+      <c r="B143" s="7">
+        <v>27491723</v>
       </c>
       <c r="C143" s="3">
         <v>80000</v>
@@ -3115,8 +3085,8 @@
       <c r="A144" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B144" s="2" t="s">
-        <v>218</v>
+      <c r="B144" s="7">
+        <v>27491723</v>
       </c>
       <c r="C144" s="3">
         <v>100000</v>
@@ -3129,8 +3099,8 @@
       <c r="A145" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B145" s="2" t="s">
-        <v>218</v>
+      <c r="B145" s="7">
+        <v>27401724</v>
       </c>
       <c r="C145" s="3">
         <v>80000</v>
@@ -3143,8 +3113,8 @@
       <c r="A146" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B146" s="2" t="s">
-        <v>218</v>
+      <c r="B146" s="7">
+        <v>27491766</v>
       </c>
       <c r="C146" s="3">
         <v>90000</v>
@@ -3157,8 +3127,8 @@
       <c r="A147" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B147" s="2" t="s">
-        <v>218</v>
+      <c r="B147" s="7">
+        <v>27512259</v>
       </c>
       <c r="C147" s="3">
         <v>70000</v>
@@ -3171,8 +3141,8 @@
       <c r="A148" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B148" s="2" t="s">
-        <v>218</v>
+      <c r="B148" s="7">
+        <v>27512259</v>
       </c>
       <c r="C148" s="3">
         <v>70000</v>
@@ -3185,8 +3155,8 @@
       <c r="A149" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B149" s="2" t="s">
-        <v>218</v>
+      <c r="B149" s="7">
+        <v>27512259</v>
       </c>
       <c r="C149" s="3">
         <v>70000</v>
@@ -3199,8 +3169,8 @@
       <c r="A150" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B150" s="2" t="s">
-        <v>218</v>
+      <c r="B150" s="7">
+        <v>27512259</v>
       </c>
       <c r="C150" s="3">
         <v>70000</v>
@@ -3213,8 +3183,8 @@
       <c r="A151" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B151" s="2" t="s">
-        <v>218</v>
+      <c r="B151" s="7">
+        <v>27401724</v>
       </c>
       <c r="C151" s="3">
         <v>80000</v>
@@ -3227,8 +3197,8 @@
       <c r="A152" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B152" s="2" t="s">
-        <v>218</v>
+      <c r="B152" s="7">
+        <v>27401724</v>
       </c>
       <c r="C152" s="3">
         <v>80000</v>
@@ -3241,8 +3211,8 @@
       <c r="A153" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B153" s="2" t="s">
-        <v>218</v>
+      <c r="B153" s="7">
+        <v>27512259</v>
       </c>
       <c r="C153" s="3">
         <v>70000</v>
@@ -3255,8 +3225,8 @@
       <c r="A154" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B154" s="2" t="s">
-        <v>218</v>
+      <c r="B154" s="7">
+        <v>27512259</v>
       </c>
       <c r="C154" s="3">
         <v>70000</v>
@@ -3269,8 +3239,8 @@
       <c r="A155" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B155" s="2" t="s">
-        <v>218</v>
+      <c r="B155" s="7">
+        <v>27512259</v>
       </c>
       <c r="C155" s="3">
         <v>70000</v>
@@ -3283,8 +3253,8 @@
       <c r="A156" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B156" s="2" t="s">
-        <v>218</v>
+      <c r="B156" s="7">
+        <v>27512259</v>
       </c>
       <c r="C156" s="3">
         <v>70000</v>
@@ -3297,8 +3267,8 @@
       <c r="A157" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B157" s="2" t="s">
-        <v>218</v>
+      <c r="B157" s="7">
+        <v>27512259</v>
       </c>
       <c r="C157" s="3">
         <v>70000</v>
@@ -3311,8 +3281,8 @@
       <c r="A158" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B158" s="2" t="s">
-        <v>218</v>
+      <c r="B158" s="7">
+        <v>27512259</v>
       </c>
       <c r="C158" s="3">
         <v>70000</v>
@@ -3325,8 +3295,8 @@
       <c r="A159" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B159" s="2" t="s">
-        <v>218</v>
+      <c r="B159" s="7">
+        <v>27491766</v>
       </c>
       <c r="C159" s="3">
         <v>90000</v>
@@ -3339,8 +3309,8 @@
       <c r="A160" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B160" s="2" t="s">
-        <v>218</v>
+      <c r="B160" s="7">
+        <v>27491766</v>
       </c>
       <c r="C160" s="3">
         <v>90000</v>
@@ -3353,8 +3323,8 @@
       <c r="A161" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B161" s="2" t="s">
-        <v>218</v>
+      <c r="B161" s="7">
+        <v>27512259</v>
       </c>
       <c r="C161" s="3">
         <v>70000</v>
@@ -3367,8 +3337,8 @@
       <c r="A162" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B162" s="2" t="s">
-        <v>218</v>
+      <c r="B162" s="7">
+        <v>27512259</v>
       </c>
       <c r="C162" s="3">
         <v>70000</v>
@@ -3381,8 +3351,8 @@
       <c r="A163" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B163" s="2" t="s">
-        <v>218</v>
+      <c r="B163" s="7">
+        <v>27491731</v>
       </c>
       <c r="C163" s="3">
         <v>120000</v>
@@ -3395,8 +3365,8 @@
       <c r="A164" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B164" s="2" t="s">
-        <v>218</v>
+      <c r="B164" s="7">
+        <v>27491731</v>
       </c>
       <c r="C164" s="3">
         <v>120000</v>
@@ -3409,8 +3379,8 @@
       <c r="A165" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B165" s="2" t="s">
-        <v>218</v>
+      <c r="B165" s="7">
+        <v>27512259</v>
       </c>
       <c r="C165" s="3">
         <v>70000</v>
@@ -3423,8 +3393,8 @@
       <c r="A166" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B166" s="2" t="s">
-        <v>218</v>
+      <c r="B166" s="7">
+        <v>27491731</v>
       </c>
       <c r="C166" s="3">
         <v>120000</v>
@@ -3437,8 +3407,8 @@
       <c r="A167" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B167" s="2" t="s">
-        <v>218</v>
+      <c r="B167" s="7">
+        <v>27491731</v>
       </c>
       <c r="C167" s="3">
         <v>120000</v>
@@ -3451,8 +3421,8 @@
       <c r="A168" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B168" s="2" t="s">
-        <v>218</v>
+      <c r="B168" s="7">
+        <v>27512259</v>
       </c>
       <c r="C168" s="3">
         <v>70000</v>
@@ -3465,8 +3435,8 @@
       <c r="A169" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B169" s="2" t="s">
-        <v>218</v>
+      <c r="B169" s="7">
+        <v>27512259</v>
       </c>
       <c r="C169" s="3">
         <v>70000</v>
@@ -3479,8 +3449,8 @@
       <c r="A170" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B170" s="2" t="s">
-        <v>219</v>
+      <c r="B170" s="7">
+        <v>27512259</v>
       </c>
       <c r="C170" s="3">
         <v>70000</v>
@@ -3493,8 +3463,8 @@
       <c r="A171" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B171" s="2" t="s">
-        <v>219</v>
+      <c r="B171" s="7">
+        <v>27512259</v>
       </c>
       <c r="C171" s="3">
         <v>70000</v>
@@ -3507,8 +3477,8 @@
       <c r="A172" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B172" s="2" t="s">
-        <v>219</v>
+      <c r="B172" s="7">
+        <v>27512259</v>
       </c>
       <c r="C172" s="3">
         <v>70000</v>
@@ -3521,8 +3491,8 @@
       <c r="A173" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B173" s="2" t="s">
-        <v>219</v>
+      <c r="B173" s="7">
+        <v>27512259</v>
       </c>
       <c r="C173" s="3">
         <v>70000</v>
@@ -3535,8 +3505,8 @@
       <c r="A174" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B174" s="2" t="s">
-        <v>219</v>
+      <c r="B174" s="7">
+        <v>27512259</v>
       </c>
       <c r="C174" s="3">
         <v>70000</v>
@@ -3549,8 +3519,8 @@
       <c r="A175" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B175" s="2" t="s">
-        <v>220</v>
+      <c r="B175" s="7">
+        <v>27497756</v>
       </c>
       <c r="C175" s="3">
         <v>100000</v>
@@ -3563,8 +3533,8 @@
       <c r="A176" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B176" s="2" t="s">
-        <v>220</v>
+      <c r="B176" s="7">
+        <v>27497756</v>
       </c>
       <c r="C176" s="3">
         <v>100000</v>
@@ -3577,8 +3547,8 @@
       <c r="A177" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B177" s="2" t="s">
-        <v>220</v>
+      <c r="B177" s="7">
+        <v>27512259</v>
       </c>
       <c r="C177" s="3">
         <v>70000</v>
@@ -3591,8 +3561,8 @@
       <c r="A178" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B178" s="2" t="s">
-        <v>220</v>
+      <c r="B178" s="7">
+        <v>27512259</v>
       </c>
       <c r="C178" s="3">
         <v>70000</v>
@@ -3605,8 +3575,8 @@
       <c r="A179" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B179" s="2" t="s">
-        <v>220</v>
+      <c r="B179" s="7">
+        <v>27401724</v>
       </c>
       <c r="C179" s="3">
         <v>80000</v>
@@ -3619,8 +3589,8 @@
       <c r="A180" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B180" s="2" t="s">
-        <v>220</v>
+      <c r="B180" s="7">
+        <v>27401724</v>
       </c>
       <c r="C180" s="3">
         <v>80000</v>
@@ -3633,8 +3603,8 @@
       <c r="A181" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B181" s="2" t="s">
-        <v>220</v>
+      <c r="B181" s="7">
+        <v>27512259</v>
       </c>
       <c r="C181" s="3">
         <v>70000</v>
@@ -3647,8 +3617,8 @@
       <c r="A182" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B182" s="2" t="s">
-        <v>220</v>
+      <c r="B182" s="7">
+        <v>27512267</v>
       </c>
       <c r="C182" s="3">
         <v>100000</v>
@@ -3661,8 +3631,8 @@
       <c r="A183" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B183" s="2" t="s">
-        <v>220</v>
+      <c r="B183" s="7">
+        <v>27512259</v>
       </c>
       <c r="C183" s="3">
         <v>70000</v>
@@ -3675,8 +3645,8 @@
       <c r="A184" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B184" s="2" t="s">
-        <v>220</v>
+      <c r="B184" s="7">
+        <v>27512259</v>
       </c>
       <c r="C184" s="3">
         <v>70000</v>
@@ -3689,8 +3659,8 @@
       <c r="A185" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B185" s="2" t="s">
-        <v>220</v>
+      <c r="B185" s="7">
+        <v>27512267</v>
       </c>
       <c r="C185" s="3">
         <v>100000</v>
@@ -3703,8 +3673,8 @@
       <c r="A186" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B186" s="2" t="s">
-        <v>220</v>
+      <c r="B186" s="7">
+        <v>27512267</v>
       </c>
       <c r="C186" s="3">
         <v>100000</v>
@@ -3717,8 +3687,8 @@
       <c r="A187" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B187" s="2" t="s">
-        <v>220</v>
+      <c r="B187" s="7">
+        <v>27512267</v>
       </c>
       <c r="C187" s="3">
         <v>100000</v>
@@ -3731,8 +3701,8 @@
       <c r="A188" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B188" s="2" t="s">
-        <v>220</v>
+      <c r="B188" s="7">
+        <v>27512267</v>
       </c>
       <c r="C188" s="3">
         <v>100000</v>
@@ -3745,8 +3715,8 @@
       <c r="A189" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B189" s="2" t="s">
-        <v>220</v>
+      <c r="B189" s="7">
+        <v>21983039</v>
       </c>
       <c r="C189" s="3">
         <v>150000</v>
@@ -3759,8 +3729,8 @@
       <c r="A190" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B190" s="2" t="s">
-        <v>220</v>
+      <c r="B190" s="7">
+        <v>21983039</v>
       </c>
       <c r="C190" s="3">
         <v>150000</v>
@@ -3773,8 +3743,8 @@
       <c r="A191" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B191" s="2" t="s">
-        <v>220</v>
+      <c r="B191" s="7">
+        <v>27512267</v>
       </c>
       <c r="C191" s="3">
         <v>100000</v>
@@ -3787,8 +3757,8 @@
       <c r="A192" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B192" s="2" t="s">
-        <v>221</v>
+      <c r="B192" s="7">
+        <v>27512259</v>
       </c>
       <c r="C192" s="3">
         <v>70000</v>
@@ -3801,8 +3771,8 @@
       <c r="A193" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B193" s="2" t="s">
-        <v>221</v>
+      <c r="B193" s="7">
+        <v>27512259</v>
       </c>
       <c r="C193" s="3">
         <v>70000</v>
@@ -3815,8 +3785,8 @@
       <c r="A194" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B194" s="2" t="s">
-        <v>221</v>
+      <c r="B194" s="7">
+        <v>27512259</v>
       </c>
       <c r="C194" s="3">
         <v>70000</v>
@@ -3829,8 +3799,8 @@
       <c r="A195" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B195" s="2" t="s">
-        <v>221</v>
+      <c r="B195" s="7">
+        <v>27512259</v>
       </c>
       <c r="C195" s="3">
         <v>70000</v>
@@ -3843,8 +3813,8 @@
       <c r="A196" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B196" s="2" t="s">
-        <v>221</v>
+      <c r="B196" s="7">
+        <v>27512259</v>
       </c>
       <c r="C196" s="3">
         <v>70000</v>
@@ -3857,8 +3827,8 @@
       <c r="A197" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B197" s="2" t="s">
-        <v>221</v>
+      <c r="B197" s="7">
+        <v>27512259</v>
       </c>
       <c r="C197" s="3">
         <v>70000</v>
@@ -3871,8 +3841,8 @@
       <c r="A198" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B198" s="2" t="s">
-        <v>221</v>
+      <c r="B198" s="7">
+        <v>27512259</v>
       </c>
       <c r="C198" s="3">
         <v>70000</v>
@@ -3885,8 +3855,8 @@
       <c r="A199" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B199" s="2" t="s">
-        <v>221</v>
+      <c r="B199" s="7">
+        <v>27512259</v>
       </c>
       <c r="C199" s="3">
         <v>70000</v>
@@ -3899,8 +3869,8 @@
       <c r="A200" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B200" s="2" t="s">
-        <v>221</v>
+      <c r="B200" s="7">
+        <v>27512259</v>
       </c>
       <c r="C200" s="3">
         <v>70000</v>
@@ -3913,8 +3883,8 @@
       <c r="A201" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B201" s="2" t="s">
-        <v>222</v>
+      <c r="B201" s="7">
+        <v>26975042</v>
       </c>
       <c r="C201" s="3">
         <v>70000</v>
@@ -3927,8 +3897,8 @@
       <c r="A202" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B202" s="2" t="s">
-        <v>222</v>
+      <c r="B202" s="7">
+        <v>27491723</v>
       </c>
       <c r="C202" s="3">
         <v>70000</v>
@@ -3941,8 +3911,8 @@
       <c r="A203" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B203" s="2" t="s">
-        <v>222</v>
+      <c r="B203" s="7">
+        <v>26951291</v>
       </c>
       <c r="C203" s="3">
         <v>70000</v>
@@ -3955,8 +3925,8 @@
       <c r="A204" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B204" s="2" t="s">
-        <v>222</v>
+      <c r="B204" s="7">
+        <v>27512259</v>
       </c>
       <c r="C204" s="3">
         <v>70000</v>
@@ -3969,8 +3939,8 @@
       <c r="A205" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B205" s="2" t="s">
-        <v>223</v>
+      <c r="B205" s="7">
+        <v>26951291</v>
       </c>
       <c r="C205" s="3">
         <v>70000</v>
@@ -3983,8 +3953,8 @@
       <c r="A206" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B206" s="2" t="s">
-        <v>223</v>
+      <c r="B206" s="7">
+        <v>27497756</v>
       </c>
       <c r="C206" s="3">
         <v>70000</v>
@@ -3997,8 +3967,8 @@
       <c r="A207" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B207" s="2" t="s">
-        <v>223</v>
+      <c r="B207" s="7">
+        <v>27512216</v>
       </c>
       <c r="C207" s="3">
         <v>44000</v>
@@ -4011,8 +3981,8 @@
       <c r="A208" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="B208" s="2" t="s">
-        <v>223</v>
+      <c r="B208" s="7">
+        <v>26975042</v>
       </c>
       <c r="C208" s="3">
         <v>39000</v>
@@ -4025,8 +3995,8 @@
       <c r="A209" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B209" s="2" t="s">
-        <v>223</v>
+      <c r="B209" s="7">
+        <v>26975042</v>
       </c>
       <c r="C209" s="3">
         <v>69000</v>
@@ -4039,8 +4009,8 @@
       <c r="A210" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B210" s="2" t="s">
-        <v>224</v>
+      <c r="B210" s="7">
+        <v>25160720</v>
       </c>
       <c r="C210" s="3">
         <v>75000</v>
@@ -4053,8 +4023,8 @@
       <c r="A211" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B211" s="2" t="s">
-        <v>224</v>
+      <c r="B211" s="7">
+        <v>25160720</v>
       </c>
       <c r="C211" s="3">
         <v>75000</v>
@@ -4067,8 +4037,8 @@
       <c r="A212" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="B212" s="2" t="s">
-        <v>224</v>
+      <c r="B212" s="7">
+        <v>27401902</v>
       </c>
       <c r="C212" s="3">
         <v>95000</v>
@@ -4081,8 +4051,8 @@
       <c r="A213" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B213" s="2" t="s">
-        <v>224</v>
+      <c r="B213" s="7">
+        <v>27401902</v>
       </c>
       <c r="C213" s="3">
         <v>95000</v>
@@ -4095,8 +4065,8 @@
       <c r="A214" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B214" s="2" t="s">
-        <v>224</v>
+      <c r="B214" s="7">
+        <v>27512267</v>
       </c>
       <c r="C214" s="3">
         <v>100000</v>
@@ -4109,8 +4079,8 @@
       <c r="A215" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B215" s="2" t="s">
-        <v>224</v>
+      <c r="B215" s="7">
+        <v>27512267</v>
       </c>
       <c r="C215" s="3">
         <v>100000</v>
@@ -4123,8 +4093,8 @@
       <c r="A216" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B216" s="2" t="s">
-        <v>224</v>
+      <c r="B216" s="7">
+        <v>27512267</v>
       </c>
       <c r="C216" s="3">
         <v>100000</v>
@@ -4137,8 +4107,8 @@
       <c r="A217" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B217" s="2" t="s">
-        <v>224</v>
+      <c r="B217" s="7">
+        <v>27512267</v>
       </c>
       <c r="C217" s="3">
         <v>100000</v>

--- a/precios.xlsx
+++ b/precios.xlsx
@@ -674,7 +674,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="12.0"/>
       <color rgb="FF000000"/>
@@ -699,22 +699,43 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12.0"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <b/>
       <sz val="12.0"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border/>
     <border>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -737,7 +758,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -756,22 +777,40 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="3" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
+    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -5989,6 +6028,9 @@
       <c r="D212" s="9">
         <v>39990.0</v>
       </c>
+      <c r="E212" s="10"/>
+      <c r="F212" s="11"/>
+      <c r="G212" s="11"/>
       <c r="H212" s="5"/>
       <c r="I212" s="5"/>
       <c r="J212" s="5"/>
@@ -6000,10 +6042,10 @@
       <c r="P212" s="5"/>
     </row>
     <row r="213" ht="18.0" customHeight="1">
-      <c r="A213" s="6" t="s">
+      <c r="A213" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="B213" s="7">
+      <c r="B213" s="13">
         <v>2.7401902E7</v>
       </c>
       <c r="C213" s="8">
@@ -6023,10 +6065,10 @@
       <c r="P213" s="5"/>
     </row>
     <row r="214" ht="18.0" customHeight="1">
-      <c r="A214" s="6" t="s">
+      <c r="A214" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="B214" s="7">
+      <c r="B214" s="13">
         <v>2.7491766E7</v>
       </c>
       <c r="C214" s="8">
@@ -6046,10 +6088,10 @@
       <c r="P214" s="5"/>
     </row>
     <row r="215" ht="18.0" customHeight="1">
-      <c r="A215" s="6" t="s">
+      <c r="A215" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="B215" s="7">
+      <c r="B215" s="13">
         <v>2.7491766E7</v>
       </c>
       <c r="C215" s="8">
@@ -6069,10 +6111,10 @@
       <c r="P215" s="5"/>
     </row>
     <row r="216" ht="18.0" customHeight="1">
-      <c r="A216" s="6" t="s">
+      <c r="A216" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="B216" s="7">
+      <c r="B216" s="13">
         <v>2.7401902E7</v>
       </c>
       <c r="C216" s="8">
@@ -6092,10 +6134,10 @@
       <c r="P216" s="5"/>
     </row>
     <row r="217" ht="18.0" customHeight="1">
-      <c r="A217" s="6" t="s">
+      <c r="A217" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="B217" s="7">
+      <c r="B217" s="13">
         <v>2.7401902E7</v>
       </c>
       <c r="C217" s="8">
@@ -6115,13 +6157,10 @@
       <c r="P217" s="5"/>
     </row>
     <row r="218" ht="18.0" customHeight="1">
-      <c r="A218" s="6"/>
-      <c r="B218" s="6"/>
-      <c r="C218" s="6"/>
-      <c r="D218" s="6"/>
-      <c r="E218" s="6"/>
-      <c r="F218" s="8"/>
-      <c r="G218" s="8"/>
+      <c r="A218" s="14"/>
+      <c r="B218" s="14"/>
+      <c r="C218" s="15"/>
+      <c r="D218" s="15"/>
       <c r="H218" s="5"/>
       <c r="I218" s="5"/>
       <c r="J218" s="5"/>
@@ -6133,6 +6172,10 @@
       <c r="P218" s="5"/>
     </row>
     <row r="219" ht="18.0" customHeight="1">
+      <c r="A219" s="12"/>
+      <c r="B219" s="12"/>
+      <c r="C219" s="8"/>
+      <c r="D219" s="15"/>
       <c r="H219" s="5"/>
       <c r="I219" s="5"/>
       <c r="J219" s="5"/>
@@ -6144,6 +6187,10 @@
       <c r="P219" s="5"/>
     </row>
     <row r="220" ht="18.0" customHeight="1">
+      <c r="A220" s="12"/>
+      <c r="B220" s="12"/>
+      <c r="C220" s="8"/>
+      <c r="D220" s="15"/>
       <c r="H220" s="5"/>
       <c r="I220" s="5"/>
       <c r="J220" s="5"/>
@@ -6155,6 +6202,10 @@
       <c r="P220" s="5"/>
     </row>
     <row r="221" ht="18.0" customHeight="1">
+      <c r="A221" s="12"/>
+      <c r="B221" s="12"/>
+      <c r="C221" s="8"/>
+      <c r="D221" s="15"/>
       <c r="H221" s="5"/>
       <c r="I221" s="5"/>
       <c r="J221" s="5"/>
@@ -6166,6 +6217,10 @@
       <c r="P221" s="5"/>
     </row>
     <row r="222" ht="18.0" customHeight="1">
+      <c r="A222" s="12"/>
+      <c r="B222" s="12"/>
+      <c r="C222" s="8"/>
+      <c r="D222" s="15"/>
       <c r="H222" s="5"/>
       <c r="I222" s="5"/>
       <c r="J222" s="5"/>
@@ -6177,6 +6232,10 @@
       <c r="P222" s="5"/>
     </row>
     <row r="223" ht="18.0" customHeight="1">
+      <c r="A223" s="12"/>
+      <c r="B223" s="12"/>
+      <c r="C223" s="8"/>
+      <c r="D223" s="15"/>
       <c r="H223" s="5"/>
       <c r="I223" s="5"/>
       <c r="J223" s="5"/>
@@ -6188,6 +6247,10 @@
       <c r="P223" s="5"/>
     </row>
     <row r="224" ht="18.0" customHeight="1">
+      <c r="A224" s="12"/>
+      <c r="B224" s="12"/>
+      <c r="C224" s="8"/>
+      <c r="D224" s="15"/>
       <c r="H224" s="5"/>
       <c r="I224" s="5"/>
       <c r="J224" s="5"/>
@@ -6199,6 +6262,10 @@
       <c r="P224" s="5"/>
     </row>
     <row r="225" ht="18.0" customHeight="1">
+      <c r="A225" s="12"/>
+      <c r="B225" s="12"/>
+      <c r="C225" s="8"/>
+      <c r="D225" s="15"/>
       <c r="H225" s="5"/>
       <c r="I225" s="5"/>
       <c r="J225" s="5"/>
@@ -6210,6 +6277,10 @@
       <c r="P225" s="5"/>
     </row>
     <row r="226" ht="18.0" customHeight="1">
+      <c r="A226" s="12"/>
+      <c r="B226" s="12"/>
+      <c r="C226" s="8"/>
+      <c r="D226" s="15"/>
       <c r="H226" s="5"/>
       <c r="I226" s="5"/>
       <c r="J226" s="5"/>
@@ -6221,6 +6292,10 @@
       <c r="P226" s="5"/>
     </row>
     <row r="227" ht="18.0" customHeight="1">
+      <c r="A227" s="12"/>
+      <c r="B227" s="12"/>
+      <c r="C227" s="8"/>
+      <c r="D227" s="15"/>
       <c r="H227" s="5"/>
       <c r="I227" s="5"/>
       <c r="J227" s="5"/>
@@ -6232,6 +6307,10 @@
       <c r="P227" s="5"/>
     </row>
     <row r="228" ht="18.0" customHeight="1">
+      <c r="A228" s="12"/>
+      <c r="B228" s="12"/>
+      <c r="C228" s="8"/>
+      <c r="D228" s="15"/>
       <c r="H228" s="5"/>
       <c r="I228" s="5"/>
       <c r="J228" s="5"/>
@@ -6243,6 +6322,10 @@
       <c r="P228" s="5"/>
     </row>
     <row r="229" ht="18.0" customHeight="1">
+      <c r="A229" s="12"/>
+      <c r="B229" s="12"/>
+      <c r="C229" s="8"/>
+      <c r="D229" s="15"/>
       <c r="H229" s="5"/>
       <c r="I229" s="5"/>
       <c r="J229" s="5"/>
@@ -6254,6 +6337,10 @@
       <c r="P229" s="5"/>
     </row>
     <row r="230" ht="18.0" customHeight="1">
+      <c r="A230" s="12"/>
+      <c r="B230" s="12"/>
+      <c r="C230" s="8"/>
+      <c r="D230" s="15"/>
       <c r="H230" s="5"/>
       <c r="I230" s="5"/>
       <c r="J230" s="5"/>
@@ -6265,6 +6352,10 @@
       <c r="P230" s="5"/>
     </row>
     <row r="231" ht="18.0" customHeight="1">
+      <c r="A231" s="12"/>
+      <c r="B231" s="12"/>
+      <c r="C231" s="8"/>
+      <c r="D231" s="15"/>
       <c r="H231" s="5"/>
       <c r="I231" s="5"/>
       <c r="J231" s="5"/>
@@ -6276,6 +6367,10 @@
       <c r="P231" s="5"/>
     </row>
     <row r="232" ht="18.0" customHeight="1">
+      <c r="A232" s="12"/>
+      <c r="B232" s="12"/>
+      <c r="C232" s="8"/>
+      <c r="D232" s="15"/>
       <c r="H232" s="5"/>
       <c r="I232" s="5"/>
       <c r="J232" s="5"/>
@@ -6287,6 +6382,10 @@
       <c r="P232" s="5"/>
     </row>
     <row r="233" ht="18.0" customHeight="1">
+      <c r="A233" s="12"/>
+      <c r="B233" s="12"/>
+      <c r="C233" s="8"/>
+      <c r="D233" s="15"/>
       <c r="H233" s="5"/>
       <c r="I233" s="5"/>
       <c r="J233" s="5"/>
@@ -6298,6 +6397,10 @@
       <c r="P233" s="5"/>
     </row>
     <row r="234" ht="18.0" customHeight="1">
+      <c r="A234" s="12"/>
+      <c r="B234" s="12"/>
+      <c r="C234" s="8"/>
+      <c r="D234" s="15"/>
       <c r="H234" s="5"/>
       <c r="I234" s="5"/>
       <c r="J234" s="5"/>
@@ -6309,6 +6412,10 @@
       <c r="P234" s="5"/>
     </row>
     <row r="235" ht="18.0" customHeight="1">
+      <c r="A235" s="12"/>
+      <c r="B235" s="12"/>
+      <c r="C235" s="8"/>
+      <c r="D235" s="15"/>
       <c r="H235" s="5"/>
       <c r="I235" s="5"/>
       <c r="J235" s="5"/>
@@ -6320,6 +6427,10 @@
       <c r="P235" s="5"/>
     </row>
     <row r="236" ht="18.0" customHeight="1">
+      <c r="A236" s="12"/>
+      <c r="B236" s="12"/>
+      <c r="C236" s="8"/>
+      <c r="D236" s="15"/>
       <c r="H236" s="5"/>
       <c r="I236" s="5"/>
       <c r="J236" s="5"/>
@@ -6331,6 +6442,10 @@
       <c r="P236" s="5"/>
     </row>
     <row r="237" ht="18.0" customHeight="1">
+      <c r="A237" s="12"/>
+      <c r="B237" s="12"/>
+      <c r="C237" s="8"/>
+      <c r="D237" s="15"/>
       <c r="H237" s="5"/>
       <c r="I237" s="5"/>
       <c r="J237" s="5"/>
@@ -6342,6 +6457,10 @@
       <c r="P237" s="5"/>
     </row>
     <row r="238" ht="18.0" customHeight="1">
+      <c r="A238" s="12"/>
+      <c r="B238" s="12"/>
+      <c r="C238" s="8"/>
+      <c r="D238" s="15"/>
       <c r="H238" s="5"/>
       <c r="I238" s="5"/>
       <c r="J238" s="5"/>
@@ -6353,6 +6472,10 @@
       <c r="P238" s="5"/>
     </row>
     <row r="239" ht="18.0" customHeight="1">
+      <c r="A239" s="12"/>
+      <c r="B239" s="12"/>
+      <c r="C239" s="8"/>
+      <c r="D239" s="15"/>
       <c r="H239" s="5"/>
       <c r="I239" s="5"/>
       <c r="J239" s="5"/>
@@ -6364,6 +6487,10 @@
       <c r="P239" s="5"/>
     </row>
     <row r="240" ht="18.0" customHeight="1">
+      <c r="A240" s="12"/>
+      <c r="B240" s="12"/>
+      <c r="C240" s="8"/>
+      <c r="D240" s="15"/>
       <c r="H240" s="5"/>
       <c r="I240" s="5"/>
       <c r="J240" s="5"/>
@@ -6375,6 +6502,10 @@
       <c r="P240" s="5"/>
     </row>
     <row r="241" ht="18.0" customHeight="1">
+      <c r="A241" s="12"/>
+      <c r="B241" s="12"/>
+      <c r="C241" s="8"/>
+      <c r="D241" s="15"/>
       <c r="H241" s="5"/>
       <c r="I241" s="5"/>
       <c r="J241" s="5"/>
@@ -6386,6 +6517,10 @@
       <c r="P241" s="5"/>
     </row>
     <row r="242" ht="18.0" customHeight="1">
+      <c r="A242" s="12"/>
+      <c r="B242" s="12"/>
+      <c r="C242" s="8"/>
+      <c r="D242" s="15"/>
       <c r="H242" s="5"/>
       <c r="I242" s="5"/>
       <c r="J242" s="5"/>
@@ -6397,6 +6532,10 @@
       <c r="P242" s="5"/>
     </row>
     <row r="243" ht="18.0" customHeight="1">
+      <c r="A243" s="12"/>
+      <c r="B243" s="12"/>
+      <c r="C243" s="8"/>
+      <c r="D243" s="15"/>
       <c r="H243" s="5"/>
       <c r="I243" s="5"/>
       <c r="J243" s="5"/>
@@ -6408,6 +6547,10 @@
       <c r="P243" s="5"/>
     </row>
     <row r="244" ht="18.0" customHeight="1">
+      <c r="A244" s="12"/>
+      <c r="B244" s="12"/>
+      <c r="C244" s="8"/>
+      <c r="D244" s="15"/>
       <c r="H244" s="5"/>
       <c r="I244" s="5"/>
       <c r="J244" s="5"/>
@@ -6419,6 +6562,10 @@
       <c r="P244" s="5"/>
     </row>
     <row r="245" ht="18.0" customHeight="1">
+      <c r="A245" s="12"/>
+      <c r="B245" s="12"/>
+      <c r="C245" s="8"/>
+      <c r="D245" s="15"/>
       <c r="H245" s="5"/>
       <c r="I245" s="5"/>
       <c r="J245" s="5"/>
@@ -6430,6 +6577,10 @@
       <c r="P245" s="5"/>
     </row>
     <row r="246" ht="18.0" customHeight="1">
+      <c r="A246" s="12"/>
+      <c r="B246" s="12"/>
+      <c r="C246" s="8"/>
+      <c r="D246" s="15"/>
       <c r="H246" s="5"/>
       <c r="I246" s="5"/>
       <c r="J246" s="5"/>
@@ -6441,6 +6592,10 @@
       <c r="P246" s="5"/>
     </row>
     <row r="247" ht="18.0" customHeight="1">
+      <c r="A247" s="12"/>
+      <c r="B247" s="12"/>
+      <c r="C247" s="8"/>
+      <c r="D247" s="15"/>
       <c r="H247" s="5"/>
       <c r="I247" s="5"/>
       <c r="J247" s="5"/>
@@ -6452,6 +6607,10 @@
       <c r="P247" s="5"/>
     </row>
     <row r="248" ht="18.0" customHeight="1">
+      <c r="A248" s="12"/>
+      <c r="B248" s="12"/>
+      <c r="C248" s="8"/>
+      <c r="D248" s="15"/>
       <c r="H248" s="5"/>
       <c r="I248" s="5"/>
       <c r="J248" s="5"/>
@@ -6463,6 +6622,10 @@
       <c r="P248" s="5"/>
     </row>
     <row r="249" ht="18.0" customHeight="1">
+      <c r="A249" s="12"/>
+      <c r="B249" s="12"/>
+      <c r="C249" s="8"/>
+      <c r="D249" s="15"/>
       <c r="H249" s="5"/>
       <c r="I249" s="5"/>
       <c r="J249" s="5"/>
@@ -6474,6 +6637,10 @@
       <c r="P249" s="5"/>
     </row>
     <row r="250" ht="18.0" customHeight="1">
+      <c r="A250" s="12"/>
+      <c r="B250" s="12"/>
+      <c r="C250" s="8"/>
+      <c r="D250" s="15"/>
       <c r="H250" s="5"/>
       <c r="I250" s="5"/>
       <c r="J250" s="5"/>
@@ -6485,6 +6652,10 @@
       <c r="P250" s="5"/>
     </row>
     <row r="251" ht="18.0" customHeight="1">
+      <c r="A251" s="12"/>
+      <c r="B251" s="12"/>
+      <c r="C251" s="8"/>
+      <c r="D251" s="15"/>
       <c r="H251" s="5"/>
       <c r="I251" s="5"/>
       <c r="J251" s="5"/>
@@ -6496,6 +6667,10 @@
       <c r="P251" s="5"/>
     </row>
     <row r="252" ht="18.0" customHeight="1">
+      <c r="A252" s="12"/>
+      <c r="B252" s="12"/>
+      <c r="C252" s="8"/>
+      <c r="D252" s="15"/>
       <c r="H252" s="5"/>
       <c r="I252" s="5"/>
       <c r="J252" s="5"/>
@@ -6507,6 +6682,10 @@
       <c r="P252" s="5"/>
     </row>
     <row r="253" ht="18.0" customHeight="1">
+      <c r="A253" s="12"/>
+      <c r="B253" s="12"/>
+      <c r="C253" s="8"/>
+      <c r="D253" s="15"/>
       <c r="H253" s="5"/>
       <c r="I253" s="5"/>
       <c r="J253" s="5"/>
@@ -6518,6 +6697,10 @@
       <c r="P253" s="5"/>
     </row>
     <row r="254" ht="18.0" customHeight="1">
+      <c r="A254" s="12"/>
+      <c r="B254" s="12"/>
+      <c r="C254" s="8"/>
+      <c r="D254" s="15"/>
       <c r="H254" s="5"/>
       <c r="I254" s="5"/>
       <c r="J254" s="5"/>
@@ -6529,6 +6712,10 @@
       <c r="P254" s="5"/>
     </row>
     <row r="255" ht="18.0" customHeight="1">
+      <c r="A255" s="12"/>
+      <c r="B255" s="12"/>
+      <c r="C255" s="8"/>
+      <c r="D255" s="15"/>
       <c r="H255" s="5"/>
       <c r="I255" s="5"/>
       <c r="J255" s="5"/>
@@ -6540,6 +6727,10 @@
       <c r="P255" s="5"/>
     </row>
     <row r="256" ht="18.0" customHeight="1">
+      <c r="A256" s="12"/>
+      <c r="B256" s="12"/>
+      <c r="C256" s="8"/>
+      <c r="D256" s="15"/>
       <c r="H256" s="5"/>
       <c r="I256" s="5"/>
       <c r="J256" s="5"/>
@@ -6551,6 +6742,10 @@
       <c r="P256" s="5"/>
     </row>
     <row r="257" ht="18.0" customHeight="1">
+      <c r="A257" s="12"/>
+      <c r="B257" s="12"/>
+      <c r="C257" s="8"/>
+      <c r="D257" s="15"/>
       <c r="H257" s="5"/>
       <c r="I257" s="5"/>
       <c r="J257" s="5"/>
@@ -6562,6 +6757,10 @@
       <c r="P257" s="5"/>
     </row>
     <row r="258" ht="18.0" customHeight="1">
+      <c r="A258" s="12"/>
+      <c r="B258" s="12"/>
+      <c r="C258" s="8"/>
+      <c r="D258" s="15"/>
       <c r="H258" s="5"/>
       <c r="I258" s="5"/>
       <c r="J258" s="5"/>
@@ -6573,6 +6772,10 @@
       <c r="P258" s="5"/>
     </row>
     <row r="259" ht="18.0" customHeight="1">
+      <c r="A259" s="12"/>
+      <c r="B259" s="12"/>
+      <c r="C259" s="8"/>
+      <c r="D259" s="15"/>
       <c r="H259" s="5"/>
       <c r="I259" s="5"/>
       <c r="J259" s="5"/>
@@ -6584,6 +6787,10 @@
       <c r="P259" s="5"/>
     </row>
     <row r="260" ht="18.0" customHeight="1">
+      <c r="A260" s="12"/>
+      <c r="B260" s="12"/>
+      <c r="C260" s="8"/>
+      <c r="D260" s="15"/>
       <c r="H260" s="5"/>
       <c r="I260" s="5"/>
       <c r="J260" s="5"/>
@@ -6595,6 +6802,10 @@
       <c r="P260" s="5"/>
     </row>
     <row r="261" ht="18.0" customHeight="1">
+      <c r="A261" s="12"/>
+      <c r="B261" s="12"/>
+      <c r="C261" s="8"/>
+      <c r="D261" s="15"/>
       <c r="H261" s="5"/>
       <c r="I261" s="5"/>
       <c r="J261" s="5"/>
@@ -6606,6 +6817,10 @@
       <c r="P261" s="5"/>
     </row>
     <row r="262" ht="18.0" customHeight="1">
+      <c r="A262" s="12"/>
+      <c r="B262" s="12"/>
+      <c r="C262" s="8"/>
+      <c r="D262" s="15"/>
       <c r="H262" s="5"/>
       <c r="I262" s="5"/>
       <c r="J262" s="5"/>
@@ -6617,6 +6832,10 @@
       <c r="P262" s="5"/>
     </row>
     <row r="263" ht="18.0" customHeight="1">
+      <c r="A263" s="12"/>
+      <c r="B263" s="12"/>
+      <c r="C263" s="8"/>
+      <c r="D263" s="15"/>
       <c r="H263" s="5"/>
       <c r="I263" s="5"/>
       <c r="J263" s="5"/>
@@ -6628,6 +6847,10 @@
       <c r="P263" s="5"/>
     </row>
     <row r="264" ht="18.0" customHeight="1">
+      <c r="A264" s="12"/>
+      <c r="B264" s="12"/>
+      <c r="C264" s="8"/>
+      <c r="D264" s="15"/>
       <c r="H264" s="5"/>
       <c r="I264" s="5"/>
       <c r="J264" s="5"/>
@@ -6639,6 +6862,10 @@
       <c r="P264" s="5"/>
     </row>
     <row r="265" ht="18.0" customHeight="1">
+      <c r="A265" s="12"/>
+      <c r="B265" s="12"/>
+      <c r="C265" s="8"/>
+      <c r="D265" s="15"/>
       <c r="H265" s="5"/>
       <c r="I265" s="5"/>
       <c r="J265" s="5"/>
@@ -6650,6 +6877,10 @@
       <c r="P265" s="5"/>
     </row>
     <row r="266" ht="18.0" customHeight="1">
+      <c r="A266" s="12"/>
+      <c r="B266" s="12"/>
+      <c r="C266" s="8"/>
+      <c r="D266" s="15"/>
       <c r="H266" s="5"/>
       <c r="I266" s="5"/>
       <c r="J266" s="5"/>
@@ -6661,6 +6892,10 @@
       <c r="P266" s="5"/>
     </row>
     <row r="267" ht="18.0" customHeight="1">
+      <c r="A267" s="12"/>
+      <c r="B267" s="12"/>
+      <c r="C267" s="8"/>
+      <c r="D267" s="15"/>
       <c r="H267" s="5"/>
       <c r="I267" s="5"/>
       <c r="J267" s="5"/>
@@ -6672,6 +6907,10 @@
       <c r="P267" s="5"/>
     </row>
     <row r="268" ht="18.0" customHeight="1">
+      <c r="A268" s="12"/>
+      <c r="B268" s="12"/>
+      <c r="C268" s="8"/>
+      <c r="D268" s="15"/>
       <c r="H268" s="5"/>
       <c r="I268" s="5"/>
       <c r="J268" s="5"/>
@@ -6683,6 +6922,10 @@
       <c r="P268" s="5"/>
     </row>
     <row r="269" ht="18.0" customHeight="1">
+      <c r="A269" s="12"/>
+      <c r="B269" s="12"/>
+      <c r="C269" s="8"/>
+      <c r="D269" s="15"/>
       <c r="H269" s="5"/>
       <c r="I269" s="5"/>
       <c r="J269" s="5"/>
@@ -6694,6 +6937,10 @@
       <c r="P269" s="5"/>
     </row>
     <row r="270" ht="18.0" customHeight="1">
+      <c r="A270" s="12"/>
+      <c r="B270" s="12"/>
+      <c r="C270" s="8"/>
+      <c r="D270" s="15"/>
       <c r="H270" s="5"/>
       <c r="I270" s="5"/>
       <c r="J270" s="5"/>
@@ -6705,6 +6952,10 @@
       <c r="P270" s="5"/>
     </row>
     <row r="271" ht="18.0" customHeight="1">
+      <c r="A271" s="12"/>
+      <c r="B271" s="12"/>
+      <c r="C271" s="8"/>
+      <c r="D271" s="15"/>
       <c r="H271" s="5"/>
       <c r="I271" s="5"/>
       <c r="J271" s="5"/>
@@ -6716,6 +6967,10 @@
       <c r="P271" s="5"/>
     </row>
     <row r="272" ht="18.0" customHeight="1">
+      <c r="A272" s="12"/>
+      <c r="B272" s="12"/>
+      <c r="C272" s="8"/>
+      <c r="D272" s="15"/>
       <c r="H272" s="5"/>
       <c r="I272" s="5"/>
       <c r="J272" s="5"/>
@@ -6727,6 +6982,10 @@
       <c r="P272" s="5"/>
     </row>
     <row r="273" ht="18.0" customHeight="1">
+      <c r="A273" s="12"/>
+      <c r="B273" s="12"/>
+      <c r="C273" s="8"/>
+      <c r="D273" s="15"/>
       <c r="H273" s="5"/>
       <c r="I273" s="5"/>
       <c r="J273" s="5"/>
@@ -6738,6 +6997,10 @@
       <c r="P273" s="5"/>
     </row>
     <row r="274" ht="18.0" customHeight="1">
+      <c r="A274" s="12"/>
+      <c r="B274" s="12"/>
+      <c r="C274" s="8"/>
+      <c r="D274" s="15"/>
       <c r="H274" s="5"/>
       <c r="I274" s="5"/>
       <c r="J274" s="5"/>
@@ -6749,6 +7012,10 @@
       <c r="P274" s="5"/>
     </row>
     <row r="275" ht="18.0" customHeight="1">
+      <c r="A275" s="12"/>
+      <c r="B275" s="12"/>
+      <c r="C275" s="8"/>
+      <c r="D275" s="15"/>
       <c r="H275" s="5"/>
       <c r="I275" s="5"/>
       <c r="J275" s="5"/>
@@ -6760,6 +7027,10 @@
       <c r="P275" s="5"/>
     </row>
     <row r="276" ht="18.0" customHeight="1">
+      <c r="A276" s="12"/>
+      <c r="B276" s="12"/>
+      <c r="C276" s="8"/>
+      <c r="D276" s="15"/>
       <c r="H276" s="5"/>
       <c r="I276" s="5"/>
       <c r="J276" s="5"/>
@@ -6771,6 +7042,10 @@
       <c r="P276" s="5"/>
     </row>
     <row r="277" ht="18.0" customHeight="1">
+      <c r="A277" s="12"/>
+      <c r="B277" s="12"/>
+      <c r="C277" s="8"/>
+      <c r="D277" s="15"/>
       <c r="H277" s="5"/>
       <c r="I277" s="5"/>
       <c r="J277" s="5"/>
@@ -6782,6 +7057,10 @@
       <c r="P277" s="5"/>
     </row>
     <row r="278" ht="18.0" customHeight="1">
+      <c r="A278" s="12"/>
+      <c r="B278" s="12"/>
+      <c r="C278" s="8"/>
+      <c r="D278" s="15"/>
       <c r="H278" s="5"/>
       <c r="I278" s="5"/>
       <c r="J278" s="5"/>
@@ -6793,6 +7072,10 @@
       <c r="P278" s="5"/>
     </row>
     <row r="279" ht="18.0" customHeight="1">
+      <c r="A279" s="12"/>
+      <c r="B279" s="12"/>
+      <c r="C279" s="8"/>
+      <c r="D279" s="15"/>
       <c r="H279" s="5"/>
       <c r="I279" s="5"/>
       <c r="J279" s="5"/>
@@ -6804,6 +7087,10 @@
       <c r="P279" s="5"/>
     </row>
     <row r="280" ht="18.0" customHeight="1">
+      <c r="A280" s="12"/>
+      <c r="B280" s="12"/>
+      <c r="C280" s="8"/>
+      <c r="D280" s="15"/>
       <c r="H280" s="5"/>
       <c r="I280" s="5"/>
       <c r="J280" s="5"/>
@@ -6815,6 +7102,10 @@
       <c r="P280" s="5"/>
     </row>
     <row r="281" ht="18.0" customHeight="1">
+      <c r="A281" s="12"/>
+      <c r="B281" s="12"/>
+      <c r="C281" s="8"/>
+      <c r="D281" s="15"/>
       <c r="H281" s="5"/>
       <c r="I281" s="5"/>
       <c r="J281" s="5"/>
@@ -6826,6 +7117,10 @@
       <c r="P281" s="5"/>
     </row>
     <row r="282" ht="18.0" customHeight="1">
+      <c r="A282" s="12"/>
+      <c r="B282" s="12"/>
+      <c r="C282" s="8"/>
+      <c r="D282" s="15"/>
       <c r="H282" s="5"/>
       <c r="I282" s="5"/>
       <c r="J282" s="5"/>
@@ -6837,6 +7132,10 @@
       <c r="P282" s="5"/>
     </row>
     <row r="283" ht="18.0" customHeight="1">
+      <c r="A283" s="12"/>
+      <c r="B283" s="12"/>
+      <c r="C283" s="8"/>
+      <c r="D283" s="15"/>
       <c r="H283" s="5"/>
       <c r="I283" s="5"/>
       <c r="J283" s="5"/>
@@ -6848,6 +7147,10 @@
       <c r="P283" s="5"/>
     </row>
     <row r="284" ht="18.0" customHeight="1">
+      <c r="A284" s="12"/>
+      <c r="B284" s="12"/>
+      <c r="C284" s="8"/>
+      <c r="D284" s="15"/>
       <c r="H284" s="5"/>
       <c r="I284" s="5"/>
       <c r="J284" s="5"/>
@@ -6859,6 +7162,10 @@
       <c r="P284" s="5"/>
     </row>
     <row r="285" ht="18.0" customHeight="1">
+      <c r="A285" s="12"/>
+      <c r="B285" s="12"/>
+      <c r="C285" s="8"/>
+      <c r="D285" s="15"/>
       <c r="H285" s="5"/>
       <c r="I285" s="5"/>
       <c r="J285" s="5"/>
@@ -6870,6 +7177,10 @@
       <c r="P285" s="5"/>
     </row>
     <row r="286" ht="18.0" customHeight="1">
+      <c r="A286" s="12"/>
+      <c r="B286" s="12"/>
+      <c r="C286" s="8"/>
+      <c r="D286" s="15"/>
       <c r="H286" s="5"/>
       <c r="I286" s="5"/>
       <c r="J286" s="5"/>
@@ -6881,6 +7192,10 @@
       <c r="P286" s="5"/>
     </row>
     <row r="287" ht="18.0" customHeight="1">
+      <c r="A287" s="12"/>
+      <c r="B287" s="12"/>
+      <c r="C287" s="8"/>
+      <c r="D287" s="15"/>
       <c r="H287" s="5"/>
       <c r="I287" s="5"/>
       <c r="J287" s="5"/>
@@ -6892,6 +7207,10 @@
       <c r="P287" s="5"/>
     </row>
     <row r="288" ht="18.0" customHeight="1">
+      <c r="A288" s="12"/>
+      <c r="B288" s="12"/>
+      <c r="C288" s="8"/>
+      <c r="D288" s="15"/>
       <c r="H288" s="5"/>
       <c r="I288" s="5"/>
       <c r="J288" s="5"/>
@@ -6903,6 +7222,10 @@
       <c r="P288" s="5"/>
     </row>
     <row r="289" ht="18.0" customHeight="1">
+      <c r="A289" s="12"/>
+      <c r="B289" s="12"/>
+      <c r="C289" s="8"/>
+      <c r="D289" s="15"/>
       <c r="H289" s="5"/>
       <c r="I289" s="5"/>
       <c r="J289" s="5"/>
@@ -6914,6 +7237,10 @@
       <c r="P289" s="5"/>
     </row>
     <row r="290" ht="18.0" customHeight="1">
+      <c r="A290" s="12"/>
+      <c r="B290" s="12"/>
+      <c r="C290" s="8"/>
+      <c r="D290" s="15"/>
       <c r="H290" s="5"/>
       <c r="I290" s="5"/>
       <c r="J290" s="5"/>
@@ -6925,6 +7252,10 @@
       <c r="P290" s="5"/>
     </row>
     <row r="291" ht="18.0" customHeight="1">
+      <c r="A291" s="12"/>
+      <c r="B291" s="12"/>
+      <c r="C291" s="8"/>
+      <c r="D291" s="15"/>
       <c r="H291" s="5"/>
       <c r="I291" s="5"/>
       <c r="J291" s="5"/>
@@ -6936,6 +7267,10 @@
       <c r="P291" s="5"/>
     </row>
     <row r="292" ht="18.0" customHeight="1">
+      <c r="A292" s="12"/>
+      <c r="B292" s="12"/>
+      <c r="C292" s="8"/>
+      <c r="D292" s="15"/>
       <c r="H292" s="5"/>
       <c r="I292" s="5"/>
       <c r="J292" s="5"/>
@@ -6947,6 +7282,10 @@
       <c r="P292" s="5"/>
     </row>
     <row r="293" ht="18.0" customHeight="1">
+      <c r="A293" s="12"/>
+      <c r="B293" s="12"/>
+      <c r="C293" s="8"/>
+      <c r="D293" s="15"/>
       <c r="H293" s="5"/>
       <c r="I293" s="5"/>
       <c r="J293" s="5"/>
@@ -6958,6 +7297,10 @@
       <c r="P293" s="5"/>
     </row>
     <row r="294" ht="18.0" customHeight="1">
+      <c r="A294" s="12"/>
+      <c r="B294" s="12"/>
+      <c r="C294" s="8"/>
+      <c r="D294" s="15"/>
       <c r="H294" s="5"/>
       <c r="I294" s="5"/>
       <c r="J294" s="5"/>
@@ -6969,6 +7312,10 @@
       <c r="P294" s="5"/>
     </row>
     <row r="295" ht="18.0" customHeight="1">
+      <c r="A295" s="12"/>
+      <c r="B295" s="12"/>
+      <c r="C295" s="8"/>
+      <c r="D295" s="15"/>
       <c r="H295" s="5"/>
       <c r="I295" s="5"/>
       <c r="J295" s="5"/>
@@ -6980,6 +7327,10 @@
       <c r="P295" s="5"/>
     </row>
     <row r="296" ht="18.0" customHeight="1">
+      <c r="A296" s="12"/>
+      <c r="B296" s="12"/>
+      <c r="C296" s="8"/>
+      <c r="D296" s="15"/>
       <c r="H296" s="5"/>
       <c r="I296" s="5"/>
       <c r="J296" s="5"/>
@@ -6991,6 +7342,10 @@
       <c r="P296" s="5"/>
     </row>
     <row r="297" ht="18.0" customHeight="1">
+      <c r="A297" s="12"/>
+      <c r="B297" s="12"/>
+      <c r="C297" s="8"/>
+      <c r="D297" s="15"/>
       <c r="H297" s="5"/>
       <c r="I297" s="5"/>
       <c r="J297" s="5"/>
@@ -7002,6 +7357,10 @@
       <c r="P297" s="5"/>
     </row>
     <row r="298" ht="18.0" customHeight="1">
+      <c r="A298" s="12"/>
+      <c r="B298" s="12"/>
+      <c r="C298" s="8"/>
+      <c r="D298" s="15"/>
       <c r="H298" s="5"/>
       <c r="I298" s="5"/>
       <c r="J298" s="5"/>
@@ -7013,6 +7372,10 @@
       <c r="P298" s="5"/>
     </row>
     <row r="299" ht="18.0" customHeight="1">
+      <c r="A299" s="12"/>
+      <c r="B299" s="12"/>
+      <c r="C299" s="8"/>
+      <c r="D299" s="15"/>
       <c r="H299" s="5"/>
       <c r="I299" s="5"/>
       <c r="J299" s="5"/>
@@ -7024,6 +7387,10 @@
       <c r="P299" s="5"/>
     </row>
     <row r="300" ht="18.0" customHeight="1">
+      <c r="A300" s="12"/>
+      <c r="B300" s="12"/>
+      <c r="C300" s="8"/>
+      <c r="D300" s="15"/>
       <c r="H300" s="5"/>
       <c r="I300" s="5"/>
       <c r="J300" s="5"/>
@@ -7035,6 +7402,10 @@
       <c r="P300" s="5"/>
     </row>
     <row r="301" ht="18.0" customHeight="1">
+      <c r="A301" s="12"/>
+      <c r="B301" s="12"/>
+      <c r="C301" s="8"/>
+      <c r="D301" s="15"/>
       <c r="H301" s="5"/>
       <c r="I301" s="5"/>
       <c r="J301" s="5"/>
@@ -7046,6 +7417,10 @@
       <c r="P301" s="5"/>
     </row>
     <row r="302" ht="18.0" customHeight="1">
+      <c r="A302" s="12"/>
+      <c r="B302" s="12"/>
+      <c r="C302" s="8"/>
+      <c r="D302" s="15"/>
       <c r="H302" s="5"/>
       <c r="I302" s="5"/>
       <c r="J302" s="5"/>
@@ -7057,6 +7432,10 @@
       <c r="P302" s="5"/>
     </row>
     <row r="303" ht="18.0" customHeight="1">
+      <c r="A303" s="12"/>
+      <c r="B303" s="12"/>
+      <c r="C303" s="8"/>
+      <c r="D303" s="15"/>
       <c r="H303" s="5"/>
       <c r="I303" s="5"/>
       <c r="J303" s="5"/>
@@ -7068,6 +7447,10 @@
       <c r="P303" s="5"/>
     </row>
     <row r="304" ht="18.0" customHeight="1">
+      <c r="A304" s="12"/>
+      <c r="B304" s="12"/>
+      <c r="C304" s="8"/>
+      <c r="D304" s="15"/>
       <c r="H304" s="5"/>
       <c r="I304" s="5"/>
       <c r="J304" s="5"/>
@@ -7079,6 +7462,10 @@
       <c r="P304" s="5"/>
     </row>
     <row r="305" ht="18.0" customHeight="1">
+      <c r="A305" s="12"/>
+      <c r="B305" s="12"/>
+      <c r="C305" s="8"/>
+      <c r="D305" s="15"/>
       <c r="H305" s="5"/>
       <c r="I305" s="5"/>
       <c r="J305" s="5"/>
@@ -7090,6 +7477,10 @@
       <c r="P305" s="5"/>
     </row>
     <row r="306" ht="18.0" customHeight="1">
+      <c r="A306" s="12"/>
+      <c r="B306" s="12"/>
+      <c r="C306" s="8"/>
+      <c r="D306" s="15"/>
       <c r="H306" s="5"/>
       <c r="I306" s="5"/>
       <c r="J306" s="5"/>
@@ -7101,6 +7492,10 @@
       <c r="P306" s="5"/>
     </row>
     <row r="307" ht="18.0" customHeight="1">
+      <c r="A307" s="12"/>
+      <c r="B307" s="12"/>
+      <c r="C307" s="8"/>
+      <c r="D307" s="15"/>
       <c r="H307" s="5"/>
       <c r="I307" s="5"/>
       <c r="J307" s="5"/>
@@ -7112,6 +7507,10 @@
       <c r="P307" s="5"/>
     </row>
     <row r="308" ht="18.0" customHeight="1">
+      <c r="A308" s="12"/>
+      <c r="B308" s="12"/>
+      <c r="C308" s="8"/>
+      <c r="D308" s="15"/>
       <c r="H308" s="5"/>
       <c r="I308" s="5"/>
       <c r="J308" s="5"/>
@@ -7123,6 +7522,10 @@
       <c r="P308" s="5"/>
     </row>
     <row r="309" ht="18.0" customHeight="1">
+      <c r="A309" s="12"/>
+      <c r="B309" s="12"/>
+      <c r="C309" s="8"/>
+      <c r="D309" s="15"/>
       <c r="H309" s="5"/>
       <c r="I309" s="5"/>
       <c r="J309" s="5"/>
@@ -7134,6 +7537,10 @@
       <c r="P309" s="5"/>
     </row>
     <row r="310" ht="18.0" customHeight="1">
+      <c r="A310" s="12"/>
+      <c r="B310" s="12"/>
+      <c r="C310" s="8"/>
+      <c r="D310" s="15"/>
       <c r="H310" s="5"/>
       <c r="I310" s="5"/>
       <c r="J310" s="5"/>
@@ -7145,6 +7552,10 @@
       <c r="P310" s="5"/>
     </row>
     <row r="311" ht="18.0" customHeight="1">
+      <c r="A311" s="12"/>
+      <c r="B311" s="12"/>
+      <c r="C311" s="8"/>
+      <c r="D311" s="15"/>
       <c r="H311" s="5"/>
       <c r="I311" s="5"/>
       <c r="J311" s="5"/>
@@ -7156,6 +7567,10 @@
       <c r="P311" s="5"/>
     </row>
     <row r="312" ht="18.0" customHeight="1">
+      <c r="A312" s="12"/>
+      <c r="B312" s="12"/>
+      <c r="C312" s="8"/>
+      <c r="D312" s="15"/>
       <c r="H312" s="5"/>
       <c r="I312" s="5"/>
       <c r="J312" s="5"/>
@@ -7167,6 +7582,10 @@
       <c r="P312" s="5"/>
     </row>
     <row r="313" ht="18.0" customHeight="1">
+      <c r="A313" s="12"/>
+      <c r="B313" s="12"/>
+      <c r="C313" s="8"/>
+      <c r="D313" s="15"/>
       <c r="H313" s="5"/>
       <c r="I313" s="5"/>
       <c r="J313" s="5"/>
@@ -7178,6 +7597,10 @@
       <c r="P313" s="5"/>
     </row>
     <row r="314" ht="18.0" customHeight="1">
+      <c r="A314" s="12"/>
+      <c r="B314" s="12"/>
+      <c r="C314" s="8"/>
+      <c r="D314" s="15"/>
       <c r="H314" s="5"/>
       <c r="I314" s="5"/>
       <c r="J314" s="5"/>
@@ -7189,6 +7612,10 @@
       <c r="P314" s="5"/>
     </row>
     <row r="315" ht="18.0" customHeight="1">
+      <c r="A315" s="12"/>
+      <c r="B315" s="12"/>
+      <c r="C315" s="8"/>
+      <c r="D315" s="15"/>
       <c r="H315" s="5"/>
       <c r="I315" s="5"/>
       <c r="J315" s="5"/>
@@ -7200,6 +7627,10 @@
       <c r="P315" s="5"/>
     </row>
     <row r="316" ht="18.0" customHeight="1">
+      <c r="A316" s="12"/>
+      <c r="B316" s="12"/>
+      <c r="C316" s="8"/>
+      <c r="D316" s="15"/>
       <c r="H316" s="5"/>
       <c r="I316" s="5"/>
       <c r="J316" s="5"/>
@@ -7211,6 +7642,10 @@
       <c r="P316" s="5"/>
     </row>
     <row r="317" ht="18.0" customHeight="1">
+      <c r="A317" s="12"/>
+      <c r="B317" s="12"/>
+      <c r="C317" s="8"/>
+      <c r="D317" s="15"/>
       <c r="H317" s="5"/>
       <c r="I317" s="5"/>
       <c r="J317" s="5"/>
@@ -7222,6 +7657,10 @@
       <c r="P317" s="5"/>
     </row>
     <row r="318" ht="18.0" customHeight="1">
+      <c r="A318" s="12"/>
+      <c r="B318" s="12"/>
+      <c r="C318" s="8"/>
+      <c r="D318" s="15"/>
       <c r="H318" s="5"/>
       <c r="I318" s="5"/>
       <c r="J318" s="5"/>
@@ -7233,6 +7672,10 @@
       <c r="P318" s="5"/>
     </row>
     <row r="319" ht="18.0" customHeight="1">
+      <c r="A319" s="12"/>
+      <c r="B319" s="12"/>
+      <c r="C319" s="8"/>
+      <c r="D319" s="15"/>
       <c r="H319" s="5"/>
       <c r="I319" s="5"/>
       <c r="J319" s="5"/>
@@ -7244,6 +7687,10 @@
       <c r="P319" s="5"/>
     </row>
     <row r="320" ht="18.0" customHeight="1">
+      <c r="A320" s="12"/>
+      <c r="B320" s="12"/>
+      <c r="C320" s="8"/>
+      <c r="D320" s="15"/>
       <c r="H320" s="5"/>
       <c r="I320" s="5"/>
       <c r="J320" s="5"/>
@@ -7255,6 +7702,10 @@
       <c r="P320" s="5"/>
     </row>
     <row r="321" ht="18.0" customHeight="1">
+      <c r="A321" s="12"/>
+      <c r="B321" s="12"/>
+      <c r="C321" s="8"/>
+      <c r="D321" s="15"/>
       <c r="H321" s="5"/>
       <c r="I321" s="5"/>
       <c r="J321" s="5"/>
@@ -7266,6 +7717,10 @@
       <c r="P321" s="5"/>
     </row>
     <row r="322" ht="18.0" customHeight="1">
+      <c r="A322" s="12"/>
+      <c r="B322" s="12"/>
+      <c r="C322" s="8"/>
+      <c r="D322" s="15"/>
       <c r="H322" s="5"/>
       <c r="I322" s="5"/>
       <c r="J322" s="5"/>
@@ -7277,6 +7732,10 @@
       <c r="P322" s="5"/>
     </row>
     <row r="323" ht="18.0" customHeight="1">
+      <c r="A323" s="12"/>
+      <c r="B323" s="12"/>
+      <c r="C323" s="8"/>
+      <c r="D323" s="15"/>
       <c r="H323" s="5"/>
       <c r="I323" s="5"/>
       <c r="J323" s="5"/>
@@ -7288,6 +7747,10 @@
       <c r="P323" s="5"/>
     </row>
     <row r="324" ht="18.0" customHeight="1">
+      <c r="A324" s="12"/>
+      <c r="B324" s="12"/>
+      <c r="C324" s="8"/>
+      <c r="D324" s="15"/>
       <c r="H324" s="5"/>
       <c r="I324" s="5"/>
       <c r="J324" s="5"/>
@@ -7299,6 +7762,10 @@
       <c r="P324" s="5"/>
     </row>
     <row r="325" ht="18.0" customHeight="1">
+      <c r="A325" s="12"/>
+      <c r="B325" s="12"/>
+      <c r="C325" s="8"/>
+      <c r="D325" s="15"/>
       <c r="H325" s="5"/>
       <c r="I325" s="5"/>
       <c r="J325" s="5"/>
@@ -7310,6 +7777,10 @@
       <c r="P325" s="5"/>
     </row>
     <row r="326" ht="18.0" customHeight="1">
+      <c r="A326" s="12"/>
+      <c r="B326" s="12"/>
+      <c r="C326" s="8"/>
+      <c r="D326" s="15"/>
       <c r="H326" s="5"/>
       <c r="I326" s="5"/>
       <c r="J326" s="5"/>
@@ -7321,6 +7792,10 @@
       <c r="P326" s="5"/>
     </row>
     <row r="327" ht="18.0" customHeight="1">
+      <c r="A327" s="12"/>
+      <c r="B327" s="12"/>
+      <c r="C327" s="8"/>
+      <c r="D327" s="15"/>
       <c r="H327" s="5"/>
       <c r="I327" s="5"/>
       <c r="J327" s="5"/>
@@ -7332,6 +7807,10 @@
       <c r="P327" s="5"/>
     </row>
     <row r="328" ht="18.0" customHeight="1">
+      <c r="A328" s="12"/>
+      <c r="B328" s="12"/>
+      <c r="C328" s="8"/>
+      <c r="D328" s="15"/>
       <c r="H328" s="5"/>
       <c r="I328" s="5"/>
       <c r="J328" s="5"/>
@@ -7343,6 +7822,10 @@
       <c r="P328" s="5"/>
     </row>
     <row r="329" ht="18.0" customHeight="1">
+      <c r="A329" s="12"/>
+      <c r="B329" s="12"/>
+      <c r="C329" s="8"/>
+      <c r="D329" s="15"/>
       <c r="H329" s="5"/>
       <c r="I329" s="5"/>
       <c r="J329" s="5"/>
@@ -7354,6 +7837,10 @@
       <c r="P329" s="5"/>
     </row>
     <row r="330" ht="18.0" customHeight="1">
+      <c r="A330" s="12"/>
+      <c r="B330" s="12"/>
+      <c r="C330" s="8"/>
+      <c r="D330" s="15"/>
       <c r="H330" s="5"/>
       <c r="I330" s="5"/>
       <c r="J330" s="5"/>
@@ -7365,6 +7852,10 @@
       <c r="P330" s="5"/>
     </row>
     <row r="331" ht="18.0" customHeight="1">
+      <c r="A331" s="12"/>
+      <c r="B331" s="12"/>
+      <c r="C331" s="8"/>
+      <c r="D331" s="15"/>
       <c r="H331" s="5"/>
       <c r="I331" s="5"/>
       <c r="J331" s="5"/>
@@ -7376,6 +7867,10 @@
       <c r="P331" s="5"/>
     </row>
     <row r="332" ht="18.0" customHeight="1">
+      <c r="A332" s="12"/>
+      <c r="B332" s="12"/>
+      <c r="C332" s="8"/>
+      <c r="D332" s="15"/>
       <c r="H332" s="5"/>
       <c r="I332" s="5"/>
       <c r="J332" s="5"/>
@@ -7387,6 +7882,10 @@
       <c r="P332" s="5"/>
     </row>
     <row r="333" ht="18.0" customHeight="1">
+      <c r="A333" s="12"/>
+      <c r="B333" s="12"/>
+      <c r="C333" s="8"/>
+      <c r="D333" s="15"/>
       <c r="H333" s="5"/>
       <c r="I333" s="5"/>
       <c r="J333" s="5"/>
@@ -7398,6 +7897,10 @@
       <c r="P333" s="5"/>
     </row>
     <row r="334" ht="18.0" customHeight="1">
+      <c r="A334" s="12"/>
+      <c r="B334" s="12"/>
+      <c r="C334" s="8"/>
+      <c r="D334" s="15"/>
       <c r="H334" s="5"/>
       <c r="I334" s="5"/>
       <c r="J334" s="5"/>
@@ -7409,6 +7912,10 @@
       <c r="P334" s="5"/>
     </row>
     <row r="335" ht="18.0" customHeight="1">
+      <c r="A335" s="12"/>
+      <c r="B335" s="12"/>
+      <c r="C335" s="8"/>
+      <c r="D335" s="15"/>
       <c r="H335" s="5"/>
       <c r="I335" s="5"/>
       <c r="J335" s="5"/>
@@ -7420,6 +7927,10 @@
       <c r="P335" s="5"/>
     </row>
     <row r="336" ht="18.0" customHeight="1">
+      <c r="A336" s="12"/>
+      <c r="B336" s="12"/>
+      <c r="C336" s="8"/>
+      <c r="D336" s="15"/>
       <c r="H336" s="5"/>
       <c r="I336" s="5"/>
       <c r="J336" s="5"/>
@@ -7431,6 +7942,10 @@
       <c r="P336" s="5"/>
     </row>
     <row r="337" ht="18.0" customHeight="1">
+      <c r="A337" s="12"/>
+      <c r="B337" s="12"/>
+      <c r="C337" s="8"/>
+      <c r="D337" s="15"/>
       <c r="H337" s="5"/>
       <c r="I337" s="5"/>
       <c r="J337" s="5"/>
@@ -7442,6 +7957,10 @@
       <c r="P337" s="5"/>
     </row>
     <row r="338" ht="18.0" customHeight="1">
+      <c r="A338" s="12"/>
+      <c r="B338" s="12"/>
+      <c r="C338" s="8"/>
+      <c r="D338" s="15"/>
       <c r="H338" s="5"/>
       <c r="I338" s="5"/>
       <c r="J338" s="5"/>
@@ -7453,6 +7972,10 @@
       <c r="P338" s="5"/>
     </row>
     <row r="339" ht="18.0" customHeight="1">
+      <c r="A339" s="12"/>
+      <c r="B339" s="12"/>
+      <c r="C339" s="8"/>
+      <c r="D339" s="15"/>
       <c r="H339" s="5"/>
       <c r="I339" s="5"/>
       <c r="J339" s="5"/>
@@ -7464,6 +7987,10 @@
       <c r="P339" s="5"/>
     </row>
     <row r="340" ht="18.0" customHeight="1">
+      <c r="A340" s="12"/>
+      <c r="B340" s="12"/>
+      <c r="C340" s="8"/>
+      <c r="D340" s="15"/>
       <c r="H340" s="5"/>
       <c r="I340" s="5"/>
       <c r="J340" s="5"/>
@@ -7475,6 +8002,10 @@
       <c r="P340" s="5"/>
     </row>
     <row r="341" ht="18.0" customHeight="1">
+      <c r="A341" s="12"/>
+      <c r="B341" s="12"/>
+      <c r="C341" s="8"/>
+      <c r="D341" s="15"/>
       <c r="H341" s="5"/>
       <c r="I341" s="5"/>
       <c r="J341" s="5"/>
@@ -7486,6 +8017,10 @@
       <c r="P341" s="5"/>
     </row>
     <row r="342" ht="18.0" customHeight="1">
+      <c r="A342" s="12"/>
+      <c r="B342" s="12"/>
+      <c r="C342" s="8"/>
+      <c r="D342" s="15"/>
       <c r="H342" s="5"/>
       <c r="I342" s="5"/>
       <c r="J342" s="5"/>
@@ -7497,6 +8032,10 @@
       <c r="P342" s="5"/>
     </row>
     <row r="343" ht="18.0" customHeight="1">
+      <c r="A343" s="12"/>
+      <c r="B343" s="12"/>
+      <c r="C343" s="8"/>
+      <c r="D343" s="15"/>
       <c r="H343" s="5"/>
       <c r="I343" s="5"/>
       <c r="J343" s="5"/>
@@ -7508,6 +8047,10 @@
       <c r="P343" s="5"/>
     </row>
     <row r="344" ht="18.0" customHeight="1">
+      <c r="A344" s="12"/>
+      <c r="B344" s="12"/>
+      <c r="C344" s="8"/>
+      <c r="D344" s="15"/>
       <c r="H344" s="5"/>
       <c r="I344" s="5"/>
       <c r="J344" s="5"/>
@@ -7519,6 +8062,10 @@
       <c r="P344" s="5"/>
     </row>
     <row r="345" ht="18.0" customHeight="1">
+      <c r="A345" s="12"/>
+      <c r="B345" s="12"/>
+      <c r="C345" s="8"/>
+      <c r="D345" s="15"/>
       <c r="H345" s="5"/>
       <c r="I345" s="5"/>
       <c r="J345" s="5"/>
@@ -7530,6 +8077,10 @@
       <c r="P345" s="5"/>
     </row>
     <row r="346" ht="18.0" customHeight="1">
+      <c r="A346" s="12"/>
+      <c r="B346" s="12"/>
+      <c r="C346" s="8"/>
+      <c r="D346" s="15"/>
       <c r="H346" s="5"/>
       <c r="I346" s="5"/>
       <c r="J346" s="5"/>
@@ -7541,6 +8092,10 @@
       <c r="P346" s="5"/>
     </row>
     <row r="347" ht="18.0" customHeight="1">
+      <c r="A347" s="12"/>
+      <c r="B347" s="12"/>
+      <c r="C347" s="8"/>
+      <c r="D347" s="15"/>
       <c r="H347" s="5"/>
       <c r="I347" s="5"/>
       <c r="J347" s="5"/>
@@ -7552,6 +8107,10 @@
       <c r="P347" s="5"/>
     </row>
     <row r="348" ht="18.0" customHeight="1">
+      <c r="A348" s="12"/>
+      <c r="B348" s="12"/>
+      <c r="C348" s="8"/>
+      <c r="D348" s="15"/>
       <c r="H348" s="5"/>
       <c r="I348" s="5"/>
       <c r="J348" s="5"/>
@@ -7563,6 +8122,10 @@
       <c r="P348" s="5"/>
     </row>
     <row r="349" ht="18.0" customHeight="1">
+      <c r="A349" s="12"/>
+      <c r="B349" s="12"/>
+      <c r="C349" s="8"/>
+      <c r="D349" s="15"/>
       <c r="H349" s="5"/>
       <c r="I349" s="5"/>
       <c r="J349" s="5"/>
@@ -7574,6 +8137,10 @@
       <c r="P349" s="5"/>
     </row>
     <row r="350" ht="18.0" customHeight="1">
+      <c r="A350" s="12"/>
+      <c r="B350" s="12"/>
+      <c r="C350" s="8"/>
+      <c r="D350" s="15"/>
       <c r="H350" s="5"/>
       <c r="I350" s="5"/>
       <c r="J350" s="5"/>
@@ -7585,6 +8152,10 @@
       <c r="P350" s="5"/>
     </row>
     <row r="351" ht="18.0" customHeight="1">
+      <c r="A351" s="12"/>
+      <c r="B351" s="12"/>
+      <c r="C351" s="8"/>
+      <c r="D351" s="15"/>
       <c r="H351" s="5"/>
       <c r="I351" s="5"/>
       <c r="J351" s="5"/>
@@ -7596,6 +8167,10 @@
       <c r="P351" s="5"/>
     </row>
     <row r="352" ht="18.0" customHeight="1">
+      <c r="A352" s="12"/>
+      <c r="B352" s="12"/>
+      <c r="C352" s="8"/>
+      <c r="D352" s="15"/>
       <c r="H352" s="5"/>
       <c r="I352" s="5"/>
       <c r="J352" s="5"/>
@@ -7607,6 +8182,10 @@
       <c r="P352" s="5"/>
     </row>
     <row r="353" ht="18.0" customHeight="1">
+      <c r="A353" s="12"/>
+      <c r="B353" s="12"/>
+      <c r="C353" s="8"/>
+      <c r="D353" s="15"/>
       <c r="H353" s="5"/>
       <c r="I353" s="5"/>
       <c r="J353" s="5"/>
@@ -7618,6 +8197,10 @@
       <c r="P353" s="5"/>
     </row>
     <row r="354" ht="18.0" customHeight="1">
+      <c r="A354" s="12"/>
+      <c r="B354" s="12"/>
+      <c r="C354" s="8"/>
+      <c r="D354" s="15"/>
       <c r="H354" s="5"/>
       <c r="I354" s="5"/>
       <c r="J354" s="5"/>
@@ -7629,6 +8212,10 @@
       <c r="P354" s="5"/>
     </row>
     <row r="355" ht="18.0" customHeight="1">
+      <c r="A355" s="12"/>
+      <c r="B355" s="12"/>
+      <c r="C355" s="8"/>
+      <c r="D355" s="15"/>
       <c r="H355" s="5"/>
       <c r="I355" s="5"/>
       <c r="J355" s="5"/>
@@ -7640,6 +8227,10 @@
       <c r="P355" s="5"/>
     </row>
     <row r="356" ht="18.0" customHeight="1">
+      <c r="A356" s="12"/>
+      <c r="B356" s="12"/>
+      <c r="C356" s="8"/>
+      <c r="D356" s="15"/>
       <c r="H356" s="5"/>
       <c r="I356" s="5"/>
       <c r="J356" s="5"/>
@@ -7651,6 +8242,10 @@
       <c r="P356" s="5"/>
     </row>
     <row r="357" ht="18.0" customHeight="1">
+      <c r="A357" s="12"/>
+      <c r="B357" s="12"/>
+      <c r="C357" s="8"/>
+      <c r="D357" s="15"/>
       <c r="H357" s="5"/>
       <c r="I357" s="5"/>
       <c r="J357" s="5"/>
@@ -7662,6 +8257,10 @@
       <c r="P357" s="5"/>
     </row>
     <row r="358" ht="18.0" customHeight="1">
+      <c r="A358" s="12"/>
+      <c r="B358" s="12"/>
+      <c r="C358" s="8"/>
+      <c r="D358" s="15"/>
       <c r="H358" s="5"/>
       <c r="I358" s="5"/>
       <c r="J358" s="5"/>
@@ -7673,6 +8272,10 @@
       <c r="P358" s="5"/>
     </row>
     <row r="359" ht="18.0" customHeight="1">
+      <c r="A359" s="12"/>
+      <c r="B359" s="12"/>
+      <c r="C359" s="8"/>
+      <c r="D359" s="15"/>
       <c r="H359" s="5"/>
       <c r="I359" s="5"/>
       <c r="J359" s="5"/>
@@ -7684,6 +8287,10 @@
       <c r="P359" s="5"/>
     </row>
     <row r="360" ht="18.0" customHeight="1">
+      <c r="A360" s="12"/>
+      <c r="B360" s="12"/>
+      <c r="C360" s="8"/>
+      <c r="D360" s="15"/>
       <c r="H360" s="5"/>
       <c r="I360" s="5"/>
       <c r="J360" s="5"/>
@@ -7695,6 +8302,10 @@
       <c r="P360" s="5"/>
     </row>
     <row r="361" ht="18.0" customHeight="1">
+      <c r="A361" s="12"/>
+      <c r="B361" s="12"/>
+      <c r="C361" s="8"/>
+      <c r="D361" s="15"/>
       <c r="H361" s="5"/>
       <c r="I361" s="5"/>
       <c r="J361" s="5"/>
@@ -7706,6 +8317,10 @@
       <c r="P361" s="5"/>
     </row>
     <row r="362" ht="18.0" customHeight="1">
+      <c r="A362" s="12"/>
+      <c r="B362" s="12"/>
+      <c r="C362" s="8"/>
+      <c r="D362" s="15"/>
       <c r="H362" s="5"/>
       <c r="I362" s="5"/>
       <c r="J362" s="5"/>
@@ -7717,6 +8332,10 @@
       <c r="P362" s="5"/>
     </row>
     <row r="363" ht="18.0" customHeight="1">
+      <c r="A363" s="12"/>
+      <c r="B363" s="12"/>
+      <c r="C363" s="8"/>
+      <c r="D363" s="15"/>
       <c r="H363" s="5"/>
       <c r="I363" s="5"/>
       <c r="J363" s="5"/>
@@ -7728,6 +8347,10 @@
       <c r="P363" s="5"/>
     </row>
     <row r="364" ht="18.0" customHeight="1">
+      <c r="A364" s="12"/>
+      <c r="B364" s="12"/>
+      <c r="C364" s="8"/>
+      <c r="D364" s="15"/>
       <c r="H364" s="5"/>
       <c r="I364" s="5"/>
       <c r="J364" s="5"/>
@@ -7739,6 +8362,10 @@
       <c r="P364" s="5"/>
     </row>
     <row r="365" ht="18.0" customHeight="1">
+      <c r="A365" s="12"/>
+      <c r="B365" s="12"/>
+      <c r="C365" s="8"/>
+      <c r="D365" s="15"/>
       <c r="H365" s="5"/>
       <c r="I365" s="5"/>
       <c r="J365" s="5"/>
@@ -7750,6 +8377,10 @@
       <c r="P365" s="5"/>
     </row>
     <row r="366" ht="18.0" customHeight="1">
+      <c r="A366" s="12"/>
+      <c r="B366" s="12"/>
+      <c r="C366" s="8"/>
+      <c r="D366" s="15"/>
       <c r="H366" s="5"/>
       <c r="I366" s="5"/>
       <c r="J366" s="5"/>
@@ -7761,6 +8392,10 @@
       <c r="P366" s="5"/>
     </row>
     <row r="367" ht="18.0" customHeight="1">
+      <c r="A367" s="12"/>
+      <c r="B367" s="12"/>
+      <c r="C367" s="8"/>
+      <c r="D367" s="15"/>
       <c r="H367" s="5"/>
       <c r="I367" s="5"/>
       <c r="J367" s="5"/>
@@ -7772,6 +8407,10 @@
       <c r="P367" s="5"/>
     </row>
     <row r="368" ht="18.0" customHeight="1">
+      <c r="A368" s="12"/>
+      <c r="B368" s="12"/>
+      <c r="C368" s="8"/>
+      <c r="D368" s="15"/>
       <c r="H368" s="5"/>
       <c r="I368" s="5"/>
       <c r="J368" s="5"/>
@@ -7783,6 +8422,10 @@
       <c r="P368" s="5"/>
     </row>
     <row r="369" ht="18.0" customHeight="1">
+      <c r="A369" s="12"/>
+      <c r="B369" s="12"/>
+      <c r="C369" s="8"/>
+      <c r="D369" s="15"/>
       <c r="H369" s="5"/>
       <c r="I369" s="5"/>
       <c r="J369" s="5"/>
@@ -7794,6 +8437,10 @@
       <c r="P369" s="5"/>
     </row>
     <row r="370" ht="18.0" customHeight="1">
+      <c r="A370" s="12"/>
+      <c r="B370" s="12"/>
+      <c r="C370" s="8"/>
+      <c r="D370" s="15"/>
       <c r="H370" s="5"/>
       <c r="I370" s="5"/>
       <c r="J370" s="5"/>
@@ -7805,6 +8452,10 @@
       <c r="P370" s="5"/>
     </row>
     <row r="371" ht="18.0" customHeight="1">
+      <c r="A371" s="12"/>
+      <c r="B371" s="12"/>
+      <c r="C371" s="8"/>
+      <c r="D371" s="15"/>
       <c r="H371" s="5"/>
       <c r="I371" s="5"/>
       <c r="J371" s="5"/>
@@ -7816,6 +8467,10 @@
       <c r="P371" s="5"/>
     </row>
     <row r="372" ht="18.0" customHeight="1">
+      <c r="A372" s="12"/>
+      <c r="B372" s="12"/>
+      <c r="C372" s="8"/>
+      <c r="D372" s="15"/>
       <c r="H372" s="5"/>
       <c r="I372" s="5"/>
       <c r="J372" s="5"/>
@@ -7827,6 +8482,10 @@
       <c r="P372" s="5"/>
     </row>
     <row r="373" ht="18.0" customHeight="1">
+      <c r="A373" s="12"/>
+      <c r="B373" s="12"/>
+      <c r="C373" s="8"/>
+      <c r="D373" s="15"/>
       <c r="H373" s="5"/>
       <c r="I373" s="5"/>
       <c r="J373" s="5"/>
@@ -7838,6 +8497,10 @@
       <c r="P373" s="5"/>
     </row>
     <row r="374" ht="18.0" customHeight="1">
+      <c r="A374" s="12"/>
+      <c r="B374" s="12"/>
+      <c r="C374" s="8"/>
+      <c r="D374" s="15"/>
       <c r="H374" s="5"/>
       <c r="I374" s="5"/>
       <c r="J374" s="5"/>
@@ -7849,6 +8512,10 @@
       <c r="P374" s="5"/>
     </row>
     <row r="375" ht="18.0" customHeight="1">
+      <c r="A375" s="12"/>
+      <c r="B375" s="12"/>
+      <c r="C375" s="8"/>
+      <c r="D375" s="15"/>
       <c r="H375" s="5"/>
       <c r="I375" s="5"/>
       <c r="J375" s="5"/>
@@ -7860,6 +8527,10 @@
       <c r="P375" s="5"/>
     </row>
     <row r="376" ht="18.0" customHeight="1">
+      <c r="A376" s="12"/>
+      <c r="B376" s="12"/>
+      <c r="C376" s="8"/>
+      <c r="D376" s="15"/>
       <c r="H376" s="5"/>
       <c r="I376" s="5"/>
       <c r="J376" s="5"/>
@@ -7871,6 +8542,10 @@
       <c r="P376" s="5"/>
     </row>
     <row r="377" ht="18.0" customHeight="1">
+      <c r="A377" s="12"/>
+      <c r="B377" s="12"/>
+      <c r="C377" s="8"/>
+      <c r="D377" s="15"/>
       <c r="H377" s="5"/>
       <c r="I377" s="5"/>
       <c r="J377" s="5"/>
@@ -7882,6 +8557,10 @@
       <c r="P377" s="5"/>
     </row>
     <row r="378" ht="18.0" customHeight="1">
+      <c r="A378" s="12"/>
+      <c r="B378" s="12"/>
+      <c r="C378" s="8"/>
+      <c r="D378" s="15"/>
       <c r="H378" s="5"/>
       <c r="I378" s="5"/>
       <c r="J378" s="5"/>
@@ -7893,6 +8572,10 @@
       <c r="P378" s="5"/>
     </row>
     <row r="379" ht="18.0" customHeight="1">
+      <c r="A379" s="12"/>
+      <c r="B379" s="12"/>
+      <c r="C379" s="8"/>
+      <c r="D379" s="15"/>
       <c r="H379" s="5"/>
       <c r="I379" s="5"/>
       <c r="J379" s="5"/>
@@ -7904,6 +8587,10 @@
       <c r="P379" s="5"/>
     </row>
     <row r="380" ht="18.0" customHeight="1">
+      <c r="A380" s="12"/>
+      <c r="B380" s="12"/>
+      <c r="C380" s="8"/>
+      <c r="D380" s="15"/>
       <c r="H380" s="5"/>
       <c r="I380" s="5"/>
       <c r="J380" s="5"/>
@@ -7915,6 +8602,10 @@
       <c r="P380" s="5"/>
     </row>
     <row r="381" ht="18.0" customHeight="1">
+      <c r="A381" s="12"/>
+      <c r="B381" s="12"/>
+      <c r="C381" s="8"/>
+      <c r="D381" s="15"/>
       <c r="H381" s="5"/>
       <c r="I381" s="5"/>
       <c r="J381" s="5"/>
@@ -7926,6 +8617,10 @@
       <c r="P381" s="5"/>
     </row>
     <row r="382" ht="18.0" customHeight="1">
+      <c r="A382" s="12"/>
+      <c r="B382" s="12"/>
+      <c r="C382" s="8"/>
+      <c r="D382" s="15"/>
       <c r="H382" s="5"/>
       <c r="I382" s="5"/>
       <c r="J382" s="5"/>
@@ -7937,6 +8632,10 @@
       <c r="P382" s="5"/>
     </row>
     <row r="383" ht="18.0" customHeight="1">
+      <c r="A383" s="12"/>
+      <c r="B383" s="12"/>
+      <c r="C383" s="8"/>
+      <c r="D383" s="15"/>
       <c r="H383" s="5"/>
       <c r="I383" s="5"/>
       <c r="J383" s="5"/>
@@ -7948,6 +8647,10 @@
       <c r="P383" s="5"/>
     </row>
     <row r="384" ht="18.0" customHeight="1">
+      <c r="A384" s="12"/>
+      <c r="B384" s="12"/>
+      <c r="C384" s="8"/>
+      <c r="D384" s="15"/>
       <c r="H384" s="5"/>
       <c r="I384" s="5"/>
       <c r="J384" s="5"/>
@@ -7958,7 +8661,14 @@
       <c r="O384" s="5"/>
       <c r="P384" s="5"/>
     </row>
-    <row r="385" ht="18.0" customHeight="1">
+    <row r="385" ht="34.5" customHeight="1">
+      <c r="A385" s="6"/>
+      <c r="B385" s="6"/>
+      <c r="C385" s="8"/>
+      <c r="D385" s="15"/>
+      <c r="E385" s="16"/>
+      <c r="F385" s="16"/>
+      <c r="G385" s="16"/>
       <c r="H385" s="5"/>
       <c r="I385" s="5"/>
       <c r="J385" s="5"/>
@@ -7970,6 +8680,13 @@
       <c r="P385" s="5"/>
     </row>
     <row r="386" ht="18.0" customHeight="1">
+      <c r="A386" s="6"/>
+      <c r="B386" s="6"/>
+      <c r="C386" s="8"/>
+      <c r="D386" s="15"/>
+      <c r="E386" s="16"/>
+      <c r="F386" s="17"/>
+      <c r="G386" s="17"/>
       <c r="H386" s="5"/>
       <c r="I386" s="5"/>
       <c r="J386" s="5"/>
@@ -7981,6 +8698,13 @@
       <c r="P386" s="5"/>
     </row>
     <row r="387" ht="18.0" customHeight="1">
+      <c r="A387" s="6"/>
+      <c r="B387" s="6"/>
+      <c r="C387" s="8"/>
+      <c r="D387" s="15"/>
+      <c r="E387" s="18"/>
+      <c r="F387" s="19"/>
+      <c r="G387" s="19"/>
       <c r="H387" s="5"/>
       <c r="I387" s="5"/>
       <c r="J387" s="5"/>
@@ -7992,6 +8716,13 @@
       <c r="P387" s="5"/>
     </row>
     <row r="388" ht="18.0" customHeight="1">
+      <c r="A388" s="6"/>
+      <c r="B388" s="6"/>
+      <c r="C388" s="8"/>
+      <c r="D388" s="15"/>
+      <c r="E388" s="18"/>
+      <c r="F388" s="19"/>
+      <c r="G388" s="19"/>
       <c r="H388" s="5"/>
       <c r="I388" s="5"/>
       <c r="J388" s="5"/>
@@ -8003,6 +8734,13 @@
       <c r="P388" s="5"/>
     </row>
     <row r="389" ht="18.0" customHeight="1">
+      <c r="A389" s="6"/>
+      <c r="B389" s="6"/>
+      <c r="C389" s="8"/>
+      <c r="D389" s="15"/>
+      <c r="E389" s="18"/>
+      <c r="F389" s="19"/>
+      <c r="G389" s="19"/>
       <c r="H389" s="5"/>
       <c r="I389" s="5"/>
       <c r="J389" s="5"/>
@@ -8014,6 +8752,13 @@
       <c r="P389" s="5"/>
     </row>
     <row r="390" ht="18.0" customHeight="1">
+      <c r="A390" s="6"/>
+      <c r="B390" s="6"/>
+      <c r="C390" s="8"/>
+      <c r="D390" s="15"/>
+      <c r="E390" s="18"/>
+      <c r="F390" s="19"/>
+      <c r="G390" s="19"/>
       <c r="H390" s="5"/>
       <c r="I390" s="5"/>
       <c r="J390" s="5"/>
@@ -8025,6 +8770,13 @@
       <c r="P390" s="5"/>
     </row>
     <row r="391" ht="18.0" customHeight="1">
+      <c r="A391" s="6"/>
+      <c r="B391" s="6"/>
+      <c r="C391" s="8"/>
+      <c r="D391" s="15"/>
+      <c r="E391" s="18"/>
+      <c r="F391" s="19"/>
+      <c r="G391" s="19"/>
       <c r="H391" s="5"/>
       <c r="I391" s="5"/>
       <c r="J391" s="5"/>
@@ -8036,6 +8788,13 @@
       <c r="P391" s="5"/>
     </row>
     <row r="392" ht="18.0" customHeight="1">
+      <c r="A392" s="6"/>
+      <c r="B392" s="6"/>
+      <c r="C392" s="8"/>
+      <c r="D392" s="15"/>
+      <c r="E392" s="18"/>
+      <c r="F392" s="19"/>
+      <c r="G392" s="19"/>
       <c r="H392" s="5"/>
       <c r="I392" s="5"/>
       <c r="J392" s="5"/>
@@ -8046,8 +8805,14 @@
       <c r="O392" s="5"/>
       <c r="P392" s="5"/>
     </row>
-    <row r="393" ht="34.5" customHeight="1">
-      <c r="A393" s="10"/>
+    <row r="393" ht="18.0" customHeight="1">
+      <c r="A393" s="6"/>
+      <c r="B393" s="6"/>
+      <c r="C393" s="8"/>
+      <c r="D393" s="15"/>
+      <c r="E393" s="18"/>
+      <c r="F393" s="19"/>
+      <c r="G393" s="19"/>
       <c r="H393" s="5"/>
       <c r="I393" s="5"/>
       <c r="J393" s="5"/>
@@ -8059,13 +8824,13 @@
       <c r="P393" s="5"/>
     </row>
     <row r="394" ht="18.0" customHeight="1">
-      <c r="A394" s="10"/>
-      <c r="B394" s="10"/>
-      <c r="C394" s="10"/>
-      <c r="D394" s="10"/>
-      <c r="E394" s="10"/>
-      <c r="F394" s="11"/>
-      <c r="G394" s="11"/>
+      <c r="A394" s="6"/>
+      <c r="B394" s="6"/>
+      <c r="C394" s="8"/>
+      <c r="D394" s="15"/>
+      <c r="E394" s="18"/>
+      <c r="F394" s="19"/>
+      <c r="G394" s="19"/>
       <c r="H394" s="5"/>
       <c r="I394" s="5"/>
       <c r="J394" s="5"/>
@@ -8077,13 +8842,13 @@
       <c r="P394" s="5"/>
     </row>
     <row r="395" ht="18.0" customHeight="1">
-      <c r="A395" s="12"/>
-      <c r="B395" s="12"/>
-      <c r="C395" s="12"/>
-      <c r="D395" s="12"/>
-      <c r="E395" s="12"/>
-      <c r="F395" s="13"/>
-      <c r="G395" s="13"/>
+      <c r="A395" s="6"/>
+      <c r="B395" s="6"/>
+      <c r="C395" s="8"/>
+      <c r="D395" s="15"/>
+      <c r="E395" s="18"/>
+      <c r="F395" s="19"/>
+      <c r="G395" s="19"/>
       <c r="H395" s="5"/>
       <c r="I395" s="5"/>
       <c r="J395" s="5"/>
@@ -8095,13 +8860,13 @@
       <c r="P395" s="5"/>
     </row>
     <row r="396" ht="18.0" customHeight="1">
-      <c r="A396" s="12"/>
-      <c r="B396" s="12"/>
-      <c r="C396" s="12"/>
-      <c r="D396" s="12"/>
-      <c r="E396" s="12"/>
-      <c r="F396" s="13"/>
-      <c r="G396" s="13"/>
+      <c r="A396" s="6"/>
+      <c r="B396" s="6"/>
+      <c r="C396" s="8"/>
+      <c r="D396" s="15"/>
+      <c r="E396" s="18"/>
+      <c r="F396" s="19"/>
+      <c r="G396" s="19"/>
       <c r="H396" s="5"/>
       <c r="I396" s="5"/>
       <c r="J396" s="5"/>
@@ -8113,13 +8878,13 @@
       <c r="P396" s="5"/>
     </row>
     <row r="397" ht="18.0" customHeight="1">
-      <c r="A397" s="12"/>
-      <c r="B397" s="12"/>
-      <c r="C397" s="12"/>
-      <c r="D397" s="12"/>
-      <c r="E397" s="12"/>
-      <c r="F397" s="13"/>
-      <c r="G397" s="13"/>
+      <c r="A397" s="6"/>
+      <c r="B397" s="6"/>
+      <c r="C397" s="8"/>
+      <c r="D397" s="15"/>
+      <c r="E397" s="18"/>
+      <c r="F397" s="19"/>
+      <c r="G397" s="19"/>
       <c r="H397" s="5"/>
       <c r="I397" s="5"/>
       <c r="J397" s="5"/>
@@ -8131,13 +8896,13 @@
       <c r="P397" s="5"/>
     </row>
     <row r="398" ht="18.0" customHeight="1">
-      <c r="A398" s="12"/>
-      <c r="B398" s="12"/>
-      <c r="C398" s="12"/>
-      <c r="D398" s="12"/>
-      <c r="E398" s="12"/>
-      <c r="F398" s="13"/>
-      <c r="G398" s="13"/>
+      <c r="A398" s="6"/>
+      <c r="B398" s="6"/>
+      <c r="C398" s="8"/>
+      <c r="D398" s="15"/>
+      <c r="E398" s="18"/>
+      <c r="F398" s="19"/>
+      <c r="G398" s="19"/>
       <c r="H398" s="5"/>
       <c r="I398" s="5"/>
       <c r="J398" s="5"/>
@@ -8149,13 +8914,13 @@
       <c r="P398" s="5"/>
     </row>
     <row r="399" ht="18.0" customHeight="1">
-      <c r="A399" s="12"/>
-      <c r="B399" s="12"/>
-      <c r="C399" s="12"/>
-      <c r="D399" s="12"/>
-      <c r="E399" s="12"/>
-      <c r="F399" s="13"/>
-      <c r="G399" s="13"/>
+      <c r="A399" s="6"/>
+      <c r="B399" s="6"/>
+      <c r="C399" s="8"/>
+      <c r="D399" s="15"/>
+      <c r="E399" s="18"/>
+      <c r="F399" s="19"/>
+      <c r="G399" s="19"/>
       <c r="H399" s="5"/>
       <c r="I399" s="5"/>
       <c r="J399" s="5"/>
@@ -8167,13 +8932,13 @@
       <c r="P399" s="5"/>
     </row>
     <row r="400" ht="18.0" customHeight="1">
-      <c r="A400" s="12"/>
-      <c r="B400" s="12"/>
-      <c r="C400" s="12"/>
-      <c r="D400" s="12"/>
-      <c r="E400" s="12"/>
-      <c r="F400" s="13"/>
-      <c r="G400" s="13"/>
+      <c r="A400" s="6"/>
+      <c r="B400" s="6"/>
+      <c r="C400" s="8"/>
+      <c r="D400" s="15"/>
+      <c r="E400" s="18"/>
+      <c r="F400" s="19"/>
+      <c r="G400" s="19"/>
       <c r="H400" s="5"/>
       <c r="I400" s="5"/>
       <c r="J400" s="5"/>
@@ -8185,13 +8950,13 @@
       <c r="P400" s="5"/>
     </row>
     <row r="401" ht="18.0" customHeight="1">
-      <c r="A401" s="12"/>
-      <c r="B401" s="12"/>
-      <c r="C401" s="12"/>
-      <c r="D401" s="12"/>
-      <c r="E401" s="12"/>
-      <c r="F401" s="13"/>
-      <c r="G401" s="13"/>
+      <c r="A401" s="6"/>
+      <c r="B401" s="6"/>
+      <c r="C401" s="8"/>
+      <c r="D401" s="15"/>
+      <c r="E401" s="18"/>
+      <c r="F401" s="19"/>
+      <c r="G401" s="19"/>
       <c r="H401" s="5"/>
       <c r="I401" s="5"/>
       <c r="J401" s="5"/>
@@ -8203,13 +8968,13 @@
       <c r="P401" s="5"/>
     </row>
     <row r="402" ht="18.0" customHeight="1">
-      <c r="A402" s="12"/>
-      <c r="B402" s="12"/>
-      <c r="C402" s="12"/>
-      <c r="D402" s="12"/>
-      <c r="E402" s="12"/>
-      <c r="F402" s="13"/>
-      <c r="G402" s="13"/>
+      <c r="A402" s="6"/>
+      <c r="B402" s="6"/>
+      <c r="C402" s="8"/>
+      <c r="D402" s="15"/>
+      <c r="E402" s="18"/>
+      <c r="F402" s="19"/>
+      <c r="G402" s="19"/>
       <c r="H402" s="5"/>
       <c r="I402" s="5"/>
       <c r="J402" s="5"/>
@@ -8221,13 +8986,13 @@
       <c r="P402" s="5"/>
     </row>
     <row r="403" ht="18.0" customHeight="1">
-      <c r="A403" s="12"/>
-      <c r="B403" s="12"/>
-      <c r="C403" s="12"/>
-      <c r="D403" s="12"/>
-      <c r="E403" s="12"/>
-      <c r="F403" s="13"/>
-      <c r="G403" s="13"/>
+      <c r="A403" s="6"/>
+      <c r="B403" s="6"/>
+      <c r="C403" s="8"/>
+      <c r="D403" s="15"/>
+      <c r="E403" s="18"/>
+      <c r="F403" s="19"/>
+      <c r="G403" s="19"/>
       <c r="H403" s="5"/>
       <c r="I403" s="5"/>
       <c r="J403" s="5"/>
@@ -8239,13 +9004,13 @@
       <c r="P403" s="5"/>
     </row>
     <row r="404" ht="18.0" customHeight="1">
-      <c r="A404" s="12"/>
-      <c r="B404" s="12"/>
-      <c r="C404" s="12"/>
-      <c r="D404" s="12"/>
-      <c r="E404" s="12"/>
-      <c r="F404" s="13"/>
-      <c r="G404" s="13"/>
+      <c r="A404" s="6"/>
+      <c r="B404" s="6"/>
+      <c r="C404" s="8"/>
+      <c r="D404" s="15"/>
+      <c r="E404" s="18"/>
+      <c r="F404" s="19"/>
+      <c r="G404" s="19"/>
       <c r="H404" s="5"/>
       <c r="I404" s="5"/>
       <c r="J404" s="5"/>
@@ -8257,13 +9022,13 @@
       <c r="P404" s="5"/>
     </row>
     <row r="405" ht="18.0" customHeight="1">
-      <c r="A405" s="12"/>
-      <c r="B405" s="12"/>
-      <c r="C405" s="12"/>
-      <c r="D405" s="12"/>
-      <c r="E405" s="12"/>
-      <c r="F405" s="13"/>
-      <c r="G405" s="13"/>
+      <c r="A405" s="6"/>
+      <c r="B405" s="6"/>
+      <c r="C405" s="8"/>
+      <c r="D405" s="15"/>
+      <c r="E405" s="18"/>
+      <c r="F405" s="19"/>
+      <c r="G405" s="19"/>
       <c r="H405" s="5"/>
       <c r="I405" s="5"/>
       <c r="J405" s="5"/>
@@ -8275,13 +9040,13 @@
       <c r="P405" s="5"/>
     </row>
     <row r="406" ht="18.0" customHeight="1">
-      <c r="A406" s="12"/>
-      <c r="B406" s="12"/>
-      <c r="C406" s="12"/>
-      <c r="D406" s="12"/>
-      <c r="E406" s="12"/>
-      <c r="F406" s="13"/>
-      <c r="G406" s="13"/>
+      <c r="A406" s="6"/>
+      <c r="B406" s="6"/>
+      <c r="C406" s="8"/>
+      <c r="D406" s="15"/>
+      <c r="E406" s="18"/>
+      <c r="F406" s="19"/>
+      <c r="G406" s="19"/>
       <c r="H406" s="5"/>
       <c r="I406" s="5"/>
       <c r="J406" s="5"/>
@@ -8293,13 +9058,13 @@
       <c r="P406" s="5"/>
     </row>
     <row r="407" ht="18.0" customHeight="1">
-      <c r="A407" s="12"/>
-      <c r="B407" s="12"/>
-      <c r="C407" s="12"/>
-      <c r="D407" s="12"/>
-      <c r="E407" s="12"/>
-      <c r="F407" s="13"/>
-      <c r="G407" s="13"/>
+      <c r="A407" s="6"/>
+      <c r="B407" s="6"/>
+      <c r="C407" s="8"/>
+      <c r="D407" s="15"/>
+      <c r="E407" s="18"/>
+      <c r="F407" s="19"/>
+      <c r="G407" s="19"/>
       <c r="H407" s="5"/>
       <c r="I407" s="5"/>
       <c r="J407" s="5"/>
@@ -8311,13 +9076,13 @@
       <c r="P407" s="5"/>
     </row>
     <row r="408" ht="18.0" customHeight="1">
-      <c r="A408" s="12"/>
-      <c r="B408" s="12"/>
-      <c r="C408" s="12"/>
-      <c r="D408" s="12"/>
-      <c r="E408" s="12"/>
-      <c r="F408" s="13"/>
-      <c r="G408" s="13"/>
+      <c r="A408" s="6"/>
+      <c r="B408" s="6"/>
+      <c r="C408" s="8"/>
+      <c r="D408" s="15"/>
+      <c r="E408" s="18"/>
+      <c r="F408" s="19"/>
+      <c r="G408" s="19"/>
       <c r="H408" s="5"/>
       <c r="I408" s="5"/>
       <c r="J408" s="5"/>
@@ -8329,13 +9094,13 @@
       <c r="P408" s="5"/>
     </row>
     <row r="409" ht="18.0" customHeight="1">
-      <c r="A409" s="12"/>
-      <c r="B409" s="12"/>
-      <c r="C409" s="12"/>
-      <c r="D409" s="12"/>
-      <c r="E409" s="12"/>
-      <c r="F409" s="13"/>
-      <c r="G409" s="13"/>
+      <c r="A409" s="6"/>
+      <c r="B409" s="6"/>
+      <c r="C409" s="8"/>
+      <c r="D409" s="15"/>
+      <c r="E409" s="18"/>
+      <c r="F409" s="19"/>
+      <c r="G409" s="19"/>
       <c r="H409" s="5"/>
       <c r="I409" s="5"/>
       <c r="J409" s="5"/>
@@ -8347,13 +9112,13 @@
       <c r="P409" s="5"/>
     </row>
     <row r="410" ht="18.0" customHeight="1">
-      <c r="A410" s="12"/>
-      <c r="B410" s="12"/>
-      <c r="C410" s="12"/>
-      <c r="D410" s="12"/>
-      <c r="E410" s="12"/>
-      <c r="F410" s="13"/>
-      <c r="G410" s="13"/>
+      <c r="A410" s="6"/>
+      <c r="B410" s="6"/>
+      <c r="C410" s="8"/>
+      <c r="D410" s="15"/>
+      <c r="E410" s="18"/>
+      <c r="F410" s="19"/>
+      <c r="G410" s="19"/>
       <c r="H410" s="5"/>
       <c r="I410" s="5"/>
       <c r="J410" s="5"/>
@@ -8365,13 +9130,13 @@
       <c r="P410" s="5"/>
     </row>
     <row r="411" ht="18.0" customHeight="1">
-      <c r="A411" s="12"/>
-      <c r="B411" s="12"/>
-      <c r="C411" s="12"/>
-      <c r="D411" s="12"/>
-      <c r="E411" s="12"/>
-      <c r="F411" s="13"/>
-      <c r="G411" s="13"/>
+      <c r="A411" s="6"/>
+      <c r="B411" s="6"/>
+      <c r="C411" s="8"/>
+      <c r="D411" s="15"/>
+      <c r="E411" s="18"/>
+      <c r="F411" s="19"/>
+      <c r="G411" s="19"/>
       <c r="H411" s="5"/>
       <c r="I411" s="5"/>
       <c r="J411" s="5"/>
@@ -8383,13 +9148,13 @@
       <c r="P411" s="5"/>
     </row>
     <row r="412" ht="18.0" customHeight="1">
-      <c r="A412" s="12"/>
-      <c r="B412" s="12"/>
-      <c r="C412" s="12"/>
-      <c r="D412" s="12"/>
-      <c r="E412" s="12"/>
-      <c r="F412" s="13"/>
-      <c r="G412" s="13"/>
+      <c r="A412" s="6"/>
+      <c r="B412" s="6"/>
+      <c r="C412" s="8"/>
+      <c r="D412" s="15"/>
+      <c r="E412" s="18"/>
+      <c r="F412" s="19"/>
+      <c r="G412" s="19"/>
       <c r="H412" s="5"/>
       <c r="I412" s="5"/>
       <c r="J412" s="5"/>
@@ -8401,13 +9166,13 @@
       <c r="P412" s="5"/>
     </row>
     <row r="413" ht="18.0" customHeight="1">
-      <c r="A413" s="12"/>
-      <c r="B413" s="12"/>
-      <c r="C413" s="12"/>
-      <c r="D413" s="12"/>
-      <c r="E413" s="12"/>
-      <c r="F413" s="13"/>
-      <c r="G413" s="13"/>
+      <c r="A413" s="6"/>
+      <c r="B413" s="6"/>
+      <c r="C413" s="8"/>
+      <c r="D413" s="15"/>
+      <c r="E413" s="18"/>
+      <c r="F413" s="19"/>
+      <c r="G413" s="19"/>
       <c r="H413" s="5"/>
       <c r="I413" s="5"/>
       <c r="J413" s="5"/>
@@ -8419,13 +9184,13 @@
       <c r="P413" s="5"/>
     </row>
     <row r="414" ht="18.0" customHeight="1">
-      <c r="A414" s="12"/>
-      <c r="B414" s="12"/>
-      <c r="C414" s="12"/>
-      <c r="D414" s="12"/>
-      <c r="E414" s="12"/>
-      <c r="F414" s="13"/>
-      <c r="G414" s="13"/>
+      <c r="A414" s="6"/>
+      <c r="B414" s="6"/>
+      <c r="C414" s="8"/>
+      <c r="D414" s="15"/>
+      <c r="E414" s="18"/>
+      <c r="F414" s="19"/>
+      <c r="G414" s="19"/>
       <c r="H414" s="5"/>
       <c r="I414" s="5"/>
       <c r="J414" s="5"/>
@@ -8437,13 +9202,13 @@
       <c r="P414" s="5"/>
     </row>
     <row r="415" ht="18.0" customHeight="1">
-      <c r="A415" s="12"/>
-      <c r="B415" s="12"/>
-      <c r="C415" s="12"/>
-      <c r="D415" s="12"/>
-      <c r="E415" s="12"/>
-      <c r="F415" s="13"/>
-      <c r="G415" s="13"/>
+      <c r="A415" s="6"/>
+      <c r="B415" s="6"/>
+      <c r="C415" s="8"/>
+      <c r="D415" s="15"/>
+      <c r="E415" s="18"/>
+      <c r="F415" s="19"/>
+      <c r="G415" s="19"/>
       <c r="H415" s="5"/>
       <c r="I415" s="5"/>
       <c r="J415" s="5"/>
@@ -8455,13 +9220,13 @@
       <c r="P415" s="5"/>
     </row>
     <row r="416" ht="18.0" customHeight="1">
-      <c r="A416" s="12"/>
-      <c r="B416" s="12"/>
-      <c r="C416" s="12"/>
-      <c r="D416" s="12"/>
-      <c r="E416" s="12"/>
-      <c r="F416" s="13"/>
-      <c r="G416" s="13"/>
+      <c r="A416" s="6"/>
+      <c r="B416" s="6"/>
+      <c r="C416" s="8"/>
+      <c r="D416" s="15"/>
+      <c r="E416" s="18"/>
+      <c r="F416" s="19"/>
+      <c r="G416" s="19"/>
       <c r="H416" s="5"/>
       <c r="I416" s="5"/>
       <c r="J416" s="5"/>
@@ -8473,13 +9238,13 @@
       <c r="P416" s="5"/>
     </row>
     <row r="417" ht="18.0" customHeight="1">
-      <c r="A417" s="12"/>
-      <c r="B417" s="12"/>
-      <c r="C417" s="12"/>
-      <c r="D417" s="12"/>
-      <c r="E417" s="12"/>
-      <c r="F417" s="13"/>
-      <c r="G417" s="13"/>
+      <c r="A417" s="6"/>
+      <c r="B417" s="6"/>
+      <c r="C417" s="8"/>
+      <c r="D417" s="15"/>
+      <c r="E417" s="18"/>
+      <c r="F417" s="19"/>
+      <c r="G417" s="19"/>
       <c r="H417" s="5"/>
       <c r="I417" s="5"/>
       <c r="J417" s="5"/>
@@ -8491,13 +9256,13 @@
       <c r="P417" s="5"/>
     </row>
     <row r="418" ht="18.0" customHeight="1">
-      <c r="A418" s="12"/>
-      <c r="B418" s="12"/>
-      <c r="C418" s="12"/>
-      <c r="D418" s="12"/>
-      <c r="E418" s="12"/>
-      <c r="F418" s="13"/>
-      <c r="G418" s="13"/>
+      <c r="A418" s="6"/>
+      <c r="B418" s="6"/>
+      <c r="C418" s="8"/>
+      <c r="D418" s="15"/>
+      <c r="E418" s="18"/>
+      <c r="F418" s="19"/>
+      <c r="G418" s="19"/>
       <c r="H418" s="5"/>
       <c r="I418" s="5"/>
       <c r="J418" s="5"/>
@@ -8509,13 +9274,13 @@
       <c r="P418" s="5"/>
     </row>
     <row r="419" ht="18.0" customHeight="1">
-      <c r="A419" s="12"/>
-      <c r="B419" s="12"/>
-      <c r="C419" s="12"/>
-      <c r="D419" s="12"/>
-      <c r="E419" s="12"/>
-      <c r="F419" s="13"/>
-      <c r="G419" s="13"/>
+      <c r="A419" s="6"/>
+      <c r="B419" s="6"/>
+      <c r="C419" s="8"/>
+      <c r="D419" s="15"/>
+      <c r="E419" s="18"/>
+      <c r="F419" s="19"/>
+      <c r="G419" s="19"/>
       <c r="H419" s="5"/>
       <c r="I419" s="5"/>
       <c r="J419" s="5"/>
@@ -8527,13 +9292,13 @@
       <c r="P419" s="5"/>
     </row>
     <row r="420" ht="18.0" customHeight="1">
-      <c r="A420" s="12"/>
-      <c r="B420" s="12"/>
-      <c r="C420" s="12"/>
-      <c r="D420" s="12"/>
-      <c r="E420" s="12"/>
-      <c r="F420" s="13"/>
-      <c r="G420" s="13"/>
+      <c r="A420" s="6"/>
+      <c r="B420" s="6"/>
+      <c r="C420" s="8"/>
+      <c r="D420" s="15"/>
+      <c r="E420" s="18"/>
+      <c r="F420" s="19"/>
+      <c r="G420" s="19"/>
       <c r="H420" s="5"/>
       <c r="I420" s="5"/>
       <c r="J420" s="5"/>
@@ -8545,13 +9310,13 @@
       <c r="P420" s="5"/>
     </row>
     <row r="421" ht="18.0" customHeight="1">
-      <c r="A421" s="12"/>
-      <c r="B421" s="12"/>
-      <c r="C421" s="12"/>
-      <c r="D421" s="12"/>
-      <c r="E421" s="12"/>
-      <c r="F421" s="13"/>
-      <c r="G421" s="13"/>
+      <c r="A421" s="6"/>
+      <c r="B421" s="6"/>
+      <c r="C421" s="8"/>
+      <c r="D421" s="15"/>
+      <c r="E421" s="18"/>
+      <c r="F421" s="19"/>
+      <c r="G421" s="19"/>
       <c r="H421" s="5"/>
       <c r="I421" s="5"/>
       <c r="J421" s="5"/>
@@ -8563,13 +9328,13 @@
       <c r="P421" s="5"/>
     </row>
     <row r="422" ht="18.0" customHeight="1">
-      <c r="A422" s="12"/>
-      <c r="B422" s="12"/>
-      <c r="C422" s="12"/>
-      <c r="D422" s="12"/>
-      <c r="E422" s="12"/>
-      <c r="F422" s="13"/>
-      <c r="G422" s="13"/>
+      <c r="A422" s="6"/>
+      <c r="B422" s="6"/>
+      <c r="C422" s="8"/>
+      <c r="D422" s="15"/>
+      <c r="E422" s="18"/>
+      <c r="F422" s="19"/>
+      <c r="G422" s="19"/>
       <c r="H422" s="5"/>
       <c r="I422" s="5"/>
       <c r="J422" s="5"/>
@@ -8581,13 +9346,13 @@
       <c r="P422" s="5"/>
     </row>
     <row r="423" ht="18.0" customHeight="1">
-      <c r="A423" s="12"/>
-      <c r="B423" s="12"/>
-      <c r="C423" s="12"/>
-      <c r="D423" s="12"/>
-      <c r="E423" s="12"/>
-      <c r="F423" s="13"/>
-      <c r="G423" s="13"/>
+      <c r="A423" s="6"/>
+      <c r="B423" s="6"/>
+      <c r="C423" s="8"/>
+      <c r="D423" s="15"/>
+      <c r="E423" s="18"/>
+      <c r="F423" s="19"/>
+      <c r="G423" s="19"/>
       <c r="H423" s="5"/>
       <c r="I423" s="5"/>
       <c r="J423" s="5"/>
@@ -8599,13 +9364,13 @@
       <c r="P423" s="5"/>
     </row>
     <row r="424" ht="18.0" customHeight="1">
-      <c r="A424" s="12"/>
-      <c r="B424" s="12"/>
-      <c r="C424" s="12"/>
-      <c r="D424" s="12"/>
-      <c r="E424" s="12"/>
-      <c r="F424" s="13"/>
-      <c r="G424" s="13"/>
+      <c r="A424" s="6"/>
+      <c r="B424" s="6"/>
+      <c r="C424" s="8"/>
+      <c r="D424" s="15"/>
+      <c r="E424" s="18"/>
+      <c r="F424" s="19"/>
+      <c r="G424" s="19"/>
       <c r="H424" s="5"/>
       <c r="I424" s="5"/>
       <c r="J424" s="5"/>
@@ -8617,13 +9382,13 @@
       <c r="P424" s="5"/>
     </row>
     <row r="425" ht="18.0" customHeight="1">
-      <c r="A425" s="12"/>
-      <c r="B425" s="12"/>
-      <c r="C425" s="12"/>
-      <c r="D425" s="12"/>
-      <c r="E425" s="12"/>
-      <c r="F425" s="13"/>
-      <c r="G425" s="13"/>
+      <c r="A425" s="6"/>
+      <c r="B425" s="6"/>
+      <c r="C425" s="8"/>
+      <c r="D425" s="15"/>
+      <c r="E425" s="18"/>
+      <c r="F425" s="19"/>
+      <c r="G425" s="19"/>
       <c r="H425" s="5"/>
       <c r="I425" s="5"/>
       <c r="J425" s="5"/>
@@ -8635,13 +9400,13 @@
       <c r="P425" s="5"/>
     </row>
     <row r="426" ht="18.0" customHeight="1">
-      <c r="A426" s="12"/>
-      <c r="B426" s="12"/>
-      <c r="C426" s="12"/>
-      <c r="D426" s="12"/>
-      <c r="E426" s="12"/>
-      <c r="F426" s="13"/>
-      <c r="G426" s="13"/>
+      <c r="A426" s="6"/>
+      <c r="B426" s="6"/>
+      <c r="C426" s="8"/>
+      <c r="D426" s="15"/>
+      <c r="E426" s="18"/>
+      <c r="F426" s="19"/>
+      <c r="G426" s="19"/>
       <c r="H426" s="5"/>
       <c r="I426" s="5"/>
       <c r="J426" s="5"/>
@@ -8652,1792 +9417,7 @@
       <c r="O426" s="5"/>
       <c r="P426" s="5"/>
     </row>
-    <row r="427" ht="18.0" customHeight="1">
-      <c r="A427" s="12"/>
-      <c r="B427" s="12"/>
-      <c r="C427" s="12"/>
-      <c r="D427" s="12"/>
-      <c r="E427" s="12"/>
-      <c r="F427" s="13"/>
-      <c r="G427" s="13"/>
-      <c r="H427" s="5"/>
-      <c r="I427" s="5"/>
-      <c r="J427" s="5"/>
-      <c r="K427" s="5"/>
-      <c r="L427" s="5"/>
-      <c r="M427" s="5"/>
-      <c r="N427" s="5"/>
-      <c r="O427" s="5"/>
-      <c r="P427" s="5"/>
-    </row>
-    <row r="428" ht="18.0" customHeight="1">
-      <c r="A428" s="12"/>
-      <c r="B428" s="12"/>
-      <c r="C428" s="12"/>
-      <c r="D428" s="12"/>
-      <c r="E428" s="12"/>
-      <c r="F428" s="13"/>
-      <c r="G428" s="13"/>
-      <c r="H428" s="5"/>
-      <c r="I428" s="5"/>
-      <c r="J428" s="5"/>
-      <c r="K428" s="5"/>
-      <c r="L428" s="5"/>
-      <c r="M428" s="5"/>
-      <c r="N428" s="5"/>
-      <c r="O428" s="5"/>
-      <c r="P428" s="5"/>
-    </row>
-    <row r="429" ht="18.0" customHeight="1">
-      <c r="A429" s="12"/>
-      <c r="B429" s="12"/>
-      <c r="C429" s="12"/>
-      <c r="D429" s="12"/>
-      <c r="E429" s="12"/>
-      <c r="F429" s="13"/>
-      <c r="G429" s="13"/>
-      <c r="H429" s="5"/>
-      <c r="I429" s="5"/>
-      <c r="J429" s="5"/>
-      <c r="K429" s="5"/>
-      <c r="L429" s="5"/>
-      <c r="M429" s="5"/>
-      <c r="N429" s="5"/>
-      <c r="O429" s="5"/>
-      <c r="P429" s="5"/>
-    </row>
-    <row r="430" ht="18.0" customHeight="1">
-      <c r="A430" s="12"/>
-      <c r="B430" s="12"/>
-      <c r="C430" s="12"/>
-      <c r="D430" s="12"/>
-      <c r="E430" s="12"/>
-      <c r="F430" s="13"/>
-      <c r="G430" s="13"/>
-      <c r="H430" s="5"/>
-      <c r="I430" s="5"/>
-      <c r="J430" s="5"/>
-      <c r="K430" s="5"/>
-      <c r="L430" s="5"/>
-      <c r="M430" s="5"/>
-      <c r="N430" s="5"/>
-      <c r="O430" s="5"/>
-      <c r="P430" s="5"/>
-    </row>
-    <row r="431" ht="18.0" customHeight="1">
-      <c r="A431" s="12"/>
-      <c r="B431" s="12"/>
-      <c r="C431" s="12"/>
-      <c r="D431" s="12"/>
-      <c r="E431" s="12"/>
-      <c r="F431" s="13"/>
-      <c r="G431" s="13"/>
-      <c r="H431" s="5"/>
-      <c r="I431" s="5"/>
-      <c r="J431" s="5"/>
-      <c r="K431" s="5"/>
-      <c r="L431" s="5"/>
-      <c r="M431" s="5"/>
-      <c r="N431" s="5"/>
-      <c r="O431" s="5"/>
-      <c r="P431" s="5"/>
-    </row>
-    <row r="432" ht="18.0" customHeight="1">
-      <c r="A432" s="12"/>
-      <c r="B432" s="12"/>
-      <c r="C432" s="12"/>
-      <c r="D432" s="12"/>
-      <c r="E432" s="12"/>
-      <c r="F432" s="13"/>
-      <c r="G432" s="13"/>
-      <c r="H432" s="5"/>
-      <c r="I432" s="5"/>
-      <c r="J432" s="5"/>
-      <c r="K432" s="5"/>
-      <c r="L432" s="5"/>
-      <c r="M432" s="5"/>
-      <c r="N432" s="5"/>
-      <c r="O432" s="5"/>
-      <c r="P432" s="5"/>
-    </row>
-    <row r="433" ht="18.0" customHeight="1">
-      <c r="A433" s="12"/>
-      <c r="B433" s="12"/>
-      <c r="C433" s="12"/>
-      <c r="D433" s="12"/>
-      <c r="E433" s="12"/>
-      <c r="F433" s="13"/>
-      <c r="G433" s="13"/>
-      <c r="H433" s="5"/>
-      <c r="I433" s="5"/>
-      <c r="J433" s="5"/>
-      <c r="K433" s="5"/>
-      <c r="L433" s="5"/>
-      <c r="M433" s="5"/>
-      <c r="N433" s="5"/>
-      <c r="O433" s="5"/>
-      <c r="P433" s="5"/>
-    </row>
-    <row r="434" ht="18.0" customHeight="1">
-      <c r="A434" s="12"/>
-      <c r="B434" s="12"/>
-      <c r="C434" s="12"/>
-      <c r="D434" s="12"/>
-      <c r="E434" s="12"/>
-      <c r="F434" s="13"/>
-      <c r="G434" s="13"/>
-      <c r="H434" s="5"/>
-      <c r="I434" s="5"/>
-      <c r="J434" s="5"/>
-      <c r="K434" s="5"/>
-      <c r="L434" s="5"/>
-      <c r="M434" s="5"/>
-      <c r="N434" s="5"/>
-      <c r="O434" s="5"/>
-      <c r="P434" s="5"/>
-    </row>
-    <row r="435" ht="18.0" customHeight="1">
-      <c r="A435" s="12"/>
-      <c r="B435" s="12"/>
-      <c r="C435" s="12"/>
-      <c r="D435" s="12"/>
-      <c r="E435" s="12"/>
-      <c r="F435" s="13"/>
-      <c r="G435" s="13"/>
-      <c r="H435" s="5"/>
-      <c r="I435" s="5"/>
-      <c r="J435" s="5"/>
-      <c r="K435" s="5"/>
-      <c r="L435" s="5"/>
-      <c r="M435" s="5"/>
-      <c r="N435" s="5"/>
-      <c r="O435" s="5"/>
-      <c r="P435" s="5"/>
-    </row>
-    <row r="436" ht="18.0" customHeight="1">
-      <c r="A436" s="12"/>
-      <c r="B436" s="12"/>
-      <c r="C436" s="12"/>
-      <c r="D436" s="12"/>
-      <c r="E436" s="12"/>
-      <c r="F436" s="13"/>
-      <c r="G436" s="13"/>
-      <c r="H436" s="5"/>
-      <c r="I436" s="5"/>
-      <c r="J436" s="5"/>
-      <c r="K436" s="5"/>
-      <c r="L436" s="5"/>
-      <c r="M436" s="5"/>
-      <c r="N436" s="5"/>
-      <c r="O436" s="5"/>
-      <c r="P436" s="5"/>
-    </row>
-    <row r="437" ht="18.0" customHeight="1">
-      <c r="A437" s="12"/>
-      <c r="B437" s="12"/>
-      <c r="C437" s="12"/>
-      <c r="D437" s="12"/>
-      <c r="E437" s="12"/>
-      <c r="F437" s="13"/>
-      <c r="G437" s="13"/>
-      <c r="H437" s="5"/>
-      <c r="I437" s="5"/>
-      <c r="J437" s="5"/>
-      <c r="K437" s="5"/>
-      <c r="L437" s="5"/>
-      <c r="M437" s="5"/>
-      <c r="N437" s="5"/>
-      <c r="O437" s="5"/>
-      <c r="P437" s="5"/>
-    </row>
-    <row r="438" ht="18.0" customHeight="1">
-      <c r="A438" s="12"/>
-      <c r="B438" s="12"/>
-      <c r="C438" s="12"/>
-      <c r="D438" s="12"/>
-      <c r="E438" s="12"/>
-      <c r="F438" s="13"/>
-      <c r="G438" s="13"/>
-      <c r="H438" s="5"/>
-      <c r="I438" s="5"/>
-      <c r="J438" s="5"/>
-      <c r="K438" s="5"/>
-      <c r="L438" s="5"/>
-      <c r="M438" s="5"/>
-      <c r="N438" s="5"/>
-      <c r="O438" s="5"/>
-      <c r="P438" s="5"/>
-    </row>
-    <row r="439" ht="18.0" customHeight="1">
-      <c r="A439" s="12"/>
-      <c r="B439" s="12"/>
-      <c r="C439" s="12"/>
-      <c r="D439" s="12"/>
-      <c r="E439" s="12"/>
-      <c r="F439" s="13"/>
-      <c r="G439" s="13"/>
-      <c r="H439" s="5"/>
-      <c r="I439" s="5"/>
-      <c r="J439" s="5"/>
-      <c r="K439" s="5"/>
-      <c r="L439" s="5"/>
-      <c r="M439" s="5"/>
-      <c r="N439" s="5"/>
-      <c r="O439" s="5"/>
-      <c r="P439" s="5"/>
-    </row>
-    <row r="440" ht="18.0" customHeight="1">
-      <c r="A440" s="12"/>
-      <c r="B440" s="12"/>
-      <c r="C440" s="12"/>
-      <c r="D440" s="12"/>
-      <c r="E440" s="12"/>
-      <c r="F440" s="13"/>
-      <c r="G440" s="13"/>
-      <c r="H440" s="5"/>
-      <c r="I440" s="5"/>
-      <c r="J440" s="5"/>
-      <c r="K440" s="5"/>
-      <c r="L440" s="5"/>
-      <c r="M440" s="5"/>
-      <c r="N440" s="5"/>
-      <c r="O440" s="5"/>
-      <c r="P440" s="5"/>
-    </row>
-    <row r="441" ht="18.0" customHeight="1">
-      <c r="A441" s="12"/>
-      <c r="B441" s="12"/>
-      <c r="C441" s="12"/>
-      <c r="D441" s="12"/>
-      <c r="E441" s="12"/>
-      <c r="F441" s="13"/>
-      <c r="G441" s="13"/>
-      <c r="H441" s="5"/>
-      <c r="I441" s="5"/>
-      <c r="J441" s="5"/>
-      <c r="K441" s="5"/>
-      <c r="L441" s="5"/>
-      <c r="M441" s="5"/>
-      <c r="N441" s="5"/>
-      <c r="O441" s="5"/>
-      <c r="P441" s="5"/>
-    </row>
-    <row r="442" ht="18.0" customHeight="1">
-      <c r="A442" s="12"/>
-      <c r="B442" s="12"/>
-      <c r="C442" s="12"/>
-      <c r="D442" s="12"/>
-      <c r="E442" s="12"/>
-      <c r="F442" s="13"/>
-      <c r="G442" s="13"/>
-      <c r="H442" s="5"/>
-      <c r="I442" s="5"/>
-      <c r="J442" s="5"/>
-      <c r="K442" s="5"/>
-      <c r="L442" s="5"/>
-      <c r="M442" s="5"/>
-      <c r="N442" s="5"/>
-      <c r="O442" s="5"/>
-      <c r="P442" s="5"/>
-    </row>
-    <row r="443" ht="18.0" customHeight="1">
-      <c r="A443" s="12"/>
-      <c r="B443" s="12"/>
-      <c r="C443" s="12"/>
-      <c r="D443" s="12"/>
-      <c r="E443" s="12"/>
-      <c r="F443" s="13"/>
-      <c r="G443" s="13"/>
-      <c r="H443" s="5"/>
-      <c r="I443" s="5"/>
-      <c r="J443" s="5"/>
-      <c r="K443" s="5"/>
-      <c r="L443" s="5"/>
-      <c r="M443" s="5"/>
-      <c r="N443" s="5"/>
-      <c r="O443" s="5"/>
-      <c r="P443" s="5"/>
-    </row>
-    <row r="444" ht="18.0" customHeight="1">
-      <c r="A444" s="12"/>
-      <c r="B444" s="12"/>
-      <c r="C444" s="12"/>
-      <c r="D444" s="12"/>
-      <c r="E444" s="12"/>
-      <c r="F444" s="13"/>
-      <c r="G444" s="13"/>
-      <c r="H444" s="5"/>
-      <c r="I444" s="5"/>
-      <c r="J444" s="5"/>
-      <c r="K444" s="5"/>
-      <c r="L444" s="5"/>
-      <c r="M444" s="5"/>
-      <c r="N444" s="5"/>
-      <c r="O444" s="5"/>
-      <c r="P444" s="5"/>
-    </row>
-    <row r="445" ht="18.0" customHeight="1">
-      <c r="A445" s="12"/>
-      <c r="B445" s="12"/>
-      <c r="C445" s="12"/>
-      <c r="D445" s="12"/>
-      <c r="E445" s="12"/>
-      <c r="F445" s="13"/>
-      <c r="G445" s="13"/>
-      <c r="H445" s="5"/>
-      <c r="I445" s="5"/>
-      <c r="J445" s="5"/>
-      <c r="K445" s="5"/>
-      <c r="L445" s="5"/>
-      <c r="M445" s="5"/>
-      <c r="N445" s="5"/>
-      <c r="O445" s="5"/>
-      <c r="P445" s="5"/>
-    </row>
-    <row r="446" ht="18.0" customHeight="1">
-      <c r="A446" s="12"/>
-      <c r="B446" s="12"/>
-      <c r="C446" s="12"/>
-      <c r="D446" s="12"/>
-      <c r="E446" s="12"/>
-      <c r="F446" s="13"/>
-      <c r="G446" s="13"/>
-      <c r="H446" s="5"/>
-      <c r="I446" s="5"/>
-      <c r="J446" s="5"/>
-      <c r="K446" s="5"/>
-      <c r="L446" s="5"/>
-      <c r="M446" s="5"/>
-      <c r="N446" s="5"/>
-      <c r="O446" s="5"/>
-      <c r="P446" s="5"/>
-    </row>
-    <row r="447" ht="18.0" customHeight="1">
-      <c r="A447" s="12"/>
-      <c r="B447" s="12"/>
-      <c r="C447" s="12"/>
-      <c r="D447" s="12"/>
-      <c r="E447" s="12"/>
-      <c r="F447" s="13"/>
-      <c r="G447" s="13"/>
-      <c r="H447" s="5"/>
-      <c r="I447" s="5"/>
-      <c r="J447" s="5"/>
-      <c r="K447" s="5"/>
-      <c r="L447" s="5"/>
-      <c r="M447" s="5"/>
-      <c r="N447" s="5"/>
-      <c r="O447" s="5"/>
-      <c r="P447" s="5"/>
-    </row>
-    <row r="448" ht="18.0" customHeight="1">
-      <c r="A448" s="12"/>
-      <c r="B448" s="12"/>
-      <c r="C448" s="12"/>
-      <c r="D448" s="12"/>
-      <c r="E448" s="12"/>
-      <c r="F448" s="13"/>
-      <c r="G448" s="13"/>
-      <c r="H448" s="5"/>
-      <c r="I448" s="5"/>
-      <c r="J448" s="5"/>
-      <c r="K448" s="5"/>
-      <c r="L448" s="5"/>
-      <c r="M448" s="5"/>
-      <c r="N448" s="5"/>
-      <c r="O448" s="5"/>
-      <c r="P448" s="5"/>
-    </row>
-    <row r="449" ht="18.0" customHeight="1">
-      <c r="A449" s="12"/>
-      <c r="B449" s="12"/>
-      <c r="C449" s="12"/>
-      <c r="D449" s="12"/>
-      <c r="E449" s="12"/>
-      <c r="F449" s="13"/>
-      <c r="G449" s="13"/>
-      <c r="H449" s="5"/>
-      <c r="I449" s="5"/>
-      <c r="J449" s="5"/>
-      <c r="K449" s="5"/>
-      <c r="L449" s="5"/>
-      <c r="M449" s="5"/>
-      <c r="N449" s="5"/>
-      <c r="O449" s="5"/>
-      <c r="P449" s="5"/>
-    </row>
-    <row r="450" ht="18.0" customHeight="1">
-      <c r="A450" s="12"/>
-      <c r="B450" s="12"/>
-      <c r="C450" s="12"/>
-      <c r="D450" s="12"/>
-      <c r="E450" s="12"/>
-      <c r="F450" s="13"/>
-      <c r="G450" s="13"/>
-      <c r="H450" s="5"/>
-      <c r="I450" s="5"/>
-      <c r="J450" s="5"/>
-      <c r="K450" s="5"/>
-      <c r="L450" s="5"/>
-      <c r="M450" s="5"/>
-      <c r="N450" s="5"/>
-      <c r="O450" s="5"/>
-      <c r="P450" s="5"/>
-    </row>
-    <row r="451" ht="18.0" customHeight="1">
-      <c r="A451" s="12"/>
-      <c r="B451" s="12"/>
-      <c r="C451" s="12"/>
-      <c r="D451" s="12"/>
-      <c r="E451" s="12"/>
-      <c r="F451" s="13"/>
-      <c r="G451" s="13"/>
-      <c r="H451" s="5"/>
-      <c r="I451" s="5"/>
-      <c r="J451" s="5"/>
-      <c r="K451" s="5"/>
-      <c r="L451" s="5"/>
-      <c r="M451" s="5"/>
-      <c r="N451" s="5"/>
-      <c r="O451" s="5"/>
-      <c r="P451" s="5"/>
-    </row>
-    <row r="452" ht="18.0" customHeight="1">
-      <c r="A452" s="12"/>
-      <c r="B452" s="12"/>
-      <c r="C452" s="12"/>
-      <c r="D452" s="12"/>
-      <c r="E452" s="12"/>
-      <c r="F452" s="13"/>
-      <c r="G452" s="13"/>
-      <c r="H452" s="5"/>
-      <c r="I452" s="5"/>
-      <c r="J452" s="5"/>
-      <c r="K452" s="5"/>
-      <c r="L452" s="5"/>
-      <c r="M452" s="5"/>
-      <c r="N452" s="5"/>
-      <c r="O452" s="5"/>
-      <c r="P452" s="5"/>
-    </row>
-    <row r="453" ht="18.0" customHeight="1">
-      <c r="A453" s="12"/>
-      <c r="B453" s="12"/>
-      <c r="C453" s="12"/>
-      <c r="D453" s="12"/>
-      <c r="E453" s="12"/>
-      <c r="F453" s="13"/>
-      <c r="G453" s="13"/>
-      <c r="H453" s="5"/>
-      <c r="I453" s="5"/>
-      <c r="J453" s="5"/>
-      <c r="K453" s="5"/>
-      <c r="L453" s="5"/>
-      <c r="M453" s="5"/>
-      <c r="N453" s="5"/>
-      <c r="O453" s="5"/>
-      <c r="P453" s="5"/>
-    </row>
-    <row r="454" ht="18.0" customHeight="1">
-      <c r="A454" s="12"/>
-      <c r="B454" s="12"/>
-      <c r="C454" s="12"/>
-      <c r="D454" s="12"/>
-      <c r="E454" s="12"/>
-      <c r="F454" s="13"/>
-      <c r="G454" s="13"/>
-      <c r="H454" s="5"/>
-      <c r="I454" s="5"/>
-      <c r="J454" s="5"/>
-      <c r="K454" s="5"/>
-      <c r="L454" s="5"/>
-      <c r="M454" s="5"/>
-      <c r="N454" s="5"/>
-      <c r="O454" s="5"/>
-      <c r="P454" s="5"/>
-    </row>
-    <row r="455" ht="18.0" customHeight="1">
-      <c r="A455" s="12"/>
-      <c r="B455" s="12"/>
-      <c r="C455" s="12"/>
-      <c r="D455" s="12"/>
-      <c r="E455" s="12"/>
-      <c r="F455" s="13"/>
-      <c r="G455" s="13"/>
-      <c r="H455" s="5"/>
-      <c r="I455" s="5"/>
-      <c r="J455" s="5"/>
-      <c r="K455" s="5"/>
-      <c r="L455" s="5"/>
-      <c r="M455" s="5"/>
-      <c r="N455" s="5"/>
-      <c r="O455" s="5"/>
-      <c r="P455" s="5"/>
-    </row>
-    <row r="456" ht="18.0" customHeight="1">
-      <c r="A456" s="12"/>
-      <c r="B456" s="12"/>
-      <c r="C456" s="12"/>
-      <c r="D456" s="12"/>
-      <c r="E456" s="12"/>
-      <c r="F456" s="13"/>
-      <c r="G456" s="13"/>
-      <c r="H456" s="5"/>
-      <c r="I456" s="5"/>
-      <c r="J456" s="5"/>
-      <c r="K456" s="5"/>
-      <c r="L456" s="5"/>
-      <c r="M456" s="5"/>
-      <c r="N456" s="5"/>
-      <c r="O456" s="5"/>
-      <c r="P456" s="5"/>
-    </row>
-    <row r="457" ht="18.0" customHeight="1">
-      <c r="A457" s="12"/>
-      <c r="B457" s="12"/>
-      <c r="C457" s="12"/>
-      <c r="D457" s="12"/>
-      <c r="E457" s="12"/>
-      <c r="F457" s="13"/>
-      <c r="G457" s="13"/>
-      <c r="H457" s="5"/>
-      <c r="I457" s="5"/>
-      <c r="J457" s="5"/>
-      <c r="K457" s="5"/>
-      <c r="L457" s="5"/>
-      <c r="M457" s="5"/>
-      <c r="N457" s="5"/>
-      <c r="O457" s="5"/>
-      <c r="P457" s="5"/>
-    </row>
-    <row r="458" ht="18.0" customHeight="1">
-      <c r="A458" s="12"/>
-      <c r="B458" s="12"/>
-      <c r="C458" s="12"/>
-      <c r="D458" s="12"/>
-      <c r="E458" s="12"/>
-      <c r="F458" s="13"/>
-      <c r="G458" s="13"/>
-      <c r="H458" s="5"/>
-      <c r="I458" s="5"/>
-      <c r="J458" s="5"/>
-      <c r="K458" s="5"/>
-      <c r="L458" s="5"/>
-      <c r="M458" s="5"/>
-      <c r="N458" s="5"/>
-      <c r="O458" s="5"/>
-      <c r="P458" s="5"/>
-    </row>
-    <row r="459" ht="18.0" customHeight="1">
-      <c r="A459" s="12"/>
-      <c r="B459" s="12"/>
-      <c r="C459" s="12"/>
-      <c r="D459" s="12"/>
-      <c r="E459" s="12"/>
-      <c r="F459" s="13"/>
-      <c r="G459" s="13"/>
-      <c r="H459" s="5"/>
-      <c r="I459" s="5"/>
-      <c r="J459" s="5"/>
-      <c r="K459" s="5"/>
-      <c r="L459" s="5"/>
-      <c r="M459" s="5"/>
-      <c r="N459" s="5"/>
-      <c r="O459" s="5"/>
-      <c r="P459" s="5"/>
-    </row>
-    <row r="460" ht="18.0" customHeight="1">
-      <c r="A460" s="12"/>
-      <c r="B460" s="12"/>
-      <c r="C460" s="12"/>
-      <c r="D460" s="12"/>
-      <c r="E460" s="12"/>
-      <c r="F460" s="13"/>
-      <c r="G460" s="13"/>
-      <c r="H460" s="5"/>
-      <c r="I460" s="5"/>
-      <c r="J460" s="5"/>
-      <c r="K460" s="5"/>
-      <c r="L460" s="5"/>
-      <c r="M460" s="5"/>
-      <c r="N460" s="5"/>
-      <c r="O460" s="5"/>
-      <c r="P460" s="5"/>
-    </row>
-    <row r="461" ht="18.0" customHeight="1">
-      <c r="A461" s="12"/>
-      <c r="B461" s="12"/>
-      <c r="C461" s="12"/>
-      <c r="D461" s="12"/>
-      <c r="E461" s="12"/>
-      <c r="F461" s="13"/>
-      <c r="G461" s="13"/>
-      <c r="H461" s="5"/>
-      <c r="I461" s="5"/>
-      <c r="J461" s="5"/>
-      <c r="K461" s="5"/>
-      <c r="L461" s="5"/>
-      <c r="M461" s="5"/>
-      <c r="N461" s="5"/>
-      <c r="O461" s="5"/>
-      <c r="P461" s="5"/>
-    </row>
-    <row r="462" ht="18.0" customHeight="1">
-      <c r="A462" s="12"/>
-      <c r="B462" s="12"/>
-      <c r="C462" s="12"/>
-      <c r="D462" s="12"/>
-      <c r="E462" s="12"/>
-      <c r="F462" s="13"/>
-      <c r="G462" s="13"/>
-      <c r="H462" s="5"/>
-      <c r="I462" s="5"/>
-      <c r="J462" s="5"/>
-      <c r="K462" s="5"/>
-      <c r="L462" s="5"/>
-      <c r="M462" s="5"/>
-      <c r="N462" s="5"/>
-      <c r="O462" s="5"/>
-      <c r="P462" s="5"/>
-    </row>
-    <row r="463" ht="18.0" customHeight="1">
-      <c r="A463" s="12"/>
-      <c r="B463" s="12"/>
-      <c r="C463" s="12"/>
-      <c r="D463" s="12"/>
-      <c r="E463" s="12"/>
-      <c r="F463" s="13"/>
-      <c r="G463" s="13"/>
-      <c r="H463" s="5"/>
-      <c r="I463" s="5"/>
-      <c r="J463" s="5"/>
-      <c r="K463" s="5"/>
-      <c r="L463" s="5"/>
-      <c r="M463" s="5"/>
-      <c r="N463" s="5"/>
-      <c r="O463" s="5"/>
-      <c r="P463" s="5"/>
-    </row>
-    <row r="464" ht="18.0" customHeight="1">
-      <c r="A464" s="12"/>
-      <c r="B464" s="12"/>
-      <c r="C464" s="12"/>
-      <c r="D464" s="12"/>
-      <c r="E464" s="12"/>
-      <c r="F464" s="13"/>
-      <c r="G464" s="13"/>
-      <c r="H464" s="5"/>
-      <c r="I464" s="5"/>
-      <c r="J464" s="5"/>
-      <c r="K464" s="5"/>
-      <c r="L464" s="5"/>
-      <c r="M464" s="5"/>
-      <c r="N464" s="5"/>
-      <c r="O464" s="5"/>
-      <c r="P464" s="5"/>
-    </row>
-    <row r="465" ht="18.0" customHeight="1">
-      <c r="A465" s="12"/>
-      <c r="B465" s="12"/>
-      <c r="C465" s="12"/>
-      <c r="D465" s="12"/>
-      <c r="E465" s="12"/>
-      <c r="F465" s="13"/>
-      <c r="G465" s="13"/>
-      <c r="H465" s="5"/>
-      <c r="I465" s="5"/>
-      <c r="J465" s="5"/>
-      <c r="K465" s="5"/>
-      <c r="L465" s="5"/>
-      <c r="M465" s="5"/>
-      <c r="N465" s="5"/>
-      <c r="O465" s="5"/>
-      <c r="P465" s="5"/>
-    </row>
-    <row r="466" ht="18.0" customHeight="1">
-      <c r="A466" s="12"/>
-      <c r="B466" s="12"/>
-      <c r="C466" s="12"/>
-      <c r="D466" s="12"/>
-      <c r="E466" s="12"/>
-      <c r="F466" s="13"/>
-      <c r="G466" s="13"/>
-      <c r="H466" s="5"/>
-      <c r="I466" s="5"/>
-      <c r="J466" s="5"/>
-      <c r="K466" s="5"/>
-      <c r="L466" s="5"/>
-      <c r="M466" s="5"/>
-      <c r="N466" s="5"/>
-      <c r="O466" s="5"/>
-      <c r="P466" s="5"/>
-    </row>
-    <row r="467" ht="18.0" customHeight="1">
-      <c r="A467" s="12"/>
-      <c r="B467" s="12"/>
-      <c r="C467" s="12"/>
-      <c r="D467" s="12"/>
-      <c r="E467" s="12"/>
-      <c r="F467" s="13"/>
-      <c r="G467" s="13"/>
-      <c r="H467" s="5"/>
-      <c r="I467" s="5"/>
-      <c r="J467" s="5"/>
-      <c r="K467" s="5"/>
-      <c r="L467" s="5"/>
-      <c r="M467" s="5"/>
-      <c r="N467" s="5"/>
-      <c r="O467" s="5"/>
-      <c r="P467" s="5"/>
-    </row>
-    <row r="468" ht="18.0" customHeight="1">
-      <c r="A468" s="12"/>
-      <c r="B468" s="12"/>
-      <c r="C468" s="12"/>
-      <c r="D468" s="12"/>
-      <c r="E468" s="12"/>
-      <c r="F468" s="13"/>
-      <c r="G468" s="13"/>
-      <c r="H468" s="5"/>
-      <c r="I468" s="5"/>
-      <c r="J468" s="5"/>
-      <c r="K468" s="5"/>
-      <c r="L468" s="5"/>
-      <c r="M468" s="5"/>
-      <c r="N468" s="5"/>
-      <c r="O468" s="5"/>
-      <c r="P468" s="5"/>
-    </row>
-    <row r="469" ht="18.0" customHeight="1">
-      <c r="A469" s="12"/>
-      <c r="B469" s="12"/>
-      <c r="C469" s="12"/>
-      <c r="D469" s="12"/>
-      <c r="E469" s="12"/>
-      <c r="F469" s="13"/>
-      <c r="G469" s="13"/>
-      <c r="H469" s="5"/>
-      <c r="I469" s="5"/>
-      <c r="J469" s="5"/>
-      <c r="K469" s="5"/>
-      <c r="L469" s="5"/>
-      <c r="M469" s="5"/>
-      <c r="N469" s="5"/>
-      <c r="O469" s="5"/>
-      <c r="P469" s="5"/>
-    </row>
-    <row r="470" ht="18.0" customHeight="1">
-      <c r="A470" s="12"/>
-      <c r="B470" s="12"/>
-      <c r="C470" s="12"/>
-      <c r="D470" s="12"/>
-      <c r="E470" s="12"/>
-      <c r="F470" s="13"/>
-      <c r="G470" s="13"/>
-      <c r="H470" s="5"/>
-      <c r="I470" s="5"/>
-      <c r="J470" s="5"/>
-      <c r="K470" s="5"/>
-      <c r="L470" s="5"/>
-      <c r="M470" s="5"/>
-      <c r="N470" s="5"/>
-      <c r="O470" s="5"/>
-      <c r="P470" s="5"/>
-    </row>
-    <row r="471" ht="18.0" customHeight="1">
-      <c r="A471" s="12"/>
-      <c r="B471" s="12"/>
-      <c r="C471" s="12"/>
-      <c r="D471" s="12"/>
-      <c r="E471" s="12"/>
-      <c r="F471" s="13"/>
-      <c r="G471" s="13"/>
-      <c r="H471" s="5"/>
-      <c r="I471" s="5"/>
-      <c r="J471" s="5"/>
-      <c r="K471" s="5"/>
-      <c r="L471" s="5"/>
-      <c r="M471" s="5"/>
-      <c r="N471" s="5"/>
-      <c r="O471" s="5"/>
-      <c r="P471" s="5"/>
-    </row>
-    <row r="472" ht="18.0" customHeight="1">
-      <c r="A472" s="12"/>
-      <c r="B472" s="12"/>
-      <c r="C472" s="12"/>
-      <c r="D472" s="12"/>
-      <c r="E472" s="12"/>
-      <c r="F472" s="13"/>
-      <c r="G472" s="13"/>
-      <c r="H472" s="5"/>
-      <c r="I472" s="5"/>
-      <c r="J472" s="5"/>
-      <c r="K472" s="5"/>
-      <c r="L472" s="5"/>
-      <c r="M472" s="5"/>
-      <c r="N472" s="5"/>
-      <c r="O472" s="5"/>
-      <c r="P472" s="5"/>
-    </row>
-    <row r="473" ht="18.0" customHeight="1">
-      <c r="A473" s="12"/>
-      <c r="B473" s="12"/>
-      <c r="C473" s="12"/>
-      <c r="D473" s="12"/>
-      <c r="E473" s="12"/>
-      <c r="F473" s="13"/>
-      <c r="G473" s="13"/>
-      <c r="H473" s="5"/>
-      <c r="I473" s="5"/>
-      <c r="J473" s="5"/>
-      <c r="K473" s="5"/>
-      <c r="L473" s="5"/>
-      <c r="M473" s="5"/>
-      <c r="N473" s="5"/>
-      <c r="O473" s="5"/>
-      <c r="P473" s="5"/>
-    </row>
-    <row r="474" ht="18.0" customHeight="1">
-      <c r="A474" s="12"/>
-      <c r="B474" s="12"/>
-      <c r="C474" s="12"/>
-      <c r="D474" s="12"/>
-      <c r="E474" s="12"/>
-      <c r="F474" s="13"/>
-      <c r="G474" s="13"/>
-      <c r="H474" s="5"/>
-      <c r="I474" s="5"/>
-      <c r="J474" s="5"/>
-      <c r="K474" s="5"/>
-      <c r="L474" s="5"/>
-      <c r="M474" s="5"/>
-      <c r="N474" s="5"/>
-      <c r="O474" s="5"/>
-      <c r="P474" s="5"/>
-    </row>
-    <row r="475" ht="18.0" customHeight="1">
-      <c r="A475" s="12"/>
-      <c r="B475" s="12"/>
-      <c r="C475" s="12"/>
-      <c r="D475" s="12"/>
-      <c r="E475" s="12"/>
-      <c r="F475" s="13"/>
-      <c r="G475" s="13"/>
-      <c r="H475" s="5"/>
-      <c r="I475" s="5"/>
-      <c r="J475" s="5"/>
-      <c r="K475" s="5"/>
-      <c r="L475" s="5"/>
-      <c r="M475" s="5"/>
-      <c r="N475" s="5"/>
-      <c r="O475" s="5"/>
-      <c r="P475" s="5"/>
-    </row>
-    <row r="476" ht="18.0" customHeight="1">
-      <c r="A476" s="12"/>
-      <c r="B476" s="12"/>
-      <c r="C476" s="12"/>
-      <c r="D476" s="12"/>
-      <c r="E476" s="12"/>
-      <c r="F476" s="13"/>
-      <c r="G476" s="13"/>
-      <c r="H476" s="5"/>
-      <c r="I476" s="5"/>
-      <c r="J476" s="5"/>
-      <c r="K476" s="5"/>
-      <c r="L476" s="5"/>
-      <c r="M476" s="5"/>
-      <c r="N476" s="5"/>
-      <c r="O476" s="5"/>
-      <c r="P476" s="5"/>
-    </row>
-    <row r="477" ht="18.0" customHeight="1">
-      <c r="A477" s="12"/>
-      <c r="B477" s="12"/>
-      <c r="C477" s="12"/>
-      <c r="D477" s="12"/>
-      <c r="E477" s="12"/>
-      <c r="F477" s="13"/>
-      <c r="G477" s="13"/>
-      <c r="H477" s="5"/>
-      <c r="I477" s="5"/>
-      <c r="J477" s="5"/>
-      <c r="K477" s="5"/>
-      <c r="L477" s="5"/>
-      <c r="M477" s="5"/>
-      <c r="N477" s="5"/>
-      <c r="O477" s="5"/>
-      <c r="P477" s="5"/>
-    </row>
-    <row r="478" ht="18.0" customHeight="1">
-      <c r="A478" s="12"/>
-      <c r="B478" s="12"/>
-      <c r="C478" s="12"/>
-      <c r="D478" s="12"/>
-      <c r="E478" s="12"/>
-      <c r="F478" s="13"/>
-      <c r="G478" s="13"/>
-      <c r="H478" s="5"/>
-      <c r="I478" s="5"/>
-      <c r="J478" s="5"/>
-      <c r="K478" s="5"/>
-      <c r="L478" s="5"/>
-      <c r="M478" s="5"/>
-      <c r="N478" s="5"/>
-      <c r="O478" s="5"/>
-      <c r="P478" s="5"/>
-    </row>
-    <row r="479" ht="18.0" customHeight="1">
-      <c r="A479" s="12"/>
-      <c r="B479" s="12"/>
-      <c r="C479" s="12"/>
-      <c r="D479" s="12"/>
-      <c r="E479" s="12"/>
-      <c r="F479" s="13"/>
-      <c r="G479" s="13"/>
-      <c r="H479" s="5"/>
-      <c r="I479" s="5"/>
-      <c r="J479" s="5"/>
-      <c r="K479" s="5"/>
-      <c r="L479" s="5"/>
-      <c r="M479" s="5"/>
-      <c r="N479" s="5"/>
-      <c r="O479" s="5"/>
-      <c r="P479" s="5"/>
-    </row>
-    <row r="480" ht="18.0" customHeight="1">
-      <c r="A480" s="12"/>
-      <c r="B480" s="12"/>
-      <c r="C480" s="12"/>
-      <c r="D480" s="12"/>
-      <c r="E480" s="12"/>
-      <c r="F480" s="13"/>
-      <c r="G480" s="13"/>
-      <c r="H480" s="5"/>
-      <c r="I480" s="5"/>
-      <c r="J480" s="5"/>
-      <c r="K480" s="5"/>
-      <c r="L480" s="5"/>
-      <c r="M480" s="5"/>
-      <c r="N480" s="5"/>
-      <c r="O480" s="5"/>
-      <c r="P480" s="5"/>
-    </row>
-    <row r="481" ht="18.0" customHeight="1">
-      <c r="A481" s="12"/>
-      <c r="B481" s="12"/>
-      <c r="C481" s="12"/>
-      <c r="D481" s="12"/>
-      <c r="E481" s="12"/>
-      <c r="F481" s="13"/>
-      <c r="G481" s="13"/>
-      <c r="H481" s="5"/>
-      <c r="I481" s="5"/>
-      <c r="J481" s="5"/>
-      <c r="K481" s="5"/>
-      <c r="L481" s="5"/>
-      <c r="M481" s="5"/>
-      <c r="N481" s="5"/>
-      <c r="O481" s="5"/>
-      <c r="P481" s="5"/>
-    </row>
-    <row r="482" ht="18.0" customHeight="1">
-      <c r="A482" s="12"/>
-      <c r="B482" s="12"/>
-      <c r="C482" s="12"/>
-      <c r="D482" s="12"/>
-      <c r="E482" s="12"/>
-      <c r="F482" s="13"/>
-      <c r="G482" s="13"/>
-      <c r="H482" s="5"/>
-      <c r="I482" s="5"/>
-      <c r="J482" s="5"/>
-      <c r="K482" s="5"/>
-      <c r="L482" s="5"/>
-      <c r="M482" s="5"/>
-      <c r="N482" s="5"/>
-      <c r="O482" s="5"/>
-      <c r="P482" s="5"/>
-    </row>
-    <row r="483" ht="18.0" customHeight="1">
-      <c r="A483" s="12"/>
-      <c r="B483" s="12"/>
-      <c r="C483" s="12"/>
-      <c r="D483" s="12"/>
-      <c r="E483" s="12"/>
-      <c r="F483" s="13"/>
-      <c r="G483" s="13"/>
-      <c r="H483" s="5"/>
-      <c r="I483" s="5"/>
-      <c r="J483" s="5"/>
-      <c r="K483" s="5"/>
-      <c r="L483" s="5"/>
-      <c r="M483" s="5"/>
-      <c r="N483" s="5"/>
-      <c r="O483" s="5"/>
-      <c r="P483" s="5"/>
-    </row>
-    <row r="484" ht="18.0" customHeight="1">
-      <c r="A484" s="12"/>
-      <c r="B484" s="12"/>
-      <c r="C484" s="12"/>
-      <c r="D484" s="12"/>
-      <c r="E484" s="12"/>
-      <c r="F484" s="13"/>
-      <c r="G484" s="13"/>
-      <c r="H484" s="5"/>
-      <c r="I484" s="5"/>
-      <c r="J484" s="5"/>
-      <c r="K484" s="5"/>
-      <c r="L484" s="5"/>
-      <c r="M484" s="5"/>
-      <c r="N484" s="5"/>
-      <c r="O484" s="5"/>
-      <c r="P484" s="5"/>
-    </row>
-    <row r="485" ht="18.0" customHeight="1">
-      <c r="A485" s="12"/>
-      <c r="B485" s="12"/>
-      <c r="C485" s="12"/>
-      <c r="D485" s="12"/>
-      <c r="E485" s="12"/>
-      <c r="F485" s="13"/>
-      <c r="G485" s="13"/>
-      <c r="H485" s="5"/>
-      <c r="I485" s="5"/>
-      <c r="J485" s="5"/>
-      <c r="K485" s="5"/>
-      <c r="L485" s="5"/>
-      <c r="M485" s="5"/>
-      <c r="N485" s="5"/>
-      <c r="O485" s="5"/>
-      <c r="P485" s="5"/>
-    </row>
-    <row r="486" ht="18.0" customHeight="1">
-      <c r="A486" s="12"/>
-      <c r="B486" s="12"/>
-      <c r="C486" s="12"/>
-      <c r="D486" s="12"/>
-      <c r="E486" s="12"/>
-      <c r="F486" s="13"/>
-      <c r="G486" s="13"/>
-      <c r="H486" s="5"/>
-      <c r="I486" s="5"/>
-      <c r="J486" s="5"/>
-      <c r="K486" s="5"/>
-      <c r="L486" s="5"/>
-      <c r="M486" s="5"/>
-      <c r="N486" s="5"/>
-      <c r="O486" s="5"/>
-      <c r="P486" s="5"/>
-    </row>
-    <row r="487" ht="18.0" customHeight="1">
-      <c r="A487" s="12"/>
-      <c r="B487" s="12"/>
-      <c r="C487" s="12"/>
-      <c r="D487" s="12"/>
-      <c r="E487" s="12"/>
-      <c r="F487" s="13"/>
-      <c r="G487" s="13"/>
-      <c r="H487" s="5"/>
-      <c r="I487" s="5"/>
-      <c r="J487" s="5"/>
-      <c r="K487" s="5"/>
-      <c r="L487" s="5"/>
-      <c r="M487" s="5"/>
-      <c r="N487" s="5"/>
-      <c r="O487" s="5"/>
-      <c r="P487" s="5"/>
-    </row>
-    <row r="488" ht="18.0" customHeight="1">
-      <c r="A488" s="12"/>
-      <c r="B488" s="12"/>
-      <c r="C488" s="12"/>
-      <c r="D488" s="12"/>
-      <c r="E488" s="12"/>
-      <c r="F488" s="13"/>
-      <c r="G488" s="13"/>
-      <c r="H488" s="5"/>
-      <c r="I488" s="5"/>
-      <c r="J488" s="5"/>
-      <c r="K488" s="5"/>
-      <c r="L488" s="5"/>
-      <c r="M488" s="5"/>
-      <c r="N488" s="5"/>
-      <c r="O488" s="5"/>
-      <c r="P488" s="5"/>
-    </row>
-    <row r="489" ht="18.0" customHeight="1">
-      <c r="A489" s="12"/>
-      <c r="B489" s="12"/>
-      <c r="C489" s="12"/>
-      <c r="D489" s="12"/>
-      <c r="E489" s="12"/>
-      <c r="F489" s="13"/>
-      <c r="G489" s="13"/>
-      <c r="H489" s="5"/>
-      <c r="I489" s="5"/>
-      <c r="J489" s="5"/>
-      <c r="K489" s="5"/>
-      <c r="L489" s="5"/>
-      <c r="M489" s="5"/>
-      <c r="N489" s="5"/>
-      <c r="O489" s="5"/>
-      <c r="P489" s="5"/>
-    </row>
-    <row r="490" ht="18.0" customHeight="1">
-      <c r="A490" s="12"/>
-      <c r="B490" s="12"/>
-      <c r="C490" s="12"/>
-      <c r="D490" s="12"/>
-      <c r="E490" s="12"/>
-      <c r="F490" s="13"/>
-      <c r="G490" s="13"/>
-      <c r="H490" s="5"/>
-      <c r="I490" s="5"/>
-      <c r="J490" s="5"/>
-      <c r="K490" s="5"/>
-      <c r="L490" s="5"/>
-      <c r="M490" s="5"/>
-      <c r="N490" s="5"/>
-      <c r="O490" s="5"/>
-      <c r="P490" s="5"/>
-    </row>
-    <row r="491" ht="18.0" customHeight="1">
-      <c r="A491" s="12"/>
-      <c r="B491" s="12"/>
-      <c r="C491" s="12"/>
-      <c r="D491" s="12"/>
-      <c r="E491" s="12"/>
-      <c r="F491" s="13"/>
-      <c r="G491" s="13"/>
-      <c r="H491" s="5"/>
-      <c r="I491" s="5"/>
-      <c r="J491" s="5"/>
-      <c r="K491" s="5"/>
-      <c r="L491" s="5"/>
-      <c r="M491" s="5"/>
-      <c r="N491" s="5"/>
-      <c r="O491" s="5"/>
-      <c r="P491" s="5"/>
-    </row>
-    <row r="492" ht="18.0" customHeight="1">
-      <c r="A492" s="12"/>
-      <c r="B492" s="12"/>
-      <c r="C492" s="12"/>
-      <c r="D492" s="12"/>
-      <c r="E492" s="12"/>
-      <c r="F492" s="13"/>
-      <c r="G492" s="13"/>
-      <c r="H492" s="5"/>
-      <c r="I492" s="5"/>
-      <c r="J492" s="5"/>
-      <c r="K492" s="5"/>
-      <c r="L492" s="5"/>
-      <c r="M492" s="5"/>
-      <c r="N492" s="5"/>
-      <c r="O492" s="5"/>
-      <c r="P492" s="5"/>
-    </row>
-    <row r="493" ht="18.0" customHeight="1">
-      <c r="A493" s="12"/>
-      <c r="B493" s="12"/>
-      <c r="C493" s="12"/>
-      <c r="D493" s="12"/>
-      <c r="E493" s="12"/>
-      <c r="F493" s="13"/>
-      <c r="G493" s="13"/>
-      <c r="H493" s="5"/>
-      <c r="I493" s="5"/>
-      <c r="J493" s="5"/>
-      <c r="K493" s="5"/>
-      <c r="L493" s="5"/>
-      <c r="M493" s="5"/>
-      <c r="N493" s="5"/>
-      <c r="O493" s="5"/>
-      <c r="P493" s="5"/>
-    </row>
-    <row r="494" ht="18.0" customHeight="1">
-      <c r="A494" s="12"/>
-      <c r="B494" s="12"/>
-      <c r="C494" s="12"/>
-      <c r="D494" s="12"/>
-      <c r="E494" s="12"/>
-      <c r="F494" s="13"/>
-      <c r="G494" s="13"/>
-      <c r="H494" s="5"/>
-      <c r="I494" s="5"/>
-      <c r="J494" s="5"/>
-      <c r="K494" s="5"/>
-      <c r="L494" s="5"/>
-      <c r="M494" s="5"/>
-      <c r="N494" s="5"/>
-      <c r="O494" s="5"/>
-      <c r="P494" s="5"/>
-    </row>
-    <row r="495" ht="18.0" customHeight="1">
-      <c r="A495" s="12"/>
-      <c r="B495" s="12"/>
-      <c r="C495" s="12"/>
-      <c r="D495" s="12"/>
-      <c r="E495" s="12"/>
-      <c r="F495" s="13"/>
-      <c r="G495" s="13"/>
-      <c r="H495" s="5"/>
-      <c r="I495" s="5"/>
-      <c r="J495" s="5"/>
-      <c r="K495" s="5"/>
-      <c r="L495" s="5"/>
-      <c r="M495" s="5"/>
-      <c r="N495" s="5"/>
-      <c r="O495" s="5"/>
-      <c r="P495" s="5"/>
-    </row>
-    <row r="496" ht="18.0" customHeight="1">
-      <c r="A496" s="12"/>
-      <c r="B496" s="12"/>
-      <c r="C496" s="12"/>
-      <c r="D496" s="12"/>
-      <c r="E496" s="12"/>
-      <c r="F496" s="13"/>
-      <c r="G496" s="13"/>
-      <c r="H496" s="5"/>
-      <c r="I496" s="5"/>
-      <c r="J496" s="5"/>
-      <c r="K496" s="5"/>
-      <c r="L496" s="5"/>
-      <c r="M496" s="5"/>
-      <c r="N496" s="5"/>
-      <c r="O496" s="5"/>
-      <c r="P496" s="5"/>
-    </row>
-    <row r="497" ht="18.0" customHeight="1">
-      <c r="A497" s="12"/>
-      <c r="B497" s="12"/>
-      <c r="C497" s="12"/>
-      <c r="D497" s="12"/>
-      <c r="E497" s="12"/>
-      <c r="F497" s="13"/>
-      <c r="G497" s="13"/>
-      <c r="H497" s="5"/>
-      <c r="I497" s="5"/>
-      <c r="J497" s="5"/>
-      <c r="K497" s="5"/>
-      <c r="L497" s="5"/>
-      <c r="M497" s="5"/>
-      <c r="N497" s="5"/>
-      <c r="O497" s="5"/>
-      <c r="P497" s="5"/>
-    </row>
-    <row r="498" ht="18.0" customHeight="1">
-      <c r="A498" s="12"/>
-      <c r="B498" s="12"/>
-      <c r="C498" s="12"/>
-      <c r="D498" s="12"/>
-      <c r="E498" s="12"/>
-      <c r="F498" s="13"/>
-      <c r="G498" s="13"/>
-      <c r="H498" s="5"/>
-      <c r="I498" s="5"/>
-      <c r="J498" s="5"/>
-      <c r="K498" s="5"/>
-      <c r="L498" s="5"/>
-      <c r="M498" s="5"/>
-      <c r="N498" s="5"/>
-      <c r="O498" s="5"/>
-      <c r="P498" s="5"/>
-    </row>
-    <row r="499" ht="18.0" customHeight="1">
-      <c r="A499" s="12"/>
-      <c r="B499" s="12"/>
-      <c r="C499" s="12"/>
-      <c r="D499" s="12"/>
-      <c r="E499" s="12"/>
-      <c r="F499" s="13"/>
-      <c r="G499" s="13"/>
-      <c r="H499" s="5"/>
-      <c r="I499" s="5"/>
-      <c r="J499" s="5"/>
-      <c r="K499" s="5"/>
-      <c r="L499" s="5"/>
-      <c r="M499" s="5"/>
-      <c r="N499" s="5"/>
-      <c r="O499" s="5"/>
-      <c r="P499" s="5"/>
-    </row>
-    <row r="500" ht="18.0" customHeight="1">
-      <c r="A500" s="12"/>
-      <c r="B500" s="12"/>
-      <c r="C500" s="12"/>
-      <c r="D500" s="12"/>
-      <c r="E500" s="12"/>
-      <c r="F500" s="13"/>
-      <c r="G500" s="13"/>
-      <c r="H500" s="5"/>
-      <c r="I500" s="5"/>
-      <c r="J500" s="5"/>
-      <c r="K500" s="5"/>
-      <c r="L500" s="5"/>
-      <c r="M500" s="5"/>
-      <c r="N500" s="5"/>
-      <c r="O500" s="5"/>
-      <c r="P500" s="5"/>
-    </row>
-    <row r="501" ht="18.0" customHeight="1">
-      <c r="A501" s="12"/>
-      <c r="B501" s="12"/>
-      <c r="C501" s="12"/>
-      <c r="D501" s="12"/>
-      <c r="E501" s="12"/>
-      <c r="F501" s="13"/>
-      <c r="G501" s="13"/>
-      <c r="H501" s="5"/>
-      <c r="I501" s="5"/>
-      <c r="J501" s="5"/>
-      <c r="K501" s="5"/>
-      <c r="L501" s="5"/>
-      <c r="M501" s="5"/>
-      <c r="N501" s="5"/>
-      <c r="O501" s="5"/>
-      <c r="P501" s="5"/>
-    </row>
-    <row r="502" ht="18.0" customHeight="1">
-      <c r="A502" s="12"/>
-      <c r="B502" s="12"/>
-      <c r="C502" s="12"/>
-      <c r="D502" s="12"/>
-      <c r="E502" s="12"/>
-      <c r="F502" s="13"/>
-      <c r="G502" s="13"/>
-      <c r="H502" s="5"/>
-      <c r="I502" s="5"/>
-      <c r="J502" s="5"/>
-      <c r="K502" s="5"/>
-      <c r="L502" s="5"/>
-      <c r="M502" s="5"/>
-      <c r="N502" s="5"/>
-      <c r="O502" s="5"/>
-      <c r="P502" s="5"/>
-    </row>
-    <row r="503" ht="18.0" customHeight="1">
-      <c r="A503" s="12"/>
-      <c r="B503" s="12"/>
-      <c r="C503" s="12"/>
-      <c r="D503" s="12"/>
-      <c r="E503" s="12"/>
-      <c r="F503" s="13"/>
-      <c r="G503" s="13"/>
-      <c r="H503" s="5"/>
-      <c r="I503" s="5"/>
-      <c r="J503" s="5"/>
-      <c r="K503" s="5"/>
-      <c r="L503" s="5"/>
-      <c r="M503" s="5"/>
-      <c r="N503" s="5"/>
-      <c r="O503" s="5"/>
-      <c r="P503" s="5"/>
-    </row>
-    <row r="504" ht="18.0" customHeight="1">
-      <c r="A504" s="12"/>
-      <c r="B504" s="12"/>
-      <c r="C504" s="12"/>
-      <c r="D504" s="12"/>
-      <c r="E504" s="12"/>
-      <c r="F504" s="13"/>
-      <c r="G504" s="13"/>
-      <c r="H504" s="5"/>
-      <c r="I504" s="5"/>
-      <c r="J504" s="5"/>
-      <c r="K504" s="5"/>
-      <c r="L504" s="5"/>
-      <c r="M504" s="5"/>
-      <c r="N504" s="5"/>
-      <c r="O504" s="5"/>
-      <c r="P504" s="5"/>
-    </row>
-    <row r="505" ht="18.0" customHeight="1">
-      <c r="A505" s="12"/>
-      <c r="B505" s="12"/>
-      <c r="C505" s="12"/>
-      <c r="D505" s="12"/>
-      <c r="E505" s="12"/>
-      <c r="F505" s="13"/>
-      <c r="G505" s="13"/>
-      <c r="H505" s="5"/>
-      <c r="I505" s="5"/>
-      <c r="J505" s="5"/>
-      <c r="K505" s="5"/>
-      <c r="L505" s="5"/>
-      <c r="M505" s="5"/>
-      <c r="N505" s="5"/>
-      <c r="O505" s="5"/>
-      <c r="P505" s="5"/>
-    </row>
-    <row r="506" ht="18.0" customHeight="1">
-      <c r="A506" s="12"/>
-      <c r="B506" s="12"/>
-      <c r="C506" s="12"/>
-      <c r="D506" s="12"/>
-      <c r="E506" s="12"/>
-      <c r="F506" s="13"/>
-      <c r="G506" s="13"/>
-      <c r="H506" s="5"/>
-      <c r="I506" s="5"/>
-      <c r="J506" s="5"/>
-      <c r="K506" s="5"/>
-      <c r="L506" s="5"/>
-      <c r="M506" s="5"/>
-      <c r="N506" s="5"/>
-      <c r="O506" s="5"/>
-      <c r="P506" s="5"/>
-    </row>
-    <row r="507" ht="18.0" customHeight="1">
-      <c r="A507" s="12"/>
-      <c r="B507" s="12"/>
-      <c r="C507" s="12"/>
-      <c r="D507" s="12"/>
-      <c r="E507" s="12"/>
-      <c r="F507" s="13"/>
-      <c r="G507" s="13"/>
-      <c r="H507" s="5"/>
-      <c r="I507" s="5"/>
-      <c r="J507" s="5"/>
-      <c r="K507" s="5"/>
-      <c r="L507" s="5"/>
-      <c r="M507" s="5"/>
-      <c r="N507" s="5"/>
-      <c r="O507" s="5"/>
-      <c r="P507" s="5"/>
-    </row>
-    <row r="508" ht="18.0" customHeight="1">
-      <c r="A508" s="12"/>
-      <c r="B508" s="12"/>
-      <c r="C508" s="12"/>
-      <c r="D508" s="12"/>
-      <c r="E508" s="12"/>
-      <c r="F508" s="13"/>
-      <c r="G508" s="13"/>
-      <c r="H508" s="5"/>
-      <c r="I508" s="5"/>
-      <c r="J508" s="5"/>
-      <c r="K508" s="5"/>
-      <c r="L508" s="5"/>
-      <c r="M508" s="5"/>
-      <c r="N508" s="5"/>
-      <c r="O508" s="5"/>
-      <c r="P508" s="5"/>
-    </row>
-    <row r="509" ht="18.0" customHeight="1">
-      <c r="A509" s="12"/>
-      <c r="B509" s="12"/>
-      <c r="C509" s="12"/>
-      <c r="D509" s="12"/>
-      <c r="E509" s="12"/>
-      <c r="F509" s="13"/>
-      <c r="G509" s="13"/>
-      <c r="H509" s="5"/>
-      <c r="I509" s="5"/>
-      <c r="J509" s="5"/>
-      <c r="K509" s="5"/>
-      <c r="L509" s="5"/>
-      <c r="M509" s="5"/>
-      <c r="N509" s="5"/>
-      <c r="O509" s="5"/>
-      <c r="P509" s="5"/>
-    </row>
-    <row r="510" ht="18.0" customHeight="1">
-      <c r="A510" s="12"/>
-      <c r="B510" s="12"/>
-      <c r="C510" s="12"/>
-      <c r="D510" s="12"/>
-      <c r="E510" s="12"/>
-      <c r="F510" s="13"/>
-      <c r="G510" s="13"/>
-      <c r="H510" s="5"/>
-      <c r="I510" s="5"/>
-      <c r="J510" s="5"/>
-      <c r="K510" s="5"/>
-      <c r="L510" s="5"/>
-      <c r="M510" s="5"/>
-      <c r="N510" s="5"/>
-      <c r="O510" s="5"/>
-      <c r="P510" s="5"/>
-    </row>
-    <row r="511" ht="18.0" customHeight="1">
-      <c r="A511" s="12"/>
-      <c r="B511" s="12"/>
-      <c r="C511" s="12"/>
-      <c r="D511" s="12"/>
-      <c r="E511" s="12"/>
-      <c r="F511" s="13"/>
-      <c r="G511" s="13"/>
-      <c r="H511" s="5"/>
-      <c r="I511" s="5"/>
-      <c r="J511" s="5"/>
-      <c r="K511" s="5"/>
-      <c r="L511" s="5"/>
-      <c r="M511" s="5"/>
-      <c r="N511" s="5"/>
-      <c r="O511" s="5"/>
-      <c r="P511" s="5"/>
-    </row>
-    <row r="512" ht="18.0" customHeight="1">
-      <c r="A512" s="12"/>
-      <c r="B512" s="12"/>
-      <c r="C512" s="12"/>
-      <c r="D512" s="12"/>
-      <c r="E512" s="12"/>
-      <c r="F512" s="13"/>
-      <c r="G512" s="13"/>
-      <c r="H512" s="5"/>
-      <c r="I512" s="5"/>
-      <c r="J512" s="5"/>
-      <c r="K512" s="5"/>
-      <c r="L512" s="5"/>
-      <c r="M512" s="5"/>
-      <c r="N512" s="5"/>
-      <c r="O512" s="5"/>
-      <c r="P512" s="5"/>
-    </row>
-    <row r="513" ht="18.0" customHeight="1">
-      <c r="A513" s="12"/>
-      <c r="B513" s="12"/>
-      <c r="C513" s="12"/>
-      <c r="D513" s="12"/>
-      <c r="E513" s="12"/>
-      <c r="F513" s="13"/>
-      <c r="G513" s="13"/>
-      <c r="H513" s="5"/>
-      <c r="I513" s="5"/>
-      <c r="J513" s="5"/>
-      <c r="K513" s="5"/>
-      <c r="L513" s="5"/>
-      <c r="M513" s="5"/>
-      <c r="N513" s="5"/>
-      <c r="O513" s="5"/>
-      <c r="P513" s="5"/>
-    </row>
-    <row r="514" ht="18.0" customHeight="1">
-      <c r="A514" s="12"/>
-      <c r="B514" s="12"/>
-      <c r="C514" s="12"/>
-      <c r="D514" s="12"/>
-      <c r="E514" s="12"/>
-      <c r="F514" s="13"/>
-      <c r="G514" s="13"/>
-      <c r="H514" s="5"/>
-      <c r="I514" s="5"/>
-      <c r="J514" s="5"/>
-      <c r="K514" s="5"/>
-      <c r="L514" s="5"/>
-      <c r="M514" s="5"/>
-      <c r="N514" s="5"/>
-      <c r="O514" s="5"/>
-      <c r="P514" s="5"/>
-    </row>
-    <row r="515" ht="18.0" customHeight="1">
-      <c r="A515" s="12"/>
-      <c r="B515" s="12"/>
-      <c r="C515" s="12"/>
-      <c r="D515" s="12"/>
-      <c r="E515" s="12"/>
-      <c r="F515" s="13"/>
-      <c r="G515" s="13"/>
-      <c r="H515" s="5"/>
-      <c r="I515" s="5"/>
-      <c r="J515" s="5"/>
-      <c r="K515" s="5"/>
-      <c r="L515" s="5"/>
-      <c r="M515" s="5"/>
-      <c r="N515" s="5"/>
-      <c r="O515" s="5"/>
-      <c r="P515" s="5"/>
-    </row>
-    <row r="516" ht="18.0" customHeight="1">
-      <c r="A516" s="12"/>
-      <c r="B516" s="12"/>
-      <c r="C516" s="12"/>
-      <c r="D516" s="12"/>
-      <c r="E516" s="12"/>
-      <c r="F516" s="13"/>
-      <c r="G516" s="13"/>
-      <c r="H516" s="5"/>
-      <c r="I516" s="5"/>
-      <c r="J516" s="5"/>
-      <c r="K516" s="5"/>
-      <c r="L516" s="5"/>
-      <c r="M516" s="5"/>
-      <c r="N516" s="5"/>
-      <c r="O516" s="5"/>
-      <c r="P516" s="5"/>
-    </row>
-    <row r="517" ht="18.0" customHeight="1">
-      <c r="A517" s="12"/>
-      <c r="B517" s="12"/>
-      <c r="C517" s="12"/>
-      <c r="D517" s="12"/>
-      <c r="E517" s="12"/>
-      <c r="F517" s="13"/>
-      <c r="G517" s="13"/>
-      <c r="H517" s="5"/>
-      <c r="I517" s="5"/>
-      <c r="J517" s="5"/>
-      <c r="K517" s="5"/>
-      <c r="L517" s="5"/>
-      <c r="M517" s="5"/>
-      <c r="N517" s="5"/>
-      <c r="O517" s="5"/>
-      <c r="P517" s="5"/>
-    </row>
-    <row r="518" ht="18.0" customHeight="1">
-      <c r="A518" s="12"/>
-      <c r="B518" s="12"/>
-      <c r="C518" s="12"/>
-      <c r="D518" s="12"/>
-      <c r="E518" s="12"/>
-      <c r="F518" s="13"/>
-      <c r="G518" s="13"/>
-      <c r="H518" s="5"/>
-      <c r="I518" s="5"/>
-      <c r="J518" s="5"/>
-      <c r="K518" s="5"/>
-      <c r="L518" s="5"/>
-      <c r="M518" s="5"/>
-      <c r="N518" s="5"/>
-      <c r="O518" s="5"/>
-      <c r="P518" s="5"/>
-    </row>
-    <row r="519" ht="18.0" customHeight="1">
-      <c r="A519" s="12"/>
-      <c r="B519" s="12"/>
-      <c r="C519" s="12"/>
-      <c r="D519" s="12"/>
-      <c r="E519" s="12"/>
-      <c r="F519" s="13"/>
-      <c r="G519" s="13"/>
-      <c r="H519" s="5"/>
-      <c r="I519" s="5"/>
-      <c r="J519" s="5"/>
-      <c r="K519" s="5"/>
-      <c r="L519" s="5"/>
-      <c r="M519" s="5"/>
-      <c r="N519" s="5"/>
-      <c r="O519" s="5"/>
-      <c r="P519" s="5"/>
-    </row>
-    <row r="520" ht="18.0" customHeight="1">
-      <c r="A520" s="12"/>
-      <c r="B520" s="12"/>
-      <c r="C520" s="12"/>
-      <c r="D520" s="12"/>
-      <c r="E520" s="12"/>
-      <c r="F520" s="13"/>
-      <c r="G520" s="13"/>
-      <c r="H520" s="5"/>
-      <c r="I520" s="5"/>
-      <c r="J520" s="5"/>
-      <c r="K520" s="5"/>
-      <c r="L520" s="5"/>
-      <c r="M520" s="5"/>
-      <c r="N520" s="5"/>
-      <c r="O520" s="5"/>
-      <c r="P520" s="5"/>
-    </row>
-    <row r="521" ht="18.0" customHeight="1">
-      <c r="A521" s="12"/>
-      <c r="B521" s="12"/>
-      <c r="C521" s="12"/>
-      <c r="D521" s="12"/>
-      <c r="E521" s="12"/>
-      <c r="F521" s="13"/>
-      <c r="G521" s="13"/>
-      <c r="H521" s="5"/>
-      <c r="I521" s="5"/>
-      <c r="J521" s="5"/>
-      <c r="K521" s="5"/>
-      <c r="L521" s="5"/>
-      <c r="M521" s="5"/>
-      <c r="N521" s="5"/>
-      <c r="O521" s="5"/>
-      <c r="P521" s="5"/>
-    </row>
-    <row r="522" ht="18.0" customHeight="1">
-      <c r="A522" s="12"/>
-      <c r="B522" s="12"/>
-      <c r="C522" s="12"/>
-      <c r="D522" s="12"/>
-      <c r="E522" s="12"/>
-      <c r="F522" s="13"/>
-      <c r="G522" s="13"/>
-      <c r="H522" s="5"/>
-      <c r="I522" s="5"/>
-      <c r="J522" s="5"/>
-      <c r="K522" s="5"/>
-      <c r="L522" s="5"/>
-      <c r="M522" s="5"/>
-      <c r="N522" s="5"/>
-      <c r="O522" s="5"/>
-      <c r="P522" s="5"/>
-    </row>
-    <row r="523" ht="18.0" customHeight="1">
-      <c r="A523" s="12"/>
-      <c r="B523" s="12"/>
-      <c r="C523" s="12"/>
-      <c r="D523" s="12"/>
-      <c r="E523" s="12"/>
-      <c r="F523" s="13"/>
-      <c r="G523" s="13"/>
-      <c r="H523" s="5"/>
-      <c r="I523" s="5"/>
-      <c r="J523" s="5"/>
-      <c r="K523" s="5"/>
-      <c r="L523" s="5"/>
-      <c r="M523" s="5"/>
-      <c r="N523" s="5"/>
-      <c r="O523" s="5"/>
-      <c r="P523" s="5"/>
-    </row>
-    <row r="524" ht="18.0" customHeight="1">
-      <c r="A524" s="12"/>
-      <c r="B524" s="12"/>
-      <c r="C524" s="12"/>
-      <c r="D524" s="12"/>
-      <c r="E524" s="12"/>
-      <c r="F524" s="13"/>
-      <c r="G524" s="13"/>
-      <c r="H524" s="5"/>
-      <c r="I524" s="5"/>
-      <c r="J524" s="5"/>
-      <c r="K524" s="5"/>
-      <c r="L524" s="5"/>
-      <c r="M524" s="5"/>
-      <c r="N524" s="5"/>
-      <c r="O524" s="5"/>
-      <c r="P524" s="5"/>
-    </row>
-    <row r="525" ht="18.0" customHeight="1">
-      <c r="A525" s="12"/>
-      <c r="B525" s="12"/>
-      <c r="C525" s="12"/>
-      <c r="D525" s="12"/>
-      <c r="E525" s="12"/>
-      <c r="F525" s="13"/>
-      <c r="G525" s="13"/>
-      <c r="H525" s="5"/>
-      <c r="I525" s="5"/>
-      <c r="J525" s="5"/>
-      <c r="K525" s="5"/>
-      <c r="L525" s="5"/>
-      <c r="M525" s="5"/>
-      <c r="N525" s="5"/>
-      <c r="O525" s="5"/>
-      <c r="P525" s="5"/>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A393:G393"/>
-  </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>

--- a/precios.xlsx
+++ b/precios.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="234">
   <si>
     <t>Descripción</t>
   </si>
@@ -94,6 +94,18 @@
     <t>A36 5G 128GB GREEN</t>
   </si>
   <si>
+    <t>A37 5G 128 GB VIOLETA</t>
+  </si>
+  <si>
+    <t>A37 5G 128 GB VERDE</t>
+  </si>
+  <si>
+    <t>A37 5G 128 GB GRIS</t>
+  </si>
+  <si>
+    <t>A37 5G 128 GB BLANCO</t>
+  </si>
+  <si>
     <t>A56 5G 128GB BLACK</t>
   </si>
   <si>
@@ -103,9 +115,27 @@
     <t>A56 5G 128GB GREEN</t>
   </si>
   <si>
+    <t>A57 5G 128 GB AZUL OSCURO</t>
+  </si>
+  <si>
+    <t>A57 5G 128 GB GRIS</t>
+  </si>
+  <si>
+    <t>A57 5G 128 GB CELESTE</t>
+  </si>
+  <si>
+    <t>A57 5G 128 GB VIOLETA</t>
+  </si>
+  <si>
     <t>A56 5G 256GB NEGRO</t>
   </si>
   <si>
+    <t>A57 5G 256 GB AZUL OSCURO</t>
+  </si>
+  <si>
+    <t>A57 5G 256 GB GRIS</t>
+  </si>
+  <si>
     <t>S24FE 5G 256GB BLACK</t>
   </si>
   <si>
@@ -163,6 +193,9 @@
     <t>REDMI A5 128GB DORADO</t>
   </si>
   <si>
+    <t>Redmi A7 Pro 64</t>
+  </si>
+  <si>
     <t>REDMI 14C 128GB NEGRO</t>
   </si>
   <si>
@@ -463,6 +496,9 @@
     <t>X6B 5G 256GB PLATEADO</t>
   </si>
   <si>
+    <t>Honor Smartphone X6d 5G black 4+256GB</t>
+  </si>
+  <si>
     <t>X7C 256GB NEGRO</t>
   </si>
   <si>
@@ -649,10 +685,22 @@
     <t>CEL_LIBRE INFINIX GOLD SMART 10 4+128GB</t>
   </si>
   <si>
+    <t>smart 20 4+128 GB NEGRO</t>
+  </si>
+  <si>
+    <t>smart 20 4+128 GB TITANIUM</t>
+  </si>
+  <si>
     <t>CEL_LIBRE INFINIX BLACK HOT 60I 5G 128G</t>
   </si>
   <si>
     <t>CEL_LIBRE INFINIX BLUE HOT 60I 5G 128G</t>
+  </si>
+  <si>
+    <t>HOT 60 Pro+ 4G NEGRO</t>
+  </si>
+  <si>
+    <t>HOT 60 Pro+ 4G CORAL</t>
   </si>
   <si>
     <t>CEL_LIBRE INFINIX GREY NOTE_50X 5G 8+256GB</t>
@@ -671,8 +719,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="165" formatCode="_ &quot;$&quot;* #,##0_ ;_ &quot;$&quot;* \-#,##0_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -758,7 +807,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -777,16 +826,13 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -795,14 +841,11 @@
     <xf borderId="3" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf borderId="2" fillId="2" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
@@ -1190,12 +1233,12 @@
         <v>4</v>
       </c>
       <c r="B2" s="7">
-        <v>2.6975042E7</v>
+        <v>2.00026975041E11</v>
       </c>
       <c r="C2" s="8">
-        <v>80000.0</v>
-      </c>
-      <c r="D2" s="9">
+        <v>70000.0</v>
+      </c>
+      <c r="D2" s="8">
         <v>990.0</v>
       </c>
       <c r="H2" s="5"/>
@@ -1213,12 +1256,12 @@
         <v>5</v>
       </c>
       <c r="B3" s="7">
-        <v>2.6975042E7</v>
+        <v>2.00026975041E11</v>
       </c>
       <c r="C3" s="8">
-        <v>80000.0</v>
-      </c>
-      <c r="D3" s="9">
+        <v>70000.0</v>
+      </c>
+      <c r="D3" s="8">
         <v>990.0</v>
       </c>
       <c r="H3" s="5"/>
@@ -1236,12 +1279,12 @@
         <v>6</v>
       </c>
       <c r="B4" s="7">
-        <v>2.6975042E7</v>
+        <v>2.00026975041E11</v>
       </c>
       <c r="C4" s="8">
-        <v>80000.0</v>
-      </c>
-      <c r="D4" s="9">
+        <v>70000.0</v>
+      </c>
+      <c r="D4" s="8">
         <v>990.0</v>
       </c>
       <c r="H4" s="5"/>
@@ -1259,12 +1302,12 @@
         <v>7</v>
       </c>
       <c r="B5" s="7">
-        <v>2.6975042E7</v>
+        <v>2.00026975041E11</v>
       </c>
       <c r="C5" s="8">
-        <v>120000.0</v>
-      </c>
-      <c r="D5" s="9">
+        <v>110000.0</v>
+      </c>
+      <c r="D5" s="8">
         <v>990.0</v>
       </c>
       <c r="H5" s="5"/>
@@ -1282,12 +1325,12 @@
         <v>8</v>
       </c>
       <c r="B6" s="7">
-        <v>2.6975042E7</v>
+        <v>2.00026975041E11</v>
       </c>
       <c r="C6" s="8">
-        <v>120000.0</v>
-      </c>
-      <c r="D6" s="9">
+        <v>110000.0</v>
+      </c>
+      <c r="D6" s="8">
         <v>990.0</v>
       </c>
       <c r="H6" s="5"/>
@@ -1305,12 +1348,12 @@
         <v>9</v>
       </c>
       <c r="B7" s="7">
-        <v>2.6975042E7</v>
+        <v>2.00026975041E11</v>
       </c>
       <c r="C7" s="8">
-        <v>120000.0</v>
-      </c>
-      <c r="D7" s="9">
+        <v>110000.0</v>
+      </c>
+      <c r="D7" s="8">
         <v>990.0</v>
       </c>
       <c r="H7" s="5"/>
@@ -1328,12 +1371,12 @@
         <v>10</v>
       </c>
       <c r="B8" s="7">
-        <v>2.6951291E7</v>
+        <v>2.00026951298E11</v>
       </c>
       <c r="C8" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="8">
         <v>19990.0</v>
       </c>
       <c r="H8" s="5"/>
@@ -1351,12 +1394,12 @@
         <v>11</v>
       </c>
       <c r="B9" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C9" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="8">
         <v>89990.0</v>
       </c>
       <c r="H9" s="5"/>
@@ -1374,12 +1417,12 @@
         <v>12</v>
       </c>
       <c r="B10" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C10" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <v>89990.0</v>
       </c>
       <c r="H10" s="5"/>
@@ -1397,12 +1440,12 @@
         <v>13</v>
       </c>
       <c r="B11" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C11" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="8">
         <v>89990.0</v>
       </c>
       <c r="H11" s="5"/>
@@ -1420,12 +1463,12 @@
         <v>14</v>
       </c>
       <c r="B12" s="7">
-        <v>2.7512267E7</v>
+        <v>2.0002740173E11</v>
       </c>
       <c r="C12" s="8">
-        <v>120000.0</v>
-      </c>
-      <c r="D12" s="9">
+        <v>110000.0</v>
+      </c>
+      <c r="D12" s="8">
         <v>39990.0</v>
       </c>
       <c r="H12" s="5"/>
@@ -1443,12 +1486,12 @@
         <v>15</v>
       </c>
       <c r="B13" s="7">
-        <v>2.7512267E7</v>
+        <v>2.0002740173E11</v>
       </c>
       <c r="C13" s="8">
-        <v>120000.0</v>
-      </c>
-      <c r="D13" s="9">
+        <v>110000.0</v>
+      </c>
+      <c r="D13" s="8">
         <v>39990.0</v>
       </c>
       <c r="H13" s="5"/>
@@ -1466,12 +1509,12 @@
         <v>16</v>
       </c>
       <c r="B14" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C14" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="8">
         <v>39990.0</v>
       </c>
       <c r="H14" s="5"/>
@@ -1489,12 +1532,12 @@
         <v>17</v>
       </c>
       <c r="B15" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C15" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="8">
         <v>39990.0</v>
       </c>
       <c r="H15" s="5"/>
@@ -1512,12 +1555,12 @@
         <v>18</v>
       </c>
       <c r="B16" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C16" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="8">
         <v>39990.0</v>
       </c>
       <c r="H16" s="5"/>
@@ -1535,13 +1578,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="7">
-        <v>2.7491766E7</v>
+        <v>2.0002740173E11</v>
       </c>
       <c r="C17" s="8">
-        <v>100000.0</v>
-      </c>
-      <c r="D17" s="9">
-        <v>79990.0</v>
+        <v>110000.0</v>
+      </c>
+      <c r="D17" s="8">
+        <v>39990.0</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
@@ -1558,13 +1601,13 @@
         <v>20</v>
       </c>
       <c r="B18" s="7">
-        <v>2.7491766E7</v>
+        <v>2.00027512269E11</v>
       </c>
       <c r="C18" s="8">
         <v>100000.0</v>
       </c>
-      <c r="D18" s="9">
-        <v>109990.0</v>
+      <c r="D18" s="8">
+        <v>89990.0</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
@@ -1581,13 +1624,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="7">
-        <v>2.7491766E7</v>
+        <v>2.00027512269E11</v>
       </c>
       <c r="C19" s="8">
         <v>100000.0</v>
       </c>
-      <c r="D19" s="9">
-        <v>109990.0</v>
+      <c r="D19" s="8">
+        <v>89990.0</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
@@ -1604,13 +1647,13 @@
         <v>22</v>
       </c>
       <c r="B20" s="7">
-        <v>2.7491766E7</v>
+        <v>2.00027512269E11</v>
       </c>
       <c r="C20" s="8">
         <v>100000.0</v>
       </c>
-      <c r="D20" s="9">
-        <v>109990.0</v>
+      <c r="D20" s="8">
+        <v>89990.0</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
@@ -1627,13 +1670,13 @@
         <v>23</v>
       </c>
       <c r="B21" s="7">
-        <v>2.7491766E7</v>
+        <v>2.00027070684E11</v>
       </c>
       <c r="C21" s="8">
-        <v>100000.0</v>
-      </c>
-      <c r="D21" s="9">
-        <v>159990.0</v>
+        <v>130000.0</v>
+      </c>
+      <c r="D21" s="8">
+        <v>109990.0</v>
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
@@ -1650,13 +1693,13 @@
         <v>24</v>
       </c>
       <c r="B22" s="7">
-        <v>2.7491766E7</v>
+        <v>2.00027070684E11</v>
       </c>
       <c r="C22" s="8">
-        <v>100000.0</v>
-      </c>
-      <c r="D22" s="9">
-        <v>159990.0</v>
+        <v>130000.0</v>
+      </c>
+      <c r="D22" s="8">
+        <v>109990.0</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
@@ -1673,13 +1716,13 @@
         <v>25</v>
       </c>
       <c r="B23" s="7">
-        <v>2.7491766E7</v>
+        <v>2.00027070684E11</v>
       </c>
       <c r="C23" s="8">
-        <v>100000.0</v>
-      </c>
-      <c r="D23" s="9">
-        <v>159990.0</v>
+        <v>130000.0</v>
+      </c>
+      <c r="D23" s="8">
+        <v>109990.0</v>
       </c>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
@@ -1696,13 +1739,13 @@
         <v>26</v>
       </c>
       <c r="B24" s="7">
-        <v>2.7491766E7</v>
+        <v>2.00027070684E11</v>
       </c>
       <c r="C24" s="8">
-        <v>100000.0</v>
-      </c>
-      <c r="D24" s="9">
-        <v>159990.0</v>
+        <v>130000.0</v>
+      </c>
+      <c r="D24" s="8">
+        <v>109990.0</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
@@ -1719,13 +1762,13 @@
         <v>27</v>
       </c>
       <c r="B25" s="7">
-        <v>2.7512267E7</v>
+        <v>2.00027512269E11</v>
       </c>
       <c r="C25" s="8">
-        <v>120000.0</v>
-      </c>
-      <c r="D25" s="9">
-        <v>219990.0</v>
+        <v>100000.0</v>
+      </c>
+      <c r="D25" s="8">
+        <v>239990.0</v>
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
@@ -1742,13 +1785,13 @@
         <v>28</v>
       </c>
       <c r="B26" s="7">
-        <v>2.7512267E7</v>
+        <v>2.00027512269E11</v>
       </c>
       <c r="C26" s="8">
-        <v>120000.0</v>
-      </c>
-      <c r="D26" s="9">
-        <v>219990.0</v>
+        <v>100000.0</v>
+      </c>
+      <c r="D26" s="8">
+        <v>239990.0</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
@@ -1765,13 +1808,13 @@
         <v>29</v>
       </c>
       <c r="B27" s="7">
-        <v>2.7401732E7</v>
+        <v>2.0002740173E11</v>
       </c>
       <c r="C27" s="8">
-        <v>130000.0</v>
-      </c>
-      <c r="D27" s="9">
-        <v>209990.0</v>
+        <v>110000.0</v>
+      </c>
+      <c r="D27" s="8">
+        <v>229990.0</v>
       </c>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
@@ -1788,13 +1831,13 @@
         <v>30</v>
       </c>
       <c r="B28" s="7">
-        <v>2.7401732E7</v>
+        <v>2.00027512269E11</v>
       </c>
       <c r="C28" s="8">
-        <v>130000.0</v>
-      </c>
-      <c r="D28" s="9">
-        <v>249990.0</v>
+        <v>100000.0</v>
+      </c>
+      <c r="D28" s="8">
+        <v>239990.0</v>
       </c>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
@@ -1811,13 +1854,13 @@
         <v>31</v>
       </c>
       <c r="B29" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027491731E11</v>
       </c>
       <c r="C29" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D29" s="9">
-        <v>429990.0</v>
+        <v>120000.0</v>
+      </c>
+      <c r="D29" s="8">
+        <v>209990.0</v>
       </c>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
@@ -1834,13 +1877,13 @@
         <v>32</v>
       </c>
       <c r="B30" s="7">
-        <v>2.7497756E7</v>
+        <v>2.0002740173E11</v>
       </c>
       <c r="C30" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D30" s="9">
-        <v>429990.0</v>
+        <v>110000.0</v>
+      </c>
+      <c r="D30" s="8">
+        <v>219990.0</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
@@ -1857,13 +1900,13 @@
         <v>33</v>
       </c>
       <c r="B31" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027491731E11</v>
       </c>
       <c r="C31" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D31" s="9">
-        <v>429990.0</v>
+        <v>120000.0</v>
+      </c>
+      <c r="D31" s="8">
+        <v>209990.0</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
@@ -1880,13 +1923,13 @@
         <v>34</v>
       </c>
       <c r="B32" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512269E11</v>
       </c>
       <c r="C32" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D32" s="9">
-        <v>379990.0</v>
+        <v>100000.0</v>
+      </c>
+      <c r="D32" s="8">
+        <v>329990.0</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
@@ -1903,13 +1946,13 @@
         <v>35</v>
       </c>
       <c r="B33" s="7">
-        <v>2.7497756E7</v>
+        <v>2.0002740173E11</v>
       </c>
       <c r="C33" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D33" s="9">
-        <v>499990.0</v>
+        <v>110000.0</v>
+      </c>
+      <c r="D33" s="8">
+        <v>319990.0</v>
       </c>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
@@ -1926,13 +1969,13 @@
         <v>36</v>
       </c>
       <c r="B34" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512269E11</v>
       </c>
       <c r="C34" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D34" s="9">
-        <v>529990.0</v>
+        <v>100000.0</v>
+      </c>
+      <c r="D34" s="8">
+        <v>329990.0</v>
       </c>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
@@ -1949,13 +1992,13 @@
         <v>37</v>
       </c>
       <c r="B35" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512269E11</v>
       </c>
       <c r="C35" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D35" s="9">
-        <v>529990.0</v>
+        <v>100000.0</v>
+      </c>
+      <c r="D35" s="8">
+        <v>329990.0</v>
       </c>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
@@ -1972,13 +2015,13 @@
         <v>38</v>
       </c>
       <c r="B36" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027491731E11</v>
       </c>
       <c r="C36" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D36" s="9">
-        <v>529990.0</v>
+        <v>120000.0</v>
+      </c>
+      <c r="D36" s="8">
+        <v>229990.0</v>
       </c>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
@@ -1995,13 +2038,13 @@
         <v>39</v>
       </c>
       <c r="B37" s="7">
-        <v>2.7497756E7</v>
+        <v>2.0002740173E11</v>
       </c>
       <c r="C37" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D37" s="9">
-        <v>579990.0</v>
+        <v>110000.0</v>
+      </c>
+      <c r="D37" s="8">
+        <v>349990.0</v>
       </c>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
@@ -2018,13 +2061,13 @@
         <v>40</v>
       </c>
       <c r="B38" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512269E11</v>
       </c>
       <c r="C38" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D38" s="9">
-        <v>579990.0</v>
+        <v>100000.0</v>
+      </c>
+      <c r="D38" s="8">
+        <v>359990.0</v>
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
@@ -2041,13 +2084,13 @@
         <v>41</v>
       </c>
       <c r="B39" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C39" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D39" s="9">
-        <v>579990.0</v>
+      <c r="D39" s="8">
+        <v>379990.0</v>
       </c>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
@@ -2064,13 +2107,13 @@
         <v>42</v>
       </c>
       <c r="B40" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C40" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D40" s="9">
-        <v>689990.0</v>
+      <c r="D40" s="8">
+        <v>379990.0</v>
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
@@ -2087,13 +2130,13 @@
         <v>43</v>
       </c>
       <c r="B41" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C41" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D41" s="9">
-        <v>1059990.0</v>
+      <c r="D41" s="8">
+        <v>379990.0</v>
       </c>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
@@ -2110,13 +2153,13 @@
         <v>44</v>
       </c>
       <c r="B42" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C42" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D42" s="9">
-        <v>1059990.0</v>
+      <c r="D42" s="8">
+        <v>359990.0</v>
       </c>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
@@ -2133,13 +2176,13 @@
         <v>45</v>
       </c>
       <c r="B43" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C43" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D43" s="9">
-        <v>1059990.0</v>
+      <c r="D43" s="8">
+        <v>429990.0</v>
       </c>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
@@ -2156,13 +2199,13 @@
         <v>46</v>
       </c>
       <c r="B44" s="7">
-        <v>2.6951291E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C44" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D44" s="9">
-        <v>19990.0</v>
+      <c r="D44" s="8">
+        <v>459990.0</v>
       </c>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
@@ -2179,13 +2222,13 @@
         <v>47</v>
       </c>
       <c r="B45" s="7">
-        <v>2.6951291E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C45" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D45" s="9">
-        <v>19990.0</v>
+      <c r="D45" s="8">
+        <v>459990.0</v>
       </c>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
@@ -2202,13 +2245,13 @@
         <v>48</v>
       </c>
       <c r="B46" s="7">
-        <v>2.516072E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C46" s="8">
-        <v>80000.0</v>
-      </c>
-      <c r="D46" s="9">
-        <v>29990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D46" s="8">
+        <v>459990.0</v>
       </c>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
@@ -2225,13 +2268,13 @@
         <v>49</v>
       </c>
       <c r="B47" s="7">
-        <v>2.516072E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C47" s="8">
-        <v>80000.0</v>
-      </c>
-      <c r="D47" s="9">
-        <v>29990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D47" s="8">
+        <v>549990.0</v>
       </c>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
@@ -2248,13 +2291,13 @@
         <v>50</v>
       </c>
       <c r="B48" s="7">
-        <v>2.6975042E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C48" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D48" s="9">
-        <v>990.0</v>
+      <c r="D48" s="8">
+        <v>549990.0</v>
       </c>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
@@ -2271,13 +2314,13 @@
         <v>51</v>
       </c>
       <c r="B49" s="7">
-        <v>2.6975042E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C49" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D49" s="9">
-        <v>990.0</v>
+      <c r="D49" s="8">
+        <v>549990.0</v>
       </c>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
@@ -2294,13 +2337,13 @@
         <v>52</v>
       </c>
       <c r="B50" s="7">
-        <v>2.6951291E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C50" s="8">
-        <v>110000.0</v>
-      </c>
-      <c r="D50" s="9">
-        <v>19990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D50" s="8">
+        <v>689990.0</v>
       </c>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
@@ -2317,13 +2360,13 @@
         <v>53</v>
       </c>
       <c r="B51" s="7">
-        <v>2.6951291E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C51" s="8">
-        <v>110000.0</v>
-      </c>
-      <c r="D51" s="9">
-        <v>19990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D51" s="8">
+        <v>1029990.0</v>
       </c>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
@@ -2340,13 +2383,13 @@
         <v>54</v>
       </c>
       <c r="B52" s="7">
-        <v>2.6951291E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C52" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D52" s="9">
-        <v>19990.0</v>
+      <c r="D52" s="8">
+        <v>1029990.0</v>
       </c>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
@@ -2363,13 +2406,13 @@
         <v>55</v>
       </c>
       <c r="B53" s="7">
-        <v>2.6951291E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C53" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D53" s="9">
-        <v>19990.0</v>
+      <c r="D53" s="8">
+        <v>1029990.0</v>
       </c>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
@@ -2386,13 +2429,13 @@
         <v>56</v>
       </c>
       <c r="B54" s="7">
-        <v>2.7401902E7</v>
+        <v>2.00026951298E11</v>
       </c>
       <c r="C54" s="8">
-        <v>110000.0</v>
-      </c>
-      <c r="D54" s="9">
-        <v>39990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D54" s="8">
+        <v>19990.0</v>
       </c>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
@@ -2409,13 +2452,13 @@
         <v>57</v>
       </c>
       <c r="B55" s="7">
-        <v>2.7401902E7</v>
+        <v>2.00026951298E11</v>
       </c>
       <c r="C55" s="8">
-        <v>110000.0</v>
-      </c>
-      <c r="D55" s="9">
-        <v>39990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D55" s="8">
+        <v>19990.0</v>
       </c>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
@@ -2432,13 +2475,13 @@
         <v>58</v>
       </c>
       <c r="B56" s="7">
-        <v>2.7512259E7</v>
+        <v>2.00025160721E11</v>
       </c>
       <c r="C56" s="8">
-        <v>80000.0</v>
-      </c>
-      <c r="D56" s="9">
-        <v>49990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D56" s="8">
+        <v>29990.0</v>
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
@@ -2455,13 +2498,13 @@
         <v>59</v>
       </c>
       <c r="B57" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00025160721E11</v>
       </c>
       <c r="C57" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D57" s="9">
-        <v>79990.0</v>
+      <c r="D57" s="8">
+        <v>29990.0</v>
       </c>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
@@ -2478,13 +2521,13 @@
         <v>60</v>
       </c>
       <c r="B58" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C58" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D58" s="9">
-        <v>79990.0</v>
+      <c r="D58" s="8">
+        <v>49990.0</v>
       </c>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
@@ -2501,13 +2544,13 @@
         <v>61</v>
       </c>
       <c r="B59" s="7">
-        <v>2.7512259E7</v>
+        <v>2.00026975041E11</v>
       </c>
       <c r="C59" s="8">
-        <v>80000.0</v>
-      </c>
-      <c r="D59" s="9">
-        <v>149990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D59" s="8">
+        <v>990.0</v>
       </c>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
@@ -2524,13 +2567,13 @@
         <v>62</v>
       </c>
       <c r="B60" s="7">
-        <v>2.7512259E7</v>
+        <v>2.00026975041E11</v>
       </c>
       <c r="C60" s="8">
-        <v>80000.0</v>
-      </c>
-      <c r="D60" s="9">
-        <v>149990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D60" s="8">
+        <v>990.0</v>
       </c>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
@@ -2547,13 +2590,13 @@
         <v>63</v>
       </c>
       <c r="B61" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027491724E11</v>
       </c>
       <c r="C61" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D61" s="9">
-        <v>119990.0</v>
+        <v>110000.0</v>
+      </c>
+      <c r="D61" s="8">
+        <v>9990.0</v>
       </c>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
@@ -2570,13 +2613,13 @@
         <v>64</v>
       </c>
       <c r="B62" s="7">
-        <v>2.7401724E7</v>
+        <v>2.00027491724E11</v>
       </c>
       <c r="C62" s="8">
-        <v>90000.0</v>
-      </c>
-      <c r="D62" s="9">
-        <v>199990.0</v>
+        <v>110000.0</v>
+      </c>
+      <c r="D62" s="8">
+        <v>9990.0</v>
       </c>
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
@@ -2593,13 +2636,13 @@
         <v>65</v>
       </c>
       <c r="B63" s="7">
-        <v>2.7401724E7</v>
+        <v>2.00026951298E11</v>
       </c>
       <c r="C63" s="8">
-        <v>90000.0</v>
-      </c>
-      <c r="D63" s="9">
-        <v>179990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D63" s="8">
+        <v>19990.0</v>
       </c>
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
@@ -2616,13 +2659,13 @@
         <v>66</v>
       </c>
       <c r="B64" s="7">
-        <v>2.7401724E7</v>
+        <v>2.00026951298E11</v>
       </c>
       <c r="C64" s="8">
-        <v>90000.0</v>
-      </c>
-      <c r="D64" s="9">
-        <v>269990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D64" s="8">
+        <v>19990.0</v>
       </c>
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
@@ -2639,13 +2682,13 @@
         <v>67</v>
       </c>
       <c r="B65" s="7">
-        <v>2.7497756E7</v>
+        <v>2.0002740173E11</v>
       </c>
       <c r="C65" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D65" s="9">
-        <v>229990.0</v>
+        <v>110000.0</v>
+      </c>
+      <c r="D65" s="8">
+        <v>39990.0</v>
       </c>
       <c r="H65" s="5"/>
       <c r="I65" s="5"/>
@@ -2662,13 +2705,13 @@
         <v>68</v>
       </c>
       <c r="B66" s="7">
-        <v>2.7497756E7</v>
+        <v>2.0002740173E11</v>
       </c>
       <c r="C66" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D66" s="9">
-        <v>409990.0</v>
+        <v>110000.0</v>
+      </c>
+      <c r="D66" s="8">
+        <v>39990.0</v>
       </c>
       <c r="H66" s="5"/>
       <c r="I66" s="5"/>
@@ -2685,13 +2728,13 @@
         <v>69</v>
       </c>
       <c r="B67" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C67" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D67" s="9">
-        <v>319990.0</v>
+      <c r="D67" s="8">
+        <v>59990.0</v>
       </c>
       <c r="H67" s="5"/>
       <c r="I67" s="5"/>
@@ -2708,13 +2751,13 @@
         <v>70</v>
       </c>
       <c r="B68" s="7">
-        <v>2.7401724E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C68" s="8">
-        <v>90000.0</v>
-      </c>
-      <c r="D68" s="9">
-        <v>429990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D68" s="8">
+        <v>69990.0</v>
       </c>
       <c r="H68" s="5"/>
       <c r="I68" s="5"/>
@@ -2731,13 +2774,13 @@
         <v>71</v>
       </c>
       <c r="B69" s="7">
-        <v>2.7401724E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C69" s="8">
-        <v>90000.0</v>
-      </c>
-      <c r="D69" s="9">
-        <v>429990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D69" s="8">
+        <v>69990.0</v>
       </c>
       <c r="H69" s="5"/>
       <c r="I69" s="5"/>
@@ -2754,13 +2797,13 @@
         <v>72</v>
       </c>
       <c r="B70" s="7">
-        <v>2.7401724E7</v>
+        <v>2.00027401723E11</v>
       </c>
       <c r="C70" s="8">
-        <v>90000.0</v>
-      </c>
-      <c r="D70" s="9">
-        <v>429990.0</v>
+        <v>80000.0</v>
+      </c>
+      <c r="D70" s="8">
+        <v>149990.0</v>
       </c>
       <c r="H70" s="5"/>
       <c r="I70" s="5"/>
@@ -2777,13 +2820,13 @@
         <v>73</v>
       </c>
       <c r="B71" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027401723E11</v>
       </c>
       <c r="C71" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D71" s="9">
-        <v>629990.0</v>
+        <v>80000.0</v>
+      </c>
+      <c r="D71" s="8">
+        <v>149990.0</v>
       </c>
       <c r="H71" s="5"/>
       <c r="I71" s="5"/>
@@ -2800,13 +2843,13 @@
         <v>74</v>
       </c>
       <c r="B72" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C72" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D72" s="9">
-        <v>629990.0</v>
+      <c r="D72" s="8">
+        <v>109990.0</v>
       </c>
       <c r="H72" s="5"/>
       <c r="I72" s="5"/>
@@ -2823,13 +2866,13 @@
         <v>75</v>
       </c>
       <c r="B73" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027401723E11</v>
       </c>
       <c r="C73" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D73" s="9">
-        <v>629990.0</v>
+        <v>80000.0</v>
+      </c>
+      <c r="D73" s="8">
+        <v>199990.0</v>
       </c>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
@@ -2846,13 +2889,13 @@
         <v>76</v>
       </c>
       <c r="B74" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027401907E11</v>
       </c>
       <c r="C74" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D74" s="9">
-        <v>529990.0</v>
+        <v>90000.0</v>
+      </c>
+      <c r="D74" s="8">
+        <v>139990.0</v>
       </c>
       <c r="H74" s="5"/>
       <c r="I74" s="5"/>
@@ -2869,13 +2912,13 @@
         <v>77</v>
       </c>
       <c r="B75" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C75" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D75" s="9">
-        <v>529990.0</v>
+      <c r="D75" s="8">
+        <v>259990.0</v>
       </c>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
@@ -2892,13 +2935,13 @@
         <v>78</v>
       </c>
       <c r="B76" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C76" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D76" s="9">
-        <v>929990.0</v>
+      <c r="D76" s="8">
+        <v>199990.0</v>
       </c>
       <c r="H76" s="5"/>
       <c r="I76" s="5"/>
@@ -2915,13 +2958,13 @@
         <v>79</v>
       </c>
       <c r="B77" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027497757E11</v>
       </c>
       <c r="C77" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D77" s="9">
-        <v>929990.0</v>
+        <v>50000.0</v>
+      </c>
+      <c r="D77" s="8">
+        <v>409990.0</v>
       </c>
       <c r="H77" s="5"/>
       <c r="I77" s="5"/>
@@ -2938,13 +2981,13 @@
         <v>80</v>
       </c>
       <c r="B78" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C78" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D78" s="9">
-        <v>499990.0</v>
+      <c r="D78" s="8">
+        <v>319990.0</v>
       </c>
       <c r="H78" s="5"/>
       <c r="I78" s="5"/>
@@ -2961,13 +3004,13 @@
         <v>81</v>
       </c>
       <c r="B79" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027401723E11</v>
       </c>
       <c r="C79" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D79" s="9">
-        <v>499990.0</v>
+        <v>80000.0</v>
+      </c>
+      <c r="D79" s="8">
+        <v>389990.0</v>
       </c>
       <c r="H79" s="5"/>
       <c r="I79" s="5"/>
@@ -2984,13 +3027,13 @@
         <v>82</v>
       </c>
       <c r="B80" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027401723E11</v>
       </c>
       <c r="C80" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D80" s="9">
-        <v>619990.0</v>
+        <v>80000.0</v>
+      </c>
+      <c r="D80" s="8">
+        <v>389990.0</v>
       </c>
       <c r="H80" s="5"/>
       <c r="I80" s="5"/>
@@ -3007,13 +3050,13 @@
         <v>83</v>
       </c>
       <c r="B81" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027401723E11</v>
       </c>
       <c r="C81" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D81" s="9">
-        <v>659990.0</v>
+        <v>80000.0</v>
+      </c>
+      <c r="D81" s="8">
+        <v>389990.0</v>
       </c>
       <c r="H81" s="5"/>
       <c r="I81" s="5"/>
@@ -3030,13 +3073,13 @@
         <v>84</v>
       </c>
       <c r="B82" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C82" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D82" s="9">
-        <v>489990.0</v>
+      <c r="D82" s="8">
+        <v>609990.0</v>
       </c>
       <c r="H82" s="5"/>
       <c r="I82" s="5"/>
@@ -3053,13 +3096,13 @@
         <v>85</v>
       </c>
       <c r="B83" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C83" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D83" s="9">
-        <v>489990.0</v>
+      <c r="D83" s="8">
+        <v>609990.0</v>
       </c>
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
@@ -3076,13 +3119,13 @@
         <v>86</v>
       </c>
       <c r="B84" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C84" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D84" s="9">
-        <v>729990.0</v>
+      <c r="D84" s="8">
+        <v>609990.0</v>
       </c>
       <c r="H84" s="5"/>
       <c r="I84" s="5"/>
@@ -3099,13 +3142,13 @@
         <v>87</v>
       </c>
       <c r="B85" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C85" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D85" s="9">
-        <v>799990.0</v>
+      <c r="D85" s="8">
+        <v>489990.0</v>
       </c>
       <c r="H85" s="5"/>
       <c r="I85" s="5"/>
@@ -3122,13 +3165,13 @@
         <v>88</v>
       </c>
       <c r="B86" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C86" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D86" s="9">
-        <v>799990.0</v>
+      <c r="D86" s="8">
+        <v>489990.0</v>
       </c>
       <c r="H86" s="5"/>
       <c r="I86" s="5"/>
@@ -3145,13 +3188,13 @@
         <v>89</v>
       </c>
       <c r="B87" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C87" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D87" s="9">
-        <v>969990.0</v>
+      <c r="D87" s="8">
+        <v>859990.0</v>
       </c>
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
@@ -3168,13 +3211,13 @@
         <v>90</v>
       </c>
       <c r="B88" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C88" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D88" s="9">
-        <v>1079990.0</v>
+      <c r="D88" s="8">
+        <v>859990.0</v>
       </c>
       <c r="H88" s="5"/>
       <c r="I88" s="5"/>
@@ -3191,13 +3234,13 @@
         <v>91</v>
       </c>
       <c r="B89" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C89" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D89" s="9">
-        <v>1079990.0</v>
+      <c r="D89" s="8">
+        <v>499990.0</v>
       </c>
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
@@ -3214,13 +3257,13 @@
         <v>92</v>
       </c>
       <c r="B90" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C90" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D90" s="9">
-        <v>1229990.0</v>
+      <c r="D90" s="8">
+        <v>499990.0</v>
       </c>
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
@@ -3237,13 +3280,13 @@
         <v>93</v>
       </c>
       <c r="B91" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C91" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D91" s="9">
-        <v>1279990.0</v>
+      <c r="D91" s="8">
+        <v>619990.0</v>
       </c>
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
@@ -3260,13 +3303,13 @@
         <v>94</v>
       </c>
       <c r="B92" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C92" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D92" s="9">
-        <v>1279990.0</v>
+      <c r="D92" s="8">
+        <v>659990.0</v>
       </c>
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
@@ -3283,13 +3326,13 @@
         <v>95</v>
       </c>
       <c r="B93" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C93" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D93" s="9">
-        <v>1179990.0</v>
+      <c r="D93" s="8">
+        <v>489990.0</v>
       </c>
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
@@ -3306,13 +3349,13 @@
         <v>96</v>
       </c>
       <c r="B94" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C94" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D94" s="9">
-        <v>1179990.0</v>
+      <c r="D94" s="8">
+        <v>489990.0</v>
       </c>
       <c r="H94" s="5"/>
       <c r="I94" s="5"/>
@@ -3329,13 +3372,13 @@
         <v>97</v>
       </c>
       <c r="B95" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C95" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D95" s="9">
-        <v>1179990.0</v>
+      <c r="D95" s="8">
+        <v>729990.0</v>
       </c>
       <c r="H95" s="5"/>
       <c r="I95" s="5"/>
@@ -3352,13 +3395,13 @@
         <v>98</v>
       </c>
       <c r="B96" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C96" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D96" s="9">
-        <v>1179990.0</v>
+      <c r="D96" s="8">
+        <v>799990.0</v>
       </c>
       <c r="H96" s="5"/>
       <c r="I96" s="5"/>
@@ -3375,13 +3418,13 @@
         <v>99</v>
       </c>
       <c r="B97" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C97" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D97" s="9">
-        <v>1429990.0</v>
+      <c r="D97" s="8">
+        <v>799990.0</v>
       </c>
       <c r="H97" s="5"/>
       <c r="I97" s="5"/>
@@ -3398,13 +3441,13 @@
         <v>100</v>
       </c>
       <c r="B98" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C98" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D98" s="9">
-        <v>1429990.0</v>
+      <c r="D98" s="8">
+        <v>969990.0</v>
       </c>
       <c r="H98" s="5"/>
       <c r="I98" s="5"/>
@@ -3421,13 +3464,13 @@
         <v>101</v>
       </c>
       <c r="B99" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C99" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D99" s="9">
-        <v>1429990.0</v>
+      <c r="D99" s="8">
+        <v>1079990.0</v>
       </c>
       <c r="H99" s="5"/>
       <c r="I99" s="5"/>
@@ -3444,13 +3487,13 @@
         <v>102</v>
       </c>
       <c r="B100" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C100" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D100" s="9">
-        <v>1309990.0</v>
+      <c r="D100" s="8">
+        <v>1079990.0</v>
       </c>
       <c r="H100" s="5"/>
       <c r="I100" s="5"/>
@@ -3467,13 +3510,13 @@
         <v>103</v>
       </c>
       <c r="B101" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C101" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D101" s="9">
-        <v>1309990.0</v>
+      <c r="D101" s="8">
+        <v>1229990.0</v>
       </c>
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
@@ -3490,13 +3533,13 @@
         <v>104</v>
       </c>
       <c r="B102" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C102" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D102" s="9">
-        <v>1309990.0</v>
+      <c r="D102" s="8">
+        <v>1279990.0</v>
       </c>
       <c r="H102" s="5"/>
       <c r="I102" s="5"/>
@@ -3513,13 +3556,13 @@
         <v>105</v>
       </c>
       <c r="B103" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C103" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D103" s="9">
-        <v>909990.0</v>
+      <c r="D103" s="8">
+        <v>1279990.0</v>
       </c>
       <c r="H103" s="5"/>
       <c r="I103" s="5"/>
@@ -3536,13 +3579,13 @@
         <v>106</v>
       </c>
       <c r="B104" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C104" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D104" s="9">
-        <v>909990.0</v>
+      <c r="D104" s="8">
+        <v>1179990.0</v>
       </c>
       <c r="H104" s="5"/>
       <c r="I104" s="5"/>
@@ -3559,13 +3602,13 @@
         <v>107</v>
       </c>
       <c r="B105" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C105" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D105" s="9">
-        <v>909990.0</v>
+      <c r="D105" s="8">
+        <v>1179990.0</v>
       </c>
       <c r="H105" s="5"/>
       <c r="I105" s="5"/>
@@ -3582,13 +3625,13 @@
         <v>108</v>
       </c>
       <c r="B106" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C106" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D106" s="9">
-        <v>909990.0</v>
+      <c r="D106" s="8">
+        <v>1179990.0</v>
       </c>
       <c r="H106" s="5"/>
       <c r="I106" s="5"/>
@@ -3605,13 +3648,13 @@
         <v>109</v>
       </c>
       <c r="B107" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C107" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D107" s="9">
-        <v>909990.0</v>
+      <c r="D107" s="8">
+        <v>1179990.0</v>
       </c>
       <c r="H107" s="5"/>
       <c r="I107" s="5"/>
@@ -3628,13 +3671,13 @@
         <v>110</v>
       </c>
       <c r="B108" s="7">
-        <v>2.7491723E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C108" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D108" s="9">
-        <v>9990.0</v>
+      <c r="D108" s="8">
+        <v>1429990.0</v>
       </c>
       <c r="H108" s="5"/>
       <c r="I108" s="5"/>
@@ -3651,13 +3694,13 @@
         <v>111</v>
       </c>
       <c r="B109" s="7">
-        <v>2.7491723E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C109" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D109" s="9">
-        <v>9990.0</v>
+      <c r="D109" s="8">
+        <v>1429990.0</v>
       </c>
       <c r="H109" s="5"/>
       <c r="I109" s="5"/>
@@ -3674,13 +3717,13 @@
         <v>112</v>
       </c>
       <c r="B110" s="7">
-        <v>2.6951291E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C110" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D110" s="9">
-        <v>19990.0</v>
+      <c r="D110" s="8">
+        <v>1429990.0</v>
       </c>
       <c r="H110" s="5"/>
       <c r="I110" s="5"/>
@@ -3697,13 +3740,13 @@
         <v>113</v>
       </c>
       <c r="B111" s="7">
-        <v>2.6951291E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C111" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D111" s="9">
-        <v>19990.0</v>
+      <c r="D111" s="8">
+        <v>1309990.0</v>
       </c>
       <c r="H111" s="5"/>
       <c r="I111" s="5"/>
@@ -3720,13 +3763,13 @@
         <v>114</v>
       </c>
       <c r="B112" s="7">
-        <v>2.516072E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C112" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D112" s="9">
-        <v>29990.0</v>
+      <c r="D112" s="8">
+        <v>1309990.0</v>
       </c>
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
@@ -3743,13 +3786,13 @@
         <v>115</v>
       </c>
       <c r="B113" s="7">
-        <v>2.516072E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C113" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D113" s="9">
-        <v>29990.0</v>
+      <c r="D113" s="8">
+        <v>1309990.0</v>
       </c>
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
@@ -3766,13 +3809,13 @@
         <v>116</v>
       </c>
       <c r="B114" s="7">
-        <v>2.516072E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C114" s="8">
-        <v>90000.0</v>
-      </c>
-      <c r="D114" s="9">
-        <v>29990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D114" s="8">
+        <v>909990.0</v>
       </c>
       <c r="H114" s="5"/>
       <c r="I114" s="5"/>
@@ -3789,13 +3832,13 @@
         <v>117</v>
       </c>
       <c r="B115" s="7">
-        <v>2.516072E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C115" s="8">
-        <v>90000.0</v>
-      </c>
-      <c r="D115" s="9">
-        <v>29990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D115" s="8">
+        <v>909990.0</v>
       </c>
       <c r="H115" s="5"/>
       <c r="I115" s="5"/>
@@ -3812,13 +3855,13 @@
         <v>118</v>
       </c>
       <c r="B116" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C116" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D116" s="9">
-        <v>39990.0</v>
+      <c r="D116" s="8">
+        <v>909990.0</v>
       </c>
       <c r="H116" s="5"/>
       <c r="I116" s="5"/>
@@ -3835,13 +3878,13 @@
         <v>119</v>
       </c>
       <c r="B117" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C117" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D117" s="9">
-        <v>39990.0</v>
+      <c r="D117" s="8">
+        <v>909990.0</v>
       </c>
       <c r="H117" s="5"/>
       <c r="I117" s="5"/>
@@ -3858,13 +3901,13 @@
         <v>120</v>
       </c>
       <c r="B118" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C118" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D118" s="9">
-        <v>39990.0</v>
+      <c r="D118" s="8">
+        <v>909990.0</v>
       </c>
       <c r="H118" s="5"/>
       <c r="I118" s="5"/>
@@ -3881,13 +3924,13 @@
         <v>121</v>
       </c>
       <c r="B119" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027491724E11</v>
       </c>
       <c r="C119" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D119" s="9">
-        <v>39990.0</v>
+      <c r="D119" s="8">
+        <v>9990.0</v>
       </c>
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
@@ -3904,13 +3947,13 @@
         <v>122</v>
       </c>
       <c r="B120" s="7">
-        <v>2.7512259E7</v>
+        <v>2.00027491724E11</v>
       </c>
       <c r="C120" s="8">
-        <v>80000.0</v>
-      </c>
-      <c r="D120" s="9">
-        <v>59990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D120" s="8">
+        <v>9990.0</v>
       </c>
       <c r="H120" s="5"/>
       <c r="I120" s="5"/>
@@ -3927,13 +3970,13 @@
         <v>123</v>
       </c>
       <c r="B121" s="7">
-        <v>2.7512259E7</v>
+        <v>2.00027491724E11</v>
       </c>
       <c r="C121" s="8">
-        <v>80000.0</v>
-      </c>
-      <c r="D121" s="9">
-        <v>59990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D121" s="8">
+        <v>9990.0</v>
       </c>
       <c r="H121" s="5"/>
       <c r="I121" s="5"/>
@@ -3950,13 +3993,13 @@
         <v>124</v>
       </c>
       <c r="B122" s="7">
-        <v>2.7512259E7</v>
+        <v>2.00027491724E11</v>
       </c>
       <c r="C122" s="8">
-        <v>80000.0</v>
-      </c>
-      <c r="D122" s="9">
-        <v>59990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D122" s="8">
+        <v>9990.0</v>
       </c>
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
@@ -3973,12 +4016,12 @@
         <v>125</v>
       </c>
       <c r="B123" s="7">
-        <v>2.516072E7</v>
+        <v>2.00025160721E11</v>
       </c>
       <c r="C123" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D123" s="9">
+      <c r="D123" s="8">
         <v>29990.0</v>
       </c>
       <c r="H123" s="5"/>
@@ -3996,12 +4039,12 @@
         <v>126</v>
       </c>
       <c r="B124" s="7">
-        <v>2.516072E7</v>
+        <v>2.00025160721E11</v>
       </c>
       <c r="C124" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D124" s="9">
+      <c r="D124" s="8">
         <v>29990.0</v>
       </c>
       <c r="H124" s="5"/>
@@ -4019,13 +4062,13 @@
         <v>127</v>
       </c>
       <c r="B125" s="7">
-        <v>2.7401902E7</v>
+        <v>2.00025160721E11</v>
       </c>
       <c r="C125" s="8">
-        <v>110000.0</v>
-      </c>
-      <c r="D125" s="9">
-        <v>89990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D125" s="8">
+        <v>29990.0</v>
       </c>
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
@@ -4042,13 +4085,13 @@
         <v>128</v>
       </c>
       <c r="B126" s="7">
-        <v>2.7401902E7</v>
+        <v>2.00026951298E11</v>
       </c>
       <c r="C126" s="8">
-        <v>110000.0</v>
-      </c>
-      <c r="D126" s="9">
-        <v>89990.0</v>
+        <v>80000.0</v>
+      </c>
+      <c r="D126" s="8">
+        <v>19990.0</v>
       </c>
       <c r="H126" s="5"/>
       <c r="I126" s="5"/>
@@ -4065,13 +4108,13 @@
         <v>129</v>
       </c>
       <c r="B127" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C127" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D127" s="9">
-        <v>69990.0</v>
+      <c r="D127" s="8">
+        <v>39990.0</v>
       </c>
       <c r="H127" s="5"/>
       <c r="I127" s="5"/>
@@ -4088,13 +4131,13 @@
         <v>130</v>
       </c>
       <c r="B128" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C128" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D128" s="9">
-        <v>69990.0</v>
+      <c r="D128" s="8">
+        <v>39990.0</v>
       </c>
       <c r="H128" s="5"/>
       <c r="I128" s="5"/>
@@ -4111,13 +4154,13 @@
         <v>131</v>
       </c>
       <c r="B129" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C129" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D129" s="9">
-        <v>179990.0</v>
+      <c r="D129" s="8">
+        <v>39990.0</v>
       </c>
       <c r="H129" s="5"/>
       <c r="I129" s="5"/>
@@ -4134,13 +4177,13 @@
         <v>132</v>
       </c>
       <c r="B130" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C130" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D130" s="9">
-        <v>179990.0</v>
+      <c r="D130" s="8">
+        <v>39990.0</v>
       </c>
       <c r="H130" s="5"/>
       <c r="I130" s="5"/>
@@ -4157,13 +4200,13 @@
         <v>133</v>
       </c>
       <c r="B131" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027401723E11</v>
       </c>
       <c r="C131" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D131" s="9">
-        <v>129990.0</v>
+        <v>80000.0</v>
+      </c>
+      <c r="D131" s="8">
+        <v>49990.0</v>
       </c>
       <c r="H131" s="5"/>
       <c r="I131" s="5"/>
@@ -4180,13 +4223,13 @@
         <v>134</v>
       </c>
       <c r="B132" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027401723E11</v>
       </c>
       <c r="C132" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D132" s="9">
-        <v>159990.0</v>
+        <v>80000.0</v>
+      </c>
+      <c r="D132" s="8">
+        <v>49990.0</v>
       </c>
       <c r="H132" s="5"/>
       <c r="I132" s="5"/>
@@ -4200,16 +4243,16 @@
     </row>
     <row r="133" ht="18.0" customHeight="1">
       <c r="A133" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B133" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027401723E11</v>
       </c>
       <c r="C133" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D133" s="9">
-        <v>159990.0</v>
+        <v>80000.0</v>
+      </c>
+      <c r="D133" s="8">
+        <v>49990.0</v>
       </c>
       <c r="H133" s="5"/>
       <c r="I133" s="5"/>
@@ -4223,16 +4266,16 @@
     </row>
     <row r="134" ht="18.0" customHeight="1">
       <c r="A134" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B134" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00025160721E11</v>
       </c>
       <c r="C134" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D134" s="9">
-        <v>159990.0</v>
+      <c r="D134" s="8">
+        <v>29990.0</v>
       </c>
       <c r="H134" s="5"/>
       <c r="I134" s="5"/>
@@ -4246,16 +4289,16 @@
     </row>
     <row r="135" ht="18.0" customHeight="1">
       <c r="A135" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B135" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00025160721E11</v>
       </c>
       <c r="C135" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D135" s="9">
-        <v>229990.0</v>
+      <c r="D135" s="8">
+        <v>29990.0</v>
       </c>
       <c r="H135" s="5"/>
       <c r="I135" s="5"/>
@@ -4269,16 +4312,16 @@
     </row>
     <row r="136" ht="18.0" customHeight="1">
       <c r="A136" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B136" s="7">
-        <v>2.7497756E7</v>
+        <v>2.0002740173E11</v>
       </c>
       <c r="C136" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D136" s="9">
-        <v>229990.0</v>
+        <v>110000.0</v>
+      </c>
+      <c r="D136" s="8">
+        <v>89990.0</v>
       </c>
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
@@ -4292,16 +4335,16 @@
     </row>
     <row r="137" ht="18.0" customHeight="1">
       <c r="A137" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B137" s="7">
-        <v>2.7497756E7</v>
+        <v>2.0002740173E11</v>
       </c>
       <c r="C137" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D137" s="9">
-        <v>229990.0</v>
+        <v>110000.0</v>
+      </c>
+      <c r="D137" s="8">
+        <v>89990.0</v>
       </c>
       <c r="H137" s="5"/>
       <c r="I137" s="5"/>
@@ -4315,16 +4358,16 @@
     </row>
     <row r="138" ht="18.0" customHeight="1">
       <c r="A138" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B138" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C138" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D138" s="9">
-        <v>229990.0</v>
+      <c r="D138" s="8">
+        <v>69990.0</v>
       </c>
       <c r="H138" s="5"/>
       <c r="I138" s="5"/>
@@ -4338,16 +4381,16 @@
     </row>
     <row r="139" ht="18.0" customHeight="1">
       <c r="A139" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B139" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C139" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D139" s="9">
-        <v>279990.0</v>
+      <c r="D139" s="8">
+        <v>69990.0</v>
       </c>
       <c r="H139" s="5"/>
       <c r="I139" s="5"/>
@@ -4361,16 +4404,16 @@
     </row>
     <row r="140" ht="18.0" customHeight="1">
       <c r="A140" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B140" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C140" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D140" s="9">
-        <v>279990.0</v>
+      <c r="D140" s="8">
+        <v>169990.0</v>
       </c>
       <c r="H140" s="5"/>
       <c r="I140" s="5"/>
@@ -4384,16 +4427,16 @@
     </row>
     <row r="141" ht="18.0" customHeight="1">
       <c r="A141" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B141" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C141" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D141" s="9">
-        <v>429990.0</v>
+      <c r="D141" s="8">
+        <v>169990.0</v>
       </c>
       <c r="H141" s="5"/>
       <c r="I141" s="5"/>
@@ -4407,16 +4450,16 @@
     </row>
     <row r="142" ht="18.0" customHeight="1">
       <c r="A142" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B142" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C142" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D142" s="9">
-        <v>429990.0</v>
+      <c r="D142" s="8">
+        <v>129990.0</v>
       </c>
       <c r="H142" s="5"/>
       <c r="I142" s="5"/>
@@ -4430,16 +4473,16 @@
     </row>
     <row r="143" ht="18.0" customHeight="1">
       <c r="A143" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B143" s="7">
-        <v>2.7491723E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C143" s="8">
-        <v>80000.0</v>
-      </c>
-      <c r="D143" s="9">
-        <v>9990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D143" s="8">
+        <v>159990.0</v>
       </c>
       <c r="H143" s="5"/>
       <c r="I143" s="5"/>
@@ -4456,13 +4499,13 @@
         <v>145</v>
       </c>
       <c r="B144" s="7">
-        <v>2.7491723E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C144" s="8">
-        <v>100000.0</v>
-      </c>
-      <c r="D144" s="9">
-        <v>9990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D144" s="8">
+        <v>159990.0</v>
       </c>
       <c r="H144" s="5"/>
       <c r="I144" s="5"/>
@@ -4479,13 +4522,13 @@
         <v>146</v>
       </c>
       <c r="B145" s="7">
-        <v>2.7512259E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C145" s="8">
-        <v>80000.0</v>
-      </c>
-      <c r="D145" s="9">
-        <v>39990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D145" s="8">
+        <v>159990.0</v>
       </c>
       <c r="H145" s="5"/>
       <c r="I145" s="5"/>
@@ -4502,13 +4545,13 @@
         <v>147</v>
       </c>
       <c r="B146" s="7">
-        <v>2.7401724E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C146" s="8">
-        <v>90000.0</v>
-      </c>
-      <c r="D146" s="9">
-        <v>39990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D146" s="8">
+        <v>229990.0</v>
       </c>
       <c r="H146" s="5"/>
       <c r="I146" s="5"/>
@@ -4525,13 +4568,13 @@
         <v>148</v>
       </c>
       <c r="B147" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C147" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D147" s="9">
-        <v>69990.0</v>
+      <c r="D147" s="8">
+        <v>229990.0</v>
       </c>
       <c r="H147" s="5"/>
       <c r="I147" s="5"/>
@@ -4548,13 +4591,13 @@
         <v>149</v>
       </c>
       <c r="B148" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C148" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D148" s="9">
-        <v>69990.0</v>
+      <c r="D148" s="8">
+        <v>219990.0</v>
       </c>
       <c r="H148" s="5"/>
       <c r="I148" s="5"/>
@@ -4571,13 +4614,13 @@
         <v>150</v>
       </c>
       <c r="B149" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C149" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D149" s="9">
-        <v>79990.0</v>
+      <c r="D149" s="8">
+        <v>219990.0</v>
       </c>
       <c r="H149" s="5"/>
       <c r="I149" s="5"/>
@@ -4594,13 +4637,13 @@
         <v>151</v>
       </c>
       <c r="B150" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C150" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D150" s="9">
-        <v>79990.0</v>
+      <c r="D150" s="8">
+        <v>279990.0</v>
       </c>
       <c r="H150" s="5"/>
       <c r="I150" s="5"/>
@@ -4617,13 +4660,13 @@
         <v>152</v>
       </c>
       <c r="B151" s="7">
-        <v>2.7512259E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C151" s="8">
-        <v>80000.0</v>
-      </c>
-      <c r="D151" s="9">
-        <v>99990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D151" s="8">
+        <v>279990.0</v>
       </c>
       <c r="H151" s="5"/>
       <c r="I151" s="5"/>
@@ -4640,13 +4683,13 @@
         <v>153</v>
       </c>
       <c r="B152" s="7">
-        <v>2.7512259E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C152" s="8">
-        <v>80000.0</v>
-      </c>
-      <c r="D152" s="9">
-        <v>99990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D152" s="8">
+        <v>529990.0</v>
       </c>
       <c r="H152" s="5"/>
       <c r="I152" s="5"/>
@@ -4663,13 +4706,13 @@
         <v>154</v>
       </c>
       <c r="B153" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C153" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D153" s="9">
-        <v>109990.0</v>
+      <c r="D153" s="8">
+        <v>529990.0</v>
       </c>
       <c r="H153" s="5"/>
       <c r="I153" s="5"/>
@@ -4686,13 +4729,13 @@
         <v>155</v>
       </c>
       <c r="B154" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00026951298E11</v>
       </c>
       <c r="C154" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D154" s="9">
-        <v>109990.0</v>
+      <c r="D154" s="8">
+        <v>19990.0</v>
       </c>
       <c r="H154" s="5"/>
       <c r="I154" s="5"/>
@@ -4709,13 +4752,13 @@
         <v>156</v>
       </c>
       <c r="B155" s="7">
-        <v>2.7512259E7</v>
+        <v>2.00027491724E11</v>
       </c>
       <c r="C155" s="8">
-        <v>80000.0</v>
-      </c>
-      <c r="D155" s="9">
-        <v>149990.0</v>
+        <v>100000.0</v>
+      </c>
+      <c r="D155" s="8">
+        <v>9990.0</v>
       </c>
       <c r="H155" s="5"/>
       <c r="I155" s="5"/>
@@ -4732,13 +4775,13 @@
         <v>157</v>
       </c>
       <c r="B156" s="7">
-        <v>2.7512259E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C156" s="8">
-        <v>80000.0</v>
-      </c>
-      <c r="D156" s="9">
-        <v>149990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D156" s="8">
+        <v>39990.0</v>
       </c>
       <c r="H156" s="5"/>
       <c r="I156" s="5"/>
@@ -4755,13 +4798,13 @@
         <v>158</v>
       </c>
       <c r="B157" s="7">
-        <v>2.7512259E7</v>
+        <v>2.00027401723E11</v>
       </c>
       <c r="C157" s="8">
         <v>80000.0</v>
       </c>
-      <c r="D157" s="9">
-        <v>149990.0</v>
+      <c r="D157" s="8">
+        <v>49990.0</v>
       </c>
       <c r="H157" s="5"/>
       <c r="I157" s="5"/>
@@ -4778,13 +4821,13 @@
         <v>159</v>
       </c>
       <c r="B158" s="7">
-        <v>2.7512259E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C158" s="8">
-        <v>80000.0</v>
-      </c>
-      <c r="D158" s="9">
-        <v>149990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D158" s="8">
+        <v>69990.0</v>
       </c>
       <c r="H158" s="5"/>
       <c r="I158" s="5"/>
@@ -4801,13 +4844,13 @@
         <v>160</v>
       </c>
       <c r="B159" s="7">
-        <v>2.7512267E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C159" s="8">
-        <v>120000.0</v>
-      </c>
-      <c r="D159" s="9">
-        <v>179990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D159" s="8">
+        <v>69990.0</v>
       </c>
       <c r="H159" s="5"/>
       <c r="I159" s="5"/>
@@ -4824,13 +4867,13 @@
         <v>161</v>
       </c>
       <c r="B160" s="7">
-        <v>2.7512267E7</v>
+        <v>2.00027401723E11</v>
       </c>
       <c r="C160" s="8">
-        <v>120000.0</v>
-      </c>
-      <c r="D160" s="9">
-        <v>179990.0</v>
+        <v>80000.0</v>
+      </c>
+      <c r="D160" s="8">
+        <v>119990.0</v>
       </c>
       <c r="H160" s="5"/>
       <c r="I160" s="5"/>
@@ -4847,13 +4890,13 @@
         <v>162</v>
       </c>
       <c r="B161" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C161" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D161" s="9">
-        <v>199990.0</v>
+      <c r="D161" s="8">
+        <v>79990.0</v>
       </c>
       <c r="H161" s="5"/>
       <c r="I161" s="5"/>
@@ -4870,13 +4913,13 @@
         <v>163</v>
       </c>
       <c r="B162" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C162" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D162" s="9">
-        <v>199990.0</v>
+      <c r="D162" s="8">
+        <v>79990.0</v>
       </c>
       <c r="H162" s="5"/>
       <c r="I162" s="5"/>
@@ -4893,13 +4936,13 @@
         <v>164</v>
       </c>
       <c r="B163" s="7">
-        <v>2.7401732E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C163" s="8">
-        <v>130000.0</v>
-      </c>
-      <c r="D163" s="9">
-        <v>259990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D163" s="8">
+        <v>109990.0</v>
       </c>
       <c r="H163" s="5"/>
       <c r="I163" s="5"/>
@@ -4916,13 +4959,13 @@
         <v>165</v>
       </c>
       <c r="B164" s="7">
-        <v>2.7401732E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C164" s="8">
-        <v>130000.0</v>
-      </c>
-      <c r="D164" s="9">
-        <v>259990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D164" s="8">
+        <v>109990.0</v>
       </c>
       <c r="H164" s="5"/>
       <c r="I164" s="5"/>
@@ -4939,13 +4982,13 @@
         <v>166</v>
       </c>
       <c r="B165" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C165" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D165" s="9">
-        <v>329990.0</v>
+      <c r="D165" s="8">
+        <v>109990.0</v>
       </c>
       <c r="H165" s="5"/>
       <c r="I165" s="5"/>
@@ -4962,13 +5005,13 @@
         <v>167</v>
       </c>
       <c r="B166" s="7">
-        <v>2.7491766E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C166" s="8">
-        <v>100000.0</v>
-      </c>
-      <c r="D166" s="9">
-        <v>349990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D166" s="8">
+        <v>109990.0</v>
       </c>
       <c r="H166" s="5"/>
       <c r="I166" s="5"/>
@@ -4985,13 +5028,13 @@
         <v>168</v>
       </c>
       <c r="B167" s="7">
-        <v>2.7491766E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C167" s="8">
-        <v>100000.0</v>
-      </c>
-      <c r="D167" s="9">
-        <v>349990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D167" s="8">
+        <v>149990.0</v>
       </c>
       <c r="H167" s="5"/>
       <c r="I167" s="5"/>
@@ -5008,13 +5051,13 @@
         <v>169</v>
       </c>
       <c r="B168" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C168" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D168" s="9">
-        <v>559990.0</v>
+      <c r="D168" s="8">
+        <v>149990.0</v>
       </c>
       <c r="H168" s="5"/>
       <c r="I168" s="5"/>
@@ -5031,13 +5074,13 @@
         <v>170</v>
       </c>
       <c r="B169" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C169" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D169" s="9">
-        <v>729990.0</v>
+      <c r="D169" s="8">
+        <v>149990.0</v>
       </c>
       <c r="H169" s="5"/>
       <c r="I169" s="5"/>
@@ -5054,13 +5097,13 @@
         <v>171</v>
       </c>
       <c r="B170" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C170" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D170" s="9">
-        <v>429990.0</v>
+      <c r="D170" s="8">
+        <v>149990.0</v>
       </c>
       <c r="H170" s="5"/>
       <c r="I170" s="5"/>
@@ -5077,13 +5120,13 @@
         <v>172</v>
       </c>
       <c r="B171" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027401907E11</v>
       </c>
       <c r="C171" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D171" s="9">
-        <v>429990.0</v>
+        <v>90000.0</v>
+      </c>
+      <c r="D171" s="8">
+        <v>199990.0</v>
       </c>
       <c r="H171" s="5"/>
       <c r="I171" s="5"/>
@@ -5100,13 +5143,13 @@
         <v>173</v>
       </c>
       <c r="B172" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027401907E11</v>
       </c>
       <c r="C172" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D172" s="9">
-        <v>529990.0</v>
+        <v>90000.0</v>
+      </c>
+      <c r="D172" s="8">
+        <v>199990.0</v>
       </c>
       <c r="H172" s="5"/>
       <c r="I172" s="5"/>
@@ -5123,13 +5166,13 @@
         <v>174</v>
       </c>
       <c r="B173" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C173" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D173" s="9">
-        <v>929990.0</v>
+      <c r="D173" s="8">
+        <v>189990.0</v>
       </c>
       <c r="H173" s="5"/>
       <c r="I173" s="5"/>
@@ -5146,13 +5189,13 @@
         <v>175</v>
       </c>
       <c r="B174" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C174" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D174" s="9">
-        <v>929990.0</v>
+      <c r="D174" s="8">
+        <v>189990.0</v>
       </c>
       <c r="H174" s="5"/>
       <c r="I174" s="5"/>
@@ -5169,13 +5212,13 @@
         <v>176</v>
       </c>
       <c r="B175" s="7">
-        <v>2.516072E7</v>
+        <v>2.00027070684E11</v>
       </c>
       <c r="C175" s="8">
-        <v>100000.0</v>
-      </c>
-      <c r="D175" s="9">
-        <v>29990.0</v>
+        <v>130000.0</v>
+      </c>
+      <c r="D175" s="8">
+        <v>249990.0</v>
       </c>
       <c r="H175" s="5"/>
       <c r="I175" s="5"/>
@@ -5192,13 +5235,13 @@
         <v>177</v>
       </c>
       <c r="B176" s="7">
-        <v>2.516072E7</v>
+        <v>2.00027070684E11</v>
       </c>
       <c r="C176" s="8">
-        <v>100000.0</v>
-      </c>
-      <c r="D176" s="9">
-        <v>29990.0</v>
+        <v>130000.0</v>
+      </c>
+      <c r="D176" s="8">
+        <v>249990.0</v>
       </c>
       <c r="H176" s="5"/>
       <c r="I176" s="5"/>
@@ -5215,13 +5258,13 @@
         <v>178</v>
       </c>
       <c r="B177" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C177" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D177" s="9">
-        <v>89990.0</v>
+      <c r="D177" s="8">
+        <v>329990.0</v>
       </c>
       <c r="H177" s="5"/>
       <c r="I177" s="5"/>
@@ -5238,13 +5281,13 @@
         <v>179</v>
       </c>
       <c r="B178" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512269E11</v>
       </c>
       <c r="C178" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D178" s="9">
-        <v>89990.0</v>
+        <v>100000.0</v>
+      </c>
+      <c r="D178" s="8">
+        <v>339990.0</v>
       </c>
       <c r="H178" s="5"/>
       <c r="I178" s="5"/>
@@ -5261,13 +5304,13 @@
         <v>180</v>
       </c>
       <c r="B179" s="7">
-        <v>2.7512259E7</v>
+        <v>2.00027512269E11</v>
       </c>
       <c r="C179" s="8">
-        <v>80000.0</v>
-      </c>
-      <c r="D179" s="9">
-        <v>139990.0</v>
+        <v>100000.0</v>
+      </c>
+      <c r="D179" s="8">
+        <v>339990.0</v>
       </c>
       <c r="H179" s="5"/>
       <c r="I179" s="5"/>
@@ -5284,13 +5327,13 @@
         <v>181</v>
       </c>
       <c r="B180" s="7">
-        <v>2.7512259E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C180" s="8">
-        <v>80000.0</v>
-      </c>
-      <c r="D180" s="9">
-        <v>139990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D180" s="8">
+        <v>559990.0</v>
       </c>
       <c r="H180" s="5"/>
       <c r="I180" s="5"/>
@@ -5307,13 +5350,13 @@
         <v>182</v>
       </c>
       <c r="B181" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C181" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D181" s="9">
-        <v>169990.0</v>
+      <c r="D181" s="8">
+        <v>729990.0</v>
       </c>
       <c r="H181" s="5"/>
       <c r="I181" s="5"/>
@@ -5330,13 +5373,13 @@
         <v>183</v>
       </c>
       <c r="B182" s="7">
-        <v>2.7401902E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C182" s="8">
-        <v>110000.0</v>
-      </c>
-      <c r="D182" s="9">
-        <v>199990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D182" s="8">
+        <v>429990.0</v>
       </c>
       <c r="H182" s="5"/>
       <c r="I182" s="5"/>
@@ -5353,13 +5396,13 @@
         <v>184</v>
       </c>
       <c r="B183" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C183" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D183" s="9">
-        <v>199990.0</v>
+      <c r="D183" s="8">
+        <v>429990.0</v>
       </c>
       <c r="H183" s="5"/>
       <c r="I183" s="5"/>
@@ -5376,13 +5419,13 @@
         <v>185</v>
       </c>
       <c r="B184" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C184" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D184" s="9">
-        <v>199990.0</v>
+      <c r="D184" s="8">
+        <v>529990.0</v>
       </c>
       <c r="H184" s="5"/>
       <c r="I184" s="5"/>
@@ -5399,13 +5442,13 @@
         <v>186</v>
       </c>
       <c r="B185" s="7">
-        <v>2.7491766E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C185" s="8">
-        <v>100000.0</v>
-      </c>
-      <c r="D185" s="9">
-        <v>259990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D185" s="8">
+        <v>929990.0</v>
       </c>
       <c r="H185" s="5"/>
       <c r="I185" s="5"/>
@@ -5422,13 +5465,13 @@
         <v>187</v>
       </c>
       <c r="B186" s="7">
-        <v>2.7491766E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C186" s="8">
-        <v>100000.0</v>
-      </c>
-      <c r="D186" s="9">
-        <v>259990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D186" s="8">
+        <v>929990.0</v>
       </c>
       <c r="H186" s="5"/>
       <c r="I186" s="5"/>
@@ -5445,13 +5488,13 @@
         <v>188</v>
       </c>
       <c r="B187" s="7">
-        <v>2.7491766E7</v>
+        <v>2.00025160721E11</v>
       </c>
       <c r="C187" s="8">
         <v>100000.0</v>
       </c>
-      <c r="D187" s="9">
-        <v>259990.0</v>
+      <c r="D187" s="8">
+        <v>29990.0</v>
       </c>
       <c r="H187" s="5"/>
       <c r="I187" s="5"/>
@@ -5468,13 +5511,13 @@
         <v>189</v>
       </c>
       <c r="B188" s="7">
-        <v>2.7491766E7</v>
+        <v>2.00025160721E11</v>
       </c>
       <c r="C188" s="8">
         <v>100000.0</v>
       </c>
-      <c r="D188" s="9">
-        <v>259990.0</v>
+      <c r="D188" s="8">
+        <v>29990.0</v>
       </c>
       <c r="H188" s="5"/>
       <c r="I188" s="5"/>
@@ -5491,13 +5534,13 @@
         <v>190</v>
       </c>
       <c r="B189" s="7">
-        <v>2.7491731E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C189" s="8">
-        <v>150000.0</v>
-      </c>
-      <c r="D189" s="9">
-        <v>399990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D189" s="8">
+        <v>79990.0</v>
       </c>
       <c r="H189" s="5"/>
       <c r="I189" s="5"/>
@@ -5514,13 +5557,13 @@
         <v>191</v>
       </c>
       <c r="B190" s="7">
-        <v>2.7491731E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C190" s="8">
-        <v>150000.0</v>
-      </c>
-      <c r="D190" s="9">
-        <v>399990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D190" s="8">
+        <v>79990.0</v>
       </c>
       <c r="H190" s="5"/>
       <c r="I190" s="5"/>
@@ -5537,13 +5580,13 @@
         <v>192</v>
       </c>
       <c r="B191" s="7">
-        <v>2.7491766E7</v>
+        <v>2.00027401723E11</v>
       </c>
       <c r="C191" s="8">
-        <v>100000.0</v>
-      </c>
-      <c r="D191" s="9">
-        <v>649990.0</v>
+        <v>80000.0</v>
+      </c>
+      <c r="D191" s="8">
+        <v>139990.0</v>
       </c>
       <c r="H191" s="5"/>
       <c r="I191" s="5"/>
@@ -5560,13 +5603,13 @@
         <v>193</v>
       </c>
       <c r="B192" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027401723E11</v>
       </c>
       <c r="C192" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D192" s="9">
-        <v>79990.0</v>
+        <v>80000.0</v>
+      </c>
+      <c r="D192" s="8">
+        <v>139990.0</v>
       </c>
       <c r="H192" s="5"/>
       <c r="I192" s="5"/>
@@ -5583,13 +5626,13 @@
         <v>194</v>
       </c>
       <c r="B193" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C193" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D193" s="9">
-        <v>79990.0</v>
+      <c r="D193" s="8">
+        <v>159990.0</v>
       </c>
       <c r="H193" s="5"/>
       <c r="I193" s="5"/>
@@ -5606,13 +5649,13 @@
         <v>195</v>
       </c>
       <c r="B194" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512269E11</v>
       </c>
       <c r="C194" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D194" s="9">
-        <v>169990.0</v>
+        <v>100000.0</v>
+      </c>
+      <c r="D194" s="8">
+        <v>209990.0</v>
       </c>
       <c r="H194" s="5"/>
       <c r="I194" s="5"/>
@@ -5626,16 +5669,16 @@
     </row>
     <row r="195" ht="18.0" customHeight="1">
       <c r="A195" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B195" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C195" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D195" s="9">
-        <v>169990.0</v>
+      <c r="D195" s="8">
+        <v>199990.0</v>
       </c>
       <c r="H195" s="5"/>
       <c r="I195" s="5"/>
@@ -5649,16 +5692,16 @@
     </row>
     <row r="196" ht="18.0" customHeight="1">
       <c r="A196" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B196" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C196" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D196" s="9">
-        <v>189990.0</v>
+      <c r="D196" s="8">
+        <v>199990.0</v>
       </c>
       <c r="H196" s="5"/>
       <c r="I196" s="5"/>
@@ -5672,16 +5715,16 @@
     </row>
     <row r="197" ht="18.0" customHeight="1">
       <c r="A197" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B197" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027401907E11</v>
       </c>
       <c r="C197" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D197" s="9">
-        <v>189990.0</v>
+        <v>90000.0</v>
+      </c>
+      <c r="D197" s="8">
+        <v>259990.0</v>
       </c>
       <c r="H197" s="5"/>
       <c r="I197" s="5"/>
@@ -5695,16 +5738,16 @@
     </row>
     <row r="198" ht="18.0" customHeight="1">
       <c r="A198" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B198" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027401907E11</v>
       </c>
       <c r="C198" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D198" s="9">
-        <v>229990.0</v>
+        <v>90000.0</v>
+      </c>
+      <c r="D198" s="8">
+        <v>259990.0</v>
       </c>
       <c r="H198" s="5"/>
       <c r="I198" s="5"/>
@@ -5718,16 +5761,16 @@
     </row>
     <row r="199" ht="18.0" customHeight="1">
       <c r="A199" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B199" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027401907E11</v>
       </c>
       <c r="C199" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D199" s="9">
-        <v>279990.0</v>
+        <v>90000.0</v>
+      </c>
+      <c r="D199" s="8">
+        <v>259990.0</v>
       </c>
       <c r="H199" s="5"/>
       <c r="I199" s="5"/>
@@ -5741,16 +5784,16 @@
     </row>
     <row r="200" ht="18.0" customHeight="1">
       <c r="A200" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B200" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027401907E11</v>
       </c>
       <c r="C200" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D200" s="9">
-        <v>279990.0</v>
+        <v>90000.0</v>
+      </c>
+      <c r="D200" s="8">
+        <v>259990.0</v>
       </c>
       <c r="H200" s="5"/>
       <c r="I200" s="5"/>
@@ -5764,16 +5807,16 @@
     </row>
     <row r="201" ht="18.0" customHeight="1">
       <c r="A201" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B201" s="7">
-        <v>2.6975042E7</v>
+        <v>2.00021983034E11</v>
       </c>
       <c r="C201" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D201" s="9">
-        <v>990.0</v>
+        <v>150000.0</v>
+      </c>
+      <c r="D201" s="8">
+        <v>399990.0</v>
       </c>
       <c r="H201" s="5"/>
       <c r="I201" s="5"/>
@@ -5787,16 +5830,16 @@
     </row>
     <row r="202" ht="18.0" customHeight="1">
       <c r="A202" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B202" s="7">
-        <v>2.7491723E7</v>
+        <v>2.00021983034E11</v>
       </c>
       <c r="C202" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D202" s="9">
-        <v>9990.0</v>
+        <v>150000.0</v>
+      </c>
+      <c r="D202" s="8">
+        <v>399990.0</v>
       </c>
       <c r="H202" s="5"/>
       <c r="I202" s="5"/>
@@ -5810,16 +5853,16 @@
     </row>
     <row r="203" ht="18.0" customHeight="1">
       <c r="A203" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B203" s="7">
-        <v>2.6951291E7</v>
+        <v>2.00027512269E11</v>
       </c>
       <c r="C203" s="8">
-        <v>70000.0</v>
-      </c>
-      <c r="D203" s="9">
-        <v>19990.0</v>
+        <v>100000.0</v>
+      </c>
+      <c r="D203" s="8">
+        <v>649990.0</v>
       </c>
       <c r="H203" s="5"/>
       <c r="I203" s="5"/>
@@ -5833,16 +5876,16 @@
     </row>
     <row r="204" ht="18.0" customHeight="1">
       <c r="A204" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B204" s="7">
-        <v>2.7497756E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C204" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D204" s="9">
-        <v>129990.0</v>
+      <c r="D204" s="8">
+        <v>79990.0</v>
       </c>
       <c r="H204" s="5"/>
       <c r="I204" s="5"/>
@@ -5856,16 +5899,16 @@
     </row>
     <row r="205" ht="18.0" customHeight="1">
       <c r="A205" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B205" s="7">
-        <v>2.6951291E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C205" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D205" s="9">
-        <v>19990.0</v>
+      <c r="D205" s="8">
+        <v>79990.0</v>
       </c>
       <c r="H205" s="5"/>
       <c r="I205" s="5"/>
@@ -5879,16 +5922,16 @@
     </row>
     <row r="206" ht="18.0" customHeight="1">
       <c r="A206" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B206" s="7">
-        <v>2.516072E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C206" s="8">
         <v>70000.0</v>
       </c>
-      <c r="D206" s="9">
-        <v>29990.0</v>
+      <c r="D206" s="8">
+        <v>169990.0</v>
       </c>
       <c r="H206" s="5"/>
       <c r="I206" s="5"/>
@@ -5905,13 +5948,13 @@
         <v>207</v>
       </c>
       <c r="B207" s="7">
-        <v>2.7512216E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C207" s="8">
-        <v>44000.0</v>
-      </c>
-      <c r="D207" s="9">
-        <v>4990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D207" s="8">
+        <v>169990.0</v>
       </c>
       <c r="H207" s="5"/>
       <c r="I207" s="5"/>
@@ -5928,13 +5971,13 @@
         <v>208</v>
       </c>
       <c r="B208" s="7">
-        <v>2.6975042E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C208" s="8">
-        <v>39000.0</v>
-      </c>
-      <c r="D208" s="9">
-        <v>990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D208" s="8">
+        <v>189990.0</v>
       </c>
       <c r="H208" s="5"/>
       <c r="I208" s="5"/>
@@ -5951,13 +5994,13 @@
         <v>209</v>
       </c>
       <c r="B209" s="7">
-        <v>2.6975042E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C209" s="8">
-        <v>69000.0</v>
-      </c>
-      <c r="D209" s="9">
-        <v>990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D209" s="8">
+        <v>189990.0</v>
       </c>
       <c r="H209" s="5"/>
       <c r="I209" s="5"/>
@@ -5974,14 +6017,17 @@
         <v>210</v>
       </c>
       <c r="B210" s="7">
-        <v>2.7491723E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C210" s="8">
-        <v>89000.0</v>
-      </c>
-      <c r="D210" s="9">
-        <v>9990.0</v>
-      </c>
+        <v>70000.0</v>
+      </c>
+      <c r="D210" s="8">
+        <v>229990.0</v>
+      </c>
+      <c r="E210" s="9"/>
+      <c r="F210" s="10"/>
+      <c r="G210" s="10"/>
       <c r="H210" s="5"/>
       <c r="I210" s="5"/>
       <c r="J210" s="5"/>
@@ -5997,13 +6043,13 @@
         <v>211</v>
       </c>
       <c r="B211" s="7">
-        <v>2.6951291E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C211" s="8">
-        <v>79000.0</v>
-      </c>
-      <c r="D211" s="9">
-        <v>19990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D211" s="8">
+        <v>279990.0</v>
       </c>
       <c r="H211" s="5"/>
       <c r="I211" s="5"/>
@@ -6020,17 +6066,14 @@
         <v>212</v>
       </c>
       <c r="B212" s="7">
-        <v>2.7401902E7</v>
+        <v>2.00027512252E11</v>
       </c>
       <c r="C212" s="8">
-        <v>110000.0</v>
-      </c>
-      <c r="D212" s="9">
-        <v>39990.0</v>
-      </c>
-      <c r="E212" s="10"/>
-      <c r="F212" s="11"/>
-      <c r="G212" s="11"/>
+        <v>70000.0</v>
+      </c>
+      <c r="D212" s="8">
+        <v>279990.0</v>
+      </c>
       <c r="H212" s="5"/>
       <c r="I212" s="5"/>
       <c r="J212" s="5"/>
@@ -6042,17 +6085,17 @@
       <c r="P212" s="5"/>
     </row>
     <row r="213" ht="18.0" customHeight="1">
-      <c r="A213" s="12" t="s">
+      <c r="A213" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="B213" s="13">
-        <v>2.7401902E7</v>
+      <c r="B213" s="7">
+        <v>2.00026975041E11</v>
       </c>
       <c r="C213" s="8">
-        <v>110000.0</v>
-      </c>
-      <c r="D213" s="9">
-        <v>39990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D213" s="8">
+        <v>990.0</v>
       </c>
       <c r="H213" s="5"/>
       <c r="I213" s="5"/>
@@ -6065,17 +6108,17 @@
       <c r="P213" s="5"/>
     </row>
     <row r="214" ht="18.0" customHeight="1">
-      <c r="A214" s="12" t="s">
+      <c r="A214" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="B214" s="13">
-        <v>2.7491766E7</v>
+      <c r="B214" s="7">
+        <v>2.00027491724E11</v>
       </c>
       <c r="C214" s="8">
-        <v>100000.0</v>
-      </c>
-      <c r="D214" s="9">
-        <v>119990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D214" s="8">
+        <v>9990.0</v>
       </c>
       <c r="H214" s="5"/>
       <c r="I214" s="5"/>
@@ -6088,17 +6131,17 @@
       <c r="P214" s="5"/>
     </row>
     <row r="215" ht="18.0" customHeight="1">
-      <c r="A215" s="12" t="s">
+      <c r="A215" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="B215" s="13">
-        <v>2.7491766E7</v>
+      <c r="B215" s="7">
+        <v>2.00026951298E11</v>
       </c>
       <c r="C215" s="8">
-        <v>100000.0</v>
-      </c>
-      <c r="D215" s="9">
-        <v>119990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D215" s="8">
+        <v>19990.0</v>
       </c>
       <c r="H215" s="5"/>
       <c r="I215" s="5"/>
@@ -6111,17 +6154,17 @@
       <c r="P215" s="5"/>
     </row>
     <row r="216" ht="18.0" customHeight="1">
-      <c r="A216" s="12" t="s">
+      <c r="A216" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="B216" s="13">
-        <v>2.7401902E7</v>
+      <c r="B216" s="7">
+        <v>2.00027512252E11</v>
       </c>
       <c r="C216" s="8">
-        <v>110000.0</v>
-      </c>
-      <c r="D216" s="9">
-        <v>189990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D216" s="8">
+        <v>129990.0</v>
       </c>
       <c r="H216" s="5"/>
       <c r="I216" s="5"/>
@@ -6134,17 +6177,17 @@
       <c r="P216" s="5"/>
     </row>
     <row r="217" ht="18.0" customHeight="1">
-      <c r="A217" s="12" t="s">
+      <c r="A217" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="B217" s="13">
-        <v>2.7401902E7</v>
+      <c r="B217" s="7">
+        <v>2.00026951298E11</v>
       </c>
       <c r="C217" s="8">
-        <v>110000.0</v>
-      </c>
-      <c r="D217" s="9">
-        <v>339990.0</v>
+        <v>70000.0</v>
+      </c>
+      <c r="D217" s="8">
+        <v>19990.0</v>
       </c>
       <c r="H217" s="5"/>
       <c r="I217" s="5"/>
@@ -6157,10 +6200,18 @@
       <c r="P217" s="5"/>
     </row>
     <row r="218" ht="18.0" customHeight="1">
-      <c r="A218" s="14"/>
-      <c r="B218" s="14"/>
-      <c r="C218" s="15"/>
-      <c r="D218" s="15"/>
+      <c r="A218" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="B218" s="7">
+        <v>2.00025160721E11</v>
+      </c>
+      <c r="C218" s="8">
+        <v>70000.0</v>
+      </c>
+      <c r="D218" s="8">
+        <v>29990.0</v>
+      </c>
       <c r="H218" s="5"/>
       <c r="I218" s="5"/>
       <c r="J218" s="5"/>
@@ -6172,10 +6223,18 @@
       <c r="P218" s="5"/>
     </row>
     <row r="219" ht="18.0" customHeight="1">
-      <c r="A219" s="12"/>
-      <c r="B219" s="12"/>
-      <c r="C219" s="8"/>
-      <c r="D219" s="15"/>
+      <c r="A219" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B219" s="7">
+        <v>2.00027512214E11</v>
+      </c>
+      <c r="C219" s="8">
+        <v>44000.0</v>
+      </c>
+      <c r="D219" s="8">
+        <v>4990.0</v>
+      </c>
       <c r="H219" s="5"/>
       <c r="I219" s="5"/>
       <c r="J219" s="5"/>
@@ -6187,10 +6246,18 @@
       <c r="P219" s="5"/>
     </row>
     <row r="220" ht="18.0" customHeight="1">
-      <c r="A220" s="12"/>
-      <c r="B220" s="12"/>
-      <c r="C220" s="8"/>
-      <c r="D220" s="15"/>
+      <c r="A220" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B220" s="7">
+        <v>2.00026975041E11</v>
+      </c>
+      <c r="C220" s="8">
+        <v>39000.0</v>
+      </c>
+      <c r="D220" s="8">
+        <v>990.0</v>
+      </c>
       <c r="H220" s="5"/>
       <c r="I220" s="5"/>
       <c r="J220" s="5"/>
@@ -6202,10 +6269,18 @@
       <c r="P220" s="5"/>
     </row>
     <row r="221" ht="18.0" customHeight="1">
-      <c r="A221" s="12"/>
-      <c r="B221" s="12"/>
-      <c r="C221" s="8"/>
-      <c r="D221" s="15"/>
+      <c r="A221" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="B221" s="7">
+        <v>2.00026975041E11</v>
+      </c>
+      <c r="C221" s="8">
+        <v>69000.0</v>
+      </c>
+      <c r="D221" s="8">
+        <v>990.0</v>
+      </c>
       <c r="H221" s="5"/>
       <c r="I221" s="5"/>
       <c r="J221" s="5"/>
@@ -6217,10 +6292,18 @@
       <c r="P221" s="5"/>
     </row>
     <row r="222" ht="18.0" customHeight="1">
-      <c r="A222" s="12"/>
-      <c r="B222" s="12"/>
-      <c r="C222" s="8"/>
-      <c r="D222" s="15"/>
+      <c r="A222" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B222" s="7">
+        <v>2.00026951298E11</v>
+      </c>
+      <c r="C222" s="8">
+        <v>79000.0</v>
+      </c>
+      <c r="D222" s="8">
+        <v>19990.0</v>
+      </c>
       <c r="H222" s="5"/>
       <c r="I222" s="5"/>
       <c r="J222" s="5"/>
@@ -6232,10 +6315,18 @@
       <c r="P222" s="5"/>
     </row>
     <row r="223" ht="18.0" customHeight="1">
-      <c r="A223" s="12"/>
-      <c r="B223" s="12"/>
-      <c r="C223" s="8"/>
-      <c r="D223" s="15"/>
+      <c r="A223" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B223" s="7">
+        <v>2.00026951298E11</v>
+      </c>
+      <c r="C223" s="8">
+        <v>79000.0</v>
+      </c>
+      <c r="D223" s="8">
+        <v>19990.0</v>
+      </c>
       <c r="H223" s="5"/>
       <c r="I223" s="5"/>
       <c r="J223" s="5"/>
@@ -6247,10 +6338,18 @@
       <c r="P223" s="5"/>
     </row>
     <row r="224" ht="18.0" customHeight="1">
-      <c r="A224" s="12"/>
-      <c r="B224" s="12"/>
-      <c r="C224" s="8"/>
-      <c r="D224" s="15"/>
+      <c r="A224" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B224" s="7">
+        <v>2.00027491762E11</v>
+      </c>
+      <c r="C224" s="8">
+        <v>85000.0</v>
+      </c>
+      <c r="D224" s="8">
+        <v>64990.0</v>
+      </c>
       <c r="H224" s="5"/>
       <c r="I224" s="5"/>
       <c r="J224" s="5"/>
@@ -6262,10 +6361,18 @@
       <c r="P224" s="5"/>
     </row>
     <row r="225" ht="18.0" customHeight="1">
-      <c r="A225" s="12"/>
-      <c r="B225" s="12"/>
-      <c r="C225" s="8"/>
-      <c r="D225" s="15"/>
+      <c r="A225" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="B225" s="7">
+        <v>2.00027491762E11</v>
+      </c>
+      <c r="C225" s="8">
+        <v>85000.0</v>
+      </c>
+      <c r="D225" s="8">
+        <v>64990.0</v>
+      </c>
       <c r="H225" s="5"/>
       <c r="I225" s="5"/>
       <c r="J225" s="5"/>
@@ -6277,10 +6384,18 @@
       <c r="P225" s="5"/>
     </row>
     <row r="226" ht="18.0" customHeight="1">
-      <c r="A226" s="12"/>
-      <c r="B226" s="12"/>
-      <c r="C226" s="8"/>
-      <c r="D226" s="15"/>
+      <c r="A226" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="B226" s="7">
+        <v>2.00027512269E11</v>
+      </c>
+      <c r="C226" s="8">
+        <v>100000.0</v>
+      </c>
+      <c r="D226" s="8">
+        <v>49990.0</v>
+      </c>
       <c r="H226" s="5"/>
       <c r="I226" s="5"/>
       <c r="J226" s="5"/>
@@ -6292,10 +6407,18 @@
       <c r="P226" s="5"/>
     </row>
     <row r="227" ht="18.0" customHeight="1">
-      <c r="A227" s="12"/>
-      <c r="B227" s="12"/>
-      <c r="C227" s="8"/>
-      <c r="D227" s="15"/>
+      <c r="A227" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B227" s="7">
+        <v>2.00027512269E11</v>
+      </c>
+      <c r="C227" s="8">
+        <v>100000.0</v>
+      </c>
+      <c r="D227" s="8">
+        <v>49990.0</v>
+      </c>
       <c r="H227" s="5"/>
       <c r="I227" s="5"/>
       <c r="J227" s="5"/>
@@ -6307,10 +6430,18 @@
       <c r="P227" s="5"/>
     </row>
     <row r="228" ht="18.0" customHeight="1">
-      <c r="A228" s="12"/>
-      <c r="B228" s="12"/>
-      <c r="C228" s="8"/>
-      <c r="D228" s="15"/>
+      <c r="A228" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B228" s="7">
+        <v>2.0002740173E11</v>
+      </c>
+      <c r="C228" s="8">
+        <v>110000.0</v>
+      </c>
+      <c r="D228" s="8">
+        <v>169990.0</v>
+      </c>
       <c r="H228" s="5"/>
       <c r="I228" s="5"/>
       <c r="J228" s="5"/>
@@ -6322,10 +6453,18 @@
       <c r="P228" s="5"/>
     </row>
     <row r="229" ht="18.0" customHeight="1">
-      <c r="A229" s="12"/>
-      <c r="B229" s="12"/>
-      <c r="C229" s="8"/>
-      <c r="D229" s="15"/>
+      <c r="A229" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="B229" s="7">
+        <v>2.0002740173E11</v>
+      </c>
+      <c r="C229" s="8">
+        <v>110000.0</v>
+      </c>
+      <c r="D229" s="8">
+        <v>169990.0</v>
+      </c>
       <c r="H229" s="5"/>
       <c r="I229" s="5"/>
       <c r="J229" s="5"/>
@@ -6337,10 +6476,18 @@
       <c r="P229" s="5"/>
     </row>
     <row r="230" ht="18.0" customHeight="1">
-      <c r="A230" s="12"/>
-      <c r="B230" s="12"/>
-      <c r="C230" s="8"/>
-      <c r="D230" s="15"/>
+      <c r="A230" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B230" s="7">
+        <v>2.00027512269E11</v>
+      </c>
+      <c r="C230" s="8">
+        <v>100000.0</v>
+      </c>
+      <c r="D230" s="8">
+        <v>119990.0</v>
+      </c>
       <c r="H230" s="5"/>
       <c r="I230" s="5"/>
       <c r="J230" s="5"/>
@@ -6352,10 +6499,18 @@
       <c r="P230" s="5"/>
     </row>
     <row r="231" ht="18.0" customHeight="1">
-      <c r="A231" s="12"/>
-      <c r="B231" s="12"/>
-      <c r="C231" s="8"/>
-      <c r="D231" s="15"/>
+      <c r="A231" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="B231" s="7">
+        <v>2.00027512269E11</v>
+      </c>
+      <c r="C231" s="8">
+        <v>100000.0</v>
+      </c>
+      <c r="D231" s="8">
+        <v>119990.0</v>
+      </c>
       <c r="H231" s="5"/>
       <c r="I231" s="5"/>
       <c r="J231" s="5"/>
@@ -6367,10 +6522,18 @@
       <c r="P231" s="5"/>
     </row>
     <row r="232" ht="18.0" customHeight="1">
-      <c r="A232" s="12"/>
-      <c r="B232" s="12"/>
-      <c r="C232" s="8"/>
-      <c r="D232" s="15"/>
+      <c r="A232" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B232" s="7">
+        <v>2.0002740173E11</v>
+      </c>
+      <c r="C232" s="8">
+        <v>110000.0</v>
+      </c>
+      <c r="D232" s="8">
+        <v>189990.0</v>
+      </c>
       <c r="H232" s="5"/>
       <c r="I232" s="5"/>
       <c r="J232" s="5"/>
@@ -6382,10 +6545,18 @@
       <c r="P232" s="5"/>
     </row>
     <row r="233" ht="18.0" customHeight="1">
-      <c r="A233" s="12"/>
-      <c r="B233" s="12"/>
-      <c r="C233" s="8"/>
-      <c r="D233" s="15"/>
+      <c r="A233" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="B233" s="7">
+        <v>2.0002740173E11</v>
+      </c>
+      <c r="C233" s="8">
+        <v>110000.0</v>
+      </c>
+      <c r="D233" s="8">
+        <v>339990.0</v>
+      </c>
       <c r="H233" s="5"/>
       <c r="I233" s="5"/>
       <c r="J233" s="5"/>
@@ -6397,10 +6568,10 @@
       <c r="P233" s="5"/>
     </row>
     <row r="234" ht="18.0" customHeight="1">
-      <c r="A234" s="12"/>
-      <c r="B234" s="12"/>
-      <c r="C234" s="8"/>
-      <c r="D234" s="15"/>
+      <c r="A234" s="11"/>
+      <c r="B234" s="11"/>
+      <c r="C234" s="12"/>
+      <c r="D234" s="13"/>
       <c r="H234" s="5"/>
       <c r="I234" s="5"/>
       <c r="J234" s="5"/>
@@ -6412,10 +6583,10 @@
       <c r="P234" s="5"/>
     </row>
     <row r="235" ht="18.0" customHeight="1">
-      <c r="A235" s="12"/>
-      <c r="B235" s="12"/>
-      <c r="C235" s="8"/>
-      <c r="D235" s="15"/>
+      <c r="A235" s="11"/>
+      <c r="B235" s="11"/>
+      <c r="C235" s="12"/>
+      <c r="D235" s="13"/>
       <c r="H235" s="5"/>
       <c r="I235" s="5"/>
       <c r="J235" s="5"/>
@@ -6427,10 +6598,10 @@
       <c r="P235" s="5"/>
     </row>
     <row r="236" ht="18.0" customHeight="1">
-      <c r="A236" s="12"/>
-      <c r="B236" s="12"/>
-      <c r="C236" s="8"/>
-      <c r="D236" s="15"/>
+      <c r="A236" s="11"/>
+      <c r="B236" s="11"/>
+      <c r="C236" s="12"/>
+      <c r="D236" s="13"/>
       <c r="H236" s="5"/>
       <c r="I236" s="5"/>
       <c r="J236" s="5"/>
@@ -6442,10 +6613,10 @@
       <c r="P236" s="5"/>
     </row>
     <row r="237" ht="18.0" customHeight="1">
-      <c r="A237" s="12"/>
-      <c r="B237" s="12"/>
-      <c r="C237" s="8"/>
-      <c r="D237" s="15"/>
+      <c r="A237" s="11"/>
+      <c r="B237" s="11"/>
+      <c r="C237" s="12"/>
+      <c r="D237" s="13"/>
       <c r="H237" s="5"/>
       <c r="I237" s="5"/>
       <c r="J237" s="5"/>
@@ -6457,10 +6628,10 @@
       <c r="P237" s="5"/>
     </row>
     <row r="238" ht="18.0" customHeight="1">
-      <c r="A238" s="12"/>
-      <c r="B238" s="12"/>
-      <c r="C238" s="8"/>
-      <c r="D238" s="15"/>
+      <c r="A238" s="11"/>
+      <c r="B238" s="11"/>
+      <c r="C238" s="12"/>
+      <c r="D238" s="13"/>
       <c r="H238" s="5"/>
       <c r="I238" s="5"/>
       <c r="J238" s="5"/>
@@ -6472,10 +6643,10 @@
       <c r="P238" s="5"/>
     </row>
     <row r="239" ht="18.0" customHeight="1">
-      <c r="A239" s="12"/>
-      <c r="B239" s="12"/>
-      <c r="C239" s="8"/>
-      <c r="D239" s="15"/>
+      <c r="A239" s="11"/>
+      <c r="B239" s="11"/>
+      <c r="C239" s="12"/>
+      <c r="D239" s="13"/>
       <c r="H239" s="5"/>
       <c r="I239" s="5"/>
       <c r="J239" s="5"/>
@@ -6487,10 +6658,10 @@
       <c r="P239" s="5"/>
     </row>
     <row r="240" ht="18.0" customHeight="1">
-      <c r="A240" s="12"/>
-      <c r="B240" s="12"/>
-      <c r="C240" s="8"/>
-      <c r="D240" s="15"/>
+      <c r="A240" s="11"/>
+      <c r="B240" s="11"/>
+      <c r="C240" s="12"/>
+      <c r="D240" s="13"/>
       <c r="H240" s="5"/>
       <c r="I240" s="5"/>
       <c r="J240" s="5"/>
@@ -6502,10 +6673,10 @@
       <c r="P240" s="5"/>
     </row>
     <row r="241" ht="18.0" customHeight="1">
-      <c r="A241" s="12"/>
-      <c r="B241" s="12"/>
-      <c r="C241" s="8"/>
-      <c r="D241" s="15"/>
+      <c r="A241" s="11"/>
+      <c r="B241" s="11"/>
+      <c r="C241" s="12"/>
+      <c r="D241" s="13"/>
       <c r="H241" s="5"/>
       <c r="I241" s="5"/>
       <c r="J241" s="5"/>
@@ -6517,10 +6688,10 @@
       <c r="P241" s="5"/>
     </row>
     <row r="242" ht="18.0" customHeight="1">
-      <c r="A242" s="12"/>
-      <c r="B242" s="12"/>
-      <c r="C242" s="8"/>
-      <c r="D242" s="15"/>
+      <c r="A242" s="11"/>
+      <c r="B242" s="11"/>
+      <c r="C242" s="12"/>
+      <c r="D242" s="13"/>
       <c r="H242" s="5"/>
       <c r="I242" s="5"/>
       <c r="J242" s="5"/>
@@ -6532,10 +6703,10 @@
       <c r="P242" s="5"/>
     </row>
     <row r="243" ht="18.0" customHeight="1">
-      <c r="A243" s="12"/>
-      <c r="B243" s="12"/>
-      <c r="C243" s="8"/>
-      <c r="D243" s="15"/>
+      <c r="A243" s="11"/>
+      <c r="B243" s="11"/>
+      <c r="C243" s="12"/>
+      <c r="D243" s="13"/>
       <c r="H243" s="5"/>
       <c r="I243" s="5"/>
       <c r="J243" s="5"/>
@@ -6547,10 +6718,10 @@
       <c r="P243" s="5"/>
     </row>
     <row r="244" ht="18.0" customHeight="1">
-      <c r="A244" s="12"/>
-      <c r="B244" s="12"/>
-      <c r="C244" s="8"/>
-      <c r="D244" s="15"/>
+      <c r="A244" s="11"/>
+      <c r="B244" s="11"/>
+      <c r="C244" s="12"/>
+      <c r="D244" s="13"/>
       <c r="H244" s="5"/>
       <c r="I244" s="5"/>
       <c r="J244" s="5"/>
@@ -6562,10 +6733,10 @@
       <c r="P244" s="5"/>
     </row>
     <row r="245" ht="18.0" customHeight="1">
-      <c r="A245" s="12"/>
-      <c r="B245" s="12"/>
-      <c r="C245" s="8"/>
-      <c r="D245" s="15"/>
+      <c r="A245" s="11"/>
+      <c r="B245" s="11"/>
+      <c r="C245" s="12"/>
+      <c r="D245" s="13"/>
       <c r="H245" s="5"/>
       <c r="I245" s="5"/>
       <c r="J245" s="5"/>
@@ -6577,10 +6748,10 @@
       <c r="P245" s="5"/>
     </row>
     <row r="246" ht="18.0" customHeight="1">
-      <c r="A246" s="12"/>
-      <c r="B246" s="12"/>
-      <c r="C246" s="8"/>
-      <c r="D246" s="15"/>
+      <c r="A246" s="11"/>
+      <c r="B246" s="11"/>
+      <c r="C246" s="12"/>
+      <c r="D246" s="13"/>
       <c r="H246" s="5"/>
       <c r="I246" s="5"/>
       <c r="J246" s="5"/>
@@ -6592,10 +6763,10 @@
       <c r="P246" s="5"/>
     </row>
     <row r="247" ht="18.0" customHeight="1">
-      <c r="A247" s="12"/>
-      <c r="B247" s="12"/>
-      <c r="C247" s="8"/>
-      <c r="D247" s="15"/>
+      <c r="A247" s="11"/>
+      <c r="B247" s="11"/>
+      <c r="C247" s="12"/>
+      <c r="D247" s="13"/>
       <c r="H247" s="5"/>
       <c r="I247" s="5"/>
       <c r="J247" s="5"/>
@@ -6607,10 +6778,10 @@
       <c r="P247" s="5"/>
     </row>
     <row r="248" ht="18.0" customHeight="1">
-      <c r="A248" s="12"/>
-      <c r="B248" s="12"/>
-      <c r="C248" s="8"/>
-      <c r="D248" s="15"/>
+      <c r="A248" s="11"/>
+      <c r="B248" s="11"/>
+      <c r="C248" s="12"/>
+      <c r="D248" s="13"/>
       <c r="H248" s="5"/>
       <c r="I248" s="5"/>
       <c r="J248" s="5"/>
@@ -6622,10 +6793,10 @@
       <c r="P248" s="5"/>
     </row>
     <row r="249" ht="18.0" customHeight="1">
-      <c r="A249" s="12"/>
-      <c r="B249" s="12"/>
-      <c r="C249" s="8"/>
-      <c r="D249" s="15"/>
+      <c r="A249" s="11"/>
+      <c r="B249" s="11"/>
+      <c r="C249" s="12"/>
+      <c r="D249" s="13"/>
       <c r="H249" s="5"/>
       <c r="I249" s="5"/>
       <c r="J249" s="5"/>
@@ -6637,10 +6808,10 @@
       <c r="P249" s="5"/>
     </row>
     <row r="250" ht="18.0" customHeight="1">
-      <c r="A250" s="12"/>
-      <c r="B250" s="12"/>
-      <c r="C250" s="8"/>
-      <c r="D250" s="15"/>
+      <c r="A250" s="11"/>
+      <c r="B250" s="11"/>
+      <c r="C250" s="12"/>
+      <c r="D250" s="13"/>
       <c r="H250" s="5"/>
       <c r="I250" s="5"/>
       <c r="J250" s="5"/>
@@ -6652,10 +6823,10 @@
       <c r="P250" s="5"/>
     </row>
     <row r="251" ht="18.0" customHeight="1">
-      <c r="A251" s="12"/>
-      <c r="B251" s="12"/>
-      <c r="C251" s="8"/>
-      <c r="D251" s="15"/>
+      <c r="A251" s="11"/>
+      <c r="B251" s="11"/>
+      <c r="C251" s="12"/>
+      <c r="D251" s="13"/>
       <c r="H251" s="5"/>
       <c r="I251" s="5"/>
       <c r="J251" s="5"/>
@@ -6667,10 +6838,10 @@
       <c r="P251" s="5"/>
     </row>
     <row r="252" ht="18.0" customHeight="1">
-      <c r="A252" s="12"/>
-      <c r="B252" s="12"/>
-      <c r="C252" s="8"/>
-      <c r="D252" s="15"/>
+      <c r="A252" s="11"/>
+      <c r="B252" s="11"/>
+      <c r="C252" s="12"/>
+      <c r="D252" s="13"/>
       <c r="H252" s="5"/>
       <c r="I252" s="5"/>
       <c r="J252" s="5"/>
@@ -6682,10 +6853,10 @@
       <c r="P252" s="5"/>
     </row>
     <row r="253" ht="18.0" customHeight="1">
-      <c r="A253" s="12"/>
-      <c r="B253" s="12"/>
-      <c r="C253" s="8"/>
-      <c r="D253" s="15"/>
+      <c r="A253" s="11"/>
+      <c r="B253" s="11"/>
+      <c r="C253" s="12"/>
+      <c r="D253" s="13"/>
       <c r="H253" s="5"/>
       <c r="I253" s="5"/>
       <c r="J253" s="5"/>
@@ -6697,10 +6868,10 @@
       <c r="P253" s="5"/>
     </row>
     <row r="254" ht="18.0" customHeight="1">
-      <c r="A254" s="12"/>
-      <c r="B254" s="12"/>
-      <c r="C254" s="8"/>
-      <c r="D254" s="15"/>
+      <c r="A254" s="11"/>
+      <c r="B254" s="11"/>
+      <c r="C254" s="12"/>
+      <c r="D254" s="13"/>
       <c r="H254" s="5"/>
       <c r="I254" s="5"/>
       <c r="J254" s="5"/>
@@ -6712,10 +6883,10 @@
       <c r="P254" s="5"/>
     </row>
     <row r="255" ht="18.0" customHeight="1">
-      <c r="A255" s="12"/>
-      <c r="B255" s="12"/>
-      <c r="C255" s="8"/>
-      <c r="D255" s="15"/>
+      <c r="A255" s="11"/>
+      <c r="B255" s="11"/>
+      <c r="C255" s="12"/>
+      <c r="D255" s="13"/>
       <c r="H255" s="5"/>
       <c r="I255" s="5"/>
       <c r="J255" s="5"/>
@@ -6727,10 +6898,10 @@
       <c r="P255" s="5"/>
     </row>
     <row r="256" ht="18.0" customHeight="1">
-      <c r="A256" s="12"/>
-      <c r="B256" s="12"/>
-      <c r="C256" s="8"/>
-      <c r="D256" s="15"/>
+      <c r="A256" s="11"/>
+      <c r="B256" s="11"/>
+      <c r="C256" s="12"/>
+      <c r="D256" s="13"/>
       <c r="H256" s="5"/>
       <c r="I256" s="5"/>
       <c r="J256" s="5"/>
@@ -6742,10 +6913,10 @@
       <c r="P256" s="5"/>
     </row>
     <row r="257" ht="18.0" customHeight="1">
-      <c r="A257" s="12"/>
-      <c r="B257" s="12"/>
-      <c r="C257" s="8"/>
-      <c r="D257" s="15"/>
+      <c r="A257" s="11"/>
+      <c r="B257" s="11"/>
+      <c r="C257" s="12"/>
+      <c r="D257" s="13"/>
       <c r="H257" s="5"/>
       <c r="I257" s="5"/>
       <c r="J257" s="5"/>
@@ -6757,10 +6928,10 @@
       <c r="P257" s="5"/>
     </row>
     <row r="258" ht="18.0" customHeight="1">
-      <c r="A258" s="12"/>
-      <c r="B258" s="12"/>
-      <c r="C258" s="8"/>
-      <c r="D258" s="15"/>
+      <c r="A258" s="11"/>
+      <c r="B258" s="11"/>
+      <c r="C258" s="12"/>
+      <c r="D258" s="13"/>
       <c r="H258" s="5"/>
       <c r="I258" s="5"/>
       <c r="J258" s="5"/>
@@ -6772,10 +6943,10 @@
       <c r="P258" s="5"/>
     </row>
     <row r="259" ht="18.0" customHeight="1">
-      <c r="A259" s="12"/>
-      <c r="B259" s="12"/>
-      <c r="C259" s="8"/>
-      <c r="D259" s="15"/>
+      <c r="A259" s="11"/>
+      <c r="B259" s="11"/>
+      <c r="C259" s="12"/>
+      <c r="D259" s="13"/>
       <c r="H259" s="5"/>
       <c r="I259" s="5"/>
       <c r="J259" s="5"/>
@@ -6787,10 +6958,10 @@
       <c r="P259" s="5"/>
     </row>
     <row r="260" ht="18.0" customHeight="1">
-      <c r="A260" s="12"/>
-      <c r="B260" s="12"/>
-      <c r="C260" s="8"/>
-      <c r="D260" s="15"/>
+      <c r="A260" s="11"/>
+      <c r="B260" s="11"/>
+      <c r="C260" s="12"/>
+      <c r="D260" s="13"/>
       <c r="H260" s="5"/>
       <c r="I260" s="5"/>
       <c r="J260" s="5"/>
@@ -6802,10 +6973,10 @@
       <c r="P260" s="5"/>
     </row>
     <row r="261" ht="18.0" customHeight="1">
-      <c r="A261" s="12"/>
-      <c r="B261" s="12"/>
-      <c r="C261" s="8"/>
-      <c r="D261" s="15"/>
+      <c r="A261" s="11"/>
+      <c r="B261" s="11"/>
+      <c r="C261" s="12"/>
+      <c r="D261" s="13"/>
       <c r="H261" s="5"/>
       <c r="I261" s="5"/>
       <c r="J261" s="5"/>
@@ -6817,10 +6988,10 @@
       <c r="P261" s="5"/>
     </row>
     <row r="262" ht="18.0" customHeight="1">
-      <c r="A262" s="12"/>
-      <c r="B262" s="12"/>
-      <c r="C262" s="8"/>
-      <c r="D262" s="15"/>
+      <c r="A262" s="11"/>
+      <c r="B262" s="11"/>
+      <c r="C262" s="12"/>
+      <c r="D262" s="13"/>
       <c r="H262" s="5"/>
       <c r="I262" s="5"/>
       <c r="J262" s="5"/>
@@ -6832,10 +7003,10 @@
       <c r="P262" s="5"/>
     </row>
     <row r="263" ht="18.0" customHeight="1">
-      <c r="A263" s="12"/>
-      <c r="B263" s="12"/>
-      <c r="C263" s="8"/>
-      <c r="D263" s="15"/>
+      <c r="A263" s="11"/>
+      <c r="B263" s="11"/>
+      <c r="C263" s="12"/>
+      <c r="D263" s="13"/>
       <c r="H263" s="5"/>
       <c r="I263" s="5"/>
       <c r="J263" s="5"/>
@@ -6847,10 +7018,10 @@
       <c r="P263" s="5"/>
     </row>
     <row r="264" ht="18.0" customHeight="1">
-      <c r="A264" s="12"/>
-      <c r="B264" s="12"/>
-      <c r="C264" s="8"/>
-      <c r="D264" s="15"/>
+      <c r="A264" s="11"/>
+      <c r="B264" s="11"/>
+      <c r="C264" s="12"/>
+      <c r="D264" s="13"/>
       <c r="H264" s="5"/>
       <c r="I264" s="5"/>
       <c r="J264" s="5"/>
@@ -6862,10 +7033,10 @@
       <c r="P264" s="5"/>
     </row>
     <row r="265" ht="18.0" customHeight="1">
-      <c r="A265" s="12"/>
-      <c r="B265" s="12"/>
-      <c r="C265" s="8"/>
-      <c r="D265" s="15"/>
+      <c r="A265" s="11"/>
+      <c r="B265" s="11"/>
+      <c r="C265" s="12"/>
+      <c r="D265" s="13"/>
       <c r="H265" s="5"/>
       <c r="I265" s="5"/>
       <c r="J265" s="5"/>
@@ -6877,10 +7048,10 @@
       <c r="P265" s="5"/>
     </row>
     <row r="266" ht="18.0" customHeight="1">
-      <c r="A266" s="12"/>
-      <c r="B266" s="12"/>
-      <c r="C266" s="8"/>
-      <c r="D266" s="15"/>
+      <c r="A266" s="11"/>
+      <c r="B266" s="11"/>
+      <c r="C266" s="12"/>
+      <c r="D266" s="13"/>
       <c r="H266" s="5"/>
       <c r="I266" s="5"/>
       <c r="J266" s="5"/>
@@ -6892,10 +7063,10 @@
       <c r="P266" s="5"/>
     </row>
     <row r="267" ht="18.0" customHeight="1">
-      <c r="A267" s="12"/>
-      <c r="B267" s="12"/>
-      <c r="C267" s="8"/>
-      <c r="D267" s="15"/>
+      <c r="A267" s="11"/>
+      <c r="B267" s="11"/>
+      <c r="C267" s="12"/>
+      <c r="D267" s="13"/>
       <c r="H267" s="5"/>
       <c r="I267" s="5"/>
       <c r="J267" s="5"/>
@@ -6907,10 +7078,10 @@
       <c r="P267" s="5"/>
     </row>
     <row r="268" ht="18.0" customHeight="1">
-      <c r="A268" s="12"/>
-      <c r="B268" s="12"/>
-      <c r="C268" s="8"/>
-      <c r="D268" s="15"/>
+      <c r="A268" s="11"/>
+      <c r="B268" s="11"/>
+      <c r="C268" s="12"/>
+      <c r="D268" s="13"/>
       <c r="H268" s="5"/>
       <c r="I268" s="5"/>
       <c r="J268" s="5"/>
@@ -6922,10 +7093,10 @@
       <c r="P268" s="5"/>
     </row>
     <row r="269" ht="18.0" customHeight="1">
-      <c r="A269" s="12"/>
-      <c r="B269" s="12"/>
-      <c r="C269" s="8"/>
-      <c r="D269" s="15"/>
+      <c r="A269" s="11"/>
+      <c r="B269" s="11"/>
+      <c r="C269" s="12"/>
+      <c r="D269" s="13"/>
       <c r="H269" s="5"/>
       <c r="I269" s="5"/>
       <c r="J269" s="5"/>
@@ -6937,10 +7108,10 @@
       <c r="P269" s="5"/>
     </row>
     <row r="270" ht="18.0" customHeight="1">
-      <c r="A270" s="12"/>
-      <c r="B270" s="12"/>
-      <c r="C270" s="8"/>
-      <c r="D270" s="15"/>
+      <c r="A270" s="11"/>
+      <c r="B270" s="11"/>
+      <c r="C270" s="12"/>
+      <c r="D270" s="13"/>
       <c r="H270" s="5"/>
       <c r="I270" s="5"/>
       <c r="J270" s="5"/>
@@ -6952,10 +7123,10 @@
       <c r="P270" s="5"/>
     </row>
     <row r="271" ht="18.0" customHeight="1">
-      <c r="A271" s="12"/>
-      <c r="B271" s="12"/>
-      <c r="C271" s="8"/>
-      <c r="D271" s="15"/>
+      <c r="A271" s="11"/>
+      <c r="B271" s="11"/>
+      <c r="C271" s="12"/>
+      <c r="D271" s="13"/>
       <c r="H271" s="5"/>
       <c r="I271" s="5"/>
       <c r="J271" s="5"/>
@@ -6967,10 +7138,10 @@
       <c r="P271" s="5"/>
     </row>
     <row r="272" ht="18.0" customHeight="1">
-      <c r="A272" s="12"/>
-      <c r="B272" s="12"/>
-      <c r="C272" s="8"/>
-      <c r="D272" s="15"/>
+      <c r="A272" s="11"/>
+      <c r="B272" s="11"/>
+      <c r="C272" s="12"/>
+      <c r="D272" s="13"/>
       <c r="H272" s="5"/>
       <c r="I272" s="5"/>
       <c r="J272" s="5"/>
@@ -6982,10 +7153,10 @@
       <c r="P272" s="5"/>
     </row>
     <row r="273" ht="18.0" customHeight="1">
-      <c r="A273" s="12"/>
-      <c r="B273" s="12"/>
-      <c r="C273" s="8"/>
-      <c r="D273" s="15"/>
+      <c r="A273" s="11"/>
+      <c r="B273" s="11"/>
+      <c r="C273" s="12"/>
+      <c r="D273" s="13"/>
       <c r="H273" s="5"/>
       <c r="I273" s="5"/>
       <c r="J273" s="5"/>
@@ -6997,10 +7168,10 @@
       <c r="P273" s="5"/>
     </row>
     <row r="274" ht="18.0" customHeight="1">
-      <c r="A274" s="12"/>
-      <c r="B274" s="12"/>
-      <c r="C274" s="8"/>
-      <c r="D274" s="15"/>
+      <c r="A274" s="11"/>
+      <c r="B274" s="11"/>
+      <c r="C274" s="12"/>
+      <c r="D274" s="13"/>
       <c r="H274" s="5"/>
       <c r="I274" s="5"/>
       <c r="J274" s="5"/>
@@ -7012,10 +7183,10 @@
       <c r="P274" s="5"/>
     </row>
     <row r="275" ht="18.0" customHeight="1">
-      <c r="A275" s="12"/>
-      <c r="B275" s="12"/>
-      <c r="C275" s="8"/>
-      <c r="D275" s="15"/>
+      <c r="A275" s="11"/>
+      <c r="B275" s="11"/>
+      <c r="C275" s="12"/>
+      <c r="D275" s="13"/>
       <c r="H275" s="5"/>
       <c r="I275" s="5"/>
       <c r="J275" s="5"/>
@@ -7027,10 +7198,10 @@
       <c r="P275" s="5"/>
     </row>
     <row r="276" ht="18.0" customHeight="1">
-      <c r="A276" s="12"/>
-      <c r="B276" s="12"/>
-      <c r="C276" s="8"/>
-      <c r="D276" s="15"/>
+      <c r="A276" s="11"/>
+      <c r="B276" s="11"/>
+      <c r="C276" s="12"/>
+      <c r="D276" s="13"/>
       <c r="H276" s="5"/>
       <c r="I276" s="5"/>
       <c r="J276" s="5"/>
@@ -7042,10 +7213,10 @@
       <c r="P276" s="5"/>
     </row>
     <row r="277" ht="18.0" customHeight="1">
-      <c r="A277" s="12"/>
-      <c r="B277" s="12"/>
-      <c r="C277" s="8"/>
-      <c r="D277" s="15"/>
+      <c r="A277" s="11"/>
+      <c r="B277" s="11"/>
+      <c r="C277" s="12"/>
+      <c r="D277" s="13"/>
       <c r="H277" s="5"/>
       <c r="I277" s="5"/>
       <c r="J277" s="5"/>
@@ -7057,10 +7228,10 @@
       <c r="P277" s="5"/>
     </row>
     <row r="278" ht="18.0" customHeight="1">
-      <c r="A278" s="12"/>
-      <c r="B278" s="12"/>
-      <c r="C278" s="8"/>
-      <c r="D278" s="15"/>
+      <c r="A278" s="11"/>
+      <c r="B278" s="11"/>
+      <c r="C278" s="12"/>
+      <c r="D278" s="13"/>
       <c r="H278" s="5"/>
       <c r="I278" s="5"/>
       <c r="J278" s="5"/>
@@ -7072,10 +7243,10 @@
       <c r="P278" s="5"/>
     </row>
     <row r="279" ht="18.0" customHeight="1">
-      <c r="A279" s="12"/>
-      <c r="B279" s="12"/>
-      <c r="C279" s="8"/>
-      <c r="D279" s="15"/>
+      <c r="A279" s="11"/>
+      <c r="B279" s="11"/>
+      <c r="C279" s="12"/>
+      <c r="D279" s="13"/>
       <c r="H279" s="5"/>
       <c r="I279" s="5"/>
       <c r="J279" s="5"/>
@@ -7087,10 +7258,10 @@
       <c r="P279" s="5"/>
     </row>
     <row r="280" ht="18.0" customHeight="1">
-      <c r="A280" s="12"/>
-      <c r="B280" s="12"/>
-      <c r="C280" s="8"/>
-      <c r="D280" s="15"/>
+      <c r="A280" s="11"/>
+      <c r="B280" s="11"/>
+      <c r="C280" s="12"/>
+      <c r="D280" s="13"/>
       <c r="H280" s="5"/>
       <c r="I280" s="5"/>
       <c r="J280" s="5"/>
@@ -7102,10 +7273,10 @@
       <c r="P280" s="5"/>
     </row>
     <row r="281" ht="18.0" customHeight="1">
-      <c r="A281" s="12"/>
-      <c r="B281" s="12"/>
-      <c r="C281" s="8"/>
-      <c r="D281" s="15"/>
+      <c r="A281" s="11"/>
+      <c r="B281" s="11"/>
+      <c r="C281" s="12"/>
+      <c r="D281" s="13"/>
       <c r="H281" s="5"/>
       <c r="I281" s="5"/>
       <c r="J281" s="5"/>
@@ -7117,10 +7288,10 @@
       <c r="P281" s="5"/>
     </row>
     <row r="282" ht="18.0" customHeight="1">
-      <c r="A282" s="12"/>
-      <c r="B282" s="12"/>
-      <c r="C282" s="8"/>
-      <c r="D282" s="15"/>
+      <c r="A282" s="11"/>
+      <c r="B282" s="11"/>
+      <c r="C282" s="12"/>
+      <c r="D282" s="13"/>
       <c r="H282" s="5"/>
       <c r="I282" s="5"/>
       <c r="J282" s="5"/>
@@ -7132,10 +7303,10 @@
       <c r="P282" s="5"/>
     </row>
     <row r="283" ht="18.0" customHeight="1">
-      <c r="A283" s="12"/>
-      <c r="B283" s="12"/>
-      <c r="C283" s="8"/>
-      <c r="D283" s="15"/>
+      <c r="A283" s="11"/>
+      <c r="B283" s="11"/>
+      <c r="C283" s="12"/>
+      <c r="D283" s="13"/>
       <c r="H283" s="5"/>
       <c r="I283" s="5"/>
       <c r="J283" s="5"/>
@@ -7147,10 +7318,10 @@
       <c r="P283" s="5"/>
     </row>
     <row r="284" ht="18.0" customHeight="1">
-      <c r="A284" s="12"/>
-      <c r="B284" s="12"/>
-      <c r="C284" s="8"/>
-      <c r="D284" s="15"/>
+      <c r="A284" s="11"/>
+      <c r="B284" s="11"/>
+      <c r="C284" s="12"/>
+      <c r="D284" s="13"/>
       <c r="H284" s="5"/>
       <c r="I284" s="5"/>
       <c r="J284" s="5"/>
@@ -7162,10 +7333,10 @@
       <c r="P284" s="5"/>
     </row>
     <row r="285" ht="18.0" customHeight="1">
-      <c r="A285" s="12"/>
-      <c r="B285" s="12"/>
-      <c r="C285" s="8"/>
-      <c r="D285" s="15"/>
+      <c r="A285" s="11"/>
+      <c r="B285" s="11"/>
+      <c r="C285" s="12"/>
+      <c r="D285" s="13"/>
       <c r="H285" s="5"/>
       <c r="I285" s="5"/>
       <c r="J285" s="5"/>
@@ -7177,10 +7348,10 @@
       <c r="P285" s="5"/>
     </row>
     <row r="286" ht="18.0" customHeight="1">
-      <c r="A286" s="12"/>
-      <c r="B286" s="12"/>
-      <c r="C286" s="8"/>
-      <c r="D286" s="15"/>
+      <c r="A286" s="11"/>
+      <c r="B286" s="11"/>
+      <c r="C286" s="12"/>
+      <c r="D286" s="13"/>
       <c r="H286" s="5"/>
       <c r="I286" s="5"/>
       <c r="J286" s="5"/>
@@ -7192,10 +7363,10 @@
       <c r="P286" s="5"/>
     </row>
     <row r="287" ht="18.0" customHeight="1">
-      <c r="A287" s="12"/>
-      <c r="B287" s="12"/>
-      <c r="C287" s="8"/>
-      <c r="D287" s="15"/>
+      <c r="A287" s="11"/>
+      <c r="B287" s="11"/>
+      <c r="C287" s="12"/>
+      <c r="D287" s="13"/>
       <c r="H287" s="5"/>
       <c r="I287" s="5"/>
       <c r="J287" s="5"/>
@@ -7207,10 +7378,10 @@
       <c r="P287" s="5"/>
     </row>
     <row r="288" ht="18.0" customHeight="1">
-      <c r="A288" s="12"/>
-      <c r="B288" s="12"/>
-      <c r="C288" s="8"/>
-      <c r="D288" s="15"/>
+      <c r="A288" s="11"/>
+      <c r="B288" s="11"/>
+      <c r="C288" s="12"/>
+      <c r="D288" s="13"/>
       <c r="H288" s="5"/>
       <c r="I288" s="5"/>
       <c r="J288" s="5"/>
@@ -7222,10 +7393,10 @@
       <c r="P288" s="5"/>
     </row>
     <row r="289" ht="18.0" customHeight="1">
-      <c r="A289" s="12"/>
-      <c r="B289" s="12"/>
-      <c r="C289" s="8"/>
-      <c r="D289" s="15"/>
+      <c r="A289" s="11"/>
+      <c r="B289" s="11"/>
+      <c r="C289" s="12"/>
+      <c r="D289" s="13"/>
       <c r="H289" s="5"/>
       <c r="I289" s="5"/>
       <c r="J289" s="5"/>
@@ -7237,10 +7408,10 @@
       <c r="P289" s="5"/>
     </row>
     <row r="290" ht="18.0" customHeight="1">
-      <c r="A290" s="12"/>
-      <c r="B290" s="12"/>
-      <c r="C290" s="8"/>
-      <c r="D290" s="15"/>
+      <c r="A290" s="11"/>
+      <c r="B290" s="11"/>
+      <c r="C290" s="12"/>
+      <c r="D290" s="13"/>
       <c r="H290" s="5"/>
       <c r="I290" s="5"/>
       <c r="J290" s="5"/>
@@ -7252,10 +7423,10 @@
       <c r="P290" s="5"/>
     </row>
     <row r="291" ht="18.0" customHeight="1">
-      <c r="A291" s="12"/>
-      <c r="B291" s="12"/>
-      <c r="C291" s="8"/>
-      <c r="D291" s="15"/>
+      <c r="A291" s="11"/>
+      <c r="B291" s="11"/>
+      <c r="C291" s="12"/>
+      <c r="D291" s="13"/>
       <c r="H291" s="5"/>
       <c r="I291" s="5"/>
       <c r="J291" s="5"/>
@@ -7267,10 +7438,10 @@
       <c r="P291" s="5"/>
     </row>
     <row r="292" ht="18.0" customHeight="1">
-      <c r="A292" s="12"/>
-      <c r="B292" s="12"/>
-      <c r="C292" s="8"/>
-      <c r="D292" s="15"/>
+      <c r="A292" s="11"/>
+      <c r="B292" s="11"/>
+      <c r="C292" s="12"/>
+      <c r="D292" s="13"/>
       <c r="H292" s="5"/>
       <c r="I292" s="5"/>
       <c r="J292" s="5"/>
@@ -7282,10 +7453,10 @@
       <c r="P292" s="5"/>
     </row>
     <row r="293" ht="18.0" customHeight="1">
-      <c r="A293" s="12"/>
-      <c r="B293" s="12"/>
-      <c r="C293" s="8"/>
-      <c r="D293" s="15"/>
+      <c r="A293" s="11"/>
+      <c r="B293" s="11"/>
+      <c r="C293" s="12"/>
+      <c r="D293" s="13"/>
       <c r="H293" s="5"/>
       <c r="I293" s="5"/>
       <c r="J293" s="5"/>
@@ -7297,10 +7468,10 @@
       <c r="P293" s="5"/>
     </row>
     <row r="294" ht="18.0" customHeight="1">
-      <c r="A294" s="12"/>
-      <c r="B294" s="12"/>
-      <c r="C294" s="8"/>
-      <c r="D294" s="15"/>
+      <c r="A294" s="11"/>
+      <c r="B294" s="11"/>
+      <c r="C294" s="12"/>
+      <c r="D294" s="13"/>
       <c r="H294" s="5"/>
       <c r="I294" s="5"/>
       <c r="J294" s="5"/>
@@ -7312,10 +7483,10 @@
       <c r="P294" s="5"/>
     </row>
     <row r="295" ht="18.0" customHeight="1">
-      <c r="A295" s="12"/>
-      <c r="B295" s="12"/>
-      <c r="C295" s="8"/>
-      <c r="D295" s="15"/>
+      <c r="A295" s="11"/>
+      <c r="B295" s="11"/>
+      <c r="C295" s="12"/>
+      <c r="D295" s="13"/>
       <c r="H295" s="5"/>
       <c r="I295" s="5"/>
       <c r="J295" s="5"/>
@@ -7327,10 +7498,10 @@
       <c r="P295" s="5"/>
     </row>
     <row r="296" ht="18.0" customHeight="1">
-      <c r="A296" s="12"/>
-      <c r="B296" s="12"/>
-      <c r="C296" s="8"/>
-      <c r="D296" s="15"/>
+      <c r="A296" s="11"/>
+      <c r="B296" s="11"/>
+      <c r="C296" s="12"/>
+      <c r="D296" s="13"/>
       <c r="H296" s="5"/>
       <c r="I296" s="5"/>
       <c r="J296" s="5"/>
@@ -7342,10 +7513,10 @@
       <c r="P296" s="5"/>
     </row>
     <row r="297" ht="18.0" customHeight="1">
-      <c r="A297" s="12"/>
-      <c r="B297" s="12"/>
-      <c r="C297" s="8"/>
-      <c r="D297" s="15"/>
+      <c r="A297" s="11"/>
+      <c r="B297" s="11"/>
+      <c r="C297" s="12"/>
+      <c r="D297" s="13"/>
       <c r="H297" s="5"/>
       <c r="I297" s="5"/>
       <c r="J297" s="5"/>
@@ -7357,10 +7528,10 @@
       <c r="P297" s="5"/>
     </row>
     <row r="298" ht="18.0" customHeight="1">
-      <c r="A298" s="12"/>
-      <c r="B298" s="12"/>
-      <c r="C298" s="8"/>
-      <c r="D298" s="15"/>
+      <c r="A298" s="11"/>
+      <c r="B298" s="11"/>
+      <c r="C298" s="12"/>
+      <c r="D298" s="13"/>
       <c r="H298" s="5"/>
       <c r="I298" s="5"/>
       <c r="J298" s="5"/>
@@ -7372,10 +7543,10 @@
       <c r="P298" s="5"/>
     </row>
     <row r="299" ht="18.0" customHeight="1">
-      <c r="A299" s="12"/>
-      <c r="B299" s="12"/>
-      <c r="C299" s="8"/>
-      <c r="D299" s="15"/>
+      <c r="A299" s="11"/>
+      <c r="B299" s="11"/>
+      <c r="C299" s="12"/>
+      <c r="D299" s="13"/>
       <c r="H299" s="5"/>
       <c r="I299" s="5"/>
       <c r="J299" s="5"/>
@@ -7387,10 +7558,10 @@
       <c r="P299" s="5"/>
     </row>
     <row r="300" ht="18.0" customHeight="1">
-      <c r="A300" s="12"/>
-      <c r="B300" s="12"/>
-      <c r="C300" s="8"/>
-      <c r="D300" s="15"/>
+      <c r="A300" s="11"/>
+      <c r="B300" s="11"/>
+      <c r="C300" s="12"/>
+      <c r="D300" s="13"/>
       <c r="H300" s="5"/>
       <c r="I300" s="5"/>
       <c r="J300" s="5"/>
@@ -7402,10 +7573,10 @@
       <c r="P300" s="5"/>
     </row>
     <row r="301" ht="18.0" customHeight="1">
-      <c r="A301" s="12"/>
-      <c r="B301" s="12"/>
-      <c r="C301" s="8"/>
-      <c r="D301" s="15"/>
+      <c r="A301" s="11"/>
+      <c r="B301" s="11"/>
+      <c r="C301" s="12"/>
+      <c r="D301" s="13"/>
       <c r="H301" s="5"/>
       <c r="I301" s="5"/>
       <c r="J301" s="5"/>
@@ -7417,10 +7588,10 @@
       <c r="P301" s="5"/>
     </row>
     <row r="302" ht="18.0" customHeight="1">
-      <c r="A302" s="12"/>
-      <c r="B302" s="12"/>
-      <c r="C302" s="8"/>
-      <c r="D302" s="15"/>
+      <c r="A302" s="11"/>
+      <c r="B302" s="11"/>
+      <c r="C302" s="12"/>
+      <c r="D302" s="13"/>
       <c r="H302" s="5"/>
       <c r="I302" s="5"/>
       <c r="J302" s="5"/>
@@ -7432,10 +7603,10 @@
       <c r="P302" s="5"/>
     </row>
     <row r="303" ht="18.0" customHeight="1">
-      <c r="A303" s="12"/>
-      <c r="B303" s="12"/>
-      <c r="C303" s="8"/>
-      <c r="D303" s="15"/>
+      <c r="A303" s="11"/>
+      <c r="B303" s="11"/>
+      <c r="C303" s="12"/>
+      <c r="D303" s="13"/>
       <c r="H303" s="5"/>
       <c r="I303" s="5"/>
       <c r="J303" s="5"/>
@@ -7447,10 +7618,10 @@
       <c r="P303" s="5"/>
     </row>
     <row r="304" ht="18.0" customHeight="1">
-      <c r="A304" s="12"/>
-      <c r="B304" s="12"/>
-      <c r="C304" s="8"/>
-      <c r="D304" s="15"/>
+      <c r="A304" s="11"/>
+      <c r="B304" s="11"/>
+      <c r="C304" s="12"/>
+      <c r="D304" s="13"/>
       <c r="H304" s="5"/>
       <c r="I304" s="5"/>
       <c r="J304" s="5"/>
@@ -7462,10 +7633,10 @@
       <c r="P304" s="5"/>
     </row>
     <row r="305" ht="18.0" customHeight="1">
-      <c r="A305" s="12"/>
-      <c r="B305" s="12"/>
-      <c r="C305" s="8"/>
-      <c r="D305" s="15"/>
+      <c r="A305" s="11"/>
+      <c r="B305" s="11"/>
+      <c r="C305" s="12"/>
+      <c r="D305" s="13"/>
       <c r="H305" s="5"/>
       <c r="I305" s="5"/>
       <c r="J305" s="5"/>
@@ -7477,10 +7648,10 @@
       <c r="P305" s="5"/>
     </row>
     <row r="306" ht="18.0" customHeight="1">
-      <c r="A306" s="12"/>
-      <c r="B306" s="12"/>
-      <c r="C306" s="8"/>
-      <c r="D306" s="15"/>
+      <c r="A306" s="11"/>
+      <c r="B306" s="11"/>
+      <c r="C306" s="12"/>
+      <c r="D306" s="13"/>
       <c r="H306" s="5"/>
       <c r="I306" s="5"/>
       <c r="J306" s="5"/>
@@ -7492,10 +7663,10 @@
       <c r="P306" s="5"/>
     </row>
     <row r="307" ht="18.0" customHeight="1">
-      <c r="A307" s="12"/>
-      <c r="B307" s="12"/>
-      <c r="C307" s="8"/>
-      <c r="D307" s="15"/>
+      <c r="A307" s="11"/>
+      <c r="B307" s="11"/>
+      <c r="C307" s="12"/>
+      <c r="D307" s="13"/>
       <c r="H307" s="5"/>
       <c r="I307" s="5"/>
       <c r="J307" s="5"/>
@@ -7507,10 +7678,10 @@
       <c r="P307" s="5"/>
     </row>
     <row r="308" ht="18.0" customHeight="1">
-      <c r="A308" s="12"/>
-      <c r="B308" s="12"/>
-      <c r="C308" s="8"/>
-      <c r="D308" s="15"/>
+      <c r="A308" s="11"/>
+      <c r="B308" s="11"/>
+      <c r="C308" s="12"/>
+      <c r="D308" s="13"/>
       <c r="H308" s="5"/>
       <c r="I308" s="5"/>
       <c r="J308" s="5"/>
@@ -7522,10 +7693,10 @@
       <c r="P308" s="5"/>
     </row>
     <row r="309" ht="18.0" customHeight="1">
-      <c r="A309" s="12"/>
-      <c r="B309" s="12"/>
-      <c r="C309" s="8"/>
-      <c r="D309" s="15"/>
+      <c r="A309" s="11"/>
+      <c r="B309" s="11"/>
+      <c r="C309" s="12"/>
+      <c r="D309" s="13"/>
       <c r="H309" s="5"/>
       <c r="I309" s="5"/>
       <c r="J309" s="5"/>
@@ -7537,10 +7708,10 @@
       <c r="P309" s="5"/>
     </row>
     <row r="310" ht="18.0" customHeight="1">
-      <c r="A310" s="12"/>
-      <c r="B310" s="12"/>
-      <c r="C310" s="8"/>
-      <c r="D310" s="15"/>
+      <c r="A310" s="11"/>
+      <c r="B310" s="11"/>
+      <c r="C310" s="12"/>
+      <c r="D310" s="13"/>
       <c r="H310" s="5"/>
       <c r="I310" s="5"/>
       <c r="J310" s="5"/>
@@ -7552,10 +7723,10 @@
       <c r="P310" s="5"/>
     </row>
     <row r="311" ht="18.0" customHeight="1">
-      <c r="A311" s="12"/>
-      <c r="B311" s="12"/>
-      <c r="C311" s="8"/>
-      <c r="D311" s="15"/>
+      <c r="A311" s="11"/>
+      <c r="B311" s="11"/>
+      <c r="C311" s="12"/>
+      <c r="D311" s="13"/>
       <c r="H311" s="5"/>
       <c r="I311" s="5"/>
       <c r="J311" s="5"/>
@@ -7567,10 +7738,10 @@
       <c r="P311" s="5"/>
     </row>
     <row r="312" ht="18.0" customHeight="1">
-      <c r="A312" s="12"/>
-      <c r="B312" s="12"/>
-      <c r="C312" s="8"/>
-      <c r="D312" s="15"/>
+      <c r="A312" s="11"/>
+      <c r="B312" s="11"/>
+      <c r="C312" s="12"/>
+      <c r="D312" s="13"/>
       <c r="H312" s="5"/>
       <c r="I312" s="5"/>
       <c r="J312" s="5"/>
@@ -7582,10 +7753,10 @@
       <c r="P312" s="5"/>
     </row>
     <row r="313" ht="18.0" customHeight="1">
-      <c r="A313" s="12"/>
-      <c r="B313" s="12"/>
-      <c r="C313" s="8"/>
-      <c r="D313" s="15"/>
+      <c r="A313" s="11"/>
+      <c r="B313" s="11"/>
+      <c r="C313" s="12"/>
+      <c r="D313" s="13"/>
       <c r="H313" s="5"/>
       <c r="I313" s="5"/>
       <c r="J313" s="5"/>
@@ -7597,10 +7768,10 @@
       <c r="P313" s="5"/>
     </row>
     <row r="314" ht="18.0" customHeight="1">
-      <c r="A314" s="12"/>
-      <c r="B314" s="12"/>
-      <c r="C314" s="8"/>
-      <c r="D314" s="15"/>
+      <c r="A314" s="11"/>
+      <c r="B314" s="11"/>
+      <c r="C314" s="12"/>
+      <c r="D314" s="13"/>
       <c r="H314" s="5"/>
       <c r="I314" s="5"/>
       <c r="J314" s="5"/>
@@ -7612,10 +7783,10 @@
       <c r="P314" s="5"/>
     </row>
     <row r="315" ht="18.0" customHeight="1">
-      <c r="A315" s="12"/>
-      <c r="B315" s="12"/>
-      <c r="C315" s="8"/>
-      <c r="D315" s="15"/>
+      <c r="A315" s="11"/>
+      <c r="B315" s="11"/>
+      <c r="C315" s="12"/>
+      <c r="D315" s="13"/>
       <c r="H315" s="5"/>
       <c r="I315" s="5"/>
       <c r="J315" s="5"/>
@@ -7627,10 +7798,10 @@
       <c r="P315" s="5"/>
     </row>
     <row r="316" ht="18.0" customHeight="1">
-      <c r="A316" s="12"/>
-      <c r="B316" s="12"/>
-      <c r="C316" s="8"/>
-      <c r="D316" s="15"/>
+      <c r="A316" s="11"/>
+      <c r="B316" s="11"/>
+      <c r="C316" s="12"/>
+      <c r="D316" s="13"/>
       <c r="H316" s="5"/>
       <c r="I316" s="5"/>
       <c r="J316" s="5"/>
@@ -7642,10 +7813,10 @@
       <c r="P316" s="5"/>
     </row>
     <row r="317" ht="18.0" customHeight="1">
-      <c r="A317" s="12"/>
-      <c r="B317" s="12"/>
-      <c r="C317" s="8"/>
-      <c r="D317" s="15"/>
+      <c r="A317" s="11"/>
+      <c r="B317" s="11"/>
+      <c r="C317" s="12"/>
+      <c r="D317" s="13"/>
       <c r="H317" s="5"/>
       <c r="I317" s="5"/>
       <c r="J317" s="5"/>
@@ -7657,10 +7828,10 @@
       <c r="P317" s="5"/>
     </row>
     <row r="318" ht="18.0" customHeight="1">
-      <c r="A318" s="12"/>
-      <c r="B318" s="12"/>
-      <c r="C318" s="8"/>
-      <c r="D318" s="15"/>
+      <c r="A318" s="11"/>
+      <c r="B318" s="11"/>
+      <c r="C318" s="12"/>
+      <c r="D318" s="13"/>
       <c r="H318" s="5"/>
       <c r="I318" s="5"/>
       <c r="J318" s="5"/>
@@ -7672,10 +7843,10 @@
       <c r="P318" s="5"/>
     </row>
     <row r="319" ht="18.0" customHeight="1">
-      <c r="A319" s="12"/>
-      <c r="B319" s="12"/>
-      <c r="C319" s="8"/>
-      <c r="D319" s="15"/>
+      <c r="A319" s="11"/>
+      <c r="B319" s="11"/>
+      <c r="C319" s="12"/>
+      <c r="D319" s="13"/>
       <c r="H319" s="5"/>
       <c r="I319" s="5"/>
       <c r="J319" s="5"/>
@@ -7687,10 +7858,10 @@
       <c r="P319" s="5"/>
     </row>
     <row r="320" ht="18.0" customHeight="1">
-      <c r="A320" s="12"/>
-      <c r="B320" s="12"/>
-      <c r="C320" s="8"/>
-      <c r="D320" s="15"/>
+      <c r="A320" s="11"/>
+      <c r="B320" s="11"/>
+      <c r="C320" s="12"/>
+      <c r="D320" s="13"/>
       <c r="H320" s="5"/>
       <c r="I320" s="5"/>
       <c r="J320" s="5"/>
@@ -7702,10 +7873,10 @@
       <c r="P320" s="5"/>
     </row>
     <row r="321" ht="18.0" customHeight="1">
-      <c r="A321" s="12"/>
-      <c r="B321" s="12"/>
-      <c r="C321" s="8"/>
-      <c r="D321" s="15"/>
+      <c r="A321" s="11"/>
+      <c r="B321" s="11"/>
+      <c r="C321" s="12"/>
+      <c r="D321" s="13"/>
       <c r="H321" s="5"/>
       <c r="I321" s="5"/>
       <c r="J321" s="5"/>
@@ -7717,10 +7888,10 @@
       <c r="P321" s="5"/>
     </row>
     <row r="322" ht="18.0" customHeight="1">
-      <c r="A322" s="12"/>
-      <c r="B322" s="12"/>
-      <c r="C322" s="8"/>
-      <c r="D322" s="15"/>
+      <c r="A322" s="11"/>
+      <c r="B322" s="11"/>
+      <c r="C322" s="12"/>
+      <c r="D322" s="13"/>
       <c r="H322" s="5"/>
       <c r="I322" s="5"/>
       <c r="J322" s="5"/>
@@ -7732,10 +7903,10 @@
       <c r="P322" s="5"/>
     </row>
     <row r="323" ht="18.0" customHeight="1">
-      <c r="A323" s="12"/>
-      <c r="B323" s="12"/>
-      <c r="C323" s="8"/>
-      <c r="D323" s="15"/>
+      <c r="A323" s="11"/>
+      <c r="B323" s="11"/>
+      <c r="C323" s="12"/>
+      <c r="D323" s="13"/>
       <c r="H323" s="5"/>
       <c r="I323" s="5"/>
       <c r="J323" s="5"/>
@@ -7747,10 +7918,10 @@
       <c r="P323" s="5"/>
     </row>
     <row r="324" ht="18.0" customHeight="1">
-      <c r="A324" s="12"/>
-      <c r="B324" s="12"/>
-      <c r="C324" s="8"/>
-      <c r="D324" s="15"/>
+      <c r="A324" s="11"/>
+      <c r="B324" s="11"/>
+      <c r="C324" s="12"/>
+      <c r="D324" s="13"/>
       <c r="H324" s="5"/>
       <c r="I324" s="5"/>
       <c r="J324" s="5"/>
@@ -7762,10 +7933,10 @@
       <c r="P324" s="5"/>
     </row>
     <row r="325" ht="18.0" customHeight="1">
-      <c r="A325" s="12"/>
-      <c r="B325" s="12"/>
-      <c r="C325" s="8"/>
-      <c r="D325" s="15"/>
+      <c r="A325" s="11"/>
+      <c r="B325" s="11"/>
+      <c r="C325" s="12"/>
+      <c r="D325" s="13"/>
       <c r="H325" s="5"/>
       <c r="I325" s="5"/>
       <c r="J325" s="5"/>
@@ -7777,10 +7948,10 @@
       <c r="P325" s="5"/>
     </row>
     <row r="326" ht="18.0" customHeight="1">
-      <c r="A326" s="12"/>
-      <c r="B326" s="12"/>
-      <c r="C326" s="8"/>
-      <c r="D326" s="15"/>
+      <c r="A326" s="11"/>
+      <c r="B326" s="11"/>
+      <c r="C326" s="12"/>
+      <c r="D326" s="13"/>
       <c r="H326" s="5"/>
       <c r="I326" s="5"/>
       <c r="J326" s="5"/>
@@ -7792,10 +7963,10 @@
       <c r="P326" s="5"/>
     </row>
     <row r="327" ht="18.0" customHeight="1">
-      <c r="A327" s="12"/>
-      <c r="B327" s="12"/>
-      <c r="C327" s="8"/>
-      <c r="D327" s="15"/>
+      <c r="A327" s="11"/>
+      <c r="B327" s="11"/>
+      <c r="C327" s="12"/>
+      <c r="D327" s="13"/>
       <c r="H327" s="5"/>
       <c r="I327" s="5"/>
       <c r="J327" s="5"/>
@@ -7807,10 +7978,10 @@
       <c r="P327" s="5"/>
     </row>
     <row r="328" ht="18.0" customHeight="1">
-      <c r="A328" s="12"/>
-      <c r="B328" s="12"/>
-      <c r="C328" s="8"/>
-      <c r="D328" s="15"/>
+      <c r="A328" s="11"/>
+      <c r="B328" s="11"/>
+      <c r="C328" s="12"/>
+      <c r="D328" s="13"/>
       <c r="H328" s="5"/>
       <c r="I328" s="5"/>
       <c r="J328" s="5"/>
@@ -7822,10 +7993,10 @@
       <c r="P328" s="5"/>
     </row>
     <row r="329" ht="18.0" customHeight="1">
-      <c r="A329" s="12"/>
-      <c r="B329" s="12"/>
-      <c r="C329" s="8"/>
-      <c r="D329" s="15"/>
+      <c r="A329" s="11"/>
+      <c r="B329" s="11"/>
+      <c r="C329" s="12"/>
+      <c r="D329" s="13"/>
       <c r="H329" s="5"/>
       <c r="I329" s="5"/>
       <c r="J329" s="5"/>
@@ -7837,10 +8008,10 @@
       <c r="P329" s="5"/>
     </row>
     <row r="330" ht="18.0" customHeight="1">
-      <c r="A330" s="12"/>
-      <c r="B330" s="12"/>
-      <c r="C330" s="8"/>
-      <c r="D330" s="15"/>
+      <c r="A330" s="11"/>
+      <c r="B330" s="11"/>
+      <c r="C330" s="12"/>
+      <c r="D330" s="13"/>
       <c r="H330" s="5"/>
       <c r="I330" s="5"/>
       <c r="J330" s="5"/>
@@ -7852,10 +8023,10 @@
       <c r="P330" s="5"/>
     </row>
     <row r="331" ht="18.0" customHeight="1">
-      <c r="A331" s="12"/>
-      <c r="B331" s="12"/>
-      <c r="C331" s="8"/>
-      <c r="D331" s="15"/>
+      <c r="A331" s="11"/>
+      <c r="B331" s="11"/>
+      <c r="C331" s="12"/>
+      <c r="D331" s="13"/>
       <c r="H331" s="5"/>
       <c r="I331" s="5"/>
       <c r="J331" s="5"/>
@@ -7867,10 +8038,10 @@
       <c r="P331" s="5"/>
     </row>
     <row r="332" ht="18.0" customHeight="1">
-      <c r="A332" s="12"/>
-      <c r="B332" s="12"/>
-      <c r="C332" s="8"/>
-      <c r="D332" s="15"/>
+      <c r="A332" s="11"/>
+      <c r="B332" s="11"/>
+      <c r="C332" s="12"/>
+      <c r="D332" s="13"/>
       <c r="H332" s="5"/>
       <c r="I332" s="5"/>
       <c r="J332" s="5"/>
@@ -7882,10 +8053,10 @@
       <c r="P332" s="5"/>
     </row>
     <row r="333" ht="18.0" customHeight="1">
-      <c r="A333" s="12"/>
-      <c r="B333" s="12"/>
-      <c r="C333" s="8"/>
-      <c r="D333" s="15"/>
+      <c r="A333" s="11"/>
+      <c r="B333" s="11"/>
+      <c r="C333" s="12"/>
+      <c r="D333" s="13"/>
       <c r="H333" s="5"/>
       <c r="I333" s="5"/>
       <c r="J333" s="5"/>
@@ -7897,10 +8068,10 @@
       <c r="P333" s="5"/>
     </row>
     <row r="334" ht="18.0" customHeight="1">
-      <c r="A334" s="12"/>
-      <c r="B334" s="12"/>
-      <c r="C334" s="8"/>
-      <c r="D334" s="15"/>
+      <c r="A334" s="11"/>
+      <c r="B334" s="11"/>
+      <c r="C334" s="12"/>
+      <c r="D334" s="13"/>
       <c r="H334" s="5"/>
       <c r="I334" s="5"/>
       <c r="J334" s="5"/>
@@ -7912,10 +8083,10 @@
       <c r="P334" s="5"/>
     </row>
     <row r="335" ht="18.0" customHeight="1">
-      <c r="A335" s="12"/>
-      <c r="B335" s="12"/>
-      <c r="C335" s="8"/>
-      <c r="D335" s="15"/>
+      <c r="A335" s="11"/>
+      <c r="B335" s="11"/>
+      <c r="C335" s="12"/>
+      <c r="D335" s="13"/>
       <c r="H335" s="5"/>
       <c r="I335" s="5"/>
       <c r="J335" s="5"/>
@@ -7927,10 +8098,10 @@
       <c r="P335" s="5"/>
     </row>
     <row r="336" ht="18.0" customHeight="1">
-      <c r="A336" s="12"/>
-      <c r="B336" s="12"/>
-      <c r="C336" s="8"/>
-      <c r="D336" s="15"/>
+      <c r="A336" s="11"/>
+      <c r="B336" s="11"/>
+      <c r="C336" s="12"/>
+      <c r="D336" s="13"/>
       <c r="H336" s="5"/>
       <c r="I336" s="5"/>
       <c r="J336" s="5"/>
@@ -7942,10 +8113,10 @@
       <c r="P336" s="5"/>
     </row>
     <row r="337" ht="18.0" customHeight="1">
-      <c r="A337" s="12"/>
-      <c r="B337" s="12"/>
-      <c r="C337" s="8"/>
-      <c r="D337" s="15"/>
+      <c r="A337" s="11"/>
+      <c r="B337" s="11"/>
+      <c r="C337" s="12"/>
+      <c r="D337" s="13"/>
       <c r="H337" s="5"/>
       <c r="I337" s="5"/>
       <c r="J337" s="5"/>
@@ -7957,10 +8128,10 @@
       <c r="P337" s="5"/>
     </row>
     <row r="338" ht="18.0" customHeight="1">
-      <c r="A338" s="12"/>
-      <c r="B338" s="12"/>
-      <c r="C338" s="8"/>
-      <c r="D338" s="15"/>
+      <c r="A338" s="11"/>
+      <c r="B338" s="11"/>
+      <c r="C338" s="12"/>
+      <c r="D338" s="13"/>
       <c r="H338" s="5"/>
       <c r="I338" s="5"/>
       <c r="J338" s="5"/>
@@ -7972,10 +8143,10 @@
       <c r="P338" s="5"/>
     </row>
     <row r="339" ht="18.0" customHeight="1">
-      <c r="A339" s="12"/>
-      <c r="B339" s="12"/>
-      <c r="C339" s="8"/>
-      <c r="D339" s="15"/>
+      <c r="A339" s="11"/>
+      <c r="B339" s="11"/>
+      <c r="C339" s="12"/>
+      <c r="D339" s="13"/>
       <c r="H339" s="5"/>
       <c r="I339" s="5"/>
       <c r="J339" s="5"/>
@@ -7987,10 +8158,10 @@
       <c r="P339" s="5"/>
     </row>
     <row r="340" ht="18.0" customHeight="1">
-      <c r="A340" s="12"/>
-      <c r="B340" s="12"/>
-      <c r="C340" s="8"/>
-      <c r="D340" s="15"/>
+      <c r="A340" s="11"/>
+      <c r="B340" s="11"/>
+      <c r="C340" s="12"/>
+      <c r="D340" s="13"/>
       <c r="H340" s="5"/>
       <c r="I340" s="5"/>
       <c r="J340" s="5"/>
@@ -8002,10 +8173,10 @@
       <c r="P340" s="5"/>
     </row>
     <row r="341" ht="18.0" customHeight="1">
-      <c r="A341" s="12"/>
-      <c r="B341" s="12"/>
-      <c r="C341" s="8"/>
-      <c r="D341" s="15"/>
+      <c r="A341" s="11"/>
+      <c r="B341" s="11"/>
+      <c r="C341" s="12"/>
+      <c r="D341" s="13"/>
       <c r="H341" s="5"/>
       <c r="I341" s="5"/>
       <c r="J341" s="5"/>
@@ -8017,10 +8188,10 @@
       <c r="P341" s="5"/>
     </row>
     <row r="342" ht="18.0" customHeight="1">
-      <c r="A342" s="12"/>
-      <c r="B342" s="12"/>
-      <c r="C342" s="8"/>
-      <c r="D342" s="15"/>
+      <c r="A342" s="11"/>
+      <c r="B342" s="11"/>
+      <c r="C342" s="12"/>
+      <c r="D342" s="13"/>
       <c r="H342" s="5"/>
       <c r="I342" s="5"/>
       <c r="J342" s="5"/>
@@ -8032,10 +8203,10 @@
       <c r="P342" s="5"/>
     </row>
     <row r="343" ht="18.0" customHeight="1">
-      <c r="A343" s="12"/>
-      <c r="B343" s="12"/>
-      <c r="C343" s="8"/>
-      <c r="D343" s="15"/>
+      <c r="A343" s="11"/>
+      <c r="B343" s="11"/>
+      <c r="C343" s="12"/>
+      <c r="D343" s="13"/>
       <c r="H343" s="5"/>
       <c r="I343" s="5"/>
       <c r="J343" s="5"/>
@@ -8047,10 +8218,10 @@
       <c r="P343" s="5"/>
     </row>
     <row r="344" ht="18.0" customHeight="1">
-      <c r="A344" s="12"/>
-      <c r="B344" s="12"/>
-      <c r="C344" s="8"/>
-      <c r="D344" s="15"/>
+      <c r="A344" s="11"/>
+      <c r="B344" s="11"/>
+      <c r="C344" s="12"/>
+      <c r="D344" s="13"/>
       <c r="H344" s="5"/>
       <c r="I344" s="5"/>
       <c r="J344" s="5"/>
@@ -8062,10 +8233,10 @@
       <c r="P344" s="5"/>
     </row>
     <row r="345" ht="18.0" customHeight="1">
-      <c r="A345" s="12"/>
-      <c r="B345" s="12"/>
-      <c r="C345" s="8"/>
-      <c r="D345" s="15"/>
+      <c r="A345" s="11"/>
+      <c r="B345" s="11"/>
+      <c r="C345" s="12"/>
+      <c r="D345" s="13"/>
       <c r="H345" s="5"/>
       <c r="I345" s="5"/>
       <c r="J345" s="5"/>
@@ -8077,10 +8248,10 @@
       <c r="P345" s="5"/>
     </row>
     <row r="346" ht="18.0" customHeight="1">
-      <c r="A346" s="12"/>
-      <c r="B346" s="12"/>
-      <c r="C346" s="8"/>
-      <c r="D346" s="15"/>
+      <c r="A346" s="11"/>
+      <c r="B346" s="11"/>
+      <c r="C346" s="12"/>
+      <c r="D346" s="13"/>
       <c r="H346" s="5"/>
       <c r="I346" s="5"/>
       <c r="J346" s="5"/>
@@ -8092,10 +8263,10 @@
       <c r="P346" s="5"/>
     </row>
     <row r="347" ht="18.0" customHeight="1">
-      <c r="A347" s="12"/>
-      <c r="B347" s="12"/>
-      <c r="C347" s="8"/>
-      <c r="D347" s="15"/>
+      <c r="A347" s="11"/>
+      <c r="B347" s="11"/>
+      <c r="C347" s="12"/>
+      <c r="D347" s="13"/>
       <c r="H347" s="5"/>
       <c r="I347" s="5"/>
       <c r="J347" s="5"/>
@@ -8107,10 +8278,10 @@
       <c r="P347" s="5"/>
     </row>
     <row r="348" ht="18.0" customHeight="1">
-      <c r="A348" s="12"/>
-      <c r="B348" s="12"/>
-      <c r="C348" s="8"/>
-      <c r="D348" s="15"/>
+      <c r="A348" s="11"/>
+      <c r="B348" s="11"/>
+      <c r="C348" s="12"/>
+      <c r="D348" s="13"/>
       <c r="H348" s="5"/>
       <c r="I348" s="5"/>
       <c r="J348" s="5"/>
@@ -8122,10 +8293,10 @@
       <c r="P348" s="5"/>
     </row>
     <row r="349" ht="18.0" customHeight="1">
-      <c r="A349" s="12"/>
-      <c r="B349" s="12"/>
-      <c r="C349" s="8"/>
-      <c r="D349" s="15"/>
+      <c r="A349" s="11"/>
+      <c r="B349" s="11"/>
+      <c r="C349" s="12"/>
+      <c r="D349" s="13"/>
       <c r="H349" s="5"/>
       <c r="I349" s="5"/>
       <c r="J349" s="5"/>
@@ -8137,10 +8308,10 @@
       <c r="P349" s="5"/>
     </row>
     <row r="350" ht="18.0" customHeight="1">
-      <c r="A350" s="12"/>
-      <c r="B350" s="12"/>
-      <c r="C350" s="8"/>
-      <c r="D350" s="15"/>
+      <c r="A350" s="11"/>
+      <c r="B350" s="11"/>
+      <c r="C350" s="12"/>
+      <c r="D350" s="13"/>
       <c r="H350" s="5"/>
       <c r="I350" s="5"/>
       <c r="J350" s="5"/>
@@ -8152,10 +8323,10 @@
       <c r="P350" s="5"/>
     </row>
     <row r="351" ht="18.0" customHeight="1">
-      <c r="A351" s="12"/>
-      <c r="B351" s="12"/>
-      <c r="C351" s="8"/>
-      <c r="D351" s="15"/>
+      <c r="A351" s="11"/>
+      <c r="B351" s="11"/>
+      <c r="C351" s="12"/>
+      <c r="D351" s="13"/>
       <c r="H351" s="5"/>
       <c r="I351" s="5"/>
       <c r="J351" s="5"/>
@@ -8167,10 +8338,10 @@
       <c r="P351" s="5"/>
     </row>
     <row r="352" ht="18.0" customHeight="1">
-      <c r="A352" s="12"/>
-      <c r="B352" s="12"/>
-      <c r="C352" s="8"/>
-      <c r="D352" s="15"/>
+      <c r="A352" s="11"/>
+      <c r="B352" s="11"/>
+      <c r="C352" s="12"/>
+      <c r="D352" s="13"/>
       <c r="H352" s="5"/>
       <c r="I352" s="5"/>
       <c r="J352" s="5"/>
@@ -8182,10 +8353,10 @@
       <c r="P352" s="5"/>
     </row>
     <row r="353" ht="18.0" customHeight="1">
-      <c r="A353" s="12"/>
-      <c r="B353" s="12"/>
-      <c r="C353" s="8"/>
-      <c r="D353" s="15"/>
+      <c r="A353" s="11"/>
+      <c r="B353" s="11"/>
+      <c r="C353" s="12"/>
+      <c r="D353" s="13"/>
       <c r="H353" s="5"/>
       <c r="I353" s="5"/>
       <c r="J353" s="5"/>
@@ -8197,10 +8368,10 @@
       <c r="P353" s="5"/>
     </row>
     <row r="354" ht="18.0" customHeight="1">
-      <c r="A354" s="12"/>
-      <c r="B354" s="12"/>
-      <c r="C354" s="8"/>
-      <c r="D354" s="15"/>
+      <c r="A354" s="11"/>
+      <c r="B354" s="11"/>
+      <c r="C354" s="12"/>
+      <c r="D354" s="13"/>
       <c r="H354" s="5"/>
       <c r="I354" s="5"/>
       <c r="J354" s="5"/>
@@ -8212,10 +8383,10 @@
       <c r="P354" s="5"/>
     </row>
     <row r="355" ht="18.0" customHeight="1">
-      <c r="A355" s="12"/>
-      <c r="B355" s="12"/>
-      <c r="C355" s="8"/>
-      <c r="D355" s="15"/>
+      <c r="A355" s="11"/>
+      <c r="B355" s="11"/>
+      <c r="C355" s="12"/>
+      <c r="D355" s="13"/>
       <c r="H355" s="5"/>
       <c r="I355" s="5"/>
       <c r="J355" s="5"/>
@@ -8227,10 +8398,10 @@
       <c r="P355" s="5"/>
     </row>
     <row r="356" ht="18.0" customHeight="1">
-      <c r="A356" s="12"/>
-      <c r="B356" s="12"/>
-      <c r="C356" s="8"/>
-      <c r="D356" s="15"/>
+      <c r="A356" s="11"/>
+      <c r="B356" s="11"/>
+      <c r="C356" s="12"/>
+      <c r="D356" s="13"/>
       <c r="H356" s="5"/>
       <c r="I356" s="5"/>
       <c r="J356" s="5"/>
@@ -8242,10 +8413,10 @@
       <c r="P356" s="5"/>
     </row>
     <row r="357" ht="18.0" customHeight="1">
-      <c r="A357" s="12"/>
-      <c r="B357" s="12"/>
-      <c r="C357" s="8"/>
-      <c r="D357" s="15"/>
+      <c r="A357" s="11"/>
+      <c r="B357" s="11"/>
+      <c r="C357" s="12"/>
+      <c r="D357" s="13"/>
       <c r="H357" s="5"/>
       <c r="I357" s="5"/>
       <c r="J357" s="5"/>
@@ -8257,10 +8428,10 @@
       <c r="P357" s="5"/>
     </row>
     <row r="358" ht="18.0" customHeight="1">
-      <c r="A358" s="12"/>
-      <c r="B358" s="12"/>
-      <c r="C358" s="8"/>
-      <c r="D358" s="15"/>
+      <c r="A358" s="11"/>
+      <c r="B358" s="11"/>
+      <c r="C358" s="12"/>
+      <c r="D358" s="13"/>
       <c r="H358" s="5"/>
       <c r="I358" s="5"/>
       <c r="J358" s="5"/>
@@ -8272,10 +8443,10 @@
       <c r="P358" s="5"/>
     </row>
     <row r="359" ht="18.0" customHeight="1">
-      <c r="A359" s="12"/>
-      <c r="B359" s="12"/>
-      <c r="C359" s="8"/>
-      <c r="D359" s="15"/>
+      <c r="A359" s="11"/>
+      <c r="B359" s="11"/>
+      <c r="C359" s="12"/>
+      <c r="D359" s="13"/>
       <c r="H359" s="5"/>
       <c r="I359" s="5"/>
       <c r="J359" s="5"/>
@@ -8287,10 +8458,10 @@
       <c r="P359" s="5"/>
     </row>
     <row r="360" ht="18.0" customHeight="1">
-      <c r="A360" s="12"/>
-      <c r="B360" s="12"/>
-      <c r="C360" s="8"/>
-      <c r="D360" s="15"/>
+      <c r="A360" s="11"/>
+      <c r="B360" s="11"/>
+      <c r="C360" s="12"/>
+      <c r="D360" s="13"/>
       <c r="H360" s="5"/>
       <c r="I360" s="5"/>
       <c r="J360" s="5"/>
@@ -8302,10 +8473,10 @@
       <c r="P360" s="5"/>
     </row>
     <row r="361" ht="18.0" customHeight="1">
-      <c r="A361" s="12"/>
-      <c r="B361" s="12"/>
-      <c r="C361" s="8"/>
-      <c r="D361" s="15"/>
+      <c r="A361" s="11"/>
+      <c r="B361" s="11"/>
+      <c r="C361" s="12"/>
+      <c r="D361" s="13"/>
       <c r="H361" s="5"/>
       <c r="I361" s="5"/>
       <c r="J361" s="5"/>
@@ -8317,10 +8488,10 @@
       <c r="P361" s="5"/>
     </row>
     <row r="362" ht="18.0" customHeight="1">
-      <c r="A362" s="12"/>
-      <c r="B362" s="12"/>
-      <c r="C362" s="8"/>
-      <c r="D362" s="15"/>
+      <c r="A362" s="11"/>
+      <c r="B362" s="11"/>
+      <c r="C362" s="12"/>
+      <c r="D362" s="13"/>
       <c r="H362" s="5"/>
       <c r="I362" s="5"/>
       <c r="J362" s="5"/>
@@ -8332,10 +8503,10 @@
       <c r="P362" s="5"/>
     </row>
     <row r="363" ht="18.0" customHeight="1">
-      <c r="A363" s="12"/>
-      <c r="B363" s="12"/>
-      <c r="C363" s="8"/>
-      <c r="D363" s="15"/>
+      <c r="A363" s="11"/>
+      <c r="B363" s="11"/>
+      <c r="C363" s="12"/>
+      <c r="D363" s="13"/>
       <c r="H363" s="5"/>
       <c r="I363" s="5"/>
       <c r="J363" s="5"/>
@@ -8347,10 +8518,10 @@
       <c r="P363" s="5"/>
     </row>
     <row r="364" ht="18.0" customHeight="1">
-      <c r="A364" s="12"/>
-      <c r="B364" s="12"/>
-      <c r="C364" s="8"/>
-      <c r="D364" s="15"/>
+      <c r="A364" s="11"/>
+      <c r="B364" s="11"/>
+      <c r="C364" s="12"/>
+      <c r="D364" s="13"/>
       <c r="H364" s="5"/>
       <c r="I364" s="5"/>
       <c r="J364" s="5"/>
@@ -8362,10 +8533,10 @@
       <c r="P364" s="5"/>
     </row>
     <row r="365" ht="18.0" customHeight="1">
-      <c r="A365" s="12"/>
-      <c r="B365" s="12"/>
-      <c r="C365" s="8"/>
-      <c r="D365" s="15"/>
+      <c r="A365" s="11"/>
+      <c r="B365" s="11"/>
+      <c r="C365" s="12"/>
+      <c r="D365" s="13"/>
       <c r="H365" s="5"/>
       <c r="I365" s="5"/>
       <c r="J365" s="5"/>
@@ -8377,10 +8548,10 @@
       <c r="P365" s="5"/>
     </row>
     <row r="366" ht="18.0" customHeight="1">
-      <c r="A366" s="12"/>
-      <c r="B366" s="12"/>
-      <c r="C366" s="8"/>
-      <c r="D366" s="15"/>
+      <c r="A366" s="11"/>
+      <c r="B366" s="11"/>
+      <c r="C366" s="12"/>
+      <c r="D366" s="13"/>
       <c r="H366" s="5"/>
       <c r="I366" s="5"/>
       <c r="J366" s="5"/>
@@ -8392,10 +8563,10 @@
       <c r="P366" s="5"/>
     </row>
     <row r="367" ht="18.0" customHeight="1">
-      <c r="A367" s="12"/>
-      <c r="B367" s="12"/>
-      <c r="C367" s="8"/>
-      <c r="D367" s="15"/>
+      <c r="A367" s="11"/>
+      <c r="B367" s="11"/>
+      <c r="C367" s="12"/>
+      <c r="D367" s="13"/>
       <c r="H367" s="5"/>
       <c r="I367" s="5"/>
       <c r="J367" s="5"/>
@@ -8407,10 +8578,10 @@
       <c r="P367" s="5"/>
     </row>
     <row r="368" ht="18.0" customHeight="1">
-      <c r="A368" s="12"/>
-      <c r="B368" s="12"/>
-      <c r="C368" s="8"/>
-      <c r="D368" s="15"/>
+      <c r="A368" s="11"/>
+      <c r="B368" s="11"/>
+      <c r="C368" s="12"/>
+      <c r="D368" s="13"/>
       <c r="H368" s="5"/>
       <c r="I368" s="5"/>
       <c r="J368" s="5"/>
@@ -8422,10 +8593,10 @@
       <c r="P368" s="5"/>
     </row>
     <row r="369" ht="18.0" customHeight="1">
-      <c r="A369" s="12"/>
-      <c r="B369" s="12"/>
-      <c r="C369" s="8"/>
-      <c r="D369" s="15"/>
+      <c r="A369" s="11"/>
+      <c r="B369" s="11"/>
+      <c r="C369" s="12"/>
+      <c r="D369" s="13"/>
       <c r="H369" s="5"/>
       <c r="I369" s="5"/>
       <c r="J369" s="5"/>
@@ -8437,10 +8608,10 @@
       <c r="P369" s="5"/>
     </row>
     <row r="370" ht="18.0" customHeight="1">
-      <c r="A370" s="12"/>
-      <c r="B370" s="12"/>
-      <c r="C370" s="8"/>
-      <c r="D370" s="15"/>
+      <c r="A370" s="11"/>
+      <c r="B370" s="11"/>
+      <c r="C370" s="12"/>
+      <c r="D370" s="13"/>
       <c r="H370" s="5"/>
       <c r="I370" s="5"/>
       <c r="J370" s="5"/>
@@ -8452,10 +8623,10 @@
       <c r="P370" s="5"/>
     </row>
     <row r="371" ht="18.0" customHeight="1">
-      <c r="A371" s="12"/>
-      <c r="B371" s="12"/>
-      <c r="C371" s="8"/>
-      <c r="D371" s="15"/>
+      <c r="A371" s="11"/>
+      <c r="B371" s="11"/>
+      <c r="C371" s="12"/>
+      <c r="D371" s="13"/>
       <c r="H371" s="5"/>
       <c r="I371" s="5"/>
       <c r="J371" s="5"/>
@@ -8467,10 +8638,10 @@
       <c r="P371" s="5"/>
     </row>
     <row r="372" ht="18.0" customHeight="1">
-      <c r="A372" s="12"/>
-      <c r="B372" s="12"/>
-      <c r="C372" s="8"/>
-      <c r="D372" s="15"/>
+      <c r="A372" s="11"/>
+      <c r="B372" s="11"/>
+      <c r="C372" s="12"/>
+      <c r="D372" s="13"/>
       <c r="H372" s="5"/>
       <c r="I372" s="5"/>
       <c r="J372" s="5"/>
@@ -8482,10 +8653,10 @@
       <c r="P372" s="5"/>
     </row>
     <row r="373" ht="18.0" customHeight="1">
-      <c r="A373" s="12"/>
-      <c r="B373" s="12"/>
-      <c r="C373" s="8"/>
-      <c r="D373" s="15"/>
+      <c r="A373" s="11"/>
+      <c r="B373" s="11"/>
+      <c r="C373" s="12"/>
+      <c r="D373" s="13"/>
       <c r="H373" s="5"/>
       <c r="I373" s="5"/>
       <c r="J373" s="5"/>
@@ -8497,10 +8668,10 @@
       <c r="P373" s="5"/>
     </row>
     <row r="374" ht="18.0" customHeight="1">
-      <c r="A374" s="12"/>
-      <c r="B374" s="12"/>
-      <c r="C374" s="8"/>
-      <c r="D374" s="15"/>
+      <c r="A374" s="11"/>
+      <c r="B374" s="11"/>
+      <c r="C374" s="12"/>
+      <c r="D374" s="13"/>
       <c r="H374" s="5"/>
       <c r="I374" s="5"/>
       <c r="J374" s="5"/>
@@ -8512,10 +8683,10 @@
       <c r="P374" s="5"/>
     </row>
     <row r="375" ht="18.0" customHeight="1">
-      <c r="A375" s="12"/>
-      <c r="B375" s="12"/>
-      <c r="C375" s="8"/>
-      <c r="D375" s="15"/>
+      <c r="A375" s="11"/>
+      <c r="B375" s="11"/>
+      <c r="C375" s="12"/>
+      <c r="D375" s="13"/>
       <c r="H375" s="5"/>
       <c r="I375" s="5"/>
       <c r="J375" s="5"/>
@@ -8527,10 +8698,10 @@
       <c r="P375" s="5"/>
     </row>
     <row r="376" ht="18.0" customHeight="1">
-      <c r="A376" s="12"/>
-      <c r="B376" s="12"/>
-      <c r="C376" s="8"/>
-      <c r="D376" s="15"/>
+      <c r="A376" s="11"/>
+      <c r="B376" s="11"/>
+      <c r="C376" s="12"/>
+      <c r="D376" s="13"/>
       <c r="H376" s="5"/>
       <c r="I376" s="5"/>
       <c r="J376" s="5"/>
@@ -8542,10 +8713,10 @@
       <c r="P376" s="5"/>
     </row>
     <row r="377" ht="18.0" customHeight="1">
-      <c r="A377" s="12"/>
-      <c r="B377" s="12"/>
-      <c r="C377" s="8"/>
-      <c r="D377" s="15"/>
+      <c r="A377" s="11"/>
+      <c r="B377" s="11"/>
+      <c r="C377" s="12"/>
+      <c r="D377" s="13"/>
       <c r="H377" s="5"/>
       <c r="I377" s="5"/>
       <c r="J377" s="5"/>
@@ -8557,10 +8728,10 @@
       <c r="P377" s="5"/>
     </row>
     <row r="378" ht="18.0" customHeight="1">
-      <c r="A378" s="12"/>
-      <c r="B378" s="12"/>
-      <c r="C378" s="8"/>
-      <c r="D378" s="15"/>
+      <c r="A378" s="11"/>
+      <c r="B378" s="11"/>
+      <c r="C378" s="12"/>
+      <c r="D378" s="13"/>
       <c r="H378" s="5"/>
       <c r="I378" s="5"/>
       <c r="J378" s="5"/>
@@ -8572,10 +8743,10 @@
       <c r="P378" s="5"/>
     </row>
     <row r="379" ht="18.0" customHeight="1">
-      <c r="A379" s="12"/>
-      <c r="B379" s="12"/>
-      <c r="C379" s="8"/>
-      <c r="D379" s="15"/>
+      <c r="A379" s="11"/>
+      <c r="B379" s="11"/>
+      <c r="C379" s="12"/>
+      <c r="D379" s="13"/>
       <c r="H379" s="5"/>
       <c r="I379" s="5"/>
       <c r="J379" s="5"/>
@@ -8587,10 +8758,10 @@
       <c r="P379" s="5"/>
     </row>
     <row r="380" ht="18.0" customHeight="1">
-      <c r="A380" s="12"/>
-      <c r="B380" s="12"/>
-      <c r="C380" s="8"/>
-      <c r="D380" s="15"/>
+      <c r="A380" s="11"/>
+      <c r="B380" s="11"/>
+      <c r="C380" s="12"/>
+      <c r="D380" s="13"/>
       <c r="H380" s="5"/>
       <c r="I380" s="5"/>
       <c r="J380" s="5"/>
@@ -8602,10 +8773,10 @@
       <c r="P380" s="5"/>
     </row>
     <row r="381" ht="18.0" customHeight="1">
-      <c r="A381" s="12"/>
-      <c r="B381" s="12"/>
-      <c r="C381" s="8"/>
-      <c r="D381" s="15"/>
+      <c r="A381" s="11"/>
+      <c r="B381" s="11"/>
+      <c r="C381" s="12"/>
+      <c r="D381" s="13"/>
       <c r="H381" s="5"/>
       <c r="I381" s="5"/>
       <c r="J381" s="5"/>
@@ -8617,10 +8788,10 @@
       <c r="P381" s="5"/>
     </row>
     <row r="382" ht="18.0" customHeight="1">
-      <c r="A382" s="12"/>
-      <c r="B382" s="12"/>
-      <c r="C382" s="8"/>
-      <c r="D382" s="15"/>
+      <c r="A382" s="11"/>
+      <c r="B382" s="11"/>
+      <c r="C382" s="12"/>
+      <c r="D382" s="13"/>
       <c r="H382" s="5"/>
       <c r="I382" s="5"/>
       <c r="J382" s="5"/>
@@ -8631,11 +8802,14 @@
       <c r="O382" s="5"/>
       <c r="P382" s="5"/>
     </row>
-    <row r="383" ht="18.0" customHeight="1">
-      <c r="A383" s="12"/>
-      <c r="B383" s="12"/>
-      <c r="C383" s="8"/>
-      <c r="D383" s="15"/>
+    <row r="383" ht="34.5" customHeight="1">
+      <c r="A383" s="11"/>
+      <c r="B383" s="11"/>
+      <c r="C383" s="12"/>
+      <c r="D383" s="13"/>
+      <c r="E383" s="14"/>
+      <c r="F383" s="14"/>
+      <c r="G383" s="14"/>
       <c r="H383" s="5"/>
       <c r="I383" s="5"/>
       <c r="J383" s="5"/>
@@ -8647,10 +8821,13 @@
       <c r="P383" s="5"/>
     </row>
     <row r="384" ht="18.0" customHeight="1">
-      <c r="A384" s="12"/>
-      <c r="B384" s="12"/>
-      <c r="C384" s="8"/>
-      <c r="D384" s="15"/>
+      <c r="A384" s="11"/>
+      <c r="B384" s="11"/>
+      <c r="C384" s="12"/>
+      <c r="D384" s="13"/>
+      <c r="E384" s="14"/>
+      <c r="F384" s="15"/>
+      <c r="G384" s="15"/>
       <c r="H384" s="5"/>
       <c r="I384" s="5"/>
       <c r="J384" s="5"/>
@@ -8661,14 +8838,14 @@
       <c r="O384" s="5"/>
       <c r="P384" s="5"/>
     </row>
-    <row r="385" ht="34.5" customHeight="1">
-      <c r="A385" s="6"/>
-      <c r="B385" s="6"/>
-      <c r="C385" s="8"/>
-      <c r="D385" s="15"/>
+    <row r="385" ht="18.0" customHeight="1">
+      <c r="A385" s="11"/>
+      <c r="B385" s="11"/>
+      <c r="C385" s="12"/>
+      <c r="D385" s="13"/>
       <c r="E385" s="16"/>
-      <c r="F385" s="16"/>
-      <c r="G385" s="16"/>
+      <c r="F385" s="17"/>
+      <c r="G385" s="17"/>
       <c r="H385" s="5"/>
       <c r="I385" s="5"/>
       <c r="J385" s="5"/>
@@ -8680,10 +8857,10 @@
       <c r="P385" s="5"/>
     </row>
     <row r="386" ht="18.0" customHeight="1">
-      <c r="A386" s="6"/>
-      <c r="B386" s="6"/>
-      <c r="C386" s="8"/>
-      <c r="D386" s="15"/>
+      <c r="A386" s="11"/>
+      <c r="B386" s="11"/>
+      <c r="C386" s="12"/>
+      <c r="D386" s="13"/>
       <c r="E386" s="16"/>
       <c r="F386" s="17"/>
       <c r="G386" s="17"/>
@@ -8698,13 +8875,13 @@
       <c r="P386" s="5"/>
     </row>
     <row r="387" ht="18.0" customHeight="1">
-      <c r="A387" s="6"/>
-      <c r="B387" s="6"/>
-      <c r="C387" s="8"/>
-      <c r="D387" s="15"/>
-      <c r="E387" s="18"/>
-      <c r="F387" s="19"/>
-      <c r="G387" s="19"/>
+      <c r="A387" s="11"/>
+      <c r="B387" s="11"/>
+      <c r="C387" s="12"/>
+      <c r="D387" s="13"/>
+      <c r="E387" s="16"/>
+      <c r="F387" s="17"/>
+      <c r="G387" s="17"/>
       <c r="H387" s="5"/>
       <c r="I387" s="5"/>
       <c r="J387" s="5"/>
@@ -8716,13 +8893,13 @@
       <c r="P387" s="5"/>
     </row>
     <row r="388" ht="18.0" customHeight="1">
-      <c r="A388" s="6"/>
-      <c r="B388" s="6"/>
-      <c r="C388" s="8"/>
-      <c r="D388" s="15"/>
-      <c r="E388" s="18"/>
-      <c r="F388" s="19"/>
-      <c r="G388" s="19"/>
+      <c r="A388" s="11"/>
+      <c r="B388" s="11"/>
+      <c r="C388" s="12"/>
+      <c r="D388" s="13"/>
+      <c r="E388" s="16"/>
+      <c r="F388" s="17"/>
+      <c r="G388" s="17"/>
       <c r="H388" s="5"/>
       <c r="I388" s="5"/>
       <c r="J388" s="5"/>
@@ -8734,13 +8911,13 @@
       <c r="P388" s="5"/>
     </row>
     <row r="389" ht="18.0" customHeight="1">
-      <c r="A389" s="6"/>
-      <c r="B389" s="6"/>
-      <c r="C389" s="8"/>
-      <c r="D389" s="15"/>
-      <c r="E389" s="18"/>
-      <c r="F389" s="19"/>
-      <c r="G389" s="19"/>
+      <c r="A389" s="11"/>
+      <c r="B389" s="11"/>
+      <c r="C389" s="12"/>
+      <c r="D389" s="13"/>
+      <c r="E389" s="16"/>
+      <c r="F389" s="17"/>
+      <c r="G389" s="17"/>
       <c r="H389" s="5"/>
       <c r="I389" s="5"/>
       <c r="J389" s="5"/>
@@ -8752,13 +8929,13 @@
       <c r="P389" s="5"/>
     </row>
     <row r="390" ht="18.0" customHeight="1">
-      <c r="A390" s="6"/>
-      <c r="B390" s="6"/>
-      <c r="C390" s="8"/>
-      <c r="D390" s="15"/>
-      <c r="E390" s="18"/>
-      <c r="F390" s="19"/>
-      <c r="G390" s="19"/>
+      <c r="A390" s="11"/>
+      <c r="B390" s="11"/>
+      <c r="C390" s="12"/>
+      <c r="D390" s="13"/>
+      <c r="E390" s="16"/>
+      <c r="F390" s="17"/>
+      <c r="G390" s="17"/>
       <c r="H390" s="5"/>
       <c r="I390" s="5"/>
       <c r="J390" s="5"/>
@@ -8770,13 +8947,13 @@
       <c r="P390" s="5"/>
     </row>
     <row r="391" ht="18.0" customHeight="1">
-      <c r="A391" s="6"/>
-      <c r="B391" s="6"/>
-      <c r="C391" s="8"/>
-      <c r="D391" s="15"/>
-      <c r="E391" s="18"/>
-      <c r="F391" s="19"/>
-      <c r="G391" s="19"/>
+      <c r="A391" s="11"/>
+      <c r="B391" s="11"/>
+      <c r="C391" s="12"/>
+      <c r="D391" s="13"/>
+      <c r="E391" s="16"/>
+      <c r="F391" s="17"/>
+      <c r="G391" s="17"/>
       <c r="H391" s="5"/>
       <c r="I391" s="5"/>
       <c r="J391" s="5"/>
@@ -8788,13 +8965,13 @@
       <c r="P391" s="5"/>
     </row>
     <row r="392" ht="18.0" customHeight="1">
-      <c r="A392" s="6"/>
-      <c r="B392" s="6"/>
-      <c r="C392" s="8"/>
-      <c r="D392" s="15"/>
-      <c r="E392" s="18"/>
-      <c r="F392" s="19"/>
-      <c r="G392" s="19"/>
+      <c r="A392" s="11"/>
+      <c r="B392" s="11"/>
+      <c r="C392" s="12"/>
+      <c r="D392" s="13"/>
+      <c r="E392" s="16"/>
+      <c r="F392" s="17"/>
+      <c r="G392" s="17"/>
       <c r="H392" s="5"/>
       <c r="I392" s="5"/>
       <c r="J392" s="5"/>
@@ -8806,13 +8983,13 @@
       <c r="P392" s="5"/>
     </row>
     <row r="393" ht="18.0" customHeight="1">
-      <c r="A393" s="6"/>
-      <c r="B393" s="6"/>
-      <c r="C393" s="8"/>
-      <c r="D393" s="15"/>
-      <c r="E393" s="18"/>
-      <c r="F393" s="19"/>
-      <c r="G393" s="19"/>
+      <c r="A393" s="11"/>
+      <c r="B393" s="11"/>
+      <c r="C393" s="12"/>
+      <c r="D393" s="13"/>
+      <c r="E393" s="16"/>
+      <c r="F393" s="17"/>
+      <c r="G393" s="17"/>
       <c r="H393" s="5"/>
       <c r="I393" s="5"/>
       <c r="J393" s="5"/>
@@ -8824,13 +9001,13 @@
       <c r="P393" s="5"/>
     </row>
     <row r="394" ht="18.0" customHeight="1">
-      <c r="A394" s="6"/>
-      <c r="B394" s="6"/>
-      <c r="C394" s="8"/>
-      <c r="D394" s="15"/>
-      <c r="E394" s="18"/>
-      <c r="F394" s="19"/>
-      <c r="G394" s="19"/>
+      <c r="A394" s="11"/>
+      <c r="B394" s="11"/>
+      <c r="C394" s="12"/>
+      <c r="D394" s="13"/>
+      <c r="E394" s="16"/>
+      <c r="F394" s="17"/>
+      <c r="G394" s="17"/>
       <c r="H394" s="5"/>
       <c r="I394" s="5"/>
       <c r="J394" s="5"/>
@@ -8842,13 +9019,13 @@
       <c r="P394" s="5"/>
     </row>
     <row r="395" ht="18.0" customHeight="1">
-      <c r="A395" s="6"/>
-      <c r="B395" s="6"/>
-      <c r="C395" s="8"/>
-      <c r="D395" s="15"/>
-      <c r="E395" s="18"/>
-      <c r="F395" s="19"/>
-      <c r="G395" s="19"/>
+      <c r="A395" s="11"/>
+      <c r="B395" s="11"/>
+      <c r="C395" s="12"/>
+      <c r="D395" s="13"/>
+      <c r="E395" s="16"/>
+      <c r="F395" s="17"/>
+      <c r="G395" s="17"/>
       <c r="H395" s="5"/>
       <c r="I395" s="5"/>
       <c r="J395" s="5"/>
@@ -8860,13 +9037,13 @@
       <c r="P395" s="5"/>
     </row>
     <row r="396" ht="18.0" customHeight="1">
-      <c r="A396" s="6"/>
-      <c r="B396" s="6"/>
-      <c r="C396" s="8"/>
-      <c r="D396" s="15"/>
-      <c r="E396" s="18"/>
-      <c r="F396" s="19"/>
-      <c r="G396" s="19"/>
+      <c r="A396" s="11"/>
+      <c r="B396" s="11"/>
+      <c r="C396" s="12"/>
+      <c r="D396" s="13"/>
+      <c r="E396" s="16"/>
+      <c r="F396" s="17"/>
+      <c r="G396" s="17"/>
       <c r="H396" s="5"/>
       <c r="I396" s="5"/>
       <c r="J396" s="5"/>
@@ -8878,13 +9055,13 @@
       <c r="P396" s="5"/>
     </row>
     <row r="397" ht="18.0" customHeight="1">
-      <c r="A397" s="6"/>
-      <c r="B397" s="6"/>
-      <c r="C397" s="8"/>
-      <c r="D397" s="15"/>
-      <c r="E397" s="18"/>
-      <c r="F397" s="19"/>
-      <c r="G397" s="19"/>
+      <c r="A397" s="11"/>
+      <c r="B397" s="11"/>
+      <c r="C397" s="12"/>
+      <c r="D397" s="13"/>
+      <c r="E397" s="16"/>
+      <c r="F397" s="17"/>
+      <c r="G397" s="17"/>
       <c r="H397" s="5"/>
       <c r="I397" s="5"/>
       <c r="J397" s="5"/>
@@ -8896,13 +9073,13 @@
       <c r="P397" s="5"/>
     </row>
     <row r="398" ht="18.0" customHeight="1">
-      <c r="A398" s="6"/>
-      <c r="B398" s="6"/>
-      <c r="C398" s="8"/>
-      <c r="D398" s="15"/>
-      <c r="E398" s="18"/>
-      <c r="F398" s="19"/>
-      <c r="G398" s="19"/>
+      <c r="A398" s="11"/>
+      <c r="B398" s="11"/>
+      <c r="C398" s="12"/>
+      <c r="D398" s="13"/>
+      <c r="E398" s="16"/>
+      <c r="F398" s="17"/>
+      <c r="G398" s="17"/>
       <c r="H398" s="5"/>
       <c r="I398" s="5"/>
       <c r="J398" s="5"/>
@@ -8914,13 +9091,13 @@
       <c r="P398" s="5"/>
     </row>
     <row r="399" ht="18.0" customHeight="1">
-      <c r="A399" s="6"/>
-      <c r="B399" s="6"/>
-      <c r="C399" s="8"/>
-      <c r="D399" s="15"/>
-      <c r="E399" s="18"/>
-      <c r="F399" s="19"/>
-      <c r="G399" s="19"/>
+      <c r="A399" s="11"/>
+      <c r="B399" s="11"/>
+      <c r="C399" s="12"/>
+      <c r="D399" s="13"/>
+      <c r="E399" s="16"/>
+      <c r="F399" s="17"/>
+      <c r="G399" s="17"/>
       <c r="H399" s="5"/>
       <c r="I399" s="5"/>
       <c r="J399" s="5"/>
@@ -8932,13 +9109,13 @@
       <c r="P399" s="5"/>
     </row>
     <row r="400" ht="18.0" customHeight="1">
-      <c r="A400" s="6"/>
-      <c r="B400" s="6"/>
-      <c r="C400" s="8"/>
-      <c r="D400" s="15"/>
-      <c r="E400" s="18"/>
-      <c r="F400" s="19"/>
-      <c r="G400" s="19"/>
+      <c r="A400" s="11"/>
+      <c r="B400" s="11"/>
+      <c r="C400" s="12"/>
+      <c r="D400" s="13"/>
+      <c r="E400" s="16"/>
+      <c r="F400" s="17"/>
+      <c r="G400" s="17"/>
       <c r="H400" s="5"/>
       <c r="I400" s="5"/>
       <c r="J400" s="5"/>
@@ -8950,13 +9127,13 @@
       <c r="P400" s="5"/>
     </row>
     <row r="401" ht="18.0" customHeight="1">
-      <c r="A401" s="6"/>
-      <c r="B401" s="6"/>
-      <c r="C401" s="8"/>
-      <c r="D401" s="15"/>
-      <c r="E401" s="18"/>
-      <c r="F401" s="19"/>
-      <c r="G401" s="19"/>
+      <c r="A401" s="11"/>
+      <c r="B401" s="11"/>
+      <c r="C401" s="12"/>
+      <c r="D401" s="13"/>
+      <c r="E401" s="16"/>
+      <c r="F401" s="17"/>
+      <c r="G401" s="17"/>
       <c r="H401" s="5"/>
       <c r="I401" s="5"/>
       <c r="J401" s="5"/>
@@ -8968,13 +9145,13 @@
       <c r="P401" s="5"/>
     </row>
     <row r="402" ht="18.0" customHeight="1">
-      <c r="A402" s="6"/>
-      <c r="B402" s="6"/>
-      <c r="C402" s="8"/>
-      <c r="D402" s="15"/>
-      <c r="E402" s="18"/>
-      <c r="F402" s="19"/>
-      <c r="G402" s="19"/>
+      <c r="A402" s="11"/>
+      <c r="B402" s="11"/>
+      <c r="C402" s="12"/>
+      <c r="D402" s="13"/>
+      <c r="E402" s="16"/>
+      <c r="F402" s="17"/>
+      <c r="G402" s="17"/>
       <c r="H402" s="5"/>
       <c r="I402" s="5"/>
       <c r="J402" s="5"/>
@@ -8986,13 +9163,13 @@
       <c r="P402" s="5"/>
     </row>
     <row r="403" ht="18.0" customHeight="1">
-      <c r="A403" s="6"/>
-      <c r="B403" s="6"/>
-      <c r="C403" s="8"/>
-      <c r="D403" s="15"/>
-      <c r="E403" s="18"/>
-      <c r="F403" s="19"/>
-      <c r="G403" s="19"/>
+      <c r="A403" s="11"/>
+      <c r="B403" s="11"/>
+      <c r="C403" s="12"/>
+      <c r="D403" s="13"/>
+      <c r="E403" s="16"/>
+      <c r="F403" s="17"/>
+      <c r="G403" s="17"/>
       <c r="H403" s="5"/>
       <c r="I403" s="5"/>
       <c r="J403" s="5"/>
@@ -9004,13 +9181,13 @@
       <c r="P403" s="5"/>
     </row>
     <row r="404" ht="18.0" customHeight="1">
-      <c r="A404" s="6"/>
-      <c r="B404" s="6"/>
-      <c r="C404" s="8"/>
-      <c r="D404" s="15"/>
-      <c r="E404" s="18"/>
-      <c r="F404" s="19"/>
-      <c r="G404" s="19"/>
+      <c r="A404" s="11"/>
+      <c r="B404" s="11"/>
+      <c r="C404" s="12"/>
+      <c r="D404" s="13"/>
+      <c r="E404" s="16"/>
+      <c r="F404" s="17"/>
+      <c r="G404" s="17"/>
       <c r="H404" s="5"/>
       <c r="I404" s="5"/>
       <c r="J404" s="5"/>
@@ -9022,13 +9199,13 @@
       <c r="P404" s="5"/>
     </row>
     <row r="405" ht="18.0" customHeight="1">
-      <c r="A405" s="6"/>
-      <c r="B405" s="6"/>
-      <c r="C405" s="8"/>
-      <c r="D405" s="15"/>
-      <c r="E405" s="18"/>
-      <c r="F405" s="19"/>
-      <c r="G405" s="19"/>
+      <c r="A405" s="11"/>
+      <c r="B405" s="11"/>
+      <c r="C405" s="12"/>
+      <c r="D405" s="13"/>
+      <c r="E405" s="16"/>
+      <c r="F405" s="17"/>
+      <c r="G405" s="17"/>
       <c r="H405" s="5"/>
       <c r="I405" s="5"/>
       <c r="J405" s="5"/>
@@ -9040,13 +9217,13 @@
       <c r="P405" s="5"/>
     </row>
     <row r="406" ht="18.0" customHeight="1">
-      <c r="A406" s="6"/>
-      <c r="B406" s="6"/>
-      <c r="C406" s="8"/>
-      <c r="D406" s="15"/>
-      <c r="E406" s="18"/>
-      <c r="F406" s="19"/>
-      <c r="G406" s="19"/>
+      <c r="A406" s="11"/>
+      <c r="B406" s="11"/>
+      <c r="C406" s="12"/>
+      <c r="D406" s="13"/>
+      <c r="E406" s="16"/>
+      <c r="F406" s="17"/>
+      <c r="G406" s="17"/>
       <c r="H406" s="5"/>
       <c r="I406" s="5"/>
       <c r="J406" s="5"/>
@@ -9058,13 +9235,13 @@
       <c r="P406" s="5"/>
     </row>
     <row r="407" ht="18.0" customHeight="1">
-      <c r="A407" s="6"/>
-      <c r="B407" s="6"/>
-      <c r="C407" s="8"/>
-      <c r="D407" s="15"/>
-      <c r="E407" s="18"/>
-      <c r="F407" s="19"/>
-      <c r="G407" s="19"/>
+      <c r="A407" s="11"/>
+      <c r="B407" s="11"/>
+      <c r="C407" s="12"/>
+      <c r="D407" s="13"/>
+      <c r="E407" s="16"/>
+      <c r="F407" s="17"/>
+      <c r="G407" s="17"/>
       <c r="H407" s="5"/>
       <c r="I407" s="5"/>
       <c r="J407" s="5"/>
@@ -9076,13 +9253,13 @@
       <c r="P407" s="5"/>
     </row>
     <row r="408" ht="18.0" customHeight="1">
-      <c r="A408" s="6"/>
-      <c r="B408" s="6"/>
-      <c r="C408" s="8"/>
-      <c r="D408" s="15"/>
-      <c r="E408" s="18"/>
-      <c r="F408" s="19"/>
-      <c r="G408" s="19"/>
+      <c r="A408" s="11"/>
+      <c r="B408" s="11"/>
+      <c r="C408" s="12"/>
+      <c r="D408" s="13"/>
+      <c r="E408" s="16"/>
+      <c r="F408" s="17"/>
+      <c r="G408" s="17"/>
       <c r="H408" s="5"/>
       <c r="I408" s="5"/>
       <c r="J408" s="5"/>
@@ -9094,13 +9271,13 @@
       <c r="P408" s="5"/>
     </row>
     <row r="409" ht="18.0" customHeight="1">
-      <c r="A409" s="6"/>
-      <c r="B409" s="6"/>
-      <c r="C409" s="8"/>
-      <c r="D409" s="15"/>
-      <c r="E409" s="18"/>
-      <c r="F409" s="19"/>
-      <c r="G409" s="19"/>
+      <c r="A409" s="11"/>
+      <c r="B409" s="11"/>
+      <c r="C409" s="12"/>
+      <c r="D409" s="13"/>
+      <c r="E409" s="16"/>
+      <c r="F409" s="17"/>
+      <c r="G409" s="17"/>
       <c r="H409" s="5"/>
       <c r="I409" s="5"/>
       <c r="J409" s="5"/>
@@ -9112,13 +9289,13 @@
       <c r="P409" s="5"/>
     </row>
     <row r="410" ht="18.0" customHeight="1">
-      <c r="A410" s="6"/>
-      <c r="B410" s="6"/>
-      <c r="C410" s="8"/>
-      <c r="D410" s="15"/>
-      <c r="E410" s="18"/>
-      <c r="F410" s="19"/>
-      <c r="G410" s="19"/>
+      <c r="A410" s="11"/>
+      <c r="B410" s="11"/>
+      <c r="C410" s="12"/>
+      <c r="D410" s="13"/>
+      <c r="E410" s="16"/>
+      <c r="F410" s="17"/>
+      <c r="G410" s="17"/>
       <c r="H410" s="5"/>
       <c r="I410" s="5"/>
       <c r="J410" s="5"/>
@@ -9130,13 +9307,13 @@
       <c r="P410" s="5"/>
     </row>
     <row r="411" ht="18.0" customHeight="1">
-      <c r="A411" s="6"/>
-      <c r="B411" s="6"/>
-      <c r="C411" s="8"/>
-      <c r="D411" s="15"/>
-      <c r="E411" s="18"/>
-      <c r="F411" s="19"/>
-      <c r="G411" s="19"/>
+      <c r="A411" s="11"/>
+      <c r="B411" s="11"/>
+      <c r="C411" s="12"/>
+      <c r="D411" s="13"/>
+      <c r="E411" s="16"/>
+      <c r="F411" s="17"/>
+      <c r="G411" s="17"/>
       <c r="H411" s="5"/>
       <c r="I411" s="5"/>
       <c r="J411" s="5"/>
@@ -9148,13 +9325,13 @@
       <c r="P411" s="5"/>
     </row>
     <row r="412" ht="18.0" customHeight="1">
-      <c r="A412" s="6"/>
-      <c r="B412" s="6"/>
-      <c r="C412" s="8"/>
-      <c r="D412" s="15"/>
-      <c r="E412" s="18"/>
-      <c r="F412" s="19"/>
-      <c r="G412" s="19"/>
+      <c r="A412" s="11"/>
+      <c r="B412" s="11"/>
+      <c r="C412" s="12"/>
+      <c r="D412" s="13"/>
+      <c r="E412" s="16"/>
+      <c r="F412" s="17"/>
+      <c r="G412" s="17"/>
       <c r="H412" s="5"/>
       <c r="I412" s="5"/>
       <c r="J412" s="5"/>
@@ -9166,13 +9343,13 @@
       <c r="P412" s="5"/>
     </row>
     <row r="413" ht="18.0" customHeight="1">
-      <c r="A413" s="6"/>
-      <c r="B413" s="6"/>
-      <c r="C413" s="8"/>
-      <c r="D413" s="15"/>
-      <c r="E413" s="18"/>
-      <c r="F413" s="19"/>
-      <c r="G413" s="19"/>
+      <c r="A413" s="11"/>
+      <c r="B413" s="11"/>
+      <c r="C413" s="12"/>
+      <c r="D413" s="13"/>
+      <c r="E413" s="16"/>
+      <c r="F413" s="17"/>
+      <c r="G413" s="17"/>
       <c r="H413" s="5"/>
       <c r="I413" s="5"/>
       <c r="J413" s="5"/>
@@ -9184,13 +9361,13 @@
       <c r="P413" s="5"/>
     </row>
     <row r="414" ht="18.0" customHeight="1">
-      <c r="A414" s="6"/>
-      <c r="B414" s="6"/>
-      <c r="C414" s="8"/>
-      <c r="D414" s="15"/>
-      <c r="E414" s="18"/>
-      <c r="F414" s="19"/>
-      <c r="G414" s="19"/>
+      <c r="A414" s="11"/>
+      <c r="B414" s="11"/>
+      <c r="C414" s="12"/>
+      <c r="D414" s="13"/>
+      <c r="E414" s="16"/>
+      <c r="F414" s="17"/>
+      <c r="G414" s="17"/>
       <c r="H414" s="5"/>
       <c r="I414" s="5"/>
       <c r="J414" s="5"/>
@@ -9202,13 +9379,13 @@
       <c r="P414" s="5"/>
     </row>
     <row r="415" ht="18.0" customHeight="1">
-      <c r="A415" s="6"/>
-      <c r="B415" s="6"/>
-      <c r="C415" s="8"/>
-      <c r="D415" s="15"/>
-      <c r="E415" s="18"/>
-      <c r="F415" s="19"/>
-      <c r="G415" s="19"/>
+      <c r="A415" s="11"/>
+      <c r="B415" s="11"/>
+      <c r="C415" s="12"/>
+      <c r="D415" s="13"/>
+      <c r="E415" s="16"/>
+      <c r="F415" s="17"/>
+      <c r="G415" s="17"/>
       <c r="H415" s="5"/>
       <c r="I415" s="5"/>
       <c r="J415" s="5"/>
@@ -9219,204 +9396,6 @@
       <c r="O415" s="5"/>
       <c r="P415" s="5"/>
     </row>
-    <row r="416" ht="18.0" customHeight="1">
-      <c r="A416" s="6"/>
-      <c r="B416" s="6"/>
-      <c r="C416" s="8"/>
-      <c r="D416" s="15"/>
-      <c r="E416" s="18"/>
-      <c r="F416" s="19"/>
-      <c r="G416" s="19"/>
-      <c r="H416" s="5"/>
-      <c r="I416" s="5"/>
-      <c r="J416" s="5"/>
-      <c r="K416" s="5"/>
-      <c r="L416" s="5"/>
-      <c r="M416" s="5"/>
-      <c r="N416" s="5"/>
-      <c r="O416" s="5"/>
-      <c r="P416" s="5"/>
-    </row>
-    <row r="417" ht="18.0" customHeight="1">
-      <c r="A417" s="6"/>
-      <c r="B417" s="6"/>
-      <c r="C417" s="8"/>
-      <c r="D417" s="15"/>
-      <c r="E417" s="18"/>
-      <c r="F417" s="19"/>
-      <c r="G417" s="19"/>
-      <c r="H417" s="5"/>
-      <c r="I417" s="5"/>
-      <c r="J417" s="5"/>
-      <c r="K417" s="5"/>
-      <c r="L417" s="5"/>
-      <c r="M417" s="5"/>
-      <c r="N417" s="5"/>
-      <c r="O417" s="5"/>
-      <c r="P417" s="5"/>
-    </row>
-    <row r="418" ht="18.0" customHeight="1">
-      <c r="A418" s="6"/>
-      <c r="B418" s="6"/>
-      <c r="C418" s="8"/>
-      <c r="D418" s="15"/>
-      <c r="E418" s="18"/>
-      <c r="F418" s="19"/>
-      <c r="G418" s="19"/>
-      <c r="H418" s="5"/>
-      <c r="I418" s="5"/>
-      <c r="J418" s="5"/>
-      <c r="K418" s="5"/>
-      <c r="L418" s="5"/>
-      <c r="M418" s="5"/>
-      <c r="N418" s="5"/>
-      <c r="O418" s="5"/>
-      <c r="P418" s="5"/>
-    </row>
-    <row r="419" ht="18.0" customHeight="1">
-      <c r="A419" s="6"/>
-      <c r="B419" s="6"/>
-      <c r="C419" s="8"/>
-      <c r="D419" s="15"/>
-      <c r="E419" s="18"/>
-      <c r="F419" s="19"/>
-      <c r="G419" s="19"/>
-      <c r="H419" s="5"/>
-      <c r="I419" s="5"/>
-      <c r="J419" s="5"/>
-      <c r="K419" s="5"/>
-      <c r="L419" s="5"/>
-      <c r="M419" s="5"/>
-      <c r="N419" s="5"/>
-      <c r="O419" s="5"/>
-      <c r="P419" s="5"/>
-    </row>
-    <row r="420" ht="18.0" customHeight="1">
-      <c r="A420" s="6"/>
-      <c r="B420" s="6"/>
-      <c r="C420" s="8"/>
-      <c r="D420" s="15"/>
-      <c r="E420" s="18"/>
-      <c r="F420" s="19"/>
-      <c r="G420" s="19"/>
-      <c r="H420" s="5"/>
-      <c r="I420" s="5"/>
-      <c r="J420" s="5"/>
-      <c r="K420" s="5"/>
-      <c r="L420" s="5"/>
-      <c r="M420" s="5"/>
-      <c r="N420" s="5"/>
-      <c r="O420" s="5"/>
-      <c r="P420" s="5"/>
-    </row>
-    <row r="421" ht="18.0" customHeight="1">
-      <c r="A421" s="6"/>
-      <c r="B421" s="6"/>
-      <c r="C421" s="8"/>
-      <c r="D421" s="15"/>
-      <c r="E421" s="18"/>
-      <c r="F421" s="19"/>
-      <c r="G421" s="19"/>
-      <c r="H421" s="5"/>
-      <c r="I421" s="5"/>
-      <c r="J421" s="5"/>
-      <c r="K421" s="5"/>
-      <c r="L421" s="5"/>
-      <c r="M421" s="5"/>
-      <c r="N421" s="5"/>
-      <c r="O421" s="5"/>
-      <c r="P421" s="5"/>
-    </row>
-    <row r="422" ht="18.0" customHeight="1">
-      <c r="A422" s="6"/>
-      <c r="B422" s="6"/>
-      <c r="C422" s="8"/>
-      <c r="D422" s="15"/>
-      <c r="E422" s="18"/>
-      <c r="F422" s="19"/>
-      <c r="G422" s="19"/>
-      <c r="H422" s="5"/>
-      <c r="I422" s="5"/>
-      <c r="J422" s="5"/>
-      <c r="K422" s="5"/>
-      <c r="L422" s="5"/>
-      <c r="M422" s="5"/>
-      <c r="N422" s="5"/>
-      <c r="O422" s="5"/>
-      <c r="P422" s="5"/>
-    </row>
-    <row r="423" ht="18.0" customHeight="1">
-      <c r="A423" s="6"/>
-      <c r="B423" s="6"/>
-      <c r="C423" s="8"/>
-      <c r="D423" s="15"/>
-      <c r="E423" s="18"/>
-      <c r="F423" s="19"/>
-      <c r="G423" s="19"/>
-      <c r="H423" s="5"/>
-      <c r="I423" s="5"/>
-      <c r="J423" s="5"/>
-      <c r="K423" s="5"/>
-      <c r="L423" s="5"/>
-      <c r="M423" s="5"/>
-      <c r="N423" s="5"/>
-      <c r="O423" s="5"/>
-      <c r="P423" s="5"/>
-    </row>
-    <row r="424" ht="18.0" customHeight="1">
-      <c r="A424" s="6"/>
-      <c r="B424" s="6"/>
-      <c r="C424" s="8"/>
-      <c r="D424" s="15"/>
-      <c r="E424" s="18"/>
-      <c r="F424" s="19"/>
-      <c r="G424" s="19"/>
-      <c r="H424" s="5"/>
-      <c r="I424" s="5"/>
-      <c r="J424" s="5"/>
-      <c r="K424" s="5"/>
-      <c r="L424" s="5"/>
-      <c r="M424" s="5"/>
-      <c r="N424" s="5"/>
-      <c r="O424" s="5"/>
-      <c r="P424" s="5"/>
-    </row>
-    <row r="425" ht="18.0" customHeight="1">
-      <c r="A425" s="6"/>
-      <c r="B425" s="6"/>
-      <c r="C425" s="8"/>
-      <c r="D425" s="15"/>
-      <c r="E425" s="18"/>
-      <c r="F425" s="19"/>
-      <c r="G425" s="19"/>
-      <c r="H425" s="5"/>
-      <c r="I425" s="5"/>
-      <c r="J425" s="5"/>
-      <c r="K425" s="5"/>
-      <c r="L425" s="5"/>
-      <c r="M425" s="5"/>
-      <c r="N425" s="5"/>
-      <c r="O425" s="5"/>
-      <c r="P425" s="5"/>
-    </row>
-    <row r="426" ht="18.0" customHeight="1">
-      <c r="A426" s="6"/>
-      <c r="B426" s="6"/>
-      <c r="C426" s="8"/>
-      <c r="D426" s="15"/>
-      <c r="E426" s="18"/>
-      <c r="F426" s="19"/>
-      <c r="G426" s="19"/>
-      <c r="H426" s="5"/>
-      <c r="I426" s="5"/>
-      <c r="J426" s="5"/>
-      <c r="K426" s="5"/>
-      <c r="L426" s="5"/>
-      <c r="M426" s="5"/>
-      <c r="N426" s="5"/>
-      <c r="O426" s="5"/>
-      <c r="P426" s="5"/>
-    </row>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
